--- a/precept-financeiro/Memoria_de_Calculo_Precept.xlsx
+++ b/precept-financeiro/Memoria_de_Calculo_Precept.xlsx
@@ -345,13 +345,13 @@
     <t xml:space="preserve">Precept Sprint – imersão de 7 dias (R$, à vista)</t>
   </si>
   <si>
-    <t xml:space="preserve">Preço definido pelo grupo: planejamento estratégico e tático em 7 dias imersivos.</t>
+    <t xml:space="preserve">Preço definido pelo grupo: planejamento estratégico e tático em 7 dias imersivos. No ano 2, também vendido para escritórios fora da base Core (4 a 5 por mês), no modelo das imersões da G4.</t>
   </si>
   <si>
     <t xml:space="preserve">Precept Scale – implementação (R$ por projeto)</t>
   </si>
   <si>
-    <t xml:space="preserve">Preço definido pelo grupo: implementação e acompanhamento dos 6 pilares.</t>
+    <t xml:space="preserve">Preço proposto para o início da operação: 3× o Sprint e ~R$ 5 mil/mês por 6 meses, abaixo de consultorias de gestão para PMEs (R$ 8–15 mil/mês). Cerca de 1% a 3% do faturamento anual de um escritório de R$ 1–4 mi.</t>
   </si>
   <si>
     <t xml:space="preserve">Parcelas do Scale (meses de projeto)</t>
@@ -2037,7 +2037,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="9" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="11" t="s">
         <v>39</v>
       </c>
@@ -2048,12 +2048,12 @@
         <v>40</v>
       </c>
     </row>
-    <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+    <row r="10" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="11" t="s">
         <v>41</v>
       </c>
       <c r="B10" s="12" t="n">
-        <v>18997</v>
+        <v>29997</v>
       </c>
       <c r="C10" s="13" t="s">
         <v>42</v>
@@ -2076,7 +2076,7 @@
       </c>
       <c r="B12" s="15" t="n">
         <f aca="false">B10/B11</f>
-        <v>3166.16666666667</v>
+        <v>4999.5</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>46</v>
@@ -2645,7 +2645,7 @@
       </c>
       <c r="B71" s="28" t="n">
         <f aca="false">'VPL e TIR'!B38</f>
-        <v>84862.163322548</v>
+        <v>126073.58365125</v>
       </c>
       <c r="C71" s="13" t="s">
         <v>138</v>
@@ -2657,7 +2657,7 @@
       </c>
       <c r="B72" s="29" t="n">
         <f aca="false">'VPL e TIR'!B40</f>
-        <v>0.795151936890566</v>
+        <v>1.04844610560403</v>
       </c>
       <c r="C72" s="13" t="s">
         <v>140</v>
@@ -2669,7 +2669,7 @@
       </c>
       <c r="B73" s="30" t="n">
         <f aca="false">'VPL e TIR'!B43</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C73" s="13" t="s">
         <v>142</v>
@@ -2681,7 +2681,7 @@
       </c>
       <c r="B74" s="30" t="n">
         <f aca="false">'VPL e TIR'!B44</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C74" s="13" t="s">
         <v>144</v>
@@ -2693,7 +2693,7 @@
       </c>
       <c r="B75" s="28" t="n">
         <f aca="false">AVERAGE('Projeção Mensal'!W18:W29)</f>
-        <v>2797.33416666667</v>
+        <v>3765.465</v>
       </c>
       <c r="C75" s="13" t="s">
         <v>146</v>
@@ -2723,7 +2723,7 @@
       </c>
       <c r="B79" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A79)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>95036.919986325</v>
+        <v>138252.818253723</v>
       </c>
       <c r="C79" s="32" t="str">
         <f aca="false">IF(B79&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
@@ -2736,7 +2736,7 @@
       </c>
       <c r="B80" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A80)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>84862.163322548</v>
+        <v>126073.58365125</v>
       </c>
       <c r="C80" s="32" t="str">
         <f aca="false">IF(B80&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
@@ -2749,7 +2749,7 @@
       </c>
       <c r="B81" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A81)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>77769.5508109088</v>
+        <v>117581.793796568</v>
       </c>
       <c r="C81" s="32" t="str">
         <f aca="false">IF(B81&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
@@ -2762,7 +2762,7 @@
       </c>
       <c r="B82" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A82)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>73276.1226894992</v>
+        <v>112201.09352997</v>
       </c>
       <c r="C82" s="32" t="str">
         <f aca="false">IF(B82&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
@@ -2775,7 +2775,7 @@
       </c>
       <c r="B83" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A83)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>64807.5818985632</v>
+        <v>102058.50248802</v>
       </c>
       <c r="C83" s="32" t="str">
         <f aca="false">IF(B83&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
@@ -3502,11 +3502,11 @@
       </c>
       <c r="H11" s="15" t="n">
         <f aca="false">E11*'Premissas Precept'!$B$12</f>
-        <v>3166.16666666667</v>
+        <v>4999.5</v>
       </c>
       <c r="I11" s="22" t="n">
         <f aca="false">F11+G11+H11</f>
-        <v>32315.1666666667</v>
+        <v>34148.5</v>
       </c>
       <c r="J11" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I10)*12</f>
@@ -3518,7 +3518,7 @@
       </c>
       <c r="L11" s="15" t="n">
         <f aca="false">I11*K11</f>
-        <v>5008.85083333333</v>
+        <v>5293.0175</v>
       </c>
       <c r="M11" s="15" t="n">
         <f aca="false">B11*'Premissas Precept'!$B$15</f>
@@ -3526,15 +3526,15 @@
       </c>
       <c r="N11" s="15" t="n">
         <f aca="false">I11*'Premissas Precept'!$B$16</f>
-        <v>646.303333333333</v>
+        <v>682.97</v>
       </c>
       <c r="O11" s="15" t="n">
         <f aca="false">(G11+H11)*'Premissas Precept'!$B$17</f>
-        <v>658.158333333333</v>
+        <v>749.825</v>
       </c>
       <c r="P11" s="15" t="n">
         <f aca="false">(G11+H11)*'Premissas Precept'!$B$18</f>
-        <v>4607.10833333333</v>
+        <v>5248.775</v>
       </c>
       <c r="Q11" s="15" t="n">
         <f aca="false">C11*'Premissas Precept'!$B$19+E11*'Premissas Precept'!$B$20</f>
@@ -3542,7 +3542,7 @@
       </c>
       <c r="R11" s="22" t="n">
         <f aca="false">SUM(L11:Q11)</f>
-        <v>13160.4208333333</v>
+        <v>14214.5875</v>
       </c>
       <c r="S11" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3550,19 +3550,19 @@
       </c>
       <c r="T11" s="15" t="n">
         <f aca="false">IF(A11&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I11,0)</f>
-        <v>6786.185</v>
+        <v>7171.185</v>
       </c>
       <c r="U11" s="22" t="n">
         <f aca="false">S11+T11</f>
-        <v>18786.185</v>
+        <v>19171.185</v>
       </c>
       <c r="V11" s="22" t="n">
         <f aca="false">I11-R11-U11</f>
-        <v>368.560833333333</v>
+        <v>762.727500000001</v>
       </c>
       <c r="W11" s="15" t="n">
         <f aca="false">T11/'Premissas Precept'!$B$45</f>
-        <v>969.455</v>
+        <v>1024.455</v>
       </c>
       <c r="X11" s="35" t="str">
         <f aca="false">IF(V11&gt;=0,"Sim","Não")</f>
@@ -3596,23 +3596,23 @@
       </c>
       <c r="H12" s="15" t="n">
         <f aca="false">E12*'Premissas Precept'!$B$12</f>
-        <v>3166.16666666667</v>
+        <v>4999.5</v>
       </c>
       <c r="I12" s="22" t="n">
         <f aca="false">F12+G12+H12</f>
-        <v>35906.1666666667</v>
+        <v>37739.5</v>
       </c>
       <c r="J12" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I11)*12</f>
-        <v>209954.333333333</v>
+        <v>213621</v>
       </c>
       <c r="K12" s="38" t="n">
         <f aca="false">IF(J12&lt;=0,'Premissas Precept'!$C$24,(J12*LOOKUP(J12,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J12,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J12)</f>
-        <v>0.158566767693927</v>
+        <v>0.158934655300743</v>
       </c>
       <c r="L12" s="15" t="n">
         <f aca="false">I12*K12</f>
-        <v>5693.52478861276</v>
+        <v>5998.11442372239</v>
       </c>
       <c r="M12" s="15" t="n">
         <f aca="false">B12*'Premissas Precept'!$B$15</f>
@@ -3620,15 +3620,15 @@
       </c>
       <c r="N12" s="15" t="n">
         <f aca="false">I12*'Premissas Precept'!$B$16</f>
-        <v>718.123333333333</v>
+        <v>754.79</v>
       </c>
       <c r="O12" s="15" t="n">
         <f aca="false">(G12+H12)*'Premissas Precept'!$B$17</f>
-        <v>658.158333333333</v>
+        <v>749.825</v>
       </c>
       <c r="P12" s="15" t="n">
         <f aca="false">(G12+H12)*'Premissas Precept'!$B$18</f>
-        <v>4607.10833333333</v>
+        <v>5248.775</v>
       </c>
       <c r="Q12" s="15" t="n">
         <f aca="false">C12*'Premissas Precept'!$B$19+E12*'Premissas Precept'!$B$20</f>
@@ -3636,7 +3636,7 @@
       </c>
       <c r="R12" s="22" t="n">
         <f aca="false">SUM(L12:Q12)</f>
-        <v>14186.9147886128</v>
+        <v>15261.5044237224</v>
       </c>
       <c r="S12" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3644,19 +3644,19 @@
       </c>
       <c r="T12" s="15" t="n">
         <f aca="false">IF(A12&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I12,0)</f>
-        <v>7540.295</v>
+        <v>7925.295</v>
       </c>
       <c r="U12" s="22" t="n">
         <f aca="false">S12+T12</f>
-        <v>19540.295</v>
+        <v>19925.295</v>
       </c>
       <c r="V12" s="22" t="n">
         <f aca="false">I12-R12-U12</f>
-        <v>2178.95687805391</v>
+        <v>2552.70057627762</v>
       </c>
       <c r="W12" s="15" t="n">
         <f aca="false">T12/'Premissas Precept'!$B$45</f>
-        <v>1077.185</v>
+        <v>1132.185</v>
       </c>
       <c r="X12" s="35" t="str">
         <f aca="false">IF(V12&gt;=0,"Sim","Não")</f>
@@ -3690,23 +3690,23 @@
       </c>
       <c r="H13" s="15" t="n">
         <f aca="false">E13*'Premissas Precept'!$B$12</f>
-        <v>6332.33333333333</v>
+        <v>9999</v>
       </c>
       <c r="I13" s="22" t="n">
         <f aca="false">F13+G13+H13</f>
-        <v>41466.3333333333</v>
+        <v>45133</v>
       </c>
       <c r="J13" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I12)*12</f>
-        <v>241514.285714286</v>
+        <v>247800</v>
       </c>
       <c r="K13" s="38" t="n">
         <f aca="false">IF(J13&lt;=0,'Premissas Precept'!$C$24,(J13*LOOKUP(J13,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J13,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J13)</f>
-        <v>0.161367561812374</v>
+        <v>0.1618401937046</v>
       </c>
       <c r="L13" s="15" t="n">
         <f aca="false">I13*K13</f>
-        <v>6691.32110729919</v>
+        <v>7304.33346246973</v>
       </c>
       <c r="M13" s="15" t="n">
         <f aca="false">B13*'Premissas Precept'!$B$15</f>
@@ -3714,15 +3714,15 @@
       </c>
       <c r="N13" s="15" t="n">
         <f aca="false">I13*'Premissas Precept'!$B$16</f>
-        <v>829.326666666667</v>
+        <v>902.66</v>
       </c>
       <c r="O13" s="15" t="n">
         <f aca="false">(G13+H13)*'Premissas Precept'!$B$17</f>
-        <v>816.466666666667</v>
+        <v>999.8</v>
       </c>
       <c r="P13" s="15" t="n">
         <f aca="false">(G13+H13)*'Premissas Precept'!$B$18</f>
-        <v>5715.26666666667</v>
+        <v>6998.6</v>
       </c>
       <c r="Q13" s="15" t="n">
         <f aca="false">C13*'Premissas Precept'!$B$19+E13*'Premissas Precept'!$B$20</f>
@@ -3730,7 +3730,7 @@
       </c>
       <c r="R13" s="22" t="n">
         <f aca="false">SUM(L13:Q13)</f>
-        <v>16942.3811072992</v>
+        <v>19095.3934624697</v>
       </c>
       <c r="S13" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3738,19 +3738,19 @@
       </c>
       <c r="T13" s="15" t="n">
         <f aca="false">IF(A13&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I13,0)</f>
-        <v>8707.93</v>
+        <v>9477.93</v>
       </c>
       <c r="U13" s="22" t="n">
         <f aca="false">S13+T13</f>
-        <v>20707.93</v>
+        <v>21477.93</v>
       </c>
       <c r="V13" s="22" t="n">
         <f aca="false">I13-R13-U13</f>
-        <v>3816.02222603415</v>
+        <v>4559.67653753027</v>
       </c>
       <c r="W13" s="15" t="n">
         <f aca="false">T13/'Premissas Precept'!$B$45</f>
-        <v>1243.99</v>
+        <v>1353.99</v>
       </c>
       <c r="X13" s="35" t="str">
         <f aca="false">IF(V13&gt;=0,"Sim","Não")</f>
@@ -3784,23 +3784,23 @@
       </c>
       <c r="H14" s="15" t="n">
         <f aca="false">E14*'Premissas Precept'!$B$12</f>
-        <v>6332.33333333333</v>
+        <v>9999</v>
       </c>
       <c r="I14" s="22" t="n">
         <f aca="false">F14+G14+H14</f>
-        <v>55054.3333333333</v>
+        <v>58721</v>
       </c>
       <c r="J14" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I13)*12</f>
-        <v>273524.5</v>
+        <v>284524.5</v>
       </c>
       <c r="K14" s="38" t="n">
         <f aca="false">IF(J14&lt;=0,'Premissas Precept'!$C$24,(J14*LOOKUP(J14,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J14,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J14)</f>
-        <v>0.163548091670033</v>
+        <v>0.164184138799998</v>
       </c>
       <c r="L14" s="15" t="n">
         <f aca="false">I14*K14</f>
-        <v>9004.03115483256</v>
+        <v>9641.05681447468</v>
       </c>
       <c r="M14" s="15" t="n">
         <f aca="false">B14*'Premissas Precept'!$B$15</f>
@@ -3808,15 +3808,15 @@
       </c>
       <c r="N14" s="15" t="n">
         <f aca="false">I14*'Premissas Precept'!$B$16</f>
-        <v>1101.08666666667</v>
+        <v>1174.42</v>
       </c>
       <c r="O14" s="15" t="n">
         <f aca="false">(G14+H14)*'Premissas Precept'!$B$17</f>
-        <v>1316.31666666667</v>
+        <v>1499.65</v>
       </c>
       <c r="P14" s="15" t="n">
         <f aca="false">(G14+H14)*'Premissas Precept'!$B$18</f>
-        <v>9214.21666666667</v>
+        <v>10497.55</v>
       </c>
       <c r="Q14" s="15" t="n">
         <f aca="false">C14*'Premissas Precept'!$B$19+E14*'Premissas Precept'!$B$20</f>
@@ -3824,7 +3824,7 @@
       </c>
       <c r="R14" s="22" t="n">
         <f aca="false">SUM(L14:Q14)</f>
-        <v>24395.6511548326</v>
+        <v>26572.6768144747</v>
       </c>
       <c r="S14" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3832,19 +3832,19 @@
       </c>
       <c r="T14" s="15" t="n">
         <f aca="false">IF(A14&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I14,0)</f>
-        <v>11561.41</v>
+        <v>12331.41</v>
       </c>
       <c r="U14" s="22" t="n">
         <f aca="false">S14+T14</f>
-        <v>23561.41</v>
+        <v>24331.41</v>
       </c>
       <c r="V14" s="22" t="n">
         <f aca="false">I14-R14-U14</f>
-        <v>7097.27217850077</v>
+        <v>7816.91318552533</v>
       </c>
       <c r="W14" s="15" t="n">
         <f aca="false">T14/'Premissas Precept'!$B$45</f>
-        <v>1651.63</v>
+        <v>1761.63</v>
       </c>
       <c r="X14" s="35" t="str">
         <f aca="false">IF(V14&gt;=0,"Sim","Não")</f>
@@ -3878,23 +3878,23 @@
       </c>
       <c r="H15" s="15" t="n">
         <f aca="false">E15*'Premissas Precept'!$B$12</f>
-        <v>9498.5</v>
+        <v>14998.5</v>
       </c>
       <c r="I15" s="22" t="n">
         <f aca="false">F15+G15+H15</f>
-        <v>50617.5</v>
+        <v>56117.5</v>
       </c>
       <c r="J15" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I14)*12</f>
-        <v>316538.666666667</v>
+        <v>331205.333333333</v>
       </c>
       <c r="K15" s="38" t="n">
         <f aca="false">IF(J15&lt;=0,'Premissas Precept'!$C$24,(J15*LOOKUP(J15,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J15,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J15)</f>
-        <v>0.165783727317147</v>
+        <v>0.166413262266308</v>
       </c>
       <c r="L15" s="15" t="n">
         <f aca="false">I15*K15</f>
-        <v>8391.5578174757</v>
+        <v>9338.69624522955</v>
       </c>
       <c r="M15" s="15" t="n">
         <f aca="false">B15*'Premissas Precept'!$B$15</f>
@@ -3902,15 +3902,15 @@
       </c>
       <c r="N15" s="15" t="n">
         <f aca="false">I15*'Premissas Precept'!$B$16</f>
-        <v>1012.35</v>
+        <v>1122.35</v>
       </c>
       <c r="O15" s="15" t="n">
         <f aca="false">(G15+H15)*'Premissas Precept'!$B$17</f>
-        <v>974.775</v>
+        <v>1249.775</v>
       </c>
       <c r="P15" s="15" t="n">
         <f aca="false">(G15+H15)*'Premissas Precept'!$B$18</f>
-        <v>6823.425</v>
+        <v>8748.425</v>
       </c>
       <c r="Q15" s="15" t="n">
         <f aca="false">C15*'Premissas Precept'!$B$19+E15*'Premissas Precept'!$B$20</f>
@@ -3918,7 +3918,7 @@
       </c>
       <c r="R15" s="22" t="n">
         <f aca="false">SUM(L15:Q15)</f>
-        <v>20742.1078174757</v>
+        <v>23999.2462452295</v>
       </c>
       <c r="S15" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3926,19 +3926,19 @@
       </c>
       <c r="T15" s="15" t="n">
         <f aca="false">IF(A15&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I15,0)</f>
-        <v>10629.675</v>
+        <v>11784.675</v>
       </c>
       <c r="U15" s="22" t="n">
         <f aca="false">S15+T15</f>
-        <v>22629.675</v>
+        <v>23784.675</v>
       </c>
       <c r="V15" s="22" t="n">
         <f aca="false">I15-R15-U15</f>
-        <v>7245.71718252431</v>
+        <v>8333.57875477045</v>
       </c>
       <c r="W15" s="15" t="n">
         <f aca="false">T15/'Premissas Precept'!$B$45</f>
-        <v>1518.525</v>
+        <v>1683.525</v>
       </c>
       <c r="X15" s="35" t="str">
         <f aca="false">IF(V15&gt;=0,"Sim","Não")</f>
@@ -3972,23 +3972,23 @@
       </c>
       <c r="H16" s="15" t="n">
         <f aca="false">E16*'Premissas Precept'!$B$12</f>
-        <v>9498.5</v>
+        <v>14998.5</v>
       </c>
       <c r="I16" s="22" t="n">
         <f aca="false">F16+G16+H16</f>
-        <v>64205.5</v>
+        <v>69705.5</v>
       </c>
       <c r="J16" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I15)*12</f>
-        <v>345625.8</v>
+        <v>365425.8</v>
       </c>
       <c r="K16" s="38" t="n">
         <f aca="false">IF(J16&lt;=0,'Premissas Precept'!$C$24,(J16*LOOKUP(J16,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J16,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J16)</f>
-        <v>0.166980138635484</v>
+        <v>0.167908316818353</v>
       </c>
       <c r="L16" s="15" t="n">
         <f aca="false">I16*K16</f>
-        <v>10721.0432911606</v>
+        <v>11704.1331779817</v>
       </c>
       <c r="M16" s="15" t="n">
         <f aca="false">B16*'Premissas Precept'!$B$15</f>
@@ -3996,15 +3996,15 @@
       </c>
       <c r="N16" s="15" t="n">
         <f aca="false">I16*'Premissas Precept'!$B$16</f>
-        <v>1284.11</v>
+        <v>1394.11</v>
       </c>
       <c r="O16" s="15" t="n">
         <f aca="false">(G16+H16)*'Premissas Precept'!$B$17</f>
-        <v>1474.625</v>
+        <v>1749.625</v>
       </c>
       <c r="P16" s="15" t="n">
         <f aca="false">(G16+H16)*'Premissas Precept'!$B$18</f>
-        <v>10322.375</v>
+        <v>12247.375</v>
       </c>
       <c r="Q16" s="15" t="n">
         <f aca="false">C16*'Premissas Precept'!$B$19+E16*'Premissas Precept'!$B$20</f>
@@ -4012,7 +4012,7 @@
       </c>
       <c r="R16" s="22" t="n">
         <f aca="false">SUM(L16:Q16)</f>
-        <v>28212.1532911606</v>
+        <v>31505.2431779817</v>
       </c>
       <c r="S16" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4020,19 +4020,19 @@
       </c>
       <c r="T16" s="15" t="n">
         <f aca="false">IF(A16&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I16,0)</f>
-        <v>13483.155</v>
+        <v>14638.155</v>
       </c>
       <c r="U16" s="22" t="n">
         <f aca="false">S16+T16</f>
-        <v>25483.155</v>
+        <v>26638.155</v>
       </c>
       <c r="V16" s="22" t="n">
         <f aca="false">I16-R16-U16</f>
-        <v>10510.1917088394</v>
+        <v>11562.1018220183</v>
       </c>
       <c r="W16" s="15" t="n">
         <f aca="false">T16/'Premissas Precept'!$B$45</f>
-        <v>1926.165</v>
+        <v>2091.165</v>
       </c>
       <c r="X16" s="35" t="str">
         <f aca="false">IF(V16&gt;=0,"Sim","Não")</f>
@@ -4066,23 +4066,23 @@
       </c>
       <c r="H17" s="15" t="n">
         <f aca="false">E17*'Premissas Precept'!$B$12</f>
-        <v>9498.5</v>
+        <v>14998.5</v>
       </c>
       <c r="I17" s="22" t="n">
         <f aca="false">F17+G17+H17</f>
-        <v>56602.5</v>
+        <v>62102.5</v>
       </c>
       <c r="J17" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I16)*12</f>
-        <v>384247.636363636</v>
+        <v>408247.636363636</v>
       </c>
       <c r="K17" s="38" t="n">
         <f aca="false">IF(J17&lt;=0,'Premissas Precept'!$C$24,(J17*LOOKUP(J17,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J17,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J17)</f>
-        <v>0.169235365261607</v>
+        <v>0.170750012692831</v>
       </c>
       <c r="L17" s="15" t="n">
         <f aca="false">I17*K17</f>
-        <v>9579.1447622201</v>
+        <v>10604.0026632565</v>
       </c>
       <c r="M17" s="15" t="n">
         <f aca="false">B17*'Premissas Precept'!$B$15</f>
@@ -4090,15 +4090,15 @@
       </c>
       <c r="N17" s="15" t="n">
         <f aca="false">I17*'Premissas Precept'!$B$16</f>
-        <v>1132.05</v>
+        <v>1242.05</v>
       </c>
       <c r="O17" s="15" t="n">
         <f aca="false">(G17+H17)*'Premissas Precept'!$B$17</f>
-        <v>974.775</v>
+        <v>1249.775</v>
       </c>
       <c r="P17" s="15" t="n">
         <f aca="false">(G17+H17)*'Premissas Precept'!$B$18</f>
-        <v>6823.425</v>
+        <v>8748.425</v>
       </c>
       <c r="Q17" s="15" t="n">
         <f aca="false">C17*'Premissas Precept'!$B$19+E17*'Premissas Precept'!$B$20</f>
@@ -4106,7 +4106,7 @@
       </c>
       <c r="R17" s="22" t="n">
         <f aca="false">SUM(L17:Q17)</f>
-        <v>22499.3947622201</v>
+        <v>25834.2526632565</v>
       </c>
       <c r="S17" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4114,19 +4114,19 @@
       </c>
       <c r="T17" s="15" t="n">
         <f aca="false">IF(A17&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I17,0)</f>
-        <v>11886.525</v>
+        <v>13041.525</v>
       </c>
       <c r="U17" s="22" t="n">
         <f aca="false">S17+T17</f>
-        <v>23886.525</v>
+        <v>25041.525</v>
       </c>
       <c r="V17" s="22" t="n">
         <f aca="false">I17-R17-U17</f>
-        <v>10216.5802377799</v>
+        <v>11226.7223367435</v>
       </c>
       <c r="W17" s="15" t="n">
         <f aca="false">T17/'Premissas Precept'!$B$45</f>
-        <v>1698.075</v>
+        <v>1863.075</v>
       </c>
       <c r="X17" s="35" t="str">
         <f aca="false">IF(V17&gt;=0,"Sim","Não")</f>
@@ -4141,7 +4141,7 @@
         <v>34</v>
       </c>
       <c r="C18" s="36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D18" s="36" t="n">
         <v>1</v>
@@ -4156,27 +4156,27 @@
       </c>
       <c r="G18" s="15" t="n">
         <f aca="false">C18*'Premissas Precept'!$B$9</f>
-        <v>19994</v>
+        <v>39988</v>
       </c>
       <c r="H18" s="15" t="n">
         <f aca="false">E18*'Premissas Precept'!$B$12</f>
-        <v>12664.6666666667</v>
+        <v>19998</v>
       </c>
       <c r="I18" s="22" t="n">
         <f aca="false">F18+G18+H18</f>
-        <v>73356.6666666667</v>
+        <v>100684</v>
       </c>
       <c r="J18" s="15" t="n">
         <f aca="false">SUM(I6:I17)</f>
-        <v>408829.5</v>
+        <v>436329.5</v>
       </c>
       <c r="K18" s="38" t="n">
         <f aca="false">IF(J18&lt;=0,'Premissas Precept'!$C$24,(J18*LOOKUP(J18,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J18,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J18)</f>
-        <v>0.170784526312314</v>
+        <v>0.172310725036927</v>
       </c>
       <c r="L18" s="15" t="n">
         <f aca="false">I18*K18</f>
-        <v>12528.183568517</v>
+        <v>17348.933039618</v>
       </c>
       <c r="M18" s="15" t="n">
         <f aca="false">B18*'Premissas Precept'!$B$15</f>
@@ -4184,23 +4184,23 @@
       </c>
       <c r="N18" s="15" t="n">
         <f aca="false">I18*'Premissas Precept'!$B$16</f>
-        <v>1467.13333333333</v>
+        <v>2013.68</v>
       </c>
       <c r="O18" s="15" t="n">
         <f aca="false">(G18+H18)*'Premissas Precept'!$B$17</f>
-        <v>1632.93333333333</v>
+        <v>2999.3</v>
       </c>
       <c r="P18" s="15" t="n">
         <f aca="false">(G18+H18)*'Premissas Precept'!$B$18</f>
-        <v>11430.5333333333</v>
+        <v>20995.1</v>
       </c>
       <c r="Q18" s="15" t="n">
         <f aca="false">C18*'Premissas Precept'!$B$19+E18*'Premissas Precept'!$B$20</f>
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="R18" s="22" t="n">
         <f aca="false">SUM(L18:Q18)</f>
-        <v>32118.783568517</v>
+        <v>49617.013039618</v>
       </c>
       <c r="S18" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4208,19 +4208,19 @@
       </c>
       <c r="T18" s="15" t="n">
         <f aca="false">IF(A18&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I18,0)</f>
-        <v>15404.9</v>
+        <v>21143.64</v>
       </c>
       <c r="U18" s="22" t="n">
         <f aca="false">S18+T18</f>
-        <v>27404.9</v>
+        <v>33143.64</v>
       </c>
       <c r="V18" s="22" t="n">
         <f aca="false">I18-R18-U18</f>
-        <v>13832.9830981497</v>
+        <v>17923.346960382</v>
       </c>
       <c r="W18" s="15" t="n">
         <f aca="false">T18/'Premissas Precept'!$B$45</f>
-        <v>2200.7</v>
+        <v>3020.52</v>
       </c>
       <c r="X18" s="35" t="str">
         <f aca="false">IF(V18&gt;=0,"Sim","Não")</f>
@@ -4235,7 +4235,7 @@
         <v>36</v>
       </c>
       <c r="C19" s="36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D19" s="36" t="n">
         <v>1</v>
@@ -4250,27 +4250,27 @@
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">C19*'Premissas Precept'!$B$9</f>
-        <v>19994</v>
+        <v>39988</v>
       </c>
       <c r="H19" s="15" t="n">
         <f aca="false">E19*'Premissas Precept'!$B$12</f>
-        <v>12664.6666666667</v>
+        <v>19998</v>
       </c>
       <c r="I19" s="22" t="n">
         <f aca="false">F19+G19+H19</f>
-        <v>75750.6666666667</v>
+        <v>103078</v>
       </c>
       <c r="J19" s="15" t="n">
         <f aca="false">SUM(I7:I18)</f>
-        <v>477398.166666667</v>
+        <v>532225.5</v>
       </c>
       <c r="K19" s="38" t="n">
         <f aca="false">IF(J19&lt;=0,'Premissas Precept'!$C$24,(J19*LOOKUP(J19,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J19,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J19)</f>
-        <v>0.174262593174321</v>
+        <v>0.176398861948554</v>
       </c>
       <c r="L19" s="15" t="n">
         <f aca="false">I19*K19</f>
-        <v>13200.5076080169</v>
+        <v>18182.841891933</v>
       </c>
       <c r="M19" s="15" t="n">
         <f aca="false">B19*'Premissas Precept'!$B$15</f>
@@ -4278,23 +4278,23 @@
       </c>
       <c r="N19" s="15" t="n">
         <f aca="false">I19*'Premissas Precept'!$B$16</f>
-        <v>1515.01333333333</v>
+        <v>2061.56</v>
       </c>
       <c r="O19" s="15" t="n">
         <f aca="false">(G19+H19)*'Premissas Precept'!$B$17</f>
-        <v>1632.93333333333</v>
+        <v>2999.3</v>
       </c>
       <c r="P19" s="15" t="n">
         <f aca="false">(G19+H19)*'Premissas Precept'!$B$18</f>
-        <v>11430.5333333333</v>
+        <v>20995.1</v>
       </c>
       <c r="Q19" s="15" t="n">
         <f aca="false">C19*'Premissas Precept'!$B$19+E19*'Premissas Precept'!$B$20</f>
-        <v>2000</v>
+        <v>3200</v>
       </c>
       <c r="R19" s="22" t="n">
         <f aca="false">SUM(L19:Q19)</f>
-        <v>33018.9876080169</v>
+        <v>50678.801891933</v>
       </c>
       <c r="S19" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4302,19 +4302,19 @@
       </c>
       <c r="T19" s="15" t="n">
         <f aca="false">IF(A19&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I19,0)</f>
-        <v>15907.64</v>
+        <v>21646.38</v>
       </c>
       <c r="U19" s="22" t="n">
         <f aca="false">S19+T19</f>
-        <v>27907.64</v>
+        <v>33646.38</v>
       </c>
       <c r="V19" s="22" t="n">
         <f aca="false">I19-R19-U19</f>
-        <v>14824.0390586497</v>
+        <v>18752.818108067</v>
       </c>
       <c r="W19" s="15" t="n">
         <f aca="false">T19/'Premissas Precept'!$B$45</f>
-        <v>2272.52</v>
+        <v>3092.34</v>
       </c>
       <c r="X19" s="35" t="str">
         <f aca="false">IF(V19&gt;=0,"Sim","Não")</f>
@@ -4329,7 +4329,7 @@
         <v>38</v>
       </c>
       <c r="C20" s="36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D20" s="36" t="n">
         <v>1</v>
@@ -4344,27 +4344,27 @@
       </c>
       <c r="G20" s="15" t="n">
         <f aca="false">C20*'Premissas Precept'!$B$9</f>
-        <v>19994</v>
+        <v>39988</v>
       </c>
       <c r="H20" s="15" t="n">
         <f aca="false">E20*'Premissas Precept'!$B$12</f>
-        <v>15830.8333333333</v>
+        <v>24997.5</v>
       </c>
       <c r="I20" s="22" t="n">
         <f aca="false">F20+G20+H20</f>
-        <v>81310.8333333333</v>
+        <v>110471.5</v>
       </c>
       <c r="J20" s="15" t="n">
         <f aca="false">SUM(I8:I19)</f>
-        <v>545966.833333333</v>
+        <v>628121.5</v>
       </c>
       <c r="K20" s="38" t="n">
         <f aca="false">IF(J20&lt;=0,'Premissas Precept'!$C$24,(J20*LOOKUP(J20,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J20,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J20)</f>
-        <v>0.176867030384324</v>
+        <v>0.179238718146091</v>
       </c>
       <c r="L20" s="15" t="n">
         <f aca="false">I20*K20</f>
-        <v>14381.2056297414</v>
+        <v>19800.7700516759</v>
       </c>
       <c r="M20" s="15" t="n">
         <f aca="false">B20*'Premissas Precept'!$B$15</f>
@@ -4372,23 +4372,23 @@
       </c>
       <c r="N20" s="15" t="n">
         <f aca="false">I20*'Premissas Precept'!$B$16</f>
-        <v>1626.21666666667</v>
+        <v>2209.43</v>
       </c>
       <c r="O20" s="15" t="n">
         <f aca="false">(G20+H20)*'Premissas Precept'!$B$17</f>
-        <v>1791.24166666667</v>
+        <v>3249.275</v>
       </c>
       <c r="P20" s="15" t="n">
         <f aca="false">(G20+H20)*'Premissas Precept'!$B$18</f>
-        <v>12538.6916666667</v>
+        <v>22744.925</v>
       </c>
       <c r="Q20" s="15" t="n">
         <f aca="false">C20*'Premissas Precept'!$B$19+E20*'Premissas Precept'!$B$20</f>
-        <v>2200</v>
+        <v>3400</v>
       </c>
       <c r="R20" s="22" t="n">
         <f aca="false">SUM(L20:Q20)</f>
-        <v>35957.3556297414</v>
+        <v>54824.4000516759</v>
       </c>
       <c r="S20" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4396,19 +4396,19 @@
       </c>
       <c r="T20" s="15" t="n">
         <f aca="false">IF(A20&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I20,0)</f>
-        <v>17075.275</v>
+        <v>23199.015</v>
       </c>
       <c r="U20" s="22" t="n">
         <f aca="false">S20+T20</f>
-        <v>29075.275</v>
+        <v>35199.015</v>
       </c>
       <c r="V20" s="22" t="n">
         <f aca="false">I20-R20-U20</f>
-        <v>16278.2027035919</v>
+        <v>20448.0849483241</v>
       </c>
       <c r="W20" s="15" t="n">
         <f aca="false">T20/'Premissas Precept'!$B$45</f>
-        <v>2439.325</v>
+        <v>3314.145</v>
       </c>
       <c r="X20" s="35" t="str">
         <f aca="false">IF(V20&gt;=0,"Sim","Não")</f>
@@ -4423,7 +4423,7 @@
         <v>40</v>
       </c>
       <c r="C21" s="36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D21" s="36" t="n">
         <v>1</v>
@@ -4438,27 +4438,27 @@
       </c>
       <c r="G21" s="15" t="n">
         <f aca="false">C21*'Premissas Precept'!$B$9</f>
-        <v>19994</v>
+        <v>39988</v>
       </c>
       <c r="H21" s="15" t="n">
         <f aca="false">E21*'Premissas Precept'!$B$12</f>
-        <v>15830.8333333333</v>
+        <v>24997.5</v>
       </c>
       <c r="I21" s="22" t="n">
         <f aca="false">F21+G21+H21</f>
-        <v>83704.8333333333</v>
+        <v>112865.5</v>
       </c>
       <c r="J21" s="15" t="n">
         <f aca="false">SUM(I9:I20)</f>
-        <v>616504.666666667</v>
+        <v>727820</v>
       </c>
       <c r="K21" s="38" t="n">
         <f aca="false">IF(J21&lt;=0,'Premissas Precept'!$C$24,(J21*LOOKUP(J21,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J21,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J21)</f>
-        <v>0.178941727394332</v>
+        <v>0.181505179852161</v>
       </c>
       <c r="L21" s="15" t="n">
         <f aca="false">I21*K21</f>
-        <v>14978.2874679213</v>
+        <v>20485.6728766041</v>
       </c>
       <c r="M21" s="15" t="n">
         <f aca="false">B21*'Premissas Precept'!$B$15</f>
@@ -4466,23 +4466,23 @@
       </c>
       <c r="N21" s="15" t="n">
         <f aca="false">I21*'Premissas Precept'!$B$16</f>
-        <v>1674.09666666667</v>
+        <v>2257.31</v>
       </c>
       <c r="O21" s="15" t="n">
         <f aca="false">(G21+H21)*'Premissas Precept'!$B$17</f>
-        <v>1791.24166666667</v>
+        <v>3249.275</v>
       </c>
       <c r="P21" s="15" t="n">
         <f aca="false">(G21+H21)*'Premissas Precept'!$B$18</f>
-        <v>12538.6916666667</v>
+        <v>22744.925</v>
       </c>
       <c r="Q21" s="15" t="n">
         <f aca="false">C21*'Premissas Precept'!$B$19+E21*'Premissas Precept'!$B$20</f>
-        <v>2200</v>
+        <v>3400</v>
       </c>
       <c r="R21" s="22" t="n">
         <f aca="false">SUM(L21:Q21)</f>
-        <v>36782.3174679213</v>
+        <v>55737.1828766041</v>
       </c>
       <c r="S21" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4490,19 +4490,19 @@
       </c>
       <c r="T21" s="15" t="n">
         <f aca="false">IF(A21&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I21,0)</f>
-        <v>17578.015</v>
+        <v>23701.755</v>
       </c>
       <c r="U21" s="22" t="n">
         <f aca="false">S21+T21</f>
-        <v>29578.015</v>
+        <v>35701.755</v>
       </c>
       <c r="V21" s="22" t="n">
         <f aca="false">I21-R21-U21</f>
-        <v>17344.500865412</v>
+        <v>21426.5621233959</v>
       </c>
       <c r="W21" s="15" t="n">
         <f aca="false">T21/'Premissas Precept'!$B$45</f>
-        <v>2511.145</v>
+        <v>3385.965</v>
       </c>
       <c r="X21" s="35" t="str">
         <f aca="false">IF(V21&gt;=0,"Sim","Não")</f>
@@ -4517,7 +4517,7 @@
         <v>42</v>
       </c>
       <c r="C22" s="36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D22" s="36" t="n">
         <v>1</v>
@@ -4532,27 +4532,27 @@
       </c>
       <c r="G22" s="15" t="n">
         <f aca="false">C22*'Premissas Precept'!$B$9</f>
-        <v>19994</v>
+        <v>39988</v>
       </c>
       <c r="H22" s="15" t="n">
         <f aca="false">E22*'Premissas Precept'!$B$12</f>
-        <v>18997</v>
+        <v>29997</v>
       </c>
       <c r="I22" s="22" t="n">
         <f aca="false">F22+G22+H22</f>
-        <v>89265</v>
+        <v>120259</v>
       </c>
       <c r="J22" s="15" t="n">
         <f aca="false">SUM(I10:I21)</f>
-        <v>677045.5</v>
+        <v>817521.5</v>
       </c>
       <c r="K22" s="38" t="n">
         <f aca="false">IF(J22&lt;=0,'Premissas Precept'!$C$24,(J22*LOOKUP(J22,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J22,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J22)</f>
-        <v>0.180377644486227</v>
+        <v>0.184083118914915</v>
       </c>
       <c r="L22" s="15" t="n">
         <f aca="false">I22*K22</f>
-        <v>16101.4104350631</v>
+        <v>22137.6517975888</v>
       </c>
       <c r="M22" s="15" t="n">
         <f aca="false">B22*'Premissas Precept'!$B$15</f>
@@ -4560,23 +4560,23 @@
       </c>
       <c r="N22" s="15" t="n">
         <f aca="false">I22*'Premissas Precept'!$B$16</f>
-        <v>1785.3</v>
+        <v>2405.18</v>
       </c>
       <c r="O22" s="15" t="n">
         <f aca="false">(G22+H22)*'Premissas Precept'!$B$17</f>
-        <v>1949.55</v>
+        <v>3499.25</v>
       </c>
       <c r="P22" s="15" t="n">
         <f aca="false">(G22+H22)*'Premissas Precept'!$B$18</f>
-        <v>13646.85</v>
+        <v>24494.75</v>
       </c>
       <c r="Q22" s="15" t="n">
         <f aca="false">C22*'Premissas Precept'!$B$19+E22*'Premissas Precept'!$B$20</f>
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="R22" s="22" t="n">
         <f aca="false">SUM(L22:Q22)</f>
-        <v>39663.1104350631</v>
+        <v>59916.8317975888</v>
       </c>
       <c r="S22" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4584,19 +4584,19 @@
       </c>
       <c r="T22" s="15" t="n">
         <f aca="false">IF(A22&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I22,0)</f>
-        <v>18745.65</v>
+        <v>25254.39</v>
       </c>
       <c r="U22" s="22" t="n">
         <f aca="false">S22+T22</f>
-        <v>30745.65</v>
+        <v>37254.39</v>
       </c>
       <c r="V22" s="22" t="n">
         <f aca="false">I22-R22-U22</f>
-        <v>18856.2395649369</v>
+        <v>23087.7782024112</v>
       </c>
       <c r="W22" s="15" t="n">
         <f aca="false">T22/'Premissas Precept'!$B$45</f>
-        <v>2677.95</v>
+        <v>3607.77</v>
       </c>
       <c r="X22" s="35" t="str">
         <f aca="false">IF(V22&gt;=0,"Sim","Não")</f>
@@ -4611,7 +4611,7 @@
         <v>44</v>
       </c>
       <c r="C23" s="36" t="n">
-        <v>2</v>
+        <v>4</v>
       </c>
       <c r="D23" s="36" t="n">
         <v>1</v>
@@ -4626,27 +4626,27 @@
       </c>
       <c r="G23" s="15" t="n">
         <f aca="false">C23*'Premissas Precept'!$B$9</f>
-        <v>19994</v>
+        <v>39988</v>
       </c>
       <c r="H23" s="15" t="n">
         <f aca="false">E23*'Premissas Precept'!$B$12</f>
-        <v>18997</v>
+        <v>29997</v>
       </c>
       <c r="I23" s="22" t="n">
         <f aca="false">F23+G23+H23</f>
-        <v>91659</v>
+        <v>122653</v>
       </c>
       <c r="J23" s="15" t="n">
         <f aca="false">SUM(I11:I22)</f>
-        <v>739555.5</v>
+        <v>911025.5</v>
       </c>
       <c r="K23" s="38" t="n">
         <f aca="false">IF(J23&lt;=0,'Premissas Precept'!$C$24,(J23*LOOKUP(J23,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J23,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J23)</f>
-        <v>0.181878003070763</v>
+        <v>0.186229943618483</v>
       </c>
       <c r="L23" s="15" t="n">
         <f aca="false">I23*K23</f>
-        <v>16670.7558834631</v>
+        <v>22841.6612746378</v>
       </c>
       <c r="M23" s="15" t="n">
         <f aca="false">B23*'Premissas Precept'!$B$15</f>
@@ -4654,23 +4654,23 @@
       </c>
       <c r="N23" s="15" t="n">
         <f aca="false">I23*'Premissas Precept'!$B$16</f>
-        <v>1833.18</v>
+        <v>2453.06</v>
       </c>
       <c r="O23" s="15" t="n">
         <f aca="false">(G23+H23)*'Premissas Precept'!$B$17</f>
-        <v>1949.55</v>
+        <v>3499.25</v>
       </c>
       <c r="P23" s="15" t="n">
         <f aca="false">(G23+H23)*'Premissas Precept'!$B$18</f>
-        <v>13646.85</v>
+        <v>24494.75</v>
       </c>
       <c r="Q23" s="15" t="n">
         <f aca="false">C23*'Premissas Precept'!$B$19+E23*'Premissas Precept'!$B$20</f>
-        <v>2400</v>
+        <v>3600</v>
       </c>
       <c r="R23" s="22" t="n">
         <f aca="false">SUM(L23:Q23)</f>
-        <v>40460.3358834631</v>
+        <v>60848.7212746378</v>
       </c>
       <c r="S23" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4678,19 +4678,19 @@
       </c>
       <c r="T23" s="15" t="n">
         <f aca="false">IF(A23&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I23,0)</f>
-        <v>19248.39</v>
+        <v>25757.13</v>
       </c>
       <c r="U23" s="22" t="n">
         <f aca="false">S23+T23</f>
-        <v>31248.39</v>
+        <v>37757.13</v>
       </c>
       <c r="V23" s="22" t="n">
         <f aca="false">I23-R23-U23</f>
-        <v>19950.2741165369</v>
+        <v>24047.1487253622</v>
       </c>
       <c r="W23" s="15" t="n">
         <f aca="false">T23/'Premissas Precept'!$B$45</f>
-        <v>2749.77</v>
+        <v>3679.59</v>
       </c>
       <c r="X23" s="35" t="str">
         <f aca="false">IF(V23&gt;=0,"Sim","Não")</f>
@@ -4705,7 +4705,7 @@
         <v>46</v>
       </c>
       <c r="C24" s="36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D24" s="36" t="n">
         <v>1</v>
@@ -4720,27 +4720,27 @@
       </c>
       <c r="G24" s="15" t="n">
         <f aca="false">C24*'Premissas Precept'!$B$9</f>
-        <v>19994</v>
+        <v>49985</v>
       </c>
       <c r="H24" s="15" t="n">
         <f aca="false">E24*'Premissas Precept'!$B$12</f>
-        <v>18997</v>
+        <v>29997</v>
       </c>
       <c r="I24" s="22" t="n">
         <f aca="false">F24+G24+H24</f>
-        <v>94053</v>
+        <v>135044</v>
       </c>
       <c r="J24" s="15" t="n">
         <f aca="false">SUM(I12:I23)</f>
-        <v>798899.333333333</v>
+        <v>999530</v>
       </c>
       <c r="K24" s="38" t="n">
         <f aca="false">IF(J24&lt;=0,'Premissas Precept'!$C$24,(J24*LOOKUP(J24,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J24,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J24)</f>
-        <v>0.183595551045647</v>
+        <v>0.187891959220834</v>
       </c>
       <c r="L24" s="15" t="n">
         <f aca="false">I24*K24</f>
-        <v>17267.7123624962</v>
+        <v>25373.6817410183</v>
       </c>
       <c r="M24" s="15" t="n">
         <f aca="false">B24*'Premissas Precept'!$B$15</f>
@@ -4748,23 +4748,23 @@
       </c>
       <c r="N24" s="15" t="n">
         <f aca="false">I24*'Premissas Precept'!$B$16</f>
-        <v>1881.06</v>
+        <v>2700.88</v>
       </c>
       <c r="O24" s="15" t="n">
         <f aca="false">(G24+H24)*'Premissas Precept'!$B$17</f>
-        <v>1949.55</v>
+        <v>3999.1</v>
       </c>
       <c r="P24" s="15" t="n">
         <f aca="false">(G24+H24)*'Premissas Precept'!$B$18</f>
-        <v>13646.85</v>
+        <v>27993.7</v>
       </c>
       <c r="Q24" s="15" t="n">
         <f aca="false">C24*'Premissas Precept'!$B$19+E24*'Premissas Precept'!$B$20</f>
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="R24" s="22" t="n">
         <f aca="false">SUM(L24:Q24)</f>
-        <v>41285.1723624962</v>
+        <v>68407.3617410183</v>
       </c>
       <c r="S24" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4772,19 +4772,19 @@
       </c>
       <c r="T24" s="15" t="n">
         <f aca="false">IF(A24&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I24,0)</f>
-        <v>19751.13</v>
+        <v>28359.24</v>
       </c>
       <c r="U24" s="22" t="n">
         <f aca="false">S24+T24</f>
-        <v>31751.13</v>
+        <v>40359.24</v>
       </c>
       <c r="V24" s="22" t="n">
         <f aca="false">I24-R24-U24</f>
-        <v>21016.6976375038</v>
+        <v>26277.3982589817</v>
       </c>
       <c r="W24" s="15" t="n">
         <f aca="false">T24/'Premissas Precept'!$B$45</f>
-        <v>2821.59</v>
+        <v>4051.32</v>
       </c>
       <c r="X24" s="35" t="str">
         <f aca="false">IF(V24&gt;=0,"Sim","Não")</f>
@@ -4799,7 +4799,7 @@
         <v>48</v>
       </c>
       <c r="C25" s="36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D25" s="36" t="n">
         <v>1</v>
@@ -4814,27 +4814,27 @@
       </c>
       <c r="G25" s="15" t="n">
         <f aca="false">C25*'Premissas Precept'!$B$9</f>
-        <v>19994</v>
+        <v>49985</v>
       </c>
       <c r="H25" s="15" t="n">
         <f aca="false">E25*'Premissas Precept'!$B$12</f>
-        <v>18997</v>
+        <v>29997</v>
       </c>
       <c r="I25" s="22" t="n">
         <f aca="false">F25+G25+H25</f>
-        <v>96447</v>
+        <v>137438</v>
       </c>
       <c r="J25" s="15" t="n">
         <f aca="false">SUM(I13:I24)</f>
-        <v>857046.166666667</v>
+        <v>1096834.5</v>
       </c>
       <c r="K25" s="38" t="n">
         <f aca="false">IF(J25&lt;=0,'Premissas Precept'!$C$24,(J25*LOOKUP(J25,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J25,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J25)</f>
-        <v>0.185047749275272</v>
+        <v>0.1894096807677</v>
       </c>
       <c r="L25" s="15" t="n">
         <f aca="false">I25*K25</f>
-        <v>17847.3002743522</v>
+        <v>26032.0877053512</v>
       </c>
       <c r="M25" s="15" t="n">
         <f aca="false">B25*'Premissas Precept'!$B$15</f>
@@ -4842,23 +4842,23 @@
       </c>
       <c r="N25" s="15" t="n">
         <f aca="false">I25*'Premissas Precept'!$B$16</f>
-        <v>1928.94</v>
+        <v>2748.76</v>
       </c>
       <c r="O25" s="15" t="n">
         <f aca="false">(G25+H25)*'Premissas Precept'!$B$17</f>
-        <v>1949.55</v>
+        <v>3999.1</v>
       </c>
       <c r="P25" s="15" t="n">
         <f aca="false">(G25+H25)*'Premissas Precept'!$B$18</f>
-        <v>13646.85</v>
+        <v>27993.7</v>
       </c>
       <c r="Q25" s="15" t="n">
         <f aca="false">C25*'Premissas Precept'!$B$19+E25*'Premissas Precept'!$B$20</f>
-        <v>2400</v>
+        <v>4200</v>
       </c>
       <c r="R25" s="22" t="n">
         <f aca="false">SUM(L25:Q25)</f>
-        <v>42092.6402743522</v>
+        <v>69293.6477053512</v>
       </c>
       <c r="S25" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4866,19 +4866,19 @@
       </c>
       <c r="T25" s="15" t="n">
         <f aca="false">IF(A25&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I25,0)</f>
-        <v>20253.87</v>
+        <v>28861.98</v>
       </c>
       <c r="U25" s="22" t="n">
         <f aca="false">S25+T25</f>
-        <v>32253.87</v>
+        <v>40861.98</v>
       </c>
       <c r="V25" s="22" t="n">
         <f aca="false">I25-R25-U25</f>
-        <v>22100.4897256478</v>
+        <v>27282.3722946488</v>
       </c>
       <c r="W25" s="15" t="n">
         <f aca="false">T25/'Premissas Precept'!$B$45</f>
-        <v>2893.41</v>
+        <v>4123.14</v>
       </c>
       <c r="X25" s="35" t="str">
         <f aca="false">IF(V25&gt;=0,"Sim","Não")</f>
@@ -4893,7 +4893,7 @@
         <v>50</v>
       </c>
       <c r="C26" s="36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D26" s="36" t="n">
         <v>1</v>
@@ -4908,27 +4908,27 @@
       </c>
       <c r="G26" s="15" t="n">
         <f aca="false">C26*'Premissas Precept'!$B$9</f>
-        <v>29991</v>
+        <v>49985</v>
       </c>
       <c r="H26" s="15" t="n">
         <f aca="false">E26*'Premissas Precept'!$B$12</f>
-        <v>18997</v>
+        <v>29997</v>
       </c>
       <c r="I26" s="22" t="n">
         <f aca="false">F26+G26+H26</f>
-        <v>108838</v>
+        <v>139832</v>
       </c>
       <c r="J26" s="15" t="n">
         <f aca="false">SUM(I14:I25)</f>
-        <v>912026.833333333</v>
+        <v>1189139.5</v>
       </c>
       <c r="K26" s="38" t="n">
         <f aca="false">IF(J26&lt;=0,'Premissas Precept'!$C$24,(J26*LOOKUP(J26,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J26,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J26)</f>
-        <v>0.186250551655918</v>
+        <v>0.190619853684114</v>
       </c>
       <c r="L26" s="15" t="n">
         <f aca="false">I26*K26</f>
-        <v>20271.1375411268</v>
+        <v>26654.755380357</v>
       </c>
       <c r="M26" s="15" t="n">
         <f aca="false">B26*'Premissas Precept'!$B$15</f>
@@ -4936,23 +4936,23 @@
       </c>
       <c r="N26" s="15" t="n">
         <f aca="false">I26*'Premissas Precept'!$B$16</f>
-        <v>2176.76</v>
+        <v>2796.64</v>
       </c>
       <c r="O26" s="15" t="n">
         <f aca="false">(G26+H26)*'Premissas Precept'!$B$17</f>
-        <v>2449.4</v>
+        <v>3999.1</v>
       </c>
       <c r="P26" s="15" t="n">
         <f aca="false">(G26+H26)*'Premissas Precept'!$B$18</f>
-        <v>17145.8</v>
+        <v>27993.7</v>
       </c>
       <c r="Q26" s="15" t="n">
         <f aca="false">C26*'Premissas Precept'!$B$19+E26*'Premissas Precept'!$B$20</f>
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="R26" s="22" t="n">
         <f aca="false">SUM(L26:Q26)</f>
-        <v>49543.0975411268</v>
+        <v>70144.195380357</v>
       </c>
       <c r="S26" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4960,19 +4960,19 @@
       </c>
       <c r="T26" s="15" t="n">
         <f aca="false">IF(A26&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I26,0)</f>
-        <v>22855.98</v>
+        <v>29364.72</v>
       </c>
       <c r="U26" s="22" t="n">
         <f aca="false">S26+T26</f>
-        <v>34855.98</v>
+        <v>41364.72</v>
       </c>
       <c r="V26" s="22" t="n">
         <f aca="false">I26-R26-U26</f>
-        <v>24438.9224588732</v>
+        <v>28323.084619643</v>
       </c>
       <c r="W26" s="15" t="n">
         <f aca="false">T26/'Premissas Precept'!$B$45</f>
-        <v>3265.14</v>
+        <v>4194.96</v>
       </c>
       <c r="X26" s="35" t="str">
         <f aca="false">IF(V26&gt;=0,"Sim","Não")</f>
@@ -4987,7 +4987,7 @@
         <v>52</v>
       </c>
       <c r="C27" s="36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D27" s="36" t="n">
         <v>1</v>
@@ -5002,27 +5002,27 @@
       </c>
       <c r="G27" s="15" t="n">
         <f aca="false">C27*'Premissas Precept'!$B$9</f>
-        <v>29991</v>
+        <v>49985</v>
       </c>
       <c r="H27" s="15" t="n">
         <f aca="false">E27*'Premissas Precept'!$B$12</f>
-        <v>18997</v>
+        <v>29997</v>
       </c>
       <c r="I27" s="22" t="n">
         <f aca="false">F27+G27+H27</f>
-        <v>111232</v>
+        <v>142226</v>
       </c>
       <c r="J27" s="15" t="n">
         <f aca="false">SUM(I15:I26)</f>
-        <v>965810.5</v>
+        <v>1270250.5</v>
       </c>
       <c r="K27" s="38" t="n">
         <f aca="false">IF(J27&lt;=0,'Premissas Precept'!$C$24,(J27*LOOKUP(J27,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J27,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J27)</f>
-        <v>0.187294663394113</v>
+        <v>0.191538088353439</v>
       </c>
       <c r="L27" s="15" t="n">
         <f aca="false">I27*K27</f>
-        <v>20833.159998654</v>
+        <v>27241.6961541562</v>
       </c>
       <c r="M27" s="15" t="n">
         <f aca="false">B27*'Premissas Precept'!$B$15</f>
@@ -5030,23 +5030,23 @@
       </c>
       <c r="N27" s="15" t="n">
         <f aca="false">I27*'Premissas Precept'!$B$16</f>
-        <v>2224.64</v>
+        <v>2844.52</v>
       </c>
       <c r="O27" s="15" t="n">
         <f aca="false">(G27+H27)*'Premissas Precept'!$B$17</f>
-        <v>2449.4</v>
+        <v>3999.1</v>
       </c>
       <c r="P27" s="15" t="n">
         <f aca="false">(G27+H27)*'Premissas Precept'!$B$18</f>
-        <v>17145.8</v>
+        <v>27993.7</v>
       </c>
       <c r="Q27" s="15" t="n">
         <f aca="false">C27*'Premissas Precept'!$B$19+E27*'Premissas Precept'!$B$20</f>
-        <v>3000</v>
+        <v>4200</v>
       </c>
       <c r="R27" s="22" t="n">
         <f aca="false">SUM(L27:Q27)</f>
-        <v>50332.999998654</v>
+        <v>70959.0161541562</v>
       </c>
       <c r="S27" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5054,19 +5054,19 @@
       </c>
       <c r="T27" s="15" t="n">
         <f aca="false">IF(A27&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I27,0)</f>
-        <v>23358.72</v>
+        <v>29867.46</v>
       </c>
       <c r="U27" s="22" t="n">
         <f aca="false">S27+T27</f>
-        <v>35358.72</v>
+        <v>41867.46</v>
       </c>
       <c r="V27" s="22" t="n">
         <f aca="false">I27-R27-U27</f>
-        <v>25540.280001346</v>
+        <v>29399.5238458438</v>
       </c>
       <c r="W27" s="15" t="n">
         <f aca="false">T27/'Premissas Precept'!$B$45</f>
-        <v>3336.96</v>
+        <v>4266.78</v>
       </c>
       <c r="X27" s="35" t="str">
         <f aca="false">IF(V27&gt;=0,"Sim","Não")</f>
@@ -5081,7 +5081,7 @@
         <v>54</v>
       </c>
       <c r="C28" s="36" t="n">
-        <v>2</v>
+        <v>5</v>
       </c>
       <c r="D28" s="36" t="n">
         <v>0</v>
@@ -5096,27 +5096,27 @@
       </c>
       <c r="G28" s="15" t="n">
         <f aca="false">C28*'Premissas Precept'!$B$9</f>
-        <v>19994</v>
+        <v>49985</v>
       </c>
       <c r="H28" s="15" t="n">
         <f aca="false">E28*'Premissas Precept'!$B$12</f>
-        <v>15830.8333333333</v>
+        <v>24997.5</v>
       </c>
       <c r="I28" s="22" t="n">
         <f aca="false">F28+G28+H28</f>
-        <v>100462.833333333</v>
+        <v>139620.5</v>
       </c>
       <c r="J28" s="15" t="n">
         <f aca="false">SUM(I16:I27)</f>
-        <v>1026425</v>
+        <v>1356359</v>
       </c>
       <c r="K28" s="38" t="n">
         <f aca="false">IF(J28&lt;=0,'Premissas Precept'!$C$24,(J28*LOOKUP(J28,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J28,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J28)</f>
-        <v>0.188340234308401</v>
+        <v>0.192392718299506</v>
       </c>
       <c r="L28" s="15" t="n">
         <f aca="false">I28*K28</f>
-        <v>18921.1935692858</v>
+        <v>26861.9675253362</v>
       </c>
       <c r="M28" s="15" t="n">
         <f aca="false">B28*'Premissas Precept'!$B$15</f>
@@ -5124,23 +5124,23 @@
       </c>
       <c r="N28" s="15" t="n">
         <f aca="false">I28*'Premissas Precept'!$B$16</f>
-        <v>2009.25666666667</v>
+        <v>2792.41</v>
       </c>
       <c r="O28" s="15" t="n">
         <f aca="false">(G28+H28)*'Premissas Precept'!$B$17</f>
-        <v>1791.24166666667</v>
+        <v>3749.125</v>
       </c>
       <c r="P28" s="15" t="n">
         <f aca="false">(G28+H28)*'Premissas Precept'!$B$18</f>
-        <v>12538.6916666667</v>
+        <v>26243.875</v>
       </c>
       <c r="Q28" s="15" t="n">
         <f aca="false">C28*'Premissas Precept'!$B$19+E28*'Premissas Precept'!$B$20</f>
-        <v>2200</v>
+        <v>4000</v>
       </c>
       <c r="R28" s="22" t="n">
         <f aca="false">SUM(L28:Q28)</f>
-        <v>42320.3835692858</v>
+        <v>68507.3775253362</v>
       </c>
       <c r="S28" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5148,19 +5148,19 @@
       </c>
       <c r="T28" s="15" t="n">
         <f aca="false">IF(A28&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I28,0)</f>
-        <v>21097.195</v>
+        <v>29320.305</v>
       </c>
       <c r="U28" s="22" t="n">
         <f aca="false">S28+T28</f>
-        <v>33097.195</v>
+        <v>41320.305</v>
       </c>
       <c r="V28" s="22" t="n">
         <f aca="false">I28-R28-U28</f>
-        <v>25045.2547640475</v>
+        <v>29792.8174746638</v>
       </c>
       <c r="W28" s="15" t="n">
         <f aca="false">T28/'Premissas Precept'!$B$45</f>
-        <v>3013.885</v>
+        <v>4188.615</v>
       </c>
       <c r="X28" s="35" t="str">
         <f aca="false">IF(V28&gt;=0,"Sim","Não")</f>
@@ -5175,7 +5175,7 @@
         <v>56</v>
       </c>
       <c r="C29" s="36" t="n">
-        <v>3</v>
+        <v>5</v>
       </c>
       <c r="D29" s="36" t="n">
         <v>1</v>
@@ -5190,27 +5190,27 @@
       </c>
       <c r="G29" s="15" t="n">
         <f aca="false">C29*'Premissas Precept'!$B$9</f>
-        <v>29991</v>
+        <v>49985</v>
       </c>
       <c r="H29" s="15" t="n">
         <f aca="false">E29*'Premissas Precept'!$B$12</f>
-        <v>15830.8333333333</v>
+        <v>24997.5</v>
       </c>
       <c r="I29" s="22" t="n">
         <f aca="false">F29+G29+H29</f>
-        <v>112853.833333333</v>
+        <v>142014.5</v>
       </c>
       <c r="J29" s="15" t="n">
         <f aca="false">SUM(I17:I28)</f>
-        <v>1062682.33333333</v>
+        <v>1426274</v>
       </c>
       <c r="K29" s="38" t="n">
         <f aca="false">IF(J29&lt;=0,'Premissas Precept'!$C$24,(J29*LOOKUP(J29,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J29,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J29)</f>
-        <v>0.188908643755879</v>
+        <v>0.193010718838035</v>
       </c>
       <c r="L29" s="15" t="n">
         <f aca="false">I29*K29</f>
-        <v>21319.0645976521</v>
+        <v>27410.3207304242</v>
       </c>
       <c r="M29" s="15" t="n">
         <f aca="false">B29*'Premissas Precept'!$B$15</f>
@@ -5218,23 +5218,23 @@
       </c>
       <c r="N29" s="15" t="n">
         <f aca="false">I29*'Premissas Precept'!$B$16</f>
-        <v>2257.07666666667</v>
+        <v>2840.29</v>
       </c>
       <c r="O29" s="15" t="n">
         <f aca="false">(G29+H29)*'Premissas Precept'!$B$17</f>
-        <v>2291.09166666667</v>
+        <v>3749.125</v>
       </c>
       <c r="P29" s="15" t="n">
         <f aca="false">(G29+H29)*'Premissas Precept'!$B$18</f>
-        <v>16037.6416666667</v>
+        <v>26243.875</v>
       </c>
       <c r="Q29" s="15" t="n">
         <f aca="false">C29*'Premissas Precept'!$B$19+E29*'Premissas Precept'!$B$20</f>
-        <v>2800</v>
+        <v>4000</v>
       </c>
       <c r="R29" s="22" t="n">
         <f aca="false">SUM(L29:Q29)</f>
-        <v>49744.8745976521</v>
+        <v>69283.6107304242</v>
       </c>
       <c r="S29" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5242,19 +5242,19 @@
       </c>
       <c r="T29" s="15" t="n">
         <f aca="false">IF(A29&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I29,0)</f>
-        <v>23699.305</v>
+        <v>29823.045</v>
       </c>
       <c r="U29" s="22" t="n">
         <f aca="false">S29+T29</f>
-        <v>35699.305</v>
+        <v>41823.045</v>
       </c>
       <c r="V29" s="22" t="n">
         <f aca="false">I29-R29-U29</f>
-        <v>27409.6537356813</v>
+        <v>30907.8442695758</v>
       </c>
       <c r="W29" s="15" t="n">
         <f aca="false">T29/'Premissas Precept'!$B$45</f>
-        <v>3385.615</v>
+        <v>4260.435</v>
       </c>
       <c r="X29" s="35" t="str">
         <f aca="false">IF(V29&gt;=0,"Sim","Não")</f>
@@ -5271,7 +5271,7 @@
       </c>
       <c r="C30" s="40" t="n">
         <f aca="false">SUM(C6:C29)</f>
-        <v>38</v>
+        <v>65</v>
       </c>
       <c r="D30" s="40" t="n">
         <f aca="false">SUM(D6:D29)</f>
@@ -5284,21 +5284,21 @@
       </c>
       <c r="G30" s="22" t="n">
         <f aca="false">SUM(G6:G29)</f>
-        <v>379886</v>
+        <v>649805</v>
       </c>
       <c r="H30" s="22" t="n">
         <f aca="false">SUM(H6:H29)</f>
-        <v>250127.166666667</v>
+        <v>394960.5</v>
       </c>
       <c r="I30" s="22" t="n">
         <f aca="false">SUM(I6:I29)</f>
-        <v>1527763.16666667</v>
+        <v>1942515.5</v>
       </c>
       <c r="J30" s="32"/>
       <c r="K30" s="32"/>
       <c r="L30" s="22" t="n">
         <f aca="false">SUM(L6:L29)</f>
-        <v>270672.002691224</v>
+        <v>351518.004455835</v>
       </c>
       <c r="M30" s="22" t="n">
         <f aca="false">SUM(M6:M29)</f>
@@ -5306,23 +5306,23 @@
       </c>
       <c r="N30" s="22" t="n">
         <f aca="false">SUM(N6:N29)</f>
-        <v>30555.2633333333</v>
+        <v>38850.31</v>
       </c>
       <c r="O30" s="22" t="n">
         <f aca="false">SUM(O6:O29)</f>
-        <v>31500.6583333333</v>
+        <v>52238.275</v>
       </c>
       <c r="P30" s="22" t="n">
         <f aca="false">SUM(P6:P29)</f>
-        <v>220504.608333333</v>
+        <v>365667.925</v>
       </c>
       <c r="Q30" s="22" t="n">
         <f aca="false">SUM(Q6:Q29)</f>
-        <v>38600</v>
+        <v>54800</v>
       </c>
       <c r="R30" s="22" t="n">
         <f aca="false">SUM(R6:R29)</f>
-        <v>659332.532691224</v>
+        <v>930574.514455835</v>
       </c>
       <c r="S30" s="22" t="n">
         <f aca="false">SUM(S6:S29)</f>
@@ -5330,19 +5330,19 @@
       </c>
       <c r="T30" s="22" t="n">
         <f aca="false">SUM(T6:T29)</f>
-        <v>316054.235</v>
+        <v>403152.225</v>
       </c>
       <c r="U30" s="22" t="n">
         <f aca="false">SUM(U6:U29)</f>
-        <v>604054.235</v>
+        <v>691152.225</v>
       </c>
       <c r="V30" s="22" t="n">
         <f aca="false">SUM(V6:V29)</f>
-        <v>264376.398975443</v>
+        <v>320788.760544165</v>
       </c>
       <c r="W30" s="22" t="n">
         <f aca="false">SUM(W6:W29)</f>
-        <v>45150.605</v>
+        <v>57593.175</v>
       </c>
       <c r="X30" s="32"/>
     </row>
@@ -5427,26 +5427,26 @@
       <c r="D35" s="43"/>
       <c r="E35" s="28" t="n">
         <f aca="false">AVERAGE(I6:I11)</f>
-        <v>17496.1944444444</v>
+        <v>17801.75</v>
       </c>
       <c r="F35" s="28" t="n">
         <f aca="false">AVERAGE(R6:R11)</f>
-        <v>6505.64513888889</v>
+        <v>6681.33958333333</v>
       </c>
       <c r="G35" s="28" t="n">
         <f aca="false">AVERAGE(U6:U11)</f>
-        <v>14878.1958333333</v>
+        <v>14942.3625</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="23" t="n">
         <f aca="false">F35/E35</f>
-        <v>0.371832009500479</v>
+        <v>0.375319257001887</v>
       </c>
       <c r="J35" s="15" t="n">
         <f aca="false">E35-F35-G35</f>
-        <v>-3887.64652777778</v>
+        <v>-3821.95208333333</v>
       </c>
       <c r="K35" s="44" t="n">
         <f aca="false">AVERAGE(B6:B11)</f>
@@ -5472,26 +5472,26 @@
       <c r="D36" s="43"/>
       <c r="E36" s="28" t="n">
         <f aca="false">AVERAGE(I12:I17)</f>
-        <v>50642.0555555556</v>
+        <v>54919.8333333333</v>
       </c>
       <c r="F36" s="28" t="n">
         <f aca="false">AVERAGE(R12:R17)</f>
-        <v>21163.1004869335</v>
+        <v>23711.3861311891</v>
       </c>
       <c r="G36" s="28" t="n">
         <f aca="false">AVERAGE(U12:U17)</f>
-        <v>22634.8316666667</v>
+        <v>23533.165</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="23" t="n">
         <f aca="false">F36/E36</f>
-        <v>0.417895763802815</v>
+        <v>0.431745413123779</v>
       </c>
       <c r="J36" s="15" t="n">
         <f aca="false">E36-F36-G36</f>
-        <v>6844.12340195541</v>
+        <v>7675.28220214424</v>
       </c>
       <c r="K36" s="44" t="n">
         <f aca="false">AVERAGE(B12:B17)</f>
@@ -5517,26 +5517,26 @@
       <c r="D37" s="43"/>
       <c r="E37" s="28" t="n">
         <f aca="false">AVERAGE(I18:I29)</f>
-        <v>93244.4722222222</v>
+        <v>125515.5</v>
       </c>
       <c r="F37" s="28" t="n">
         <f aca="false">AVERAGE(R18:R29)</f>
-        <v>41110.0049113575</v>
+        <v>62351.5133473917</v>
       </c>
       <c r="G37" s="28" t="n">
         <f aca="false">AVERAGE(U18:U29)</f>
-        <v>31581.3391666667</v>
+        <v>38358.255</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="23" t="n">
         <f aca="false">F37/E37</f>
-        <v>0.440884096736407</v>
+        <v>0.496763454293627</v>
       </c>
       <c r="J37" s="15" t="n">
         <f aca="false">E37-F37-G37</f>
-        <v>20553.1281441981</v>
+        <v>24805.7316526083</v>
       </c>
       <c r="K37" s="44" t="n">
         <f aca="false">AVERAGE(B18:B29)</f>
@@ -5544,7 +5544,7 @@
       </c>
       <c r="L37" s="34" t="n">
         <f aca="false">SUM(C18:C29)</f>
-        <v>27</v>
+        <v>54</v>
       </c>
       <c r="M37" s="34" t="n">
         <f aca="false">SUM(D18:D29)</f>
@@ -5622,7 +5622,7 @@
       <c r="D44" s="45"/>
       <c r="E44" s="44" t="n">
         <f aca="false">AVERAGE(C18:C29)</f>
-        <v>2.25</v>
+        <v>4.5</v>
       </c>
       <c r="F44" s="15" t="n">
         <f aca="false">'Premissas Precept'!B9</f>
@@ -5630,7 +5630,7 @@
       </c>
       <c r="G44" s="15" t="n">
         <f aca="false">E44*F44</f>
-        <v>22493.25</v>
+        <v>44986.5</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5646,11 +5646,11 @@
       </c>
       <c r="F45" s="15" t="n">
         <f aca="false">'Premissas Precept'!B12</f>
-        <v>3166.16666666667</v>
+        <v>4999.5</v>
       </c>
       <c r="G45" s="15" t="n">
         <f aca="false">E45*F45</f>
-        <v>16886.2222222222</v>
+        <v>26664</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5664,7 +5664,7 @@
       <c r="F46" s="15"/>
       <c r="G46" s="28" t="n">
         <f aca="false">SUM(G42:G45)</f>
-        <v>93244.4722222222</v>
+        <v>125515.5</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5697,11 +5697,11 @@
       <c r="E48" s="44"/>
       <c r="F48" s="23" t="n">
         <f aca="false">G48/G46</f>
-        <v>0.182602351705945</v>
+        <v>0.186147023122443</v>
       </c>
       <c r="G48" s="15" t="n">
         <f aca="false">AVERAGE(L18:L29)</f>
-        <v>17026.6599113575</v>
+        <v>23364.3366807251</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5718,7 +5718,7 @@
       </c>
       <c r="G49" s="15" t="n">
         <f aca="false">AVERAGE(N18:N29)</f>
-        <v>1864.88944444444</v>
+        <v>2510.31</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5735,7 +5735,7 @@
       </c>
       <c r="G50" s="15" t="n">
         <f aca="false">AVERAGE(O18:O29)</f>
-        <v>1968.97361111111</v>
+        <v>3582.525</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5749,7 +5749,7 @@
       <c r="F51" s="15"/>
       <c r="G51" s="15" t="n">
         <f aca="false">AVERAGE(Q18:Q29)</f>
-        <v>2416.66666666667</v>
+        <v>3766.66666666667</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5766,7 +5766,7 @@
       </c>
       <c r="G52" s="15" t="n">
         <f aca="false">AVERAGE(P18:P29)</f>
-        <v>13782.8152777778</v>
+        <v>25077.675</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5779,11 +5779,11 @@
       <c r="E53" s="44"/>
       <c r="F53" s="23" t="n">
         <f aca="false">G53/G46</f>
-        <v>0.440884096736408</v>
+        <v>0.496763454293627</v>
       </c>
       <c r="G53" s="28" t="n">
         <f aca="false">SUM(G47:G52)</f>
-        <v>41110.0049113575</v>
+        <v>62351.5133473917</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5800,7 +5800,7 @@
       </c>
       <c r="G54" s="15" t="n">
         <f aca="false">AVERAGE(T18:T29)</f>
-        <v>19581.3391666667</v>
+        <v>26358.255</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -5828,7 +5828,7 @@
       <c r="F56" s="15"/>
       <c r="G56" s="28" t="n">
         <f aca="false">G54+G55</f>
-        <v>31581.3391666667</v>
+        <v>38358.255</v>
       </c>
     </row>
   </sheetData>
@@ -6083,24 +6083,24 @@
       </c>
       <c r="B11" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I11</f>
-        <v>32315.1666666667</v>
+        <v>34148.5</v>
       </c>
       <c r="C11" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R11</f>
-        <v>13160.4208333333</v>
+        <v>14214.5875</v>
       </c>
       <c r="D11" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U11</f>
-        <v>18786.185</v>
+        <v>19171.185</v>
       </c>
       <c r="E11" s="51" t="n">
         <f aca="false">B11-C11-D11</f>
-        <v>368.560833333333</v>
+        <v>762.727500000001</v>
       </c>
       <c r="F11" s="50"/>
       <c r="G11" s="52" t="n">
         <f aca="false">E11-F11</f>
-        <v>368.560833333333</v>
+        <v>762.727500000001</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6109,24 +6109,24 @@
       </c>
       <c r="B12" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I12</f>
-        <v>35906.1666666667</v>
+        <v>37739.5</v>
       </c>
       <c r="C12" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R12</f>
-        <v>14186.9147886128</v>
+        <v>15261.5044237224</v>
       </c>
       <c r="D12" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U12</f>
-        <v>19540.295</v>
+        <v>19925.295</v>
       </c>
       <c r="E12" s="51" t="n">
         <f aca="false">B12-C12-D12</f>
-        <v>2178.95687805391</v>
+        <v>2552.70057627762</v>
       </c>
       <c r="F12" s="50"/>
       <c r="G12" s="52" t="n">
         <f aca="false">E12-F12</f>
-        <v>2178.95687805391</v>
+        <v>2552.70057627762</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6135,24 +6135,24 @@
       </c>
       <c r="B13" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I13</f>
-        <v>41466.3333333333</v>
+        <v>45133</v>
       </c>
       <c r="C13" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R13</f>
-        <v>16942.3811072992</v>
+        <v>19095.3934624697</v>
       </c>
       <c r="D13" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U13</f>
-        <v>20707.93</v>
+        <v>21477.93</v>
       </c>
       <c r="E13" s="51" t="n">
         <f aca="false">B13-C13-D13</f>
-        <v>3816.02222603415</v>
+        <v>4559.67653753027</v>
       </c>
       <c r="F13" s="50"/>
       <c r="G13" s="52" t="n">
         <f aca="false">E13-F13</f>
-        <v>3816.02222603415</v>
+        <v>4559.67653753027</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6161,24 +6161,24 @@
       </c>
       <c r="B14" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I14</f>
-        <v>55054.3333333333</v>
+        <v>58721</v>
       </c>
       <c r="C14" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R14</f>
-        <v>24395.6511548326</v>
+        <v>26572.6768144747</v>
       </c>
       <c r="D14" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U14</f>
-        <v>23561.41</v>
+        <v>24331.41</v>
       </c>
       <c r="E14" s="51" t="n">
         <f aca="false">B14-C14-D14</f>
-        <v>7097.27217850077</v>
+        <v>7816.91318552533</v>
       </c>
       <c r="F14" s="50"/>
       <c r="G14" s="52" t="n">
         <f aca="false">E14-F14</f>
-        <v>7097.27217850077</v>
+        <v>7816.91318552533</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6187,24 +6187,24 @@
       </c>
       <c r="B15" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I15</f>
-        <v>50617.5</v>
+        <v>56117.5</v>
       </c>
       <c r="C15" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R15</f>
-        <v>20742.1078174757</v>
+        <v>23999.2462452295</v>
       </c>
       <c r="D15" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U15</f>
-        <v>22629.675</v>
+        <v>23784.675</v>
       </c>
       <c r="E15" s="51" t="n">
         <f aca="false">B15-C15-D15</f>
-        <v>7245.71718252431</v>
+        <v>8333.57875477045</v>
       </c>
       <c r="F15" s="50"/>
       <c r="G15" s="52" t="n">
         <f aca="false">E15-F15</f>
-        <v>7245.71718252431</v>
+        <v>8333.57875477045</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6213,24 +6213,24 @@
       </c>
       <c r="B16" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I16</f>
-        <v>64205.5</v>
+        <v>69705.5</v>
       </c>
       <c r="C16" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R16</f>
-        <v>28212.1532911606</v>
+        <v>31505.2431779817</v>
       </c>
       <c r="D16" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U16</f>
-        <v>25483.155</v>
+        <v>26638.155</v>
       </c>
       <c r="E16" s="51" t="n">
         <f aca="false">B16-C16-D16</f>
-        <v>10510.1917088394</v>
+        <v>11562.1018220183</v>
       </c>
       <c r="F16" s="50"/>
       <c r="G16" s="52" t="n">
         <f aca="false">E16-F16</f>
-        <v>10510.1917088394</v>
+        <v>11562.1018220183</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6239,24 +6239,24 @@
       </c>
       <c r="B17" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I17</f>
-        <v>56602.5</v>
+        <v>62102.5</v>
       </c>
       <c r="C17" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R17</f>
-        <v>22499.3947622201</v>
+        <v>25834.2526632565</v>
       </c>
       <c r="D17" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U17</f>
-        <v>23886.525</v>
+        <v>25041.525</v>
       </c>
       <c r="E17" s="51" t="n">
         <f aca="false">B17-C17-D17</f>
-        <v>10216.5802377799</v>
+        <v>11226.7223367435</v>
       </c>
       <c r="F17" s="50"/>
       <c r="G17" s="52" t="n">
         <f aca="false">E17-F17</f>
-        <v>10216.5802377799</v>
+        <v>11226.7223367435</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6265,24 +6265,24 @@
       </c>
       <c r="B18" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I18</f>
-        <v>73356.6666666667</v>
+        <v>100684</v>
       </c>
       <c r="C18" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R18</f>
-        <v>32118.783568517</v>
+        <v>49617.013039618</v>
       </c>
       <c r="D18" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U18</f>
-        <v>27404.9</v>
+        <v>33143.64</v>
       </c>
       <c r="E18" s="51" t="n">
         <f aca="false">B18-C18-D18</f>
-        <v>13832.9830981497</v>
+        <v>17923.346960382</v>
       </c>
       <c r="F18" s="50"/>
       <c r="G18" s="52" t="n">
         <f aca="false">E18-F18</f>
-        <v>13832.9830981497</v>
+        <v>17923.346960382</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6291,24 +6291,24 @@
       </c>
       <c r="B19" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I19</f>
-        <v>75750.6666666667</v>
+        <v>103078</v>
       </c>
       <c r="C19" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R19</f>
-        <v>33018.9876080169</v>
+        <v>50678.801891933</v>
       </c>
       <c r="D19" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U19</f>
-        <v>27907.64</v>
+        <v>33646.38</v>
       </c>
       <c r="E19" s="51" t="n">
         <f aca="false">B19-C19-D19</f>
-        <v>14824.0390586497</v>
+        <v>18752.818108067</v>
       </c>
       <c r="F19" s="50"/>
       <c r="G19" s="52" t="n">
         <f aca="false">E19-F19</f>
-        <v>14824.0390586497</v>
+        <v>18752.818108067</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6317,24 +6317,24 @@
       </c>
       <c r="B20" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I20</f>
-        <v>81310.8333333333</v>
+        <v>110471.5</v>
       </c>
       <c r="C20" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R20</f>
-        <v>35957.3556297414</v>
+        <v>54824.4000516759</v>
       </c>
       <c r="D20" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U20</f>
-        <v>29075.275</v>
+        <v>35199.015</v>
       </c>
       <c r="E20" s="51" t="n">
         <f aca="false">B20-C20-D20</f>
-        <v>16278.2027035919</v>
+        <v>20448.0849483241</v>
       </c>
       <c r="F20" s="50"/>
       <c r="G20" s="52" t="n">
         <f aca="false">E20-F20</f>
-        <v>16278.2027035919</v>
+        <v>20448.0849483241</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6343,24 +6343,24 @@
       </c>
       <c r="B21" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I21</f>
-        <v>83704.8333333333</v>
+        <v>112865.5</v>
       </c>
       <c r="C21" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R21</f>
-        <v>36782.3174679213</v>
+        <v>55737.1828766041</v>
       </c>
       <c r="D21" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U21</f>
-        <v>29578.015</v>
+        <v>35701.755</v>
       </c>
       <c r="E21" s="51" t="n">
         <f aca="false">B21-C21-D21</f>
-        <v>17344.500865412</v>
+        <v>21426.5621233959</v>
       </c>
       <c r="F21" s="50"/>
       <c r="G21" s="52" t="n">
         <f aca="false">E21-F21</f>
-        <v>17344.500865412</v>
+        <v>21426.5621233959</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6369,24 +6369,24 @@
       </c>
       <c r="B22" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I22</f>
-        <v>89265</v>
+        <v>120259</v>
       </c>
       <c r="C22" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R22</f>
-        <v>39663.1104350631</v>
+        <v>59916.8317975888</v>
       </c>
       <c r="D22" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U22</f>
-        <v>30745.65</v>
+        <v>37254.39</v>
       </c>
       <c r="E22" s="51" t="n">
         <f aca="false">B22-C22-D22</f>
-        <v>18856.2395649369</v>
+        <v>23087.7782024112</v>
       </c>
       <c r="F22" s="50"/>
       <c r="G22" s="52" t="n">
         <f aca="false">E22-F22</f>
-        <v>18856.2395649369</v>
+        <v>23087.7782024112</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6395,24 +6395,24 @@
       </c>
       <c r="B23" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I23</f>
-        <v>91659</v>
+        <v>122653</v>
       </c>
       <c r="C23" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R23</f>
-        <v>40460.3358834631</v>
+        <v>60848.7212746378</v>
       </c>
       <c r="D23" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U23</f>
-        <v>31248.39</v>
+        <v>37757.13</v>
       </c>
       <c r="E23" s="51" t="n">
         <f aca="false">B23-C23-D23</f>
-        <v>19950.2741165369</v>
+        <v>24047.1487253622</v>
       </c>
       <c r="F23" s="50"/>
       <c r="G23" s="52" t="n">
         <f aca="false">E23-F23</f>
-        <v>19950.2741165369</v>
+        <v>24047.1487253622</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6421,24 +6421,24 @@
       </c>
       <c r="B24" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I24</f>
-        <v>94053</v>
+        <v>135044</v>
       </c>
       <c r="C24" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R24</f>
-        <v>41285.1723624962</v>
+        <v>68407.3617410183</v>
       </c>
       <c r="D24" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U24</f>
-        <v>31751.13</v>
+        <v>40359.24</v>
       </c>
       <c r="E24" s="51" t="n">
         <f aca="false">B24-C24-D24</f>
-        <v>21016.6976375038</v>
+        <v>26277.3982589817</v>
       </c>
       <c r="F24" s="50"/>
       <c r="G24" s="52" t="n">
         <f aca="false">E24-F24</f>
-        <v>21016.6976375038</v>
+        <v>26277.3982589817</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6447,24 +6447,24 @@
       </c>
       <c r="B25" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I25</f>
-        <v>96447</v>
+        <v>137438</v>
       </c>
       <c r="C25" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R25</f>
-        <v>42092.6402743522</v>
+        <v>69293.6477053512</v>
       </c>
       <c r="D25" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U25</f>
-        <v>32253.87</v>
+        <v>40861.98</v>
       </c>
       <c r="E25" s="51" t="n">
         <f aca="false">B25-C25-D25</f>
-        <v>22100.4897256478</v>
+        <v>27282.3722946488</v>
       </c>
       <c r="F25" s="50"/>
       <c r="G25" s="52" t="n">
         <f aca="false">E25-F25</f>
-        <v>22100.4897256478</v>
+        <v>27282.3722946488</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6473,24 +6473,24 @@
       </c>
       <c r="B26" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I26</f>
-        <v>108838</v>
+        <v>139832</v>
       </c>
       <c r="C26" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R26</f>
-        <v>49543.0975411268</v>
+        <v>70144.195380357</v>
       </c>
       <c r="D26" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U26</f>
-        <v>34855.98</v>
+        <v>41364.72</v>
       </c>
       <c r="E26" s="51" t="n">
         <f aca="false">B26-C26-D26</f>
-        <v>24438.9224588732</v>
+        <v>28323.084619643</v>
       </c>
       <c r="F26" s="50"/>
       <c r="G26" s="52" t="n">
         <f aca="false">E26-F26</f>
-        <v>24438.9224588732</v>
+        <v>28323.084619643</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6499,24 +6499,24 @@
       </c>
       <c r="B27" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I27</f>
-        <v>111232</v>
+        <v>142226</v>
       </c>
       <c r="C27" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R27</f>
-        <v>50332.999998654</v>
+        <v>70959.0161541562</v>
       </c>
       <c r="D27" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U27</f>
-        <v>35358.72</v>
+        <v>41867.46</v>
       </c>
       <c r="E27" s="51" t="n">
         <f aca="false">B27-C27-D27</f>
-        <v>25540.280001346</v>
+        <v>29399.5238458438</v>
       </c>
       <c r="F27" s="50"/>
       <c r="G27" s="52" t="n">
         <f aca="false">E27-F27</f>
-        <v>25540.280001346</v>
+        <v>29399.5238458438</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6525,24 +6525,24 @@
       </c>
       <c r="B28" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I28</f>
-        <v>100462.833333333</v>
+        <v>139620.5</v>
       </c>
       <c r="C28" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R28</f>
-        <v>42320.3835692858</v>
+        <v>68507.3775253362</v>
       </c>
       <c r="D28" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U28</f>
-        <v>33097.195</v>
+        <v>41320.305</v>
       </c>
       <c r="E28" s="51" t="n">
         <f aca="false">B28-C28-D28</f>
-        <v>25045.2547640475</v>
+        <v>29792.8174746638</v>
       </c>
       <c r="F28" s="50"/>
       <c r="G28" s="52" t="n">
         <f aca="false">E28-F28</f>
-        <v>25045.2547640475</v>
+        <v>29792.8174746638</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6551,24 +6551,24 @@
       </c>
       <c r="B29" s="50" t="n">
         <f aca="false">'Projeção Mensal'!I29</f>
-        <v>112853.833333333</v>
+        <v>142014.5</v>
       </c>
       <c r="C29" s="50" t="n">
         <f aca="false">'Projeção Mensal'!R29</f>
-        <v>49744.8745976521</v>
+        <v>69283.6107304242</v>
       </c>
       <c r="D29" s="50" t="n">
         <f aca="false">'Projeção Mensal'!U29</f>
-        <v>35699.305</v>
+        <v>41823.045</v>
       </c>
       <c r="E29" s="51" t="n">
         <f aca="false">B29-C29-D29</f>
-        <v>27409.6537356813</v>
+        <v>30907.8442695758</v>
       </c>
       <c r="F29" s="50"/>
       <c r="G29" s="52" t="n">
         <f aca="false">E29-F29</f>
-        <v>27409.6537356813</v>
+        <v>30907.8442695758</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6577,19 +6577,19 @@
       </c>
       <c r="B30" s="52" t="n">
         <f aca="false">SUM(B5:B29)</f>
-        <v>1527763.16666667</v>
+        <v>1942515.5</v>
       </c>
       <c r="C30" s="52" t="n">
         <f aca="false">SUM(C5:C29)</f>
-        <v>659332.532691224</v>
+        <v>930574.514455835</v>
       </c>
       <c r="D30" s="52" t="n">
         <f aca="false">SUM(D5:D29)</f>
-        <v>604054.235</v>
+        <v>691152.225</v>
       </c>
       <c r="E30" s="52" t="n">
         <f aca="false">SUM(E5:E29)</f>
-        <v>264376.398975443</v>
+        <v>320788.760544165</v>
       </c>
       <c r="F30" s="52" t="n">
         <f aca="false">SUM(F5:F29)</f>
@@ -6597,7 +6597,7 @@
       </c>
       <c r="G30" s="52" t="n">
         <f aca="false">SUM(G5:G29)</f>
-        <v>162376.398975443</v>
+        <v>218788.760544165</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -6879,15 +6879,15 @@
       </c>
       <c r="B11" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B11</f>
-        <v>32315.1666666667</v>
+        <v>34148.5</v>
       </c>
       <c r="C11" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C11</f>
-        <v>13160.4208333333</v>
+        <v>14214.5875</v>
       </c>
       <c r="D11" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D11</f>
-        <v>18786.185</v>
+        <v>19171.185</v>
       </c>
       <c r="E11" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F11</f>
@@ -6895,11 +6895,11 @@
       </c>
       <c r="F11" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G11</f>
-        <v>368.560833333333</v>
+        <v>762.727500000001</v>
       </c>
       <c r="G11" s="52" t="n">
         <f aca="false">G10+F11</f>
-        <v>-125325.879166667</v>
+        <v>-124931.7125</v>
       </c>
       <c r="H11" s="55" t="str">
         <f aca="false">IF(G11&gt;=0,"Sim","Não")</f>
@@ -6912,15 +6912,15 @@
       </c>
       <c r="B12" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B12</f>
-        <v>35906.1666666667</v>
+        <v>37739.5</v>
       </c>
       <c r="C12" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C12</f>
-        <v>14186.9147886128</v>
+        <v>15261.5044237224</v>
       </c>
       <c r="D12" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D12</f>
-        <v>19540.295</v>
+        <v>19925.295</v>
       </c>
       <c r="E12" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F12</f>
@@ -6928,11 +6928,11 @@
       </c>
       <c r="F12" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G12</f>
-        <v>2178.95687805391</v>
+        <v>2552.70057627762</v>
       </c>
       <c r="G12" s="52" t="n">
         <f aca="false">G11+F12</f>
-        <v>-123146.922288613</v>
+        <v>-122379.011923722</v>
       </c>
       <c r="H12" s="55" t="str">
         <f aca="false">IF(G12&gt;=0,"Sim","Não")</f>
@@ -6945,15 +6945,15 @@
       </c>
       <c r="B13" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B13</f>
-        <v>41466.3333333333</v>
+        <v>45133</v>
       </c>
       <c r="C13" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C13</f>
-        <v>16942.3811072992</v>
+        <v>19095.3934624697</v>
       </c>
       <c r="D13" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D13</f>
-        <v>20707.93</v>
+        <v>21477.93</v>
       </c>
       <c r="E13" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F13</f>
@@ -6961,11 +6961,11 @@
       </c>
       <c r="F13" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G13</f>
-        <v>3816.02222603415</v>
+        <v>4559.67653753027</v>
       </c>
       <c r="G13" s="52" t="n">
         <f aca="false">G12+F13</f>
-        <v>-119330.900062579</v>
+        <v>-117819.335386192</v>
       </c>
       <c r="H13" s="55" t="str">
         <f aca="false">IF(G13&gt;=0,"Sim","Não")</f>
@@ -6978,15 +6978,15 @@
       </c>
       <c r="B14" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B14</f>
-        <v>55054.3333333333</v>
+        <v>58721</v>
       </c>
       <c r="C14" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C14</f>
-        <v>24395.6511548326</v>
+        <v>26572.6768144747</v>
       </c>
       <c r="D14" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D14</f>
-        <v>23561.41</v>
+        <v>24331.41</v>
       </c>
       <c r="E14" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F14</f>
@@ -6994,11 +6994,11 @@
       </c>
       <c r="F14" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G14</f>
-        <v>7097.27217850077</v>
+        <v>7816.91318552533</v>
       </c>
       <c r="G14" s="52" t="n">
         <f aca="false">G13+F14</f>
-        <v>-112233.627884078</v>
+        <v>-110002.422200667</v>
       </c>
       <c r="H14" s="55" t="str">
         <f aca="false">IF(G14&gt;=0,"Sim","Não")</f>
@@ -7011,15 +7011,15 @@
       </c>
       <c r="B15" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B15</f>
-        <v>50617.5</v>
+        <v>56117.5</v>
       </c>
       <c r="C15" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C15</f>
-        <v>20742.1078174757</v>
+        <v>23999.2462452295</v>
       </c>
       <c r="D15" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D15</f>
-        <v>22629.675</v>
+        <v>23784.675</v>
       </c>
       <c r="E15" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F15</f>
@@ -7027,11 +7027,11 @@
       </c>
       <c r="F15" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G15</f>
-        <v>7245.71718252431</v>
+        <v>8333.57875477045</v>
       </c>
       <c r="G15" s="52" t="n">
         <f aca="false">G14+F15</f>
-        <v>-104987.910701554</v>
+        <v>-101668.843445896</v>
       </c>
       <c r="H15" s="55" t="str">
         <f aca="false">IF(G15&gt;=0,"Sim","Não")</f>
@@ -7044,15 +7044,15 @@
       </c>
       <c r="B16" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B16</f>
-        <v>64205.5</v>
+        <v>69705.5</v>
       </c>
       <c r="C16" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C16</f>
-        <v>28212.1532911606</v>
+        <v>31505.2431779817</v>
       </c>
       <c r="D16" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D16</f>
-        <v>25483.155</v>
+        <v>26638.155</v>
       </c>
       <c r="E16" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F16</f>
@@ -7060,11 +7060,11 @@
       </c>
       <c r="F16" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G16</f>
-        <v>10510.1917088394</v>
+        <v>11562.1018220183</v>
       </c>
       <c r="G16" s="52" t="n">
         <f aca="false">G15+F16</f>
-        <v>-94477.7189927141</v>
+        <v>-90106.741623878</v>
       </c>
       <c r="H16" s="55" t="str">
         <f aca="false">IF(G16&gt;=0,"Sim","Não")</f>
@@ -7077,15 +7077,15 @@
       </c>
       <c r="B17" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B17</f>
-        <v>56602.5</v>
+        <v>62102.5</v>
       </c>
       <c r="C17" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C17</f>
-        <v>22499.3947622201</v>
+        <v>25834.2526632565</v>
       </c>
       <c r="D17" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D17</f>
-        <v>23886.525</v>
+        <v>25041.525</v>
       </c>
       <c r="E17" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F17</f>
@@ -7093,11 +7093,11 @@
       </c>
       <c r="F17" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G17</f>
-        <v>10216.5802377799</v>
+        <v>11226.7223367435</v>
       </c>
       <c r="G17" s="52" t="n">
         <f aca="false">G16+F17</f>
-        <v>-84261.1387549342</v>
+        <v>-78880.0192871346</v>
       </c>
       <c r="H17" s="55" t="str">
         <f aca="false">IF(G17&gt;=0,"Sim","Não")</f>
@@ -7110,15 +7110,15 @@
       </c>
       <c r="B18" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B18</f>
-        <v>73356.6666666667</v>
+        <v>100684</v>
       </c>
       <c r="C18" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C18</f>
-        <v>32118.783568517</v>
+        <v>49617.013039618</v>
       </c>
       <c r="D18" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D18</f>
-        <v>27404.9</v>
+        <v>33143.64</v>
       </c>
       <c r="E18" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F18</f>
@@ -7126,11 +7126,11 @@
       </c>
       <c r="F18" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G18</f>
-        <v>13832.9830981497</v>
+        <v>17923.346960382</v>
       </c>
       <c r="G18" s="52" t="n">
         <f aca="false">G17+F18</f>
-        <v>-70428.1556567845</v>
+        <v>-60956.6723267525</v>
       </c>
       <c r="H18" s="55" t="str">
         <f aca="false">IF(G18&gt;=0,"Sim","Não")</f>
@@ -7143,15 +7143,15 @@
       </c>
       <c r="B19" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B19</f>
-        <v>75750.6666666667</v>
+        <v>103078</v>
       </c>
       <c r="C19" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C19</f>
-        <v>33018.9876080169</v>
+        <v>50678.801891933</v>
       </c>
       <c r="D19" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D19</f>
-        <v>27907.64</v>
+        <v>33646.38</v>
       </c>
       <c r="E19" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F19</f>
@@ -7159,11 +7159,11 @@
       </c>
       <c r="F19" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G19</f>
-        <v>14824.0390586497</v>
+        <v>18752.818108067</v>
       </c>
       <c r="G19" s="52" t="n">
         <f aca="false">G18+F19</f>
-        <v>-55604.1165981347</v>
+        <v>-42203.8542186856</v>
       </c>
       <c r="H19" s="55" t="str">
         <f aca="false">IF(G19&gt;=0,"Sim","Não")</f>
@@ -7176,15 +7176,15 @@
       </c>
       <c r="B20" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B20</f>
-        <v>81310.8333333333</v>
+        <v>110471.5</v>
       </c>
       <c r="C20" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C20</f>
-        <v>35957.3556297414</v>
+        <v>54824.4000516759</v>
       </c>
       <c r="D20" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D20</f>
-        <v>29075.275</v>
+        <v>35199.015</v>
       </c>
       <c r="E20" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F20</f>
@@ -7192,11 +7192,11 @@
       </c>
       <c r="F20" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G20</f>
-        <v>16278.2027035919</v>
+        <v>20448.0849483241</v>
       </c>
       <c r="G20" s="52" t="n">
         <f aca="false">G19+F20</f>
-        <v>-39325.9138945428</v>
+        <v>-21755.7692703615</v>
       </c>
       <c r="H20" s="55" t="str">
         <f aca="false">IF(G20&gt;=0,"Sim","Não")</f>
@@ -7209,15 +7209,15 @@
       </c>
       <c r="B21" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B21</f>
-        <v>83704.8333333333</v>
+        <v>112865.5</v>
       </c>
       <c r="C21" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C21</f>
-        <v>36782.3174679213</v>
+        <v>55737.1828766041</v>
       </c>
       <c r="D21" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D21</f>
-        <v>29578.015</v>
+        <v>35701.755</v>
       </c>
       <c r="E21" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F21</f>
@@ -7225,11 +7225,11 @@
       </c>
       <c r="F21" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G21</f>
-        <v>17344.500865412</v>
+        <v>21426.5621233959</v>
       </c>
       <c r="G21" s="52" t="n">
         <f aca="false">G20+F21</f>
-        <v>-21981.4130291307</v>
+        <v>-329.207146965571</v>
       </c>
       <c r="H21" s="55" t="str">
         <f aca="false">IF(G21&gt;=0,"Sim","Não")</f>
@@ -7242,15 +7242,15 @@
       </c>
       <c r="B22" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B22</f>
-        <v>89265</v>
+        <v>120259</v>
       </c>
       <c r="C22" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C22</f>
-        <v>39663.1104350631</v>
+        <v>59916.8317975888</v>
       </c>
       <c r="D22" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D22</f>
-        <v>30745.65</v>
+        <v>37254.39</v>
       </c>
       <c r="E22" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F22</f>
@@ -7258,15 +7258,15 @@
       </c>
       <c r="F22" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G22</f>
-        <v>18856.2395649369</v>
+        <v>23087.7782024112</v>
       </c>
       <c r="G22" s="52" t="n">
         <f aca="false">G21+F22</f>
-        <v>-3125.17346419381</v>
+        <v>22758.5710554456</v>
       </c>
       <c r="H22" s="55" t="str">
         <f aca="false">IF(G22&gt;=0,"Sim","Não")</f>
-        <v>Não</v>
+        <v>Sim</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -7275,15 +7275,15 @@
       </c>
       <c r="B23" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B23</f>
-        <v>91659</v>
+        <v>122653</v>
       </c>
       <c r="C23" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C23</f>
-        <v>40460.3358834631</v>
+        <v>60848.7212746378</v>
       </c>
       <c r="D23" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D23</f>
-        <v>31248.39</v>
+        <v>37757.13</v>
       </c>
       <c r="E23" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F23</f>
@@ -7291,11 +7291,11 @@
       </c>
       <c r="F23" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G23</f>
-        <v>19950.2741165369</v>
+        <v>24047.1487253622</v>
       </c>
       <c r="G23" s="52" t="n">
         <f aca="false">G22+F23</f>
-        <v>16825.1006523431</v>
+        <v>46805.7197808079</v>
       </c>
       <c r="H23" s="55" t="str">
         <f aca="false">IF(G23&gt;=0,"Sim","Não")</f>
@@ -7308,15 +7308,15 @@
       </c>
       <c r="B24" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B24</f>
-        <v>94053</v>
+        <v>135044</v>
       </c>
       <c r="C24" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C24</f>
-        <v>41285.1723624962</v>
+        <v>68407.3617410183</v>
       </c>
       <c r="D24" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D24</f>
-        <v>31751.13</v>
+        <v>40359.24</v>
       </c>
       <c r="E24" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F24</f>
@@ -7324,11 +7324,11 @@
       </c>
       <c r="F24" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G24</f>
-        <v>21016.6976375038</v>
+        <v>26277.3982589817</v>
       </c>
       <c r="G24" s="52" t="n">
         <f aca="false">G23+F24</f>
-        <v>37841.7982898469</v>
+        <v>73083.1180397896</v>
       </c>
       <c r="H24" s="55" t="str">
         <f aca="false">IF(G24&gt;=0,"Sim","Não")</f>
@@ -7341,15 +7341,15 @@
       </c>
       <c r="B25" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B25</f>
-        <v>96447</v>
+        <v>137438</v>
       </c>
       <c r="C25" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C25</f>
-        <v>42092.6402743522</v>
+        <v>69293.6477053512</v>
       </c>
       <c r="D25" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D25</f>
-        <v>32253.87</v>
+        <v>40861.98</v>
       </c>
       <c r="E25" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F25</f>
@@ -7357,11 +7357,11 @@
       </c>
       <c r="F25" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G25</f>
-        <v>22100.4897256478</v>
+        <v>27282.3722946488</v>
       </c>
       <c r="G25" s="52" t="n">
         <f aca="false">G24+F25</f>
-        <v>59942.2880154947</v>
+        <v>100365.490334438</v>
       </c>
       <c r="H25" s="55" t="str">
         <f aca="false">IF(G25&gt;=0,"Sim","Não")</f>
@@ -7374,15 +7374,15 @@
       </c>
       <c r="B26" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B26</f>
-        <v>108838</v>
+        <v>139832</v>
       </c>
       <c r="C26" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C26</f>
-        <v>49543.0975411268</v>
+        <v>70144.195380357</v>
       </c>
       <c r="D26" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D26</f>
-        <v>34855.98</v>
+        <v>41364.72</v>
       </c>
       <c r="E26" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F26</f>
@@ -7390,11 +7390,11 @@
       </c>
       <c r="F26" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G26</f>
-        <v>24438.9224588732</v>
+        <v>28323.084619643</v>
       </c>
       <c r="G26" s="52" t="n">
         <f aca="false">G25+F26</f>
-        <v>84381.2104743679</v>
+        <v>128688.574954081</v>
       </c>
       <c r="H26" s="55" t="str">
         <f aca="false">IF(G26&gt;=0,"Sim","Não")</f>
@@ -7407,15 +7407,15 @@
       </c>
       <c r="B27" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B27</f>
-        <v>111232</v>
+        <v>142226</v>
       </c>
       <c r="C27" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C27</f>
-        <v>50332.999998654</v>
+        <v>70959.0161541562</v>
       </c>
       <c r="D27" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D27</f>
-        <v>35358.72</v>
+        <v>41867.46</v>
       </c>
       <c r="E27" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F27</f>
@@ -7423,11 +7423,11 @@
       </c>
       <c r="F27" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G27</f>
-        <v>25540.280001346</v>
+        <v>29399.5238458438</v>
       </c>
       <c r="G27" s="52" t="n">
         <f aca="false">G26+F27</f>
-        <v>109921.490475714</v>
+        <v>158088.098799925</v>
       </c>
       <c r="H27" s="55" t="str">
         <f aca="false">IF(G27&gt;=0,"Sim","Não")</f>
@@ -7440,15 +7440,15 @@
       </c>
       <c r="B28" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B28</f>
-        <v>100462.833333333</v>
+        <v>139620.5</v>
       </c>
       <c r="C28" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C28</f>
-        <v>42320.3835692858</v>
+        <v>68507.3775253362</v>
       </c>
       <c r="D28" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D28</f>
-        <v>33097.195</v>
+        <v>41320.305</v>
       </c>
       <c r="E28" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F28</f>
@@ -7456,11 +7456,11 @@
       </c>
       <c r="F28" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G28</f>
-        <v>25045.2547640475</v>
+        <v>29792.8174746638</v>
       </c>
       <c r="G28" s="52" t="n">
         <f aca="false">G27+F28</f>
-        <v>134966.745239761</v>
+        <v>187880.916274589</v>
       </c>
       <c r="H28" s="55" t="str">
         <f aca="false">IF(G28&gt;=0,"Sim","Não")</f>
@@ -7473,15 +7473,15 @@
       </c>
       <c r="B29" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!B29</f>
-        <v>112853.833333333</v>
+        <v>142014.5</v>
       </c>
       <c r="C29" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!C29</f>
-        <v>49744.8745976521</v>
+        <v>69283.6107304242</v>
       </c>
       <c r="D29" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!D29</f>
-        <v>35699.305</v>
+        <v>41823.045</v>
       </c>
       <c r="E29" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!F29</f>
@@ -7489,11 +7489,11 @@
       </c>
       <c r="F29" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G29</f>
-        <v>27409.6537356813</v>
+        <v>30907.8442695758</v>
       </c>
       <c r="G29" s="52" t="n">
         <f aca="false">G28+F29</f>
-        <v>162376.398975443</v>
+        <v>218788.760544165</v>
       </c>
       <c r="H29" s="55" t="str">
         <f aca="false">IF(G29&gt;=0,"Sim","Não")</f>
@@ -7529,7 +7529,7 @@
       </c>
       <c r="F33" s="58" t="n">
         <f aca="false">IFERROR(INDEX(A5:A29,MATCH("Sim",H5:H29,0)),"Não recupera")</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="G33" s="57" t="s">
         <v>233</v>
@@ -7818,7 +7818,7 @@
       </c>
       <c r="B17" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G11</f>
-        <v>368.560833333333</v>
+        <v>762.727500000001</v>
       </c>
       <c r="C17" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A17</f>
@@ -7826,11 +7826,11 @@
       </c>
       <c r="D17" s="51" t="n">
         <f aca="false">B17*C17</f>
-        <v>330.977398930366</v>
+        <v>684.949515008135</v>
       </c>
       <c r="E17" s="52" t="n">
         <f aca="false">E16+D17</f>
-        <v>-124424.020562105</v>
+        <v>-124070.048446028</v>
       </c>
       <c r="F17" s="55" t="str">
         <f aca="false">IF(E17&gt;=0,"Sim","Não")</f>
@@ -7843,7 +7843,7 @@
       </c>
       <c r="B18" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G12</f>
-        <v>2178.95687805391</v>
+        <v>2552.70057627762</v>
       </c>
       <c r="C18" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A18</f>
@@ -7851,11 +7851,11 @@
       </c>
       <c r="D18" s="51" t="n">
         <f aca="false">B18*C18</f>
-        <v>1921.99676589479</v>
+        <v>2251.66560261867</v>
       </c>
       <c r="E18" s="52" t="n">
         <f aca="false">E17+D18</f>
-        <v>-122502.023796211</v>
+        <v>-121818.382843409</v>
       </c>
       <c r="F18" s="55" t="str">
         <f aca="false">IF(E18&gt;=0,"Sim","Não")</f>
@@ -7868,7 +7868,7 @@
       </c>
       <c r="B19" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G13</f>
-        <v>3816.02222603415</v>
+        <v>4559.67653753027</v>
       </c>
       <c r="C19" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A19</f>
@@ -7876,11 +7876,11 @@
       </c>
       <c r="D19" s="51" t="n">
         <f aca="false">B19*C19</f>
-        <v>3306.20495253736</v>
+        <v>3950.5076903124</v>
       </c>
       <c r="E19" s="52" t="n">
         <f aca="false">E18+D19</f>
-        <v>-119195.818843673</v>
+        <v>-117867.875153097</v>
       </c>
       <c r="F19" s="55" t="str">
         <f aca="false">IF(E19&gt;=0,"Sim","Não")</f>
@@ -7893,7 +7893,7 @@
       </c>
       <c r="B20" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G14</f>
-        <v>7097.27217850077</v>
+        <v>7816.91318552533</v>
       </c>
       <c r="C20" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A20</f>
@@ -7901,11 +7901,11 @@
       </c>
       <c r="D20" s="51" t="n">
         <f aca="false">B20*C20</f>
-        <v>6039.83670085886</v>
+        <v>6652.25708665673</v>
       </c>
       <c r="E20" s="52" t="n">
         <f aca="false">E19+D20</f>
-        <v>-113155.982142814</v>
+        <v>-111215.61806644</v>
       </c>
       <c r="F20" s="55" t="str">
         <f aca="false">IF(E20&gt;=0,"Sim","Não")</f>
@@ -7918,7 +7918,7 @@
       </c>
       <c r="B21" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G15</f>
-        <v>7245.71718252431</v>
+        <v>8333.57875477045</v>
       </c>
       <c r="C21" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A21</f>
@@ -7926,11 +7926,11 @@
       </c>
       <c r="D21" s="51" t="n">
         <f aca="false">B21*C21</f>
-        <v>6056.61508901444</v>
+        <v>6965.94658060456</v>
       </c>
       <c r="E21" s="52" t="n">
         <f aca="false">E20+D21</f>
-        <v>-107099.3670538</v>
+        <v>-104249.671485835</v>
       </c>
       <c r="F21" s="55" t="str">
         <f aca="false">IF(E21&gt;=0,"Sim","Não")</f>
@@ -7943,7 +7943,7 @@
       </c>
       <c r="B22" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G16</f>
-        <v>10510.1917088394</v>
+        <v>11562.1018220183</v>
       </c>
       <c r="C22" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A22</f>
@@ -7951,11 +7951,11 @@
       </c>
       <c r="D22" s="51" t="n">
         <f aca="false">B22*C22</f>
-        <v>8629.27070023434</v>
+        <v>9492.92926807002</v>
       </c>
       <c r="E22" s="52" t="n">
         <f aca="false">E21+D22</f>
-        <v>-98470.0963535656</v>
+        <v>-94756.7422177652</v>
       </c>
       <c r="F22" s="55" t="str">
         <f aca="false">IF(E22&gt;=0,"Sim","Não")</f>
@@ -7968,7 +7968,7 @@
       </c>
       <c r="B23" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G17</f>
-        <v>10216.5802377799</v>
+        <v>11226.7223367435</v>
       </c>
       <c r="C23" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A23</f>
@@ -7976,11 +7976,11 @@
       </c>
       <c r="D23" s="51" t="n">
         <f aca="false">B23*C23</f>
-        <v>8239.17761111282</v>
+        <v>9053.80833608344</v>
       </c>
       <c r="E23" s="52" t="n">
         <f aca="false">E22+D23</f>
-        <v>-90230.9187424528</v>
+        <v>-85702.9338816818</v>
       </c>
       <c r="F23" s="55" t="str">
         <f aca="false">IF(E23&gt;=0,"Sim","Não")</f>
@@ -7993,7 +7993,7 @@
       </c>
       <c r="B24" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G18</f>
-        <v>13832.9830981497</v>
+        <v>17923.346960382</v>
       </c>
       <c r="C24" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A24</f>
@@ -8001,11 +8001,11 @@
       </c>
       <c r="D24" s="51" t="n">
         <f aca="false">B24*C24</f>
-        <v>10957.4379677169</v>
+        <v>14197.5133706714</v>
       </c>
       <c r="E24" s="52" t="n">
         <f aca="false">E23+D24</f>
-        <v>-79273.4807747359</v>
+        <v>-71505.4205110103</v>
       </c>
       <c r="F24" s="55" t="str">
         <f aca="false">IF(E24&gt;=0,"Sim","Não")</f>
@@ -8018,7 +8018,7 @@
       </c>
       <c r="B25" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G19</f>
-        <v>14824.0390586497</v>
+        <v>18752.818108067</v>
       </c>
       <c r="C25" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A25</f>
@@ -8026,11 +8026,11 @@
       </c>
       <c r="D25" s="51" t="n">
         <f aca="false">B25*C25</f>
-        <v>11533.857583567</v>
+        <v>14590.6478317578</v>
       </c>
       <c r="E25" s="52" t="n">
         <f aca="false">E24+D25</f>
-        <v>-67739.6231911689</v>
+        <v>-56914.7726792525</v>
       </c>
       <c r="F25" s="55" t="str">
         <f aca="false">IF(E25&gt;=0,"Sim","Não")</f>
@@ -8043,7 +8043,7 @@
       </c>
       <c r="B26" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G20</f>
-        <v>16278.2027035919</v>
+        <v>20448.0849483241</v>
       </c>
       <c r="C26" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A26</f>
@@ -8051,11 +8051,11 @@
       </c>
       <c r="D26" s="51" t="n">
         <f aca="false">B26*C26</f>
-        <v>12440.256809103</v>
+        <v>15626.9971964027</v>
       </c>
       <c r="E26" s="52" t="n">
         <f aca="false">E25+D26</f>
-        <v>-55299.3663820659</v>
+        <v>-41287.7754828498</v>
       </c>
       <c r="F26" s="55" t="str">
         <f aca="false">IF(E26&gt;=0,"Sim","Não")</f>
@@ -8068,7 +8068,7 @@
       </c>
       <c r="B27" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G21</f>
-        <v>17344.500865412</v>
+        <v>21426.5621233959</v>
       </c>
       <c r="C27" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A27</f>
@@ -8076,11 +8076,11 @@
       </c>
       <c r="D27" s="51" t="n">
         <f aca="false">B27*C27</f>
-        <v>13019.6574944928</v>
+        <v>16083.8586417551</v>
       </c>
       <c r="E27" s="52" t="n">
         <f aca="false">E26+D27</f>
-        <v>-42279.7088875731</v>
+        <v>-25203.9168410947</v>
       </c>
       <c r="F27" s="55" t="str">
         <f aca="false">IF(E27&gt;=0,"Sim","Não")</f>
@@ -8093,7 +8093,7 @@
       </c>
       <c r="B28" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G22</f>
-        <v>18856.2395649369</v>
+        <v>23087.7782024112</v>
       </c>
       <c r="C28" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A28</f>
@@ -8101,11 +8101,11 @@
       </c>
       <c r="D28" s="51" t="n">
         <f aca="false">B28*C28</f>
-        <v>13902.9736568</v>
+        <v>17022.9472868515</v>
       </c>
       <c r="E28" s="52" t="n">
         <f aca="false">E27+D28</f>
-        <v>-28376.7352307731</v>
+        <v>-8180.96955424323</v>
       </c>
       <c r="F28" s="55" t="str">
         <f aca="false">IF(E28&gt;=0,"Sim","Não")</f>
@@ -8118,7 +8118,7 @@
       </c>
       <c r="B29" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G23</f>
-        <v>19950.2741165369</v>
+        <v>24047.1487253622</v>
       </c>
       <c r="C29" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A29</f>
@@ -8126,15 +8126,15 @@
       </c>
       <c r="D29" s="51" t="n">
         <f aca="false">B29*C29</f>
-        <v>14448.2863234579</v>
+        <v>17415.3040713768</v>
       </c>
       <c r="E29" s="52" t="n">
         <f aca="false">E28+D29</f>
-        <v>-13928.4489073152</v>
+        <v>9234.33451713362</v>
       </c>
       <c r="F29" s="55" t="str">
         <f aca="false">IF(E29&gt;=0,"Sim","Não")</f>
-        <v>Não</v>
+        <v>Sim</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8143,7 +8143,7 @@
       </c>
       <c r="B30" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G24</f>
-        <v>21016.6976375038</v>
+        <v>26277.3982589817</v>
       </c>
       <c r="C30" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A30</f>
@@ -8151,11 +8151,11 @@
       </c>
       <c r="D30" s="51" t="n">
         <f aca="false">B30*C30</f>
-        <v>14950.1933019155</v>
+        <v>18692.3840376406</v>
       </c>
       <c r="E30" s="52" t="n">
         <f aca="false">E29+D30</f>
-        <v>1021.74439460032</v>
+        <v>27926.7185547742</v>
       </c>
       <c r="F30" s="55" t="str">
         <f aca="false">IF(E30&gt;=0,"Sim","Não")</f>
@@ -8168,7 +8168,7 @@
       </c>
       <c r="B31" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G25</f>
-        <v>22100.4897256478</v>
+        <v>27282.3722946488</v>
       </c>
       <c r="C31" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A31</f>
@@ -8176,11 +8176,11 @@
       </c>
       <c r="D31" s="51" t="n">
         <f aca="false">B31*C31</f>
-        <v>15441.841440735</v>
+        <v>19062.4765482983</v>
       </c>
       <c r="E31" s="52" t="n">
         <f aca="false">E30+D31</f>
-        <v>16463.5858353353</v>
+        <v>46989.1951030726</v>
       </c>
       <c r="F31" s="55" t="str">
         <f aca="false">IF(E31&gt;=0,"Sim","Não")</f>
@@ -8193,7 +8193,7 @@
       </c>
       <c r="B32" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G26</f>
-        <v>24438.9224588732</v>
+        <v>28323.084619643</v>
       </c>
       <c r="C32" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A32</f>
@@ -8201,11 +8201,11 @@
       </c>
       <c r="D32" s="51" t="n">
         <f aca="false">B32*C32</f>
-        <v>16772.3572549375</v>
+        <v>19438.0457895353</v>
       </c>
       <c r="E32" s="52" t="n">
         <f aca="false">E31+D32</f>
-        <v>33235.9430902729</v>
+        <v>66427.2408926079</v>
       </c>
       <c r="F32" s="55" t="str">
         <f aca="false">IF(E32&gt;=0,"Sim","Não")</f>
@@ -8218,7 +8218,7 @@
       </c>
       <c r="B33" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G27</f>
-        <v>25540.280001346</v>
+        <v>29399.5238458438</v>
       </c>
       <c r="C33" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A33</f>
@@ -8226,11 +8226,11 @@
       </c>
       <c r="D33" s="51" t="n">
         <f aca="false">B33*C33</f>
-        <v>17216.805162625</v>
+        <v>19818.3369133448</v>
       </c>
       <c r="E33" s="52" t="n">
         <f aca="false">E32+D33</f>
-        <v>50452.7482528978</v>
+        <v>86245.5778059527</v>
       </c>
       <c r="F33" s="55" t="str">
         <f aca="false">IF(E33&gt;=0,"Sim","Não")</f>
@@ -8243,7 +8243,7 @@
       </c>
       <c r="B34" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G28</f>
-        <v>25045.2547640475</v>
+        <v>29792.8174746638</v>
       </c>
       <c r="C34" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A34</f>
@@ -8251,11 +8251,11 @@
       </c>
       <c r="D34" s="51" t="n">
         <f aca="false">B34*C34</f>
-        <v>16583.1574371831</v>
+        <v>19726.6503109735</v>
       </c>
       <c r="E34" s="52" t="n">
         <f aca="false">E33+D34</f>
-        <v>67035.9056900809</v>
+        <v>105972.228116926</v>
       </c>
       <c r="F34" s="55" t="str">
         <f aca="false">IF(E34&gt;=0,"Sim","Não")</f>
@@ -8268,7 +8268,7 @@
       </c>
       <c r="B35" s="51" t="n">
         <f aca="false">'Fluxo de Caixa'!G29</f>
-        <v>27409.6537356813</v>
+        <v>30907.8442695758</v>
       </c>
       <c r="C35" s="62" t="n">
         <f aca="false">1/(1+$B$7)^A35</f>
@@ -8276,11 +8276,11 @@
       </c>
       <c r="D35" s="51" t="n">
         <f aca="false">B35*C35</f>
-        <v>17826.257632467</v>
+        <v>20101.3555343235</v>
       </c>
       <c r="E35" s="52" t="n">
         <f aca="false">E34+D35</f>
-        <v>84862.1633225479</v>
+        <v>126073.58365125</v>
       </c>
       <c r="F35" s="55" t="str">
         <f aca="false">IF(E35&gt;=0,"Sim","Não")</f>
@@ -8304,7 +8304,7 @@
       </c>
       <c r="B38" s="63" t="n">
         <f aca="false">SUM(D11:D35)</f>
-        <v>84862.163322548</v>
+        <v>126073.58365125</v>
       </c>
       <c r="C38" s="64" t="str">
         <f aca="false">IF(B38&gt;0,"VIÁVEL: o projeto gera mais do que a taxa exigida",IF(B38&lt;0,"INVIÁVEL: o projeto rende menos que a taxa exigida","EQUILÍBRIO: rende exatamente a taxa exigida"))</f>
@@ -8317,7 +8317,7 @@
       </c>
       <c r="B39" s="65" t="n">
         <f aca="false">IFERROR(IRR(B11:B35),"Não calculável")</f>
-        <v>0.0499656736839225</v>
+        <v>0.0615783311983349</v>
       </c>
       <c r="C39" s="64" t="str">
         <f aca="false">IF(ISNUMBER(B39),IF(B39&gt;B7,"VIÁVEL: TIR maior que a taxa de desconto","INVIÁVEL: TIR menor ou igual à taxa de desconto"),"Sem TIR: o fluxo precisa ter valores negativos E positivos")</f>
@@ -8330,7 +8330,7 @@
       </c>
       <c r="B40" s="65" t="n">
         <f aca="false">IF(ISNUMBER(B39),IF(B6="Mensal",(1+B39)^12-1,B39),"Não calculável")</f>
-        <v>0.795151936890566</v>
+        <v>1.04844610560403</v>
       </c>
       <c r="C40" s="64" t="str">
         <f aca="false">"Compare com a taxa anual de "&amp;ROUND(B5*100,2)&amp;"%"</f>
@@ -8356,11 +8356,11 @@
       </c>
       <c r="B42" s="65" t="n">
         <f aca="false">IF(B41=0,"-",B38/B41)</f>
-        <v>0.831981993358313</v>
+        <v>1.23601552599264</v>
       </c>
       <c r="C42" s="64" t="str">
         <f aca="false">"Para cada R$ 100 de investimento inicial, o projeto gera R$ "&amp;IF(ISNUMBER(B42),ROUND(B42*100,2),"-")&amp;" de VPL acima da taxa exigida"</f>
-        <v>Para cada R$ 100 de investimento inicial, o projeto gera R$ 83.2 de VPL acima da taxa exigida</v>
+        <v>Para cada R$ 100 de investimento inicial, o projeto gera R$ 123.6 de VPL acima da taxa exigida</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
@@ -8369,7 +8369,7 @@
       </c>
       <c r="B43" s="66" t="n">
         <f aca="false">'Necessidade de Caixa e Payback'!F33</f>
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="C43" s="64" t="str">
         <f aca="false">"Período em que o saldo acumulado (sem descontar) fica positivo"</f>
@@ -8382,7 +8382,7 @@
       </c>
       <c r="B44" s="66" t="n">
         <f aca="false">IFERROR(INDEX(A11:A35,MATCH("Sim",F11:F35,0)),"Não recupera")</f>
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="C44" s="64" t="str">
         <f aca="false">"Período em que o VP acumulado fica positivo"</f>

--- a/precept-financeiro/Memoria_de_Calculo_Precept.xlsx
+++ b/precept-financeiro/Memoria_de_Calculo_Precept.xlsx
@@ -223,7 +223,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="279" uniqueCount="265">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="283">
   <si>
     <t xml:space="preserve">PLANILHA DE ANÁLISE FINANCEIRA – VPL, TIR E PAYBACK</t>
   </si>
@@ -516,7 +516,7 @@
     <t xml:space="preserve">Retirada por sócio (% da receita bruta do mês)</t>
   </si>
   <si>
-    <t xml:space="preserve">Calibrado: maior % redondo que mantém o break-even no mês 6. A faixa viável vai de ~2,3% a ~3,1% por sócio.</t>
+    <t xml:space="preserve">Calibrado: maior % que mantém o break-even no mês 6 (faixa viável de ~3,0% a ~3,6% por sócio, com licenças e Core como base).</t>
   </si>
   <si>
     <t xml:space="preserve">Mês em que a retirada começa</t>
@@ -681,10 +681,55 @@
     <t xml:space="preserve">20–24% = risco Moderado · 24–29% = risco Alto · acima de 29% = risco Muito alto (tabela da disciplina).</t>
   </si>
   <si>
+    <t xml:space="preserve">10. LICENÇAS E CORE COMO BASE</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licenças incluídas por assinatura</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1 acesso master + 4 dependentes em qualquer plano. O preço do plano depende do porte da operação, não do número de pessoas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preço da licença extra (R$/mês)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decisão do grupo: cada licença acima das 5 incluídas custa R$ 300/mês.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licenças extras por cliente pagante (média)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Hipótese: 0,5 em média no plano Essencial e 1,75 no Avançado (escritórios maiores). Validar nas primeiras vendas.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Tokens de IA por licença extra (R$/mês)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mesmo consumo por usuário das 5 licenças incluídas (R$ 90 ÷ 5).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meses de Core grátis por Sprint vendido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decisão do grupo: quem compra o Sprint ganha 1 mês de Core; quem vem de fora da base vira assinante depois disso.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Meses de Core grátis por Scale vendido</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Decisão do grupo: quem compra o Scale ganha 3 meses de Core.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Ticket médio efetivo do Core (R$/mês por cliente pagante)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Plano + licenças extras.</t>
+  </si>
+  <si>
     <t xml:space="preserve">PROJEÇÃO MENSAL DA PRECEPT – 24 MESES</t>
   </si>
   <si>
-    <t xml:space="preserve">Cinza = volume de vendas por mês (premissa do grupo). Azul = automático. As colunas I, R e U alimentam a aba Fluxo de Caixa.</t>
+    <t xml:space="preserve">Cinza = volume de vendas por mês (premissa do grupo; os clientes Core incluem quem veio do Sprint de fora da base). Azul = automático. As colunas I, R e U alimentam a aba Fluxo de Caixa.</t>
   </si>
   <si>
     <t xml:space="preserve">Mês</t>
@@ -759,6 +804,12 @@
     <t xml:space="preserve">Resultado ≥ 0?</t>
   </si>
   <si>
+    <t xml:space="preserve">Meses de Core grátis</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Clientes Core pagantes</t>
+  </si>
+  <si>
     <t xml:space="preserve">–</t>
   </si>
   <si>
@@ -840,10 +891,13 @@
     <t xml:space="preserve">Valor mensal (R$)</t>
   </si>
   <si>
-    <t xml:space="preserve">Core – plano Essencial</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Core – plano Avançado</t>
+    <t xml:space="preserve">Core – plano Essencial (clientes pagantes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Core – plano Avançado (clientes pagantes)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Licenças extras (acima das 5 incluídas)</t>
   </si>
   <si>
     <t xml:space="preserve">Sprint – imersão de 7 dias</t>
@@ -855,7 +909,7 @@
     <t xml:space="preserve">TOTAL DA RECEITA MENSAL (A)</t>
   </si>
   <si>
-    <t xml:space="preserve">Tokens de IA e nuvem (por cliente Core)</t>
+    <t xml:space="preserve">Tokens de IA e nuvem (clientes ativos e licenças)</t>
   </si>
   <si>
     <t xml:space="preserve">Impostos – Simples Nacional Anexo V</t>
@@ -876,7 +930,7 @@
     <t xml:space="preserve">TOTAL DAS DESPESAS VARIÁVEIS (B)</t>
   </si>
   <si>
-    <t xml:space="preserve">Retirada dos sócios (7 × 3% da receita)</t>
+    <t xml:space="preserve">Retirada dos sócios (7 sócios × % da receita)</t>
   </si>
   <si>
     <t xml:space="preserve">Despesas fixas sem retirada</t>
@@ -1231,7 +1285,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="68">
+  <cellXfs count="69">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1361,6 +1415,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="7" fillId="4" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="172" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -1964,7 +2022,7 @@
     <tabColor rgb="FF1F4E78"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:D84"/>
+  <dimension ref="A1:D93"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="52"/>
@@ -2407,7 +2465,7 @@
         <v>96</v>
       </c>
       <c r="B46" s="14" t="n">
-        <v>0.03</v>
+        <v>0.035</v>
       </c>
       <c r="C46" s="13" t="s">
         <v>97</v>
@@ -2430,7 +2488,7 @@
       </c>
       <c r="B48" s="23" t="n">
         <f aca="false">B45*B46</f>
-        <v>0.21</v>
+        <v>0.245</v>
       </c>
       <c r="C48" s="13" t="s">
         <v>101</v>
@@ -2621,7 +2679,7 @@
       </c>
       <c r="B69" s="28" t="n">
         <f aca="false">'Necessidade de Caixa e Payback'!F32</f>
-        <v>125694.44</v>
+        <v>120917.625</v>
       </c>
       <c r="C69" s="13" t="s">
         <v>134</v>
@@ -2633,7 +2691,7 @@
       </c>
       <c r="B70" s="28" t="n">
         <f aca="false">B59-B69</f>
-        <v>24305.56</v>
+        <v>29082.375</v>
       </c>
       <c r="C70" s="13" t="s">
         <v>136</v>
@@ -2645,7 +2703,7 @@
       </c>
       <c r="B71" s="28" t="n">
         <f aca="false">'VPL e TIR'!B38</f>
-        <v>126073.58365125</v>
+        <v>167855.266272898</v>
       </c>
       <c r="C71" s="13" t="s">
         <v>138</v>
@@ -2657,7 +2715,7 @@
       </c>
       <c r="B72" s="29" t="n">
         <f aca="false">'VPL e TIR'!B40</f>
-        <v>1.04844610560403</v>
+        <v>1.26330121466574</v>
       </c>
       <c r="C72" s="13" t="s">
         <v>140</v>
@@ -2693,7 +2751,7 @@
       </c>
       <c r="B75" s="28" t="n">
         <f aca="false">AVERAGE('Projeção Mensal'!W18:W29)</f>
-        <v>3765.465</v>
+        <v>5149.34875</v>
       </c>
       <c r="C75" s="13" t="s">
         <v>146</v>
@@ -2723,7 +2781,7 @@
       </c>
       <c r="B79" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A79)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>138252.818253723</v>
+        <v>182484.377767326</v>
       </c>
       <c r="C79" s="32" t="str">
         <f aca="false">IF(B79&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
@@ -2736,7 +2794,7 @@
       </c>
       <c r="B80" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A80)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>126073.58365125</v>
+        <v>167855.266272898</v>
       </c>
       <c r="C80" s="32" t="str">
         <f aca="false">IF(B80&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
@@ -2749,7 +2807,7 @@
       </c>
       <c r="B81" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A81)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>117581.793796568</v>
+        <v>157668.32220101</v>
       </c>
       <c r="C81" s="32" t="str">
         <f aca="false">IF(B81&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
@@ -2762,7 +2820,7 @@
       </c>
       <c r="B82" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A82)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>112201.09352997</v>
+        <v>151219.258293713</v>
       </c>
       <c r="C82" s="32" t="str">
         <f aca="false">IF(B82&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
@@ -2775,7 +2833,7 @@
       </c>
       <c r="B83" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A83)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>102058.50248802</v>
+        <v>139075.399922297</v>
       </c>
       <c r="C83" s="32" t="str">
         <f aca="false">IF(B83&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
@@ -2785,6 +2843,91 @@
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A84" s="20" t="s">
         <v>151</v>
+      </c>
+    </row>
+    <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A86" s="9" t="s">
+        <v>152</v>
+      </c>
+      <c r="B86" s="10"/>
+      <c r="C86" s="10"/>
+    </row>
+    <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A87" s="11" t="s">
+        <v>153</v>
+      </c>
+      <c r="B87" s="16" t="n">
+        <v>5</v>
+      </c>
+      <c r="C87" s="13" t="s">
+        <v>154</v>
+      </c>
+    </row>
+    <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A88" s="11" t="s">
+        <v>155</v>
+      </c>
+      <c r="B88" s="12" t="n">
+        <v>300</v>
+      </c>
+      <c r="C88" s="13" t="s">
+        <v>156</v>
+      </c>
+    </row>
+    <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A89" s="11" t="s">
+        <v>157</v>
+      </c>
+      <c r="B89" s="33" t="n">
+        <v>1</v>
+      </c>
+      <c r="C89" s="13" t="s">
+        <v>158</v>
+      </c>
+    </row>
+    <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A90" s="11" t="s">
+        <v>159</v>
+      </c>
+      <c r="B90" s="12" t="n">
+        <v>18</v>
+      </c>
+      <c r="C90" s="13" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A91" s="11" t="s">
+        <v>161</v>
+      </c>
+      <c r="B91" s="16" t="n">
+        <v>1</v>
+      </c>
+      <c r="C91" s="13" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A92" s="11" t="s">
+        <v>163</v>
+      </c>
+      <c r="B92" s="16" t="n">
+        <v>3</v>
+      </c>
+      <c r="C92" s="13" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A93" s="11" t="s">
+        <v>165</v>
+      </c>
+      <c r="B93" s="15" t="n">
+        <f aca="false">B8+B88*B89</f>
+        <v>1497</v>
+      </c>
+      <c r="C93" s="13" t="s">
+        <v>166</v>
       </c>
     </row>
   </sheetData>
@@ -2804,7 +2947,7 @@
     <tabColor rgb="FF2E75B6"/>
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:X56"/>
+  <dimension ref="A1:Z57"/>
   <sheetFormatPr defaultColWidth="8.6796875" defaultRowHeight="15" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7"/>
@@ -2824,11 +2967,12 @@
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="22" min="21" style="0" width="15"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="23" min="23" style="0" width="13"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="24" min="24" style="0" width="10"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="26" min="25" style="0" width="11"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>152</v>
+        <v>167</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -2853,100 +2997,108 @@
       <c r="V1" s="7"/>
       <c r="W1" s="7"/>
       <c r="X1" s="7"/>
+      <c r="Y1" s="7"/>
+      <c r="Z1" s="7"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>153</v>
+        <v>168</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>154</v>
+        <v>169</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>155</v>
+        <v>170</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>156</v>
+        <v>171</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>157</v>
+        <v>172</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>158</v>
+        <v>173</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>159</v>
+        <v>174</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>160</v>
+        <v>175</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>161</v>
+        <v>176</v>
       </c>
       <c r="I4" s="17" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="J4" s="17" t="s">
-        <v>163</v>
+        <v>178</v>
       </c>
       <c r="K4" s="17" t="s">
-        <v>164</v>
+        <v>179</v>
       </c>
       <c r="L4" s="17" t="s">
-        <v>165</v>
+        <v>180</v>
       </c>
       <c r="M4" s="17" t="s">
-        <v>166</v>
+        <v>181</v>
       </c>
       <c r="N4" s="17" t="s">
-        <v>167</v>
+        <v>182</v>
       </c>
       <c r="O4" s="17" t="s">
-        <v>168</v>
+        <v>183</v>
       </c>
       <c r="P4" s="17" t="s">
-        <v>169</v>
+        <v>184</v>
       </c>
       <c r="Q4" s="17" t="s">
-        <v>170</v>
+        <v>185</v>
       </c>
       <c r="R4" s="17" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="S4" s="17" t="s">
-        <v>172</v>
+        <v>187</v>
       </c>
       <c r="T4" s="17" t="s">
-        <v>173</v>
+        <v>188</v>
       </c>
       <c r="U4" s="17" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="V4" s="17" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="W4" s="17" t="s">
-        <v>176</v>
+        <v>191</v>
       </c>
       <c r="X4" s="17" t="s">
-        <v>177</v>
+        <v>192</v>
+      </c>
+      <c r="Y4" s="17" t="s">
+        <v>193</v>
+      </c>
+      <c r="Z4" s="17" t="s">
+        <v>194</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="33" t="n">
-        <v>0</v>
-      </c>
-      <c r="B5" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="34" t="n">
+      <c r="A5" s="34" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="35" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="15" t="n">
@@ -3001,30 +3153,36 @@
       <c r="W5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="X5" s="35" t="s">
-        <v>178</v>
+      <c r="X5" s="36" t="s">
+        <v>195</v>
+      </c>
+      <c r="Y5" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="35" t="n">
+        <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="33" t="n">
+      <c r="A6" s="34" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="36" t="n">
+      <c r="B6" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="37" t="n">
+      <c r="C6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A6-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A6)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
       <c r="F6" s="15" t="n">
-        <f aca="false">B6*'Premissas Precept'!$B$8</f>
-        <v>4788</v>
+        <f aca="false">Z6*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>5988</v>
       </c>
       <c r="G6" s="15" t="n">
         <f aca="false">C6*'Premissas Precept'!$B$9</f>
@@ -3036,27 +3194,27 @@
       </c>
       <c r="I6" s="22" t="n">
         <f aca="false">F6+G6+H6</f>
-        <v>4788</v>
+        <v>5988</v>
       </c>
       <c r="J6" s="15" t="n">
         <f aca="false">I6*12</f>
-        <v>57456</v>
-      </c>
-      <c r="K6" s="38" t="n">
+        <v>71856</v>
+      </c>
+      <c r="K6" s="39" t="n">
         <f aca="false">IF(J6&lt;=0,'Premissas Precept'!$C$24,(J6*LOOKUP(J6,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J6,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J6)</f>
         <v>0.155</v>
       </c>
       <c r="L6" s="15" t="n">
         <f aca="false">I6*K6</f>
-        <v>742.14</v>
+        <v>928.14</v>
       </c>
       <c r="M6" s="15" t="n">
-        <f aca="false">B6*'Premissas Precept'!$B$15</f>
-        <v>360</v>
+        <f aca="false">B6*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>432</v>
       </c>
       <c r="N6" s="15" t="n">
         <f aca="false">I6*'Premissas Precept'!$B$16</f>
-        <v>95.76</v>
+        <v>119.76</v>
       </c>
       <c r="O6" s="15" t="n">
         <f aca="false">(G6+H6)*'Premissas Precept'!$B$17</f>
@@ -3072,7 +3230,7 @@
       </c>
       <c r="R6" s="22" t="n">
         <f aca="false">SUM(L6:Q6)</f>
-        <v>1197.9</v>
+        <v>1479.9</v>
       </c>
       <c r="S6" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3088,37 +3246,45 @@
       </c>
       <c r="V6" s="22" t="n">
         <f aca="false">I6-R6-U6</f>
-        <v>-8409.9</v>
+        <v>-7491.9</v>
       </c>
       <c r="W6" s="15" t="n">
         <f aca="false">T6/'Premissas Precept'!$B$45</f>
         <v>0</v>
       </c>
-      <c r="X6" s="35" t="str">
+      <c r="X6" s="36" t="str">
         <f aca="false">IF(V6&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
+      <c r="Y6" s="38" t="n">
+        <f aca="false">C6*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A6-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A6)*$D$6:$D$29)</f>
+        <v>0</v>
+      </c>
+      <c r="Z6" s="38" t="n">
+        <f aca="false">MAX(0,B6-Y6)</f>
+        <v>4</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="33" t="n">
+      <c r="A7" s="34" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="36" t="n">
+      <c r="B7" s="37" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="37" t="n">
+      <c r="C7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A7-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A7)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
       <c r="F7" s="15" t="n">
-        <f aca="false">B7*'Premissas Precept'!$B$8</f>
-        <v>7182</v>
+        <f aca="false">Z7*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>8982</v>
       </c>
       <c r="G7" s="15" t="n">
         <f aca="false">C7*'Premissas Precept'!$B$9</f>
@@ -3130,27 +3296,27 @@
       </c>
       <c r="I7" s="22" t="n">
         <f aca="false">F7+G7+H7</f>
-        <v>7182</v>
+        <v>8982</v>
       </c>
       <c r="J7" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I6)*12</f>
-        <v>57456</v>
-      </c>
-      <c r="K7" s="38" t="n">
+        <v>71856</v>
+      </c>
+      <c r="K7" s="39" t="n">
         <f aca="false">IF(J7&lt;=0,'Premissas Precept'!$C$24,(J7*LOOKUP(J7,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J7,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J7)</f>
         <v>0.155</v>
       </c>
       <c r="L7" s="15" t="n">
         <f aca="false">I7*K7</f>
-        <v>1113.21</v>
+        <v>1392.21</v>
       </c>
       <c r="M7" s="15" t="n">
-        <f aca="false">B7*'Premissas Precept'!$B$15</f>
-        <v>540</v>
+        <f aca="false">B7*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>648</v>
       </c>
       <c r="N7" s="15" t="n">
         <f aca="false">I7*'Premissas Precept'!$B$16</f>
-        <v>143.64</v>
+        <v>179.64</v>
       </c>
       <c r="O7" s="15" t="n">
         <f aca="false">(G7+H7)*'Premissas Precept'!$B$17</f>
@@ -3166,7 +3332,7 @@
       </c>
       <c r="R7" s="22" t="n">
         <f aca="false">SUM(L7:Q7)</f>
-        <v>1796.85</v>
+        <v>2219.85</v>
       </c>
       <c r="S7" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3182,37 +3348,45 @@
       </c>
       <c r="V7" s="22" t="n">
         <f aca="false">I7-R7-U7</f>
-        <v>-6614.85</v>
+        <v>-5237.85</v>
       </c>
       <c r="W7" s="15" t="n">
         <f aca="false">T7/'Premissas Precept'!$B$45</f>
         <v>0</v>
       </c>
-      <c r="X7" s="35" t="str">
+      <c r="X7" s="36" t="str">
         <f aca="false">IF(V7&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
+      <c r="Y7" s="38" t="n">
+        <f aca="false">C7*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A7-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A7)*$D$6:$D$29)</f>
+        <v>0</v>
+      </c>
+      <c r="Z7" s="38" t="n">
+        <f aca="false">MAX(0,B7-Y7)</f>
+        <v>6</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="33" t="n">
+      <c r="A8" s="34" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="36" t="n">
+      <c r="B8" s="37" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="37" t="n">
+      <c r="C8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A8-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A8)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
       <c r="F8" s="15" t="n">
-        <f aca="false">B8*'Premissas Precept'!$B$8</f>
-        <v>10773</v>
+        <f aca="false">Z8*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>13473</v>
       </c>
       <c r="G8" s="15" t="n">
         <f aca="false">C8*'Premissas Precept'!$B$9</f>
@@ -3224,27 +3398,27 @@
       </c>
       <c r="I8" s="22" t="n">
         <f aca="false">F8+G8+H8</f>
-        <v>10773</v>
+        <v>13473</v>
       </c>
       <c r="J8" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I7)*12</f>
-        <v>71820</v>
-      </c>
-      <c r="K8" s="38" t="n">
+        <v>89820</v>
+      </c>
+      <c r="K8" s="39" t="n">
         <f aca="false">IF(J8&lt;=0,'Premissas Precept'!$C$24,(J8*LOOKUP(J8,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J8,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J8)</f>
         <v>0.155</v>
       </c>
       <c r="L8" s="15" t="n">
         <f aca="false">I8*K8</f>
-        <v>1669.815</v>
+        <v>2088.315</v>
       </c>
       <c r="M8" s="15" t="n">
-        <f aca="false">B8*'Premissas Precept'!$B$15</f>
-        <v>810</v>
+        <f aca="false">B8*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>972</v>
       </c>
       <c r="N8" s="15" t="n">
         <f aca="false">I8*'Premissas Precept'!$B$16</f>
-        <v>215.46</v>
+        <v>269.46</v>
       </c>
       <c r="O8" s="15" t="n">
         <f aca="false">(G8+H8)*'Premissas Precept'!$B$17</f>
@@ -3260,7 +3434,7 @@
       </c>
       <c r="R8" s="22" t="n">
         <f aca="false">SUM(L8:Q8)</f>
-        <v>2695.275</v>
+        <v>3329.775</v>
       </c>
       <c r="S8" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3276,37 +3450,45 @@
       </c>
       <c r="V8" s="22" t="n">
         <f aca="false">I8-R8-U8</f>
-        <v>-3922.275</v>
+        <v>-1856.775</v>
       </c>
       <c r="W8" s="15" t="n">
         <f aca="false">T8/'Premissas Precept'!$B$45</f>
         <v>0</v>
       </c>
-      <c r="X8" s="35" t="str">
+      <c r="X8" s="36" t="str">
         <f aca="false">IF(V8&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
+      <c r="Y8" s="38" t="n">
+        <f aca="false">C8*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A8-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A8)*$D$6:$D$29)</f>
+        <v>0</v>
+      </c>
+      <c r="Z8" s="38" t="n">
+        <f aca="false">MAX(0,B8-Y8)</f>
+        <v>9</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="33" t="n">
+      <c r="A9" s="34" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="36" t="n">
+      <c r="B9" s="37" t="n">
         <v>11</v>
       </c>
-      <c r="C9" s="36" t="n">
+      <c r="C9" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="37" t="n">
+      <c r="D9" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A9-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A9)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
       <c r="F9" s="15" t="n">
-        <f aca="false">B9*'Premissas Precept'!$B$8</f>
-        <v>13167</v>
+        <f aca="false">Z9*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>14970</v>
       </c>
       <c r="G9" s="15" t="n">
         <f aca="false">C9*'Premissas Precept'!$B$9</f>
@@ -3318,27 +3500,27 @@
       </c>
       <c r="I9" s="22" t="n">
         <f aca="false">F9+G9+H9</f>
-        <v>23164</v>
+        <v>24967</v>
       </c>
       <c r="J9" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I8)*12</f>
-        <v>90972</v>
-      </c>
-      <c r="K9" s="38" t="n">
+        <v>113772</v>
+      </c>
+      <c r="K9" s="39" t="n">
         <f aca="false">IF(J9&lt;=0,'Premissas Precept'!$C$24,(J9*LOOKUP(J9,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J9,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J9)</f>
         <v>0.155</v>
       </c>
       <c r="L9" s="15" t="n">
         <f aca="false">I9*K9</f>
-        <v>3590.42</v>
+        <v>3869.885</v>
       </c>
       <c r="M9" s="15" t="n">
-        <f aca="false">B9*'Premissas Precept'!$B$15</f>
-        <v>990</v>
+        <f aca="false">B9*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>1188</v>
       </c>
       <c r="N9" s="15" t="n">
         <f aca="false">I9*'Premissas Precept'!$B$16</f>
-        <v>463.28</v>
+        <v>499.34</v>
       </c>
       <c r="O9" s="15" t="n">
         <f aca="false">(G9+H9)*'Premissas Precept'!$B$17</f>
@@ -3354,7 +3536,7 @@
       </c>
       <c r="R9" s="22" t="n">
         <f aca="false">SUM(L9:Q9)</f>
-        <v>9642.5</v>
+        <v>10156.025</v>
       </c>
       <c r="S9" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3362,45 +3544,53 @@
       </c>
       <c r="T9" s="15" t="n">
         <f aca="false">IF(A9&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I9,0)</f>
-        <v>4864.44</v>
+        <v>6116.915</v>
       </c>
       <c r="U9" s="22" t="n">
         <f aca="false">S9+T9</f>
-        <v>16864.44</v>
+        <v>18116.915</v>
       </c>
       <c r="V9" s="22" t="n">
         <f aca="false">I9-R9-U9</f>
-        <v>-3342.94</v>
+        <v>-3305.94</v>
       </c>
       <c r="W9" s="15" t="n">
         <f aca="false">T9/'Premissas Precept'!$B$45</f>
-        <v>694.92</v>
-      </c>
-      <c r="X9" s="35" t="str">
+        <v>873.845</v>
+      </c>
+      <c r="X9" s="36" t="str">
         <f aca="false">IF(V9&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
+      <c r="Y9" s="38" t="n">
+        <f aca="false">C9*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A9-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A9)*$D$6:$D$29)</f>
+        <v>1</v>
+      </c>
+      <c r="Z9" s="38" t="n">
+        <f aca="false">MAX(0,B9-Y9)</f>
+        <v>10</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="33" t="n">
+      <c r="A10" s="34" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="36" t="n">
+      <c r="B10" s="37" t="n">
         <v>14</v>
       </c>
-      <c r="C10" s="36" t="n">
+      <c r="C10" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="37" t="n">
+      <c r="D10" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A10-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A10)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
       <c r="F10" s="15" t="n">
-        <f aca="false">B10*'Premissas Precept'!$B$8</f>
-        <v>16758</v>
+        <f aca="false">Z10*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>19461</v>
       </c>
       <c r="G10" s="15" t="n">
         <f aca="false">C10*'Premissas Precept'!$B$9</f>
@@ -3412,27 +3602,27 @@
       </c>
       <c r="I10" s="22" t="n">
         <f aca="false">F10+G10+H10</f>
-        <v>26755</v>
+        <v>29458</v>
       </c>
       <c r="J10" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I9)*12</f>
-        <v>137721</v>
-      </c>
-      <c r="K10" s="38" t="n">
+        <v>160230</v>
+      </c>
+      <c r="K10" s="39" t="n">
         <f aca="false">IF(J10&lt;=0,'Premissas Precept'!$C$24,(J10*LOOKUP(J10,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J10,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J10)</f>
         <v>0.155</v>
       </c>
       <c r="L10" s="15" t="n">
         <f aca="false">I10*K10</f>
-        <v>4147.025</v>
+        <v>4565.99</v>
       </c>
       <c r="M10" s="15" t="n">
-        <f aca="false">B10*'Premissas Precept'!$B$15</f>
-        <v>1260</v>
+        <f aca="false">B10*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>1512</v>
       </c>
       <c r="N10" s="15" t="n">
         <f aca="false">I10*'Premissas Precept'!$B$16</f>
-        <v>535.1</v>
+        <v>589.16</v>
       </c>
       <c r="O10" s="15" t="n">
         <f aca="false">(G10+H10)*'Premissas Precept'!$B$17</f>
@@ -3448,7 +3638,7 @@
       </c>
       <c r="R10" s="22" t="n">
         <f aca="false">SUM(L10:Q10)</f>
-        <v>10540.925</v>
+        <v>11265.95</v>
       </c>
       <c r="S10" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3456,45 +3646,53 @@
       </c>
       <c r="T10" s="15" t="n">
         <f aca="false">IF(A10&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I10,0)</f>
-        <v>5618.55</v>
+        <v>7217.21</v>
       </c>
       <c r="U10" s="22" t="n">
         <f aca="false">S10+T10</f>
-        <v>17618.55</v>
+        <v>19217.21</v>
       </c>
       <c r="V10" s="22" t="n">
         <f aca="false">I10-R10-U10</f>
-        <v>-1404.475</v>
+        <v>-1025.16</v>
       </c>
       <c r="W10" s="15" t="n">
         <f aca="false">T10/'Premissas Precept'!$B$45</f>
-        <v>802.65</v>
-      </c>
-      <c r="X10" s="35" t="str">
+        <v>1031.03</v>
+      </c>
+      <c r="X10" s="36" t="str">
         <f aca="false">IF(V10&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
+      <c r="Y10" s="38" t="n">
+        <f aca="false">C10*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A10-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A10)*$D$6:$D$29)</f>
+        <v>1</v>
+      </c>
+      <c r="Z10" s="38" t="n">
+        <f aca="false">MAX(0,B10-Y10)</f>
+        <v>13</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="33" t="n">
+      <c r="A11" s="34" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="36" t="n">
+      <c r="B11" s="37" t="n">
         <v>16</v>
       </c>
-      <c r="C11" s="36" t="n">
+      <c r="C11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="36" t="n">
+      <c r="D11" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="37" t="n">
+      <c r="E11" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A11-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A11)*$D$6:$D$29)</f>
         <v>1</v>
       </c>
       <c r="F11" s="15" t="n">
-        <f aca="false">B11*'Premissas Precept'!$B$8</f>
-        <v>19152</v>
+        <f aca="false">Z11*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>20958</v>
       </c>
       <c r="G11" s="15" t="n">
         <f aca="false">C11*'Premissas Precept'!$B$9</f>
@@ -3506,27 +3704,27 @@
       </c>
       <c r="I11" s="22" t="n">
         <f aca="false">F11+G11+H11</f>
-        <v>34148.5</v>
+        <v>35954.5</v>
       </c>
       <c r="J11" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I10)*12</f>
-        <v>174388.8</v>
-      </c>
-      <c r="K11" s="38" t="n">
+        <v>198883.2</v>
+      </c>
+      <c r="K11" s="39" t="n">
         <f aca="false">IF(J11&lt;=0,'Premissas Precept'!$C$24,(J11*LOOKUP(J11,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J11,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J11)</f>
-        <v>0.155</v>
+        <v>0.157373654486653</v>
       </c>
       <c r="L11" s="15" t="n">
         <f aca="false">I11*K11</f>
-        <v>5293.0175</v>
+        <v>5658.29106024038</v>
       </c>
       <c r="M11" s="15" t="n">
-        <f aca="false">B11*'Premissas Precept'!$B$15</f>
-        <v>1440</v>
+        <f aca="false">B11*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>1728</v>
       </c>
       <c r="N11" s="15" t="n">
         <f aca="false">I11*'Premissas Precept'!$B$16</f>
-        <v>682.97</v>
+        <v>719.09</v>
       </c>
       <c r="O11" s="15" t="n">
         <f aca="false">(G11+H11)*'Premissas Precept'!$B$17</f>
@@ -3542,7 +3740,7 @@
       </c>
       <c r="R11" s="22" t="n">
         <f aca="false">SUM(L11:Q11)</f>
-        <v>14214.5875</v>
+        <v>14903.9810602404</v>
       </c>
       <c r="S11" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3550,45 +3748,53 @@
       </c>
       <c r="T11" s="15" t="n">
         <f aca="false">IF(A11&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I11,0)</f>
-        <v>7171.185</v>
+        <v>8808.8525</v>
       </c>
       <c r="U11" s="22" t="n">
         <f aca="false">S11+T11</f>
-        <v>19171.185</v>
+        <v>20808.8525</v>
       </c>
       <c r="V11" s="22" t="n">
         <f aca="false">I11-R11-U11</f>
-        <v>762.727500000001</v>
+        <v>241.666439759618</v>
       </c>
       <c r="W11" s="15" t="n">
         <f aca="false">T11/'Premissas Precept'!$B$45</f>
-        <v>1024.455</v>
-      </c>
-      <c r="X11" s="35" t="str">
+        <v>1258.4075</v>
+      </c>
+      <c r="X11" s="36" t="str">
         <f aca="false">IF(V11&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y11" s="38" t="n">
+        <f aca="false">C11*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A11-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A11)*$D$6:$D$29)</f>
+        <v>2</v>
+      </c>
+      <c r="Z11" s="38" t="n">
+        <f aca="false">MAX(0,B11-Y11)</f>
+        <v>14</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="33" t="n">
+      <c r="A12" s="34" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="36" t="n">
+      <c r="B12" s="37" t="n">
         <v>19</v>
       </c>
-      <c r="C12" s="36" t="n">
+      <c r="C12" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="37" t="n">
+      <c r="D12" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A12-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A12)*$D$6:$D$29)</f>
         <v>1</v>
       </c>
       <c r="F12" s="15" t="n">
-        <f aca="false">B12*'Premissas Precept'!$B$8</f>
-        <v>22743</v>
+        <f aca="false">Z12*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>25449</v>
       </c>
       <c r="G12" s="15" t="n">
         <f aca="false">C12*'Premissas Precept'!$B$9</f>
@@ -3600,27 +3806,27 @@
       </c>
       <c r="I12" s="22" t="n">
         <f aca="false">F12+G12+H12</f>
-        <v>37739.5</v>
+        <v>40445.5</v>
       </c>
       <c r="J12" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I11)*12</f>
-        <v>213621</v>
-      </c>
-      <c r="K12" s="38" t="n">
+        <v>237645</v>
+      </c>
+      <c r="K12" s="39" t="n">
         <f aca="false">IF(J12&lt;=0,'Premissas Precept'!$C$24,(J12*LOOKUP(J12,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J12,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J12)</f>
-        <v>0.158934655300743</v>
+        <v>0.161064192387805</v>
       </c>
       <c r="L12" s="15" t="n">
         <f aca="false">I12*K12</f>
-        <v>5998.11442372239</v>
+        <v>6514.32179322098</v>
       </c>
       <c r="M12" s="15" t="n">
-        <f aca="false">B12*'Premissas Precept'!$B$15</f>
-        <v>1710</v>
+        <f aca="false">B12*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>2052</v>
       </c>
       <c r="N12" s="15" t="n">
         <f aca="false">I12*'Premissas Precept'!$B$16</f>
-        <v>754.79</v>
+        <v>808.91</v>
       </c>
       <c r="O12" s="15" t="n">
         <f aca="false">(G12+H12)*'Premissas Precept'!$B$17</f>
@@ -3636,7 +3842,7 @@
       </c>
       <c r="R12" s="22" t="n">
         <f aca="false">SUM(L12:Q12)</f>
-        <v>15261.5044237224</v>
+        <v>16173.831793221</v>
       </c>
       <c r="S12" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3644,45 +3850,53 @@
       </c>
       <c r="T12" s="15" t="n">
         <f aca="false">IF(A12&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I12,0)</f>
-        <v>7925.295</v>
+        <v>9909.1475</v>
       </c>
       <c r="U12" s="22" t="n">
         <f aca="false">S12+T12</f>
-        <v>19925.295</v>
+        <v>21909.1475</v>
       </c>
       <c r="V12" s="22" t="n">
         <f aca="false">I12-R12-U12</f>
-        <v>2552.70057627762</v>
+        <v>2362.52070677902</v>
       </c>
       <c r="W12" s="15" t="n">
         <f aca="false">T12/'Premissas Precept'!$B$45</f>
-        <v>1132.185</v>
-      </c>
-      <c r="X12" s="35" t="str">
+        <v>1415.5925</v>
+      </c>
+      <c r="X12" s="36" t="str">
         <f aca="false">IF(V12&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y12" s="38" t="n">
+        <f aca="false">C12*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A12-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A12)*$D$6:$D$29)</f>
+        <v>2</v>
+      </c>
+      <c r="Z12" s="38" t="n">
+        <f aca="false">MAX(0,B12-Y12)</f>
+        <v>17</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="33" t="n">
+      <c r="A13" s="34" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="36" t="n">
+      <c r="B13" s="37" t="n">
         <v>21</v>
       </c>
-      <c r="C13" s="36" t="n">
+      <c r="C13" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="36" t="n">
+      <c r="D13" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="37" t="n">
+      <c r="E13" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A13-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A13)*$D$6:$D$29)</f>
         <v>2</v>
       </c>
       <c r="F13" s="15" t="n">
-        <f aca="false">B13*'Premissas Precept'!$B$8</f>
-        <v>25137</v>
+        <f aca="false">Z13*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>26946</v>
       </c>
       <c r="G13" s="15" t="n">
         <f aca="false">C13*'Premissas Precept'!$B$9</f>
@@ -3694,27 +3908,27 @@
       </c>
       <c r="I13" s="22" t="n">
         <f aca="false">F13+G13+H13</f>
-        <v>45133</v>
+        <v>46942</v>
       </c>
       <c r="J13" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I12)*12</f>
-        <v>247800</v>
-      </c>
-      <c r="K13" s="38" t="n">
+        <v>273030.857142857</v>
+      </c>
+      <c r="K13" s="39" t="n">
         <f aca="false">IF(J13&lt;=0,'Premissas Precept'!$C$24,(J13*LOOKUP(J13,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J13,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J13)</f>
-        <v>0.1618401937046</v>
+        <v>0.16351834643494</v>
       </c>
       <c r="L13" s="15" t="n">
         <f aca="false">I13*K13</f>
-        <v>7304.33346246973</v>
+        <v>7675.87821834895</v>
       </c>
       <c r="M13" s="15" t="n">
-        <f aca="false">B13*'Premissas Precept'!$B$15</f>
-        <v>1890</v>
+        <f aca="false">B13*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>2268</v>
       </c>
       <c r="N13" s="15" t="n">
         <f aca="false">I13*'Premissas Precept'!$B$16</f>
-        <v>902.66</v>
+        <v>938.84</v>
       </c>
       <c r="O13" s="15" t="n">
         <f aca="false">(G13+H13)*'Premissas Precept'!$B$17</f>
@@ -3730,7 +3944,7 @@
       </c>
       <c r="R13" s="22" t="n">
         <f aca="false">SUM(L13:Q13)</f>
-        <v>19095.3934624697</v>
+        <v>19881.1182183489</v>
       </c>
       <c r="S13" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3738,45 +3952,53 @@
       </c>
       <c r="T13" s="15" t="n">
         <f aca="false">IF(A13&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I13,0)</f>
-        <v>9477.93</v>
+        <v>11500.79</v>
       </c>
       <c r="U13" s="22" t="n">
         <f aca="false">S13+T13</f>
-        <v>21477.93</v>
+        <v>23500.79</v>
       </c>
       <c r="V13" s="22" t="n">
         <f aca="false">I13-R13-U13</f>
-        <v>4559.67653753027</v>
+        <v>3560.09178165106</v>
       </c>
       <c r="W13" s="15" t="n">
         <f aca="false">T13/'Premissas Precept'!$B$45</f>
-        <v>1353.99</v>
-      </c>
-      <c r="X13" s="35" t="str">
+        <v>1642.97</v>
+      </c>
+      <c r="X13" s="36" t="str">
         <f aca="false">IF(V13&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y13" s="38" t="n">
+        <f aca="false">C13*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A13-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A13)*$D$6:$D$29)</f>
+        <v>3</v>
+      </c>
+      <c r="Z13" s="38" t="n">
+        <f aca="false">MAX(0,B13-Y13)</f>
+        <v>18</v>
+      </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="33" t="n">
+      <c r="A14" s="34" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="36" t="n">
+      <c r="B14" s="37" t="n">
         <v>24</v>
       </c>
-      <c r="C14" s="36" t="n">
+      <c r="C14" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="37" t="n">
+      <c r="D14" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A14-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A14)*$D$6:$D$29)</f>
         <v>2</v>
       </c>
       <c r="F14" s="15" t="n">
-        <f aca="false">B14*'Premissas Precept'!$B$8</f>
-        <v>28728</v>
+        <f aca="false">Z14*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>31437</v>
       </c>
       <c r="G14" s="15" t="n">
         <f aca="false">C14*'Premissas Precept'!$B$9</f>
@@ -3788,27 +4010,27 @@
       </c>
       <c r="I14" s="22" t="n">
         <f aca="false">F14+G14+H14</f>
-        <v>58721</v>
+        <v>61430</v>
       </c>
       <c r="J14" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I13)*12</f>
-        <v>284524.5</v>
-      </c>
-      <c r="K14" s="38" t="n">
+        <v>309315</v>
+      </c>
+      <c r="K14" s="39" t="n">
         <f aca="false">IF(J14&lt;=0,'Premissas Precept'!$C$24,(J14*LOOKUP(J14,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J14,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J14)</f>
-        <v>0.164184138799998</v>
+        <v>0.165451723970709</v>
       </c>
       <c r="L14" s="15" t="n">
         <f aca="false">I14*K14</f>
-        <v>9641.05681447468</v>
+        <v>10163.6994035207</v>
       </c>
       <c r="M14" s="15" t="n">
-        <f aca="false">B14*'Premissas Precept'!$B$15</f>
-        <v>2160</v>
+        <f aca="false">B14*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>2592</v>
       </c>
       <c r="N14" s="15" t="n">
         <f aca="false">I14*'Premissas Precept'!$B$16</f>
-        <v>1174.42</v>
+        <v>1228.6</v>
       </c>
       <c r="O14" s="15" t="n">
         <f aca="false">(G14+H14)*'Premissas Precept'!$B$17</f>
@@ -3824,7 +4046,7 @@
       </c>
       <c r="R14" s="22" t="n">
         <f aca="false">SUM(L14:Q14)</f>
-        <v>26572.6768144747</v>
+        <v>27581.4994035207</v>
       </c>
       <c r="S14" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3832,45 +4054,53 @@
       </c>
       <c r="T14" s="15" t="n">
         <f aca="false">IF(A14&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I14,0)</f>
-        <v>12331.41</v>
+        <v>15050.35</v>
       </c>
       <c r="U14" s="22" t="n">
         <f aca="false">S14+T14</f>
-        <v>24331.41</v>
+        <v>27050.35</v>
       </c>
       <c r="V14" s="22" t="n">
         <f aca="false">I14-R14-U14</f>
-        <v>7816.91318552533</v>
+        <v>6798.15059647932</v>
       </c>
       <c r="W14" s="15" t="n">
         <f aca="false">T14/'Premissas Precept'!$B$45</f>
-        <v>1761.63</v>
-      </c>
-      <c r="X14" s="35" t="str">
+        <v>2150.05</v>
+      </c>
+      <c r="X14" s="36" t="str">
         <f aca="false">IF(V14&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y14" s="38" t="n">
+        <f aca="false">C14*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A14-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A14)*$D$6:$D$29)</f>
+        <v>3</v>
+      </c>
+      <c r="Z14" s="38" t="n">
+        <f aca="false">MAX(0,B14-Y14)</f>
+        <v>21</v>
+      </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="33" t="n">
+      <c r="A15" s="34" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="36" t="n">
+      <c r="B15" s="37" t="n">
         <v>26</v>
       </c>
-      <c r="C15" s="36" t="n">
+      <c r="C15" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="36" t="n">
+      <c r="D15" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="37" t="n">
+      <c r="E15" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A15-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A15)*$D$6:$D$29)</f>
         <v>3</v>
       </c>
       <c r="F15" s="15" t="n">
-        <f aca="false">B15*'Premissas Precept'!$B$8</f>
-        <v>31122</v>
+        <f aca="false">Z15*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>34431</v>
       </c>
       <c r="G15" s="15" t="n">
         <f aca="false">C15*'Premissas Precept'!$B$9</f>
@@ -3882,27 +4112,27 @@
       </c>
       <c r="I15" s="22" t="n">
         <f aca="false">F15+G15+H15</f>
-        <v>56117.5</v>
+        <v>59426.5</v>
       </c>
       <c r="J15" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I14)*12</f>
-        <v>331205.333333333</v>
-      </c>
-      <c r="K15" s="38" t="n">
+        <v>356853.333333333</v>
+      </c>
+      <c r="K15" s="39" t="n">
         <f aca="false">IF(J15&lt;=0,'Premissas Precept'!$C$24,(J15*LOOKUP(J15,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J15,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J15)</f>
-        <v>0.166413262266308</v>
+        <v>0.167389777312808</v>
       </c>
       <c r="L15" s="15" t="n">
         <f aca="false">I15*K15</f>
-        <v>9338.69624522955</v>
+        <v>9947.3886014796</v>
       </c>
       <c r="M15" s="15" t="n">
-        <f aca="false">B15*'Premissas Precept'!$B$15</f>
-        <v>2340</v>
+        <f aca="false">B15*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>2808</v>
       </c>
       <c r="N15" s="15" t="n">
         <f aca="false">I15*'Premissas Precept'!$B$16</f>
-        <v>1122.35</v>
+        <v>1188.53</v>
       </c>
       <c r="O15" s="15" t="n">
         <f aca="false">(G15+H15)*'Premissas Precept'!$B$17</f>
@@ -3918,7 +4148,7 @@
       </c>
       <c r="R15" s="22" t="n">
         <f aca="false">SUM(L15:Q15)</f>
-        <v>23999.2462452295</v>
+        <v>25142.1186014796</v>
       </c>
       <c r="S15" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3926,45 +4156,53 @@
       </c>
       <c r="T15" s="15" t="n">
         <f aca="false">IF(A15&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I15,0)</f>
-        <v>11784.675</v>
+        <v>14559.4925</v>
       </c>
       <c r="U15" s="22" t="n">
         <f aca="false">S15+T15</f>
-        <v>23784.675</v>
+        <v>26559.4925</v>
       </c>
       <c r="V15" s="22" t="n">
         <f aca="false">I15-R15-U15</f>
-        <v>8333.57875477045</v>
+        <v>7724.8888985204</v>
       </c>
       <c r="W15" s="15" t="n">
         <f aca="false">T15/'Premissas Precept'!$B$45</f>
-        <v>1683.525</v>
-      </c>
-      <c r="X15" s="35" t="str">
+        <v>2079.9275</v>
+      </c>
+      <c r="X15" s="36" t="str">
         <f aca="false">IF(V15&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y15" s="38" t="n">
+        <f aca="false">C15*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A15-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A15)*$D$6:$D$29)</f>
+        <v>3</v>
+      </c>
+      <c r="Z15" s="38" t="n">
+        <f aca="false">MAX(0,B15-Y15)</f>
+        <v>23</v>
+      </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="33" t="n">
+      <c r="A16" s="34" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="36" t="n">
+      <c r="B16" s="37" t="n">
         <v>29</v>
       </c>
-      <c r="C16" s="36" t="n">
+      <c r="C16" s="37" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="37" t="n">
+      <c r="D16" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A16-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A16)*$D$6:$D$29)</f>
         <v>3</v>
       </c>
       <c r="F16" s="15" t="n">
-        <f aca="false">B16*'Premissas Precept'!$B$8</f>
-        <v>34713</v>
+        <f aca="false">Z16*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>38922</v>
       </c>
       <c r="G16" s="15" t="n">
         <f aca="false">C16*'Premissas Precept'!$B$9</f>
@@ -3976,27 +4214,27 @@
       </c>
       <c r="I16" s="22" t="n">
         <f aca="false">F16+G16+H16</f>
-        <v>69705.5</v>
+        <v>73914.5</v>
       </c>
       <c r="J16" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I15)*12</f>
-        <v>365425.8</v>
-      </c>
-      <c r="K16" s="38" t="n">
+        <v>392479.8</v>
+      </c>
+      <c r="K16" s="39" t="n">
         <f aca="false">IF(J16&lt;=0,'Premissas Precept'!$C$24,(J16*LOOKUP(J16,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J16,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J16)</f>
-        <v>0.167908316818353</v>
+        <v>0.169775771899598</v>
       </c>
       <c r="L16" s="15" t="n">
         <f aca="false">I16*K16</f>
-        <v>11704.1331779817</v>
+        <v>12548.8912920729</v>
       </c>
       <c r="M16" s="15" t="n">
-        <f aca="false">B16*'Premissas Precept'!$B$15</f>
-        <v>2610</v>
+        <f aca="false">B16*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>3132</v>
       </c>
       <c r="N16" s="15" t="n">
         <f aca="false">I16*'Premissas Precept'!$B$16</f>
-        <v>1394.11</v>
+        <v>1478.29</v>
       </c>
       <c r="O16" s="15" t="n">
         <f aca="false">(G16+H16)*'Premissas Precept'!$B$17</f>
@@ -4012,7 +4250,7 @@
       </c>
       <c r="R16" s="22" t="n">
         <f aca="false">SUM(L16:Q16)</f>
-        <v>31505.2431779817</v>
+        <v>32956.1812920729</v>
       </c>
       <c r="S16" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4020,45 +4258,53 @@
       </c>
       <c r="T16" s="15" t="n">
         <f aca="false">IF(A16&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I16,0)</f>
-        <v>14638.155</v>
+        <v>18109.0525</v>
       </c>
       <c r="U16" s="22" t="n">
         <f aca="false">S16+T16</f>
-        <v>26638.155</v>
+        <v>30109.0525</v>
       </c>
       <c r="V16" s="22" t="n">
         <f aca="false">I16-R16-U16</f>
-        <v>11562.1018220183</v>
+        <v>10849.2662079271</v>
       </c>
       <c r="W16" s="15" t="n">
         <f aca="false">T16/'Premissas Precept'!$B$45</f>
-        <v>2091.165</v>
-      </c>
-      <c r="X16" s="35" t="str">
+        <v>2587.0075</v>
+      </c>
+      <c r="X16" s="36" t="str">
         <f aca="false">IF(V16&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y16" s="38" t="n">
+        <f aca="false">C16*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A16-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A16)*$D$6:$D$29)</f>
+        <v>3</v>
+      </c>
+      <c r="Z16" s="38" t="n">
+        <f aca="false">MAX(0,B16-Y16)</f>
+        <v>26</v>
+      </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="33" t="n">
+      <c r="A17" s="34" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="36" t="n">
+      <c r="B17" s="37" t="n">
         <v>31</v>
       </c>
-      <c r="C17" s="36" t="n">
+      <c r="C17" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="36" t="n">
+      <c r="D17" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="37" t="n">
+      <c r="E17" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A17-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A17)*$D$6:$D$29)</f>
         <v>3</v>
       </c>
       <c r="F17" s="15" t="n">
-        <f aca="false">B17*'Premissas Precept'!$B$8</f>
-        <v>37107</v>
+        <f aca="false">Z17*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>41916</v>
       </c>
       <c r="G17" s="15" t="n">
         <f aca="false">C17*'Premissas Precept'!$B$9</f>
@@ -4070,27 +4316,27 @@
       </c>
       <c r="I17" s="22" t="n">
         <f aca="false">F17+G17+H17</f>
-        <v>62102.5</v>
+        <v>66911.5</v>
       </c>
       <c r="J17" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I16)*12</f>
-        <v>408247.636363636</v>
-      </c>
-      <c r="K17" s="38" t="n">
+        <v>437433.818181818</v>
+      </c>
+      <c r="K17" s="39" t="n">
         <f aca="false">IF(J17&lt;=0,'Premissas Precept'!$C$24,(J17*LOOKUP(J17,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J17,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J17)</f>
-        <v>0.170750012692831</v>
+        <v>0.172368004967816</v>
       </c>
       <c r="L17" s="15" t="n">
         <f aca="false">I17*K17</f>
-        <v>10604.0026632565</v>
+        <v>11533.401764404</v>
       </c>
       <c r="M17" s="15" t="n">
-        <f aca="false">B17*'Premissas Precept'!$B$15</f>
-        <v>2790</v>
+        <f aca="false">B17*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>3348</v>
       </c>
       <c r="N17" s="15" t="n">
         <f aca="false">I17*'Premissas Precept'!$B$16</f>
-        <v>1242.05</v>
+        <v>1338.23</v>
       </c>
       <c r="O17" s="15" t="n">
         <f aca="false">(G17+H17)*'Premissas Precept'!$B$17</f>
@@ -4106,7 +4352,7 @@
       </c>
       <c r="R17" s="22" t="n">
         <f aca="false">SUM(L17:Q17)</f>
-        <v>25834.2526632565</v>
+        <v>27417.831764404</v>
       </c>
       <c r="S17" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4114,45 +4360,53 @@
       </c>
       <c r="T17" s="15" t="n">
         <f aca="false">IF(A17&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I17,0)</f>
-        <v>13041.525</v>
+        <v>16393.3175</v>
       </c>
       <c r="U17" s="22" t="n">
         <f aca="false">S17+T17</f>
-        <v>25041.525</v>
+        <v>28393.3175</v>
       </c>
       <c r="V17" s="22" t="n">
         <f aca="false">I17-R17-U17</f>
-        <v>11226.7223367435</v>
+        <v>11100.3507355959</v>
       </c>
       <c r="W17" s="15" t="n">
         <f aca="false">T17/'Premissas Precept'!$B$45</f>
-        <v>1863.075</v>
-      </c>
-      <c r="X17" s="35" t="str">
+        <v>2341.9025</v>
+      </c>
+      <c r="X17" s="36" t="str">
         <f aca="false">IF(V17&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y17" s="38" t="n">
+        <f aca="false">C17*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A17-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A17)*$D$6:$D$29)</f>
+        <v>3</v>
+      </c>
+      <c r="Z17" s="38" t="n">
+        <f aca="false">MAX(0,B17-Y17)</f>
+        <v>28</v>
+      </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="33" t="n">
+      <c r="A18" s="34" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="36" t="n">
-        <v>34</v>
-      </c>
-      <c r="C18" s="36" t="n">
+      <c r="B18" s="37" t="n">
+        <v>36</v>
+      </c>
+      <c r="C18" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="D18" s="36" t="n">
+      <c r="D18" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="37" t="n">
+      <c r="E18" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A18-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A18)*$D$6:$D$29)</f>
         <v>4</v>
       </c>
       <c r="F18" s="15" t="n">
-        <f aca="false">B18*'Premissas Precept'!$B$8</f>
-        <v>40698</v>
+        <f aca="false">Z18*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>44910</v>
       </c>
       <c r="G18" s="15" t="n">
         <f aca="false">C18*'Premissas Precept'!$B$9</f>
@@ -4164,27 +4418,27 @@
       </c>
       <c r="I18" s="22" t="n">
         <f aca="false">F18+G18+H18</f>
-        <v>100684</v>
+        <v>104896</v>
       </c>
       <c r="J18" s="15" t="n">
         <f aca="false">SUM(I6:I17)</f>
-        <v>436329.5</v>
-      </c>
-      <c r="K18" s="38" t="n">
+        <v>467892.5</v>
+      </c>
+      <c r="K18" s="39" t="n">
         <f aca="false">IF(J18&lt;=0,'Premissas Precept'!$C$24,(J18*LOOKUP(J18,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J18,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J18)</f>
-        <v>0.172310725036927</v>
+        <v>0.173841293673226</v>
       </c>
       <c r="L18" s="15" t="n">
         <f aca="false">I18*K18</f>
-        <v>17348.933039618</v>
+        <v>18235.2563411467</v>
       </c>
       <c r="M18" s="15" t="n">
-        <f aca="false">B18*'Premissas Precept'!$B$15</f>
-        <v>3060</v>
+        <f aca="false">B18*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>3888</v>
       </c>
       <c r="N18" s="15" t="n">
         <f aca="false">I18*'Premissas Precept'!$B$16</f>
-        <v>2013.68</v>
+        <v>2097.92</v>
       </c>
       <c r="O18" s="15" t="n">
         <f aca="false">(G18+H18)*'Premissas Precept'!$B$17</f>
@@ -4200,7 +4454,7 @@
       </c>
       <c r="R18" s="22" t="n">
         <f aca="false">SUM(L18:Q18)</f>
-        <v>49617.013039618</v>
+        <v>51415.5763411467</v>
       </c>
       <c r="S18" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4208,45 +4462,53 @@
       </c>
       <c r="T18" s="15" t="n">
         <f aca="false">IF(A18&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I18,0)</f>
-        <v>21143.64</v>
+        <v>25699.52</v>
       </c>
       <c r="U18" s="22" t="n">
         <f aca="false">S18+T18</f>
-        <v>33143.64</v>
+        <v>37699.52</v>
       </c>
       <c r="V18" s="22" t="n">
         <f aca="false">I18-R18-U18</f>
-        <v>17923.346960382</v>
+        <v>15780.9036588533</v>
       </c>
       <c r="W18" s="15" t="n">
         <f aca="false">T18/'Premissas Precept'!$B$45</f>
-        <v>3020.52</v>
-      </c>
-      <c r="X18" s="35" t="str">
+        <v>3671.36</v>
+      </c>
+      <c r="X18" s="36" t="str">
         <f aca="false">IF(V18&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y18" s="38" t="n">
+        <f aca="false">C18*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A18-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A18)*$D$6:$D$29)</f>
+        <v>6</v>
+      </c>
+      <c r="Z18" s="38" t="n">
+        <f aca="false">MAX(0,B18-Y18)</f>
+        <v>30</v>
+      </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="33" t="n">
+      <c r="A19" s="34" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="36" t="n">
-        <v>36</v>
-      </c>
-      <c r="C19" s="36" t="n">
+      <c r="B19" s="37" t="n">
+        <v>40</v>
+      </c>
+      <c r="C19" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="36" t="n">
+      <c r="D19" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="37" t="n">
+      <c r="E19" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A19-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A19)*$D$6:$D$29)</f>
         <v>4</v>
       </c>
       <c r="F19" s="15" t="n">
-        <f aca="false">B19*'Premissas Precept'!$B$8</f>
-        <v>43092</v>
+        <f aca="false">Z19*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>49401</v>
       </c>
       <c r="G19" s="15" t="n">
         <f aca="false">C19*'Premissas Precept'!$B$9</f>
@@ -4258,27 +4520,27 @@
       </c>
       <c r="I19" s="22" t="n">
         <f aca="false">F19+G19+H19</f>
-        <v>103078</v>
+        <v>109387</v>
       </c>
       <c r="J19" s="15" t="n">
         <f aca="false">SUM(I7:I18)</f>
-        <v>532225.5</v>
-      </c>
-      <c r="K19" s="38" t="n">
+        <v>566800.5</v>
+      </c>
+      <c r="K19" s="39" t="n">
         <f aca="false">IF(J19&lt;=0,'Premissas Precept'!$C$24,(J19*LOOKUP(J19,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J19,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J19)</f>
-        <v>0.176398861948554</v>
+        <v>0.177533536932307</v>
       </c>
       <c r="L19" s="15" t="n">
         <f aca="false">I19*K19</f>
-        <v>18182.841891933</v>
+        <v>19419.8610044143</v>
       </c>
       <c r="M19" s="15" t="n">
-        <f aca="false">B19*'Premissas Precept'!$B$15</f>
-        <v>3240</v>
+        <f aca="false">B19*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>4320</v>
       </c>
       <c r="N19" s="15" t="n">
         <f aca="false">I19*'Premissas Precept'!$B$16</f>
-        <v>2061.56</v>
+        <v>2187.74</v>
       </c>
       <c r="O19" s="15" t="n">
         <f aca="false">(G19+H19)*'Premissas Precept'!$B$17</f>
@@ -4294,7 +4556,7 @@
       </c>
       <c r="R19" s="22" t="n">
         <f aca="false">SUM(L19:Q19)</f>
-        <v>50678.801891933</v>
+        <v>53122.0010044143</v>
       </c>
       <c r="S19" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4302,45 +4564,53 @@
       </c>
       <c r="T19" s="15" t="n">
         <f aca="false">IF(A19&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I19,0)</f>
-        <v>21646.38</v>
+        <v>26799.815</v>
       </c>
       <c r="U19" s="22" t="n">
         <f aca="false">S19+T19</f>
-        <v>33646.38</v>
+        <v>38799.815</v>
       </c>
       <c r="V19" s="22" t="n">
         <f aca="false">I19-R19-U19</f>
-        <v>18752.818108067</v>
+        <v>17465.1839955858</v>
       </c>
       <c r="W19" s="15" t="n">
         <f aca="false">T19/'Premissas Precept'!$B$45</f>
-        <v>3092.34</v>
-      </c>
-      <c r="X19" s="35" t="str">
+        <v>3828.545</v>
+      </c>
+      <c r="X19" s="36" t="str">
         <f aca="false">IF(V19&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y19" s="38" t="n">
+        <f aca="false">C19*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A19-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A19)*$D$6:$D$29)</f>
+        <v>7</v>
+      </c>
+      <c r="Z19" s="38" t="n">
+        <f aca="false">MAX(0,B19-Y19)</f>
+        <v>33</v>
+      </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="33" t="n">
+      <c r="A20" s="34" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="36" t="n">
-        <v>38</v>
-      </c>
-      <c r="C20" s="36" t="n">
+      <c r="B20" s="37" t="n">
+        <v>44</v>
+      </c>
+      <c r="C20" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="36" t="n">
+      <c r="D20" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="37" t="n">
+      <c r="E20" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A20-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A20)*$D$6:$D$29)</f>
         <v>5</v>
       </c>
       <c r="F20" s="15" t="n">
-        <f aca="false">B20*'Premissas Precept'!$B$8</f>
-        <v>45486</v>
+        <f aca="false">Z20*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>55389</v>
       </c>
       <c r="G20" s="15" t="n">
         <f aca="false">C20*'Premissas Precept'!$B$9</f>
@@ -4352,27 +4622,27 @@
       </c>
       <c r="I20" s="22" t="n">
         <f aca="false">F20+G20+H20</f>
-        <v>110471.5</v>
+        <v>120374.5</v>
       </c>
       <c r="J20" s="15" t="n">
         <f aca="false">SUM(I8:I19)</f>
-        <v>628121.5</v>
-      </c>
-      <c r="K20" s="38" t="n">
+        <v>667205.5</v>
+      </c>
+      <c r="K20" s="39" t="n">
         <f aca="false">IF(J20&lt;=0,'Premissas Precept'!$C$24,(J20*LOOKUP(J20,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J20,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J20)</f>
-        <v>0.179238718146091</v>
+        <v>0.180161992819304</v>
       </c>
       <c r="L20" s="15" t="n">
         <f aca="false">I20*K20</f>
-        <v>19800.7700516759</v>
+        <v>21686.9098046273</v>
       </c>
       <c r="M20" s="15" t="n">
-        <f aca="false">B20*'Premissas Precept'!$B$15</f>
-        <v>3420</v>
+        <f aca="false">B20*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>4752</v>
       </c>
       <c r="N20" s="15" t="n">
         <f aca="false">I20*'Premissas Precept'!$B$16</f>
-        <v>2209.43</v>
+        <v>2407.49</v>
       </c>
       <c r="O20" s="15" t="n">
         <f aca="false">(G20+H20)*'Premissas Precept'!$B$17</f>
@@ -4388,7 +4658,7 @@
       </c>
       <c r="R20" s="22" t="n">
         <f aca="false">SUM(L20:Q20)</f>
-        <v>54824.4000516759</v>
+        <v>58240.5998046273</v>
       </c>
       <c r="S20" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4396,45 +4666,53 @@
       </c>
       <c r="T20" s="15" t="n">
         <f aca="false">IF(A20&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I20,0)</f>
-        <v>23199.015</v>
+        <v>29491.7525</v>
       </c>
       <c r="U20" s="22" t="n">
         <f aca="false">S20+T20</f>
-        <v>35199.015</v>
+        <v>41491.7525</v>
       </c>
       <c r="V20" s="22" t="n">
         <f aca="false">I20-R20-U20</f>
-        <v>20448.0849483241</v>
+        <v>20642.1476953727</v>
       </c>
       <c r="W20" s="15" t="n">
         <f aca="false">T20/'Premissas Precept'!$B$45</f>
-        <v>3314.145</v>
-      </c>
-      <c r="X20" s="35" t="str">
+        <v>4213.1075</v>
+      </c>
+      <c r="X20" s="36" t="str">
         <f aca="false">IF(V20&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y20" s="38" t="n">
+        <f aca="false">C20*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A20-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A20)*$D$6:$D$29)</f>
+        <v>7</v>
+      </c>
+      <c r="Z20" s="38" t="n">
+        <f aca="false">MAX(0,B20-Y20)</f>
+        <v>37</v>
+      </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="33" t="n">
+      <c r="A21" s="34" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="36" t="n">
-        <v>40</v>
-      </c>
-      <c r="C21" s="36" t="n">
+      <c r="B21" s="37" t="n">
+        <v>48</v>
+      </c>
+      <c r="C21" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="36" t="n">
+      <c r="D21" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="37" t="n">
+      <c r="E21" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A21-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A21)*$D$6:$D$29)</f>
         <v>5</v>
       </c>
       <c r="F21" s="15" t="n">
-        <f aca="false">B21*'Premissas Precept'!$B$8</f>
-        <v>47880</v>
+        <f aca="false">Z21*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>61377</v>
       </c>
       <c r="G21" s="15" t="n">
         <f aca="false">C21*'Premissas Precept'!$B$9</f>
@@ -4446,27 +4724,27 @@
       </c>
       <c r="I21" s="22" t="n">
         <f aca="false">F21+G21+H21</f>
-        <v>112865.5</v>
+        <v>126362.5</v>
       </c>
       <c r="J21" s="15" t="n">
         <f aca="false">SUM(I9:I20)</f>
-        <v>727820</v>
-      </c>
-      <c r="K21" s="38" t="n">
+        <v>774107</v>
+      </c>
+      <c r="K21" s="39" t="n">
         <f aca="false">IF(J21&lt;=0,'Premissas Precept'!$C$24,(J21*LOOKUP(J21,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J21,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J21)</f>
-        <v>0.181505179852161</v>
+        <v>0.182910030525496</v>
       </c>
       <c r="L21" s="15" t="n">
         <f aca="false">I21*K21</f>
-        <v>20485.6728766041</v>
+        <v>23112.968732278</v>
       </c>
       <c r="M21" s="15" t="n">
-        <f aca="false">B21*'Premissas Precept'!$B$15</f>
-        <v>3600</v>
+        <f aca="false">B21*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>5184</v>
       </c>
       <c r="N21" s="15" t="n">
         <f aca="false">I21*'Premissas Precept'!$B$16</f>
-        <v>2257.31</v>
+        <v>2527.25</v>
       </c>
       <c r="O21" s="15" t="n">
         <f aca="false">(G21+H21)*'Premissas Precept'!$B$17</f>
@@ -4482,7 +4760,7 @@
       </c>
       <c r="R21" s="22" t="n">
         <f aca="false">SUM(L21:Q21)</f>
-        <v>55737.1828766041</v>
+        <v>60218.418732278</v>
       </c>
       <c r="S21" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4490,45 +4768,53 @@
       </c>
       <c r="T21" s="15" t="n">
         <f aca="false">IF(A21&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I21,0)</f>
-        <v>23701.755</v>
+        <v>30958.8125</v>
       </c>
       <c r="U21" s="22" t="n">
         <f aca="false">S21+T21</f>
-        <v>35701.755</v>
+        <v>42958.8125</v>
       </c>
       <c r="V21" s="22" t="n">
         <f aca="false">I21-R21-U21</f>
-        <v>21426.5621233959</v>
+        <v>23185.268767722</v>
       </c>
       <c r="W21" s="15" t="n">
         <f aca="false">T21/'Premissas Precept'!$B$45</f>
-        <v>3385.965</v>
-      </c>
-      <c r="X21" s="35" t="str">
+        <v>4422.6875</v>
+      </c>
+      <c r="X21" s="36" t="str">
         <f aca="false">IF(V21&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y21" s="38" t="n">
+        <f aca="false">C21*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A21-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A21)*$D$6:$D$29)</f>
+        <v>7</v>
+      </c>
+      <c r="Z21" s="38" t="n">
+        <f aca="false">MAX(0,B21-Y21)</f>
+        <v>41</v>
+      </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="33" t="n">
+      <c r="A22" s="34" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="36" t="n">
-        <v>42</v>
-      </c>
-      <c r="C22" s="36" t="n">
+      <c r="B22" s="37" t="n">
+        <v>51</v>
+      </c>
+      <c r="C22" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="36" t="n">
+      <c r="D22" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="37" t="n">
+      <c r="E22" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A22-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A22)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
       <c r="F22" s="15" t="n">
-        <f aca="false">B22*'Premissas Precept'!$B$8</f>
-        <v>50274</v>
+        <f aca="false">Z22*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>65868</v>
       </c>
       <c r="G22" s="15" t="n">
         <f aca="false">C22*'Premissas Precept'!$B$9</f>
@@ -4540,27 +4826,27 @@
       </c>
       <c r="I22" s="22" t="n">
         <f aca="false">F22+G22+H22</f>
-        <v>120259</v>
+        <v>135853</v>
       </c>
       <c r="J22" s="15" t="n">
         <f aca="false">SUM(I10:I21)</f>
-        <v>817521.5</v>
-      </c>
-      <c r="K22" s="38" t="n">
+        <v>875502.5</v>
+      </c>
+      <c r="K22" s="39" t="n">
         <f aca="false">IF(J22&lt;=0,'Premissas Precept'!$C$24,(J22*LOOKUP(J22,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J22,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J22)</f>
-        <v>0.184083118914915</v>
+        <v>0.185468359599202</v>
       </c>
       <c r="L22" s="15" t="n">
         <f aca="false">I22*K22</f>
-        <v>22137.6517975888</v>
+        <v>25196.4330566303</v>
       </c>
       <c r="M22" s="15" t="n">
-        <f aca="false">B22*'Premissas Precept'!$B$15</f>
-        <v>3780</v>
+        <f aca="false">B22*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>5508</v>
       </c>
       <c r="N22" s="15" t="n">
         <f aca="false">I22*'Premissas Precept'!$B$16</f>
-        <v>2405.18</v>
+        <v>2717.06</v>
       </c>
       <c r="O22" s="15" t="n">
         <f aca="false">(G22+H22)*'Premissas Precept'!$B$17</f>
@@ -4576,7 +4862,7 @@
       </c>
       <c r="R22" s="22" t="n">
         <f aca="false">SUM(L22:Q22)</f>
-        <v>59916.8317975888</v>
+        <v>65015.4930566303</v>
       </c>
       <c r="S22" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4584,45 +4870,53 @@
       </c>
       <c r="T22" s="15" t="n">
         <f aca="false">IF(A22&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I22,0)</f>
-        <v>25254.39</v>
+        <v>33283.985</v>
       </c>
       <c r="U22" s="22" t="n">
         <f aca="false">S22+T22</f>
-        <v>37254.39</v>
+        <v>45283.985</v>
       </c>
       <c r="V22" s="22" t="n">
         <f aca="false">I22-R22-U22</f>
-        <v>23087.7782024112</v>
+        <v>25553.5219433697</v>
       </c>
       <c r="W22" s="15" t="n">
         <f aca="false">T22/'Premissas Precept'!$B$45</f>
-        <v>3607.77</v>
-      </c>
-      <c r="X22" s="35" t="str">
+        <v>4754.855</v>
+      </c>
+      <c r="X22" s="36" t="str">
         <f aca="false">IF(V22&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y22" s="38" t="n">
+        <f aca="false">C22*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A22-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A22)*$D$6:$D$29)</f>
+        <v>7</v>
+      </c>
+      <c r="Z22" s="38" t="n">
+        <f aca="false">MAX(0,B22-Y22)</f>
+        <v>44</v>
+      </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="33" t="n">
+      <c r="A23" s="34" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="36" t="n">
-        <v>44</v>
-      </c>
-      <c r="C23" s="36" t="n">
+      <c r="B23" s="37" t="n">
+        <v>55</v>
+      </c>
+      <c r="C23" s="37" t="n">
         <v>4</v>
       </c>
-      <c r="D23" s="36" t="n">
+      <c r="D23" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="37" t="n">
+      <c r="E23" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A23-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A23)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
       <c r="F23" s="15" t="n">
-        <f aca="false">B23*'Premissas Precept'!$B$8</f>
-        <v>52668</v>
+        <f aca="false">Z23*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>71856</v>
       </c>
       <c r="G23" s="15" t="n">
         <f aca="false">C23*'Premissas Precept'!$B$9</f>
@@ -4634,27 +4928,27 @@
       </c>
       <c r="I23" s="22" t="n">
         <f aca="false">F23+G23+H23</f>
-        <v>122653</v>
+        <v>141841</v>
       </c>
       <c r="J23" s="15" t="n">
         <f aca="false">SUM(I11:I22)</f>
-        <v>911025.5</v>
-      </c>
-      <c r="K23" s="38" t="n">
+        <v>981897.5</v>
+      </c>
+      <c r="K23" s="39" t="n">
         <f aca="false">IF(J23&lt;=0,'Premissas Precept'!$C$24,(J23*LOOKUP(J23,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J23,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J23)</f>
-        <v>0.186229943618483</v>
+        <v>0.187584740260567</v>
       </c>
       <c r="L23" s="15" t="n">
         <f aca="false">I23*K23</f>
-        <v>22841.6612746378</v>
+        <v>26607.2071432991</v>
       </c>
       <c r="M23" s="15" t="n">
-        <f aca="false">B23*'Premissas Precept'!$B$15</f>
-        <v>3960</v>
+        <f aca="false">B23*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>5940</v>
       </c>
       <c r="N23" s="15" t="n">
         <f aca="false">I23*'Premissas Precept'!$B$16</f>
-        <v>2453.06</v>
+        <v>2836.82</v>
       </c>
       <c r="O23" s="15" t="n">
         <f aca="false">(G23+H23)*'Premissas Precept'!$B$17</f>
@@ -4670,7 +4964,7 @@
       </c>
       <c r="R23" s="22" t="n">
         <f aca="false">SUM(L23:Q23)</f>
-        <v>60848.7212746378</v>
+        <v>66978.0271432991</v>
       </c>
       <c r="S23" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4678,45 +4972,53 @@
       </c>
       <c r="T23" s="15" t="n">
         <f aca="false">IF(A23&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I23,0)</f>
-        <v>25757.13</v>
+        <v>34751.045</v>
       </c>
       <c r="U23" s="22" t="n">
         <f aca="false">S23+T23</f>
-        <v>37757.13</v>
+        <v>46751.045</v>
       </c>
       <c r="V23" s="22" t="n">
         <f aca="false">I23-R23-U23</f>
-        <v>24047.1487253622</v>
+        <v>28111.9278567009</v>
       </c>
       <c r="W23" s="15" t="n">
         <f aca="false">T23/'Premissas Precept'!$B$45</f>
-        <v>3679.59</v>
-      </c>
-      <c r="X23" s="35" t="str">
+        <v>4964.435</v>
+      </c>
+      <c r="X23" s="36" t="str">
         <f aca="false">IF(V23&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y23" s="38" t="n">
+        <f aca="false">C23*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A23-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A23)*$D$6:$D$29)</f>
+        <v>7</v>
+      </c>
+      <c r="Z23" s="38" t="n">
+        <f aca="false">MAX(0,B23-Y23)</f>
+        <v>48</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="33" t="n">
+      <c r="A24" s="34" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="36" t="n">
-        <v>46</v>
-      </c>
-      <c r="C24" s="36" t="n">
+      <c r="B24" s="37" t="n">
+        <v>60</v>
+      </c>
+      <c r="C24" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="36" t="n">
+      <c r="D24" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="37" t="n">
+      <c r="E24" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A24-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A24)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
       <c r="F24" s="15" t="n">
-        <f aca="false">B24*'Premissas Precept'!$B$8</f>
-        <v>55062</v>
+        <f aca="false">Z24*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>77844</v>
       </c>
       <c r="G24" s="15" t="n">
         <f aca="false">C24*'Premissas Precept'!$B$9</f>
@@ -4728,27 +5030,27 @@
       </c>
       <c r="I24" s="22" t="n">
         <f aca="false">F24+G24+H24</f>
-        <v>135044</v>
+        <v>157826</v>
       </c>
       <c r="J24" s="15" t="n">
         <f aca="false">SUM(I12:I23)</f>
-        <v>999530</v>
-      </c>
-      <c r="K24" s="38" t="n">
+        <v>1087784</v>
+      </c>
+      <c r="K24" s="39" t="n">
         <f aca="false">IF(J24&lt;=0,'Premissas Precept'!$C$24,(J24*LOOKUP(J24,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J24,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J24)</f>
-        <v>0.187891959220834</v>
+        <v>0.189279967346459</v>
       </c>
       <c r="L24" s="15" t="n">
         <f aca="false">I24*K24</f>
-        <v>25373.6817410183</v>
+        <v>29873.3001264222</v>
       </c>
       <c r="M24" s="15" t="n">
-        <f aca="false">B24*'Premissas Precept'!$B$15</f>
-        <v>4140</v>
+        <f aca="false">B24*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>6480</v>
       </c>
       <c r="N24" s="15" t="n">
         <f aca="false">I24*'Premissas Precept'!$B$16</f>
-        <v>2700.88</v>
+        <v>3156.52</v>
       </c>
       <c r="O24" s="15" t="n">
         <f aca="false">(G24+H24)*'Premissas Precept'!$B$17</f>
@@ -4764,7 +5066,7 @@
       </c>
       <c r="R24" s="22" t="n">
         <f aca="false">SUM(L24:Q24)</f>
-        <v>68407.3617410183</v>
+        <v>75702.6201264222</v>
       </c>
       <c r="S24" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4772,45 +5074,53 @@
       </c>
       <c r="T24" s="15" t="n">
         <f aca="false">IF(A24&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I24,0)</f>
-        <v>28359.24</v>
+        <v>38667.37</v>
       </c>
       <c r="U24" s="22" t="n">
         <f aca="false">S24+T24</f>
-        <v>40359.24</v>
+        <v>50667.37</v>
       </c>
       <c r="V24" s="22" t="n">
         <f aca="false">I24-R24-U24</f>
-        <v>26277.3982589817</v>
+        <v>31456.0098735778</v>
       </c>
       <c r="W24" s="15" t="n">
         <f aca="false">T24/'Premissas Precept'!$B$45</f>
-        <v>4051.32</v>
-      </c>
-      <c r="X24" s="35" t="str">
+        <v>5523.91</v>
+      </c>
+      <c r="X24" s="36" t="str">
         <f aca="false">IF(V24&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y24" s="38" t="n">
+        <f aca="false">C24*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A24-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A24)*$D$6:$D$29)</f>
+        <v>8</v>
+      </c>
+      <c r="Z24" s="38" t="n">
+        <f aca="false">MAX(0,B24-Y24)</f>
+        <v>52</v>
+      </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="33" t="n">
+      <c r="A25" s="34" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="36" t="n">
-        <v>48</v>
-      </c>
-      <c r="C25" s="36" t="n">
+      <c r="B25" s="37" t="n">
+        <v>64</v>
+      </c>
+      <c r="C25" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="36" t="n">
+      <c r="D25" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="37" t="n">
+      <c r="E25" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A25-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A25)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
       <c r="F25" s="15" t="n">
-        <f aca="false">B25*'Premissas Precept'!$B$8</f>
-        <v>57456</v>
+        <f aca="false">Z25*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>83832</v>
       </c>
       <c r="G25" s="15" t="n">
         <f aca="false">C25*'Premissas Precept'!$B$9</f>
@@ -4822,27 +5132,27 @@
       </c>
       <c r="I25" s="22" t="n">
         <f aca="false">F25+G25+H25</f>
-        <v>137438</v>
+        <v>163814</v>
       </c>
       <c r="J25" s="15" t="n">
         <f aca="false">SUM(I13:I24)</f>
-        <v>1096834.5</v>
-      </c>
-      <c r="K25" s="38" t="n">
+        <v>1205164.5</v>
+      </c>
+      <c r="K25" s="39" t="n">
         <f aca="false">IF(J25&lt;=0,'Premissas Precept'!$C$24,(J25*LOOKUP(J25,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J25,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J25)</f>
-        <v>0.1894096807677</v>
+        <v>0.190811065626311</v>
       </c>
       <c r="L25" s="15" t="n">
         <f aca="false">I25*K25</f>
-        <v>26032.0877053512</v>
+        <v>31257.5239045085</v>
       </c>
       <c r="M25" s="15" t="n">
-        <f aca="false">B25*'Premissas Precept'!$B$15</f>
-        <v>4320</v>
+        <f aca="false">B25*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>6912</v>
       </c>
       <c r="N25" s="15" t="n">
         <f aca="false">I25*'Premissas Precept'!$B$16</f>
-        <v>2748.76</v>
+        <v>3276.28</v>
       </c>
       <c r="O25" s="15" t="n">
         <f aca="false">(G25+H25)*'Premissas Precept'!$B$17</f>
@@ -4858,7 +5168,7 @@
       </c>
       <c r="R25" s="22" t="n">
         <f aca="false">SUM(L25:Q25)</f>
-        <v>69293.6477053512</v>
+        <v>77638.6039045085</v>
       </c>
       <c r="S25" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4866,45 +5176,53 @@
       </c>
       <c r="T25" s="15" t="n">
         <f aca="false">IF(A25&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I25,0)</f>
-        <v>28861.98</v>
+        <v>40134.43</v>
       </c>
       <c r="U25" s="22" t="n">
         <f aca="false">S25+T25</f>
-        <v>40861.98</v>
+        <v>52134.43</v>
       </c>
       <c r="V25" s="22" t="n">
         <f aca="false">I25-R25-U25</f>
-        <v>27282.3722946488</v>
+        <v>34040.9660954915</v>
       </c>
       <c r="W25" s="15" t="n">
         <f aca="false">T25/'Premissas Precept'!$B$45</f>
-        <v>4123.14</v>
-      </c>
-      <c r="X25" s="35" t="str">
+        <v>5733.49</v>
+      </c>
+      <c r="X25" s="36" t="str">
         <f aca="false">IF(V25&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y25" s="38" t="n">
+        <f aca="false">C25*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A25-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A25)*$D$6:$D$29)</f>
+        <v>8</v>
+      </c>
+      <c r="Z25" s="38" t="n">
+        <f aca="false">MAX(0,B25-Y25)</f>
+        <v>56</v>
+      </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="33" t="n">
+      <c r="A26" s="34" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="36" t="n">
-        <v>50</v>
-      </c>
-      <c r="C26" s="36" t="n">
+      <c r="B26" s="37" t="n">
+        <v>68</v>
+      </c>
+      <c r="C26" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="36" t="n">
+      <c r="D26" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="37" t="n">
+      <c r="E26" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A26-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A26)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
       <c r="F26" s="15" t="n">
-        <f aca="false">B26*'Premissas Precept'!$B$8</f>
-        <v>59850</v>
+        <f aca="false">Z26*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>89820</v>
       </c>
       <c r="G26" s="15" t="n">
         <f aca="false">C26*'Premissas Precept'!$B$9</f>
@@ -4916,27 +5234,27 @@
       </c>
       <c r="I26" s="22" t="n">
         <f aca="false">F26+G26+H26</f>
-        <v>139832</v>
+        <v>169802</v>
       </c>
       <c r="J26" s="15" t="n">
         <f aca="false">SUM(I14:I25)</f>
-        <v>1189139.5</v>
-      </c>
-      <c r="K26" s="38" t="n">
+        <v>1322036.5</v>
+      </c>
+      <c r="K26" s="39" t="n">
         <f aca="false">IF(J26&lt;=0,'Premissas Precept'!$C$24,(J26*LOOKUP(J26,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J26,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J26)</f>
-        <v>0.190619853684114</v>
+        <v>0.192065410069994</v>
       </c>
       <c r="L26" s="15" t="n">
         <f aca="false">I26*K26</f>
-        <v>26654.755380357</v>
+        <v>32613.0907607052</v>
       </c>
       <c r="M26" s="15" t="n">
-        <f aca="false">B26*'Premissas Precept'!$B$15</f>
-        <v>4500</v>
+        <f aca="false">B26*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>7344</v>
       </c>
       <c r="N26" s="15" t="n">
         <f aca="false">I26*'Premissas Precept'!$B$16</f>
-        <v>2796.64</v>
+        <v>3396.04</v>
       </c>
       <c r="O26" s="15" t="n">
         <f aca="false">(G26+H26)*'Premissas Precept'!$B$17</f>
@@ -4952,7 +5270,7 @@
       </c>
       <c r="R26" s="22" t="n">
         <f aca="false">SUM(L26:Q26)</f>
-        <v>70144.195380357</v>
+        <v>79545.9307607052</v>
       </c>
       <c r="S26" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4960,45 +5278,53 @@
       </c>
       <c r="T26" s="15" t="n">
         <f aca="false">IF(A26&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I26,0)</f>
-        <v>29364.72</v>
+        <v>41601.49</v>
       </c>
       <c r="U26" s="22" t="n">
         <f aca="false">S26+T26</f>
-        <v>41364.72</v>
+        <v>53601.49</v>
       </c>
       <c r="V26" s="22" t="n">
         <f aca="false">I26-R26-U26</f>
-        <v>28323.084619643</v>
+        <v>36654.5792392948</v>
       </c>
       <c r="W26" s="15" t="n">
         <f aca="false">T26/'Premissas Precept'!$B$45</f>
-        <v>4194.96</v>
-      </c>
-      <c r="X26" s="35" t="str">
+        <v>5943.07</v>
+      </c>
+      <c r="X26" s="36" t="str">
         <f aca="false">IF(V26&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y26" s="38" t="n">
+        <f aca="false">C26*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A26-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A26)*$D$6:$D$29)</f>
+        <v>8</v>
+      </c>
+      <c r="Z26" s="38" t="n">
+        <f aca="false">MAX(0,B26-Y26)</f>
+        <v>60</v>
+      </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="33" t="n">
+      <c r="A27" s="34" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="36" t="n">
-        <v>52</v>
-      </c>
-      <c r="C27" s="36" t="n">
+      <c r="B27" s="37" t="n">
+        <v>71</v>
+      </c>
+      <c r="C27" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="36" t="n">
+      <c r="D27" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="37" t="n">
+      <c r="E27" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A27-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A27)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
       <c r="F27" s="15" t="n">
-        <f aca="false">B27*'Premissas Precept'!$B$8</f>
-        <v>62244</v>
+        <f aca="false">Z27*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>94311</v>
       </c>
       <c r="G27" s="15" t="n">
         <f aca="false">C27*'Premissas Precept'!$B$9</f>
@@ -5010,27 +5336,27 @@
       </c>
       <c r="I27" s="22" t="n">
         <f aca="false">F27+G27+H27</f>
-        <v>142226</v>
+        <v>174293</v>
       </c>
       <c r="J27" s="15" t="n">
         <f aca="false">SUM(I15:I26)</f>
-        <v>1270250.5</v>
-      </c>
-      <c r="K27" s="38" t="n">
+        <v>1430408.5</v>
+      </c>
+      <c r="K27" s="39" t="n">
         <f aca="false">IF(J27&lt;=0,'Premissas Precept'!$C$24,(J27*LOOKUP(J27,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J27,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J27)</f>
-        <v>0.191538088353439</v>
+        <v>0.193045373052523</v>
       </c>
       <c r="L27" s="15" t="n">
         <f aca="false">I27*K27</f>
-        <v>27241.6961541562</v>
+        <v>33646.4572054434</v>
       </c>
       <c r="M27" s="15" t="n">
-        <f aca="false">B27*'Premissas Precept'!$B$15</f>
-        <v>4680</v>
+        <f aca="false">B27*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>7668</v>
       </c>
       <c r="N27" s="15" t="n">
         <f aca="false">I27*'Premissas Precept'!$B$16</f>
-        <v>2844.52</v>
+        <v>3485.86</v>
       </c>
       <c r="O27" s="15" t="n">
         <f aca="false">(G27+H27)*'Premissas Precept'!$B$17</f>
@@ -5046,7 +5372,7 @@
       </c>
       <c r="R27" s="22" t="n">
         <f aca="false">SUM(L27:Q27)</f>
-        <v>70959.0161541562</v>
+        <v>80993.1172054434</v>
       </c>
       <c r="S27" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5054,45 +5380,53 @@
       </c>
       <c r="T27" s="15" t="n">
         <f aca="false">IF(A27&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I27,0)</f>
-        <v>29867.46</v>
+        <v>42701.785</v>
       </c>
       <c r="U27" s="22" t="n">
         <f aca="false">S27+T27</f>
-        <v>41867.46</v>
+        <v>54701.785</v>
       </c>
       <c r="V27" s="22" t="n">
         <f aca="false">I27-R27-U27</f>
-        <v>29399.5238458438</v>
+        <v>38598.0977945566</v>
       </c>
       <c r="W27" s="15" t="n">
         <f aca="false">T27/'Premissas Precept'!$B$45</f>
-        <v>4266.78</v>
-      </c>
-      <c r="X27" s="35" t="str">
+        <v>6100.255</v>
+      </c>
+      <c r="X27" s="36" t="str">
         <f aca="false">IF(V27&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y27" s="38" t="n">
+        <f aca="false">C27*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A27-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A27)*$D$6:$D$29)</f>
+        <v>8</v>
+      </c>
+      <c r="Z27" s="38" t="n">
+        <f aca="false">MAX(0,B27-Y27)</f>
+        <v>63</v>
+      </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="33" t="n">
+      <c r="A28" s="34" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="36" t="n">
-        <v>54</v>
-      </c>
-      <c r="C28" s="36" t="n">
+      <c r="B28" s="37" t="n">
+        <v>76</v>
+      </c>
+      <c r="C28" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="36" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="37" t="n">
+      <c r="D28" s="37" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A28-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A28)*$D$6:$D$29)</f>
         <v>5</v>
       </c>
       <c r="F28" s="15" t="n">
-        <f aca="false">B28*'Premissas Precept'!$B$8</f>
-        <v>64638</v>
+        <f aca="false">Z28*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>103293</v>
       </c>
       <c r="G28" s="15" t="n">
         <f aca="false">C28*'Premissas Precept'!$B$9</f>
@@ -5104,27 +5438,27 @@
       </c>
       <c r="I28" s="22" t="n">
         <f aca="false">F28+G28+H28</f>
-        <v>139620.5</v>
+        <v>178275.5</v>
       </c>
       <c r="J28" s="15" t="n">
         <f aca="false">SUM(I16:I27)</f>
-        <v>1356359</v>
-      </c>
-      <c r="K28" s="38" t="n">
+        <v>1545275</v>
+      </c>
+      <c r="K28" s="39" t="n">
         <f aca="false">IF(J28&lt;=0,'Premissas Precept'!$C$24,(J28*LOOKUP(J28,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J28,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J28)</f>
-        <v>0.192392718299506</v>
+        <v>0.193934008509812</v>
       </c>
       <c r="L28" s="15" t="n">
         <f aca="false">I28*K28</f>
-        <v>26861.9675253362</v>
+        <v>34573.682334091</v>
       </c>
       <c r="M28" s="15" t="n">
-        <f aca="false">B28*'Premissas Precept'!$B$15</f>
-        <v>4860</v>
+        <f aca="false">B28*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>8208</v>
       </c>
       <c r="N28" s="15" t="n">
         <f aca="false">I28*'Premissas Precept'!$B$16</f>
-        <v>2792.41</v>
+        <v>3565.51</v>
       </c>
       <c r="O28" s="15" t="n">
         <f aca="false">(G28+H28)*'Premissas Precept'!$B$17</f>
@@ -5140,7 +5474,7 @@
       </c>
       <c r="R28" s="22" t="n">
         <f aca="false">SUM(L28:Q28)</f>
-        <v>68507.3775253362</v>
+        <v>80340.192334091</v>
       </c>
       <c r="S28" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5148,45 +5482,53 @@
       </c>
       <c r="T28" s="15" t="n">
         <f aca="false">IF(A28&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I28,0)</f>
-        <v>29320.305</v>
+        <v>43677.4975</v>
       </c>
       <c r="U28" s="22" t="n">
         <f aca="false">S28+T28</f>
-        <v>41320.305</v>
+        <v>55677.4975</v>
       </c>
       <c r="V28" s="22" t="n">
         <f aca="false">I28-R28-U28</f>
-        <v>29792.8174746638</v>
+        <v>42257.810165909</v>
       </c>
       <c r="W28" s="15" t="n">
         <f aca="false">T28/'Premissas Precept'!$B$45</f>
-        <v>4188.615</v>
-      </c>
-      <c r="X28" s="35" t="str">
+        <v>6239.6425</v>
+      </c>
+      <c r="X28" s="36" t="str">
         <f aca="false">IF(V28&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y28" s="38" t="n">
+        <f aca="false">C28*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A28-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A28)*$D$6:$D$29)</f>
+        <v>7</v>
+      </c>
+      <c r="Z28" s="38" t="n">
+        <f aca="false">MAX(0,B28-Y28)</f>
+        <v>69</v>
+      </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="33" t="n">
+      <c r="A29" s="34" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="36" t="n">
-        <v>56</v>
-      </c>
-      <c r="C29" s="36" t="n">
+      <c r="B29" s="37" t="n">
+        <v>79</v>
+      </c>
+      <c r="C29" s="37" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="36" t="n">
+      <c r="D29" s="37" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="37" t="n">
+      <c r="E29" s="38" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A29-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A29)*$D$6:$D$29)</f>
         <v>5</v>
       </c>
       <c r="F29" s="15" t="n">
-        <f aca="false">B29*'Premissas Precept'!$B$8</f>
-        <v>67032</v>
+        <f aca="false">Z29*('Premissas Precept'!$B$8+'Premissas Precept'!$B$88*'Premissas Precept'!$B$89)</f>
+        <v>107784</v>
       </c>
       <c r="G29" s="15" t="n">
         <f aca="false">C29*'Premissas Precept'!$B$9</f>
@@ -5198,27 +5540,27 @@
       </c>
       <c r="I29" s="22" t="n">
         <f aca="false">F29+G29+H29</f>
-        <v>142014.5</v>
+        <v>182766.5</v>
       </c>
       <c r="J29" s="15" t="n">
         <f aca="false">SUM(I17:I28)</f>
-        <v>1426274</v>
-      </c>
-      <c r="K29" s="38" t="n">
+        <v>1649636</v>
+      </c>
+      <c r="K29" s="39" t="n">
         <f aca="false">IF(J29&lt;=0,'Premissas Precept'!$C$24,(J29*LOOKUP(J29,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J29,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J29)</f>
-        <v>0.193010718838035</v>
+        <v>0.194634076850893</v>
       </c>
       <c r="L29" s="15" t="n">
         <f aca="false">I29*K29</f>
-        <v>27410.3207304242</v>
+        <v>35572.5890067688</v>
       </c>
       <c r="M29" s="15" t="n">
-        <f aca="false">B29*'Premissas Precept'!$B$15</f>
-        <v>5040</v>
+        <f aca="false">B29*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
+        <v>8532</v>
       </c>
       <c r="N29" s="15" t="n">
         <f aca="false">I29*'Premissas Precept'!$B$16</f>
-        <v>2840.29</v>
+        <v>3655.33</v>
       </c>
       <c r="O29" s="15" t="n">
         <f aca="false">(G29+H29)*'Premissas Precept'!$B$17</f>
@@ -5234,7 +5576,7 @@
       </c>
       <c r="R29" s="22" t="n">
         <f aca="false">SUM(L29:Q29)</f>
-        <v>69283.6107304242</v>
+        <v>81752.9190067688</v>
       </c>
       <c r="S29" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5242,45 +5584,53 @@
       </c>
       <c r="T29" s="15" t="n">
         <f aca="false">IF(A29&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I29,0)</f>
-        <v>29823.045</v>
+        <v>44777.7925</v>
       </c>
       <c r="U29" s="22" t="n">
         <f aca="false">S29+T29</f>
-        <v>41823.045</v>
+        <v>56777.7925</v>
       </c>
       <c r="V29" s="22" t="n">
         <f aca="false">I29-R29-U29</f>
-        <v>30907.8442695758</v>
+        <v>44235.7884932312</v>
       </c>
       <c r="W29" s="15" t="n">
         <f aca="false">T29/'Premissas Precept'!$B$45</f>
-        <v>4260.435</v>
-      </c>
-      <c r="X29" s="35" t="str">
+        <v>6396.8275</v>
+      </c>
+      <c r="X29" s="36" t="str">
         <f aca="false">IF(V29&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
+      <c r="Y29" s="38" t="n">
+        <f aca="false">C29*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A29-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A29)*$D$6:$D$29)</f>
+        <v>7</v>
+      </c>
+      <c r="Z29" s="38" t="n">
+        <f aca="false">MAX(0,B29-Y29)</f>
+        <v>72</v>
+      </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="39" t="s">
-        <v>179</v>
-      </c>
-      <c r="B30" s="40" t="n">
+      <c r="A30" s="40" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" s="41" t="n">
         <f aca="false">SUM(B6:B29)</f>
-        <v>750</v>
-      </c>
-      <c r="C30" s="40" t="n">
+        <v>902</v>
+      </c>
+      <c r="C30" s="41" t="n">
         <f aca="false">SUM(C6:C29)</f>
         <v>65</v>
       </c>
-      <c r="D30" s="40" t="n">
+      <c r="D30" s="41" t="n">
         <f aca="false">SUM(D6:D29)</f>
         <v>15</v>
       </c>
       <c r="E30" s="32"/>
       <c r="F30" s="22" t="n">
         <f aca="false">SUM(F6:F29)</f>
-        <v>897750</v>
+        <v>1188618</v>
       </c>
       <c r="G30" s="22" t="n">
         <f aca="false">SUM(G6:G29)</f>
@@ -5292,21 +5642,21 @@
       </c>
       <c r="I30" s="22" t="n">
         <f aca="false">SUM(I6:I29)</f>
-        <v>1942515.5</v>
+        <v>2233383.5</v>
       </c>
       <c r="J30" s="32"/>
       <c r="K30" s="32"/>
       <c r="L30" s="22" t="n">
         <f aca="false">SUM(L6:L29)</f>
-        <v>351518.004455835</v>
+        <v>408681.691553622</v>
       </c>
       <c r="M30" s="22" t="n">
         <f aca="false">SUM(M6:M29)</f>
-        <v>67500</v>
+        <v>97416</v>
       </c>
       <c r="N30" s="22" t="n">
         <f aca="false">SUM(N6:N29)</f>
-        <v>38850.31</v>
+        <v>44667.67</v>
       </c>
       <c r="O30" s="22" t="n">
         <f aca="false">SUM(O6:O29)</f>
@@ -5322,7 +5672,7 @@
       </c>
       <c r="R30" s="22" t="n">
         <f aca="false">SUM(R6:R29)</f>
-        <v>930574.514455835</v>
+        <v>1023471.56155362</v>
       </c>
       <c r="S30" s="22" t="n">
         <f aca="false">SUM(S6:S29)</f>
@@ -5330,73 +5680,81 @@
       </c>
       <c r="T30" s="22" t="n">
         <f aca="false">SUM(T6:T29)</f>
-        <v>403152.225</v>
+        <v>540210.4225</v>
       </c>
       <c r="U30" s="22" t="n">
         <f aca="false">SUM(U6:U29)</f>
-        <v>691152.225</v>
+        <v>828210.4225</v>
       </c>
       <c r="V30" s="22" t="n">
         <f aca="false">SUM(V6:V29)</f>
-        <v>320788.760544165</v>
+        <v>381701.515946378</v>
       </c>
       <c r="W30" s="22" t="n">
         <f aca="false">SUM(W6:W29)</f>
-        <v>57593.175</v>
+        <v>77172.9175</v>
       </c>
       <c r="X30" s="32"/>
+      <c r="Y30" s="41" t="n">
+        <f aca="false">SUM(Y6:Y29)</f>
+        <v>108</v>
+      </c>
+      <c r="Z30" s="41" t="n">
+        <f aca="false">SUM(Z6:Z29)</f>
+        <v>794</v>
+      </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="41" t="s">
-        <v>180</v>
+      <c r="A32" s="42" t="s">
+        <v>197</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="17" t="s">
-        <v>181</v>
+        <v>198</v>
       </c>
       <c r="B33" s="17"/>
       <c r="C33" s="17" t="s">
-        <v>182</v>
+        <v>199</v>
       </c>
       <c r="D33" s="17"/>
       <c r="E33" s="17" t="s">
-        <v>183</v>
+        <v>200</v>
       </c>
       <c r="F33" s="17" t="s">
-        <v>184</v>
+        <v>201</v>
       </c>
       <c r="G33" s="17" t="s">
-        <v>185</v>
+        <v>202</v>
       </c>
       <c r="H33" s="17" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="I33" s="17" t="s">
-        <v>187</v>
+        <v>204</v>
       </c>
       <c r="J33" s="17" t="s">
-        <v>188</v>
+        <v>205</v>
       </c>
       <c r="K33" s="17" t="s">
-        <v>189</v>
+        <v>206</v>
       </c>
       <c r="L33" s="17" t="s">
-        <v>190</v>
+        <v>207</v>
       </c>
       <c r="M33" s="17" t="s">
-        <v>191</v>
+        <v>208</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="42" t="s">
-        <v>192</v>
-      </c>
-      <c r="B34" s="42"/>
-      <c r="C34" s="43" t="s">
-        <v>193</v>
-      </c>
-      <c r="D34" s="43"/>
+      <c r="A34" s="43" t="s">
+        <v>209</v>
+      </c>
+      <c r="B34" s="43"/>
+      <c r="C34" s="44" t="s">
+        <v>210</v>
+      </c>
+      <c r="D34" s="44"/>
       <c r="E34" s="15" t="n">
         <v>0</v>
       </c>
@@ -5417,172 +5775,172 @@
       <c r="M34" s="32"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="42" t="s">
-        <v>194</v>
-      </c>
-      <c r="B35" s="42"/>
-      <c r="C35" s="43" t="s">
-        <v>195</v>
-      </c>
-      <c r="D35" s="43"/>
+      <c r="A35" s="43" t="s">
+        <v>211</v>
+      </c>
+      <c r="B35" s="43"/>
+      <c r="C35" s="44" t="s">
+        <v>212</v>
+      </c>
+      <c r="D35" s="44"/>
       <c r="E35" s="28" t="n">
         <f aca="false">AVERAGE(I6:I11)</f>
-        <v>17801.75</v>
+        <v>19803.75</v>
       </c>
       <c r="F35" s="28" t="n">
         <f aca="false">AVERAGE(R6:R11)</f>
-        <v>6681.33958333333</v>
+        <v>7225.91351004006</v>
       </c>
       <c r="G35" s="28" t="n">
         <f aca="false">AVERAGE(U6:U11)</f>
-        <v>14942.3625</v>
+        <v>15690.49625</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>0</v>
       </c>
       <c r="I35" s="23" t="n">
         <f aca="false">F35/E35</f>
-        <v>0.375319257001887</v>
+        <v>0.364876021462605</v>
       </c>
       <c r="J35" s="15" t="n">
         <f aca="false">E35-F35-G35</f>
-        <v>-3821.95208333333</v>
-      </c>
-      <c r="K35" s="44" t="n">
+        <v>-3112.65976004007</v>
+      </c>
+      <c r="K35" s="45" t="n">
         <f aca="false">AVERAGE(B6:B11)</f>
         <v>10</v>
       </c>
-      <c r="L35" s="34" t="n">
+      <c r="L35" s="35" t="n">
         <f aca="false">SUM(C6:C11)</f>
         <v>3</v>
       </c>
-      <c r="M35" s="34" t="n">
+      <c r="M35" s="35" t="n">
         <f aca="false">SUM(D6:D11)</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="42" t="s">
-        <v>196</v>
-      </c>
-      <c r="B36" s="42"/>
-      <c r="C36" s="43" t="s">
-        <v>197</v>
-      </c>
-      <c r="D36" s="43"/>
+      <c r="A36" s="43" t="s">
+        <v>213</v>
+      </c>
+      <c r="B36" s="43"/>
+      <c r="C36" s="44" t="s">
+        <v>214</v>
+      </c>
+      <c r="D36" s="44"/>
       <c r="E36" s="28" t="n">
         <f aca="false">AVERAGE(I12:I17)</f>
-        <v>54919.8333333333</v>
+        <v>58178.3333333333</v>
       </c>
       <c r="F36" s="28" t="n">
         <f aca="false">AVERAGE(R12:R17)</f>
-        <v>23711.3861311891</v>
+        <v>24858.7635121745</v>
       </c>
       <c r="G36" s="28" t="n">
         <f aca="false">AVERAGE(U12:U17)</f>
-        <v>23533.165</v>
+        <v>26253.6916666667</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>0</v>
       </c>
       <c r="I36" s="23" t="n">
         <f aca="false">F36/E36</f>
-        <v>0.431745413123779</v>
+        <v>0.427285590492013</v>
       </c>
       <c r="J36" s="15" t="n">
         <f aca="false">E36-F36-G36</f>
-        <v>7675.28220214424</v>
-      </c>
-      <c r="K36" s="44" t="n">
+        <v>7065.87815449215</v>
+      </c>
+      <c r="K36" s="45" t="n">
         <f aca="false">AVERAGE(B12:B17)</f>
         <v>25</v>
       </c>
-      <c r="L36" s="34" t="n">
+      <c r="L36" s="35" t="n">
         <f aca="false">SUM(C12:C17)</f>
         <v>8</v>
       </c>
-      <c r="M36" s="34" t="n">
+      <c r="M36" s="35" t="n">
         <f aca="false">SUM(D12:D17)</f>
         <v>3</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="42" t="s">
-        <v>198</v>
-      </c>
-      <c r="B37" s="42"/>
-      <c r="C37" s="43" t="s">
-        <v>199</v>
-      </c>
-      <c r="D37" s="43"/>
+      <c r="A37" s="43" t="s">
+        <v>215</v>
+      </c>
+      <c r="B37" s="43"/>
+      <c r="C37" s="44" t="s">
+        <v>216</v>
+      </c>
+      <c r="D37" s="44"/>
       <c r="E37" s="28" t="n">
         <f aca="false">AVERAGE(I18:I29)</f>
-        <v>125515.5</v>
+        <v>147124.25</v>
       </c>
       <c r="F37" s="28" t="n">
         <f aca="false">AVERAGE(R18:R29)</f>
-        <v>62351.5133473917</v>
+        <v>69246.9582850279</v>
       </c>
       <c r="G37" s="28" t="n">
         <f aca="false">AVERAGE(U18:U29)</f>
-        <v>38358.255</v>
+        <v>48045.44125</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>0</v>
       </c>
       <c r="I37" s="23" t="n">
         <f aca="false">F37/E37</f>
-        <v>0.496763454293627</v>
+        <v>0.470669915292876</v>
       </c>
       <c r="J37" s="15" t="n">
         <f aca="false">E37-F37-G37</f>
-        <v>24805.7316526083</v>
-      </c>
-      <c r="K37" s="44" t="n">
+        <v>29831.8504649721</v>
+      </c>
+      <c r="K37" s="45" t="n">
         <f aca="false">AVERAGE(B18:B29)</f>
-        <v>45</v>
-      </c>
-      <c r="L37" s="34" t="n">
+        <v>57.6666666666667</v>
+      </c>
+      <c r="L37" s="35" t="n">
         <f aca="false">SUM(C18:C29)</f>
         <v>54</v>
       </c>
-      <c r="M37" s="34" t="n">
+      <c r="M37" s="35" t="n">
         <f aca="false">SUM(D18:D29)</f>
         <v>11</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="41" t="s">
-        <v>200</v>
+      <c r="A40" s="42" t="s">
+        <v>217</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="17" t="s">
-        <v>201</v>
+        <v>218</v>
       </c>
       <c r="B41" s="17"/>
       <c r="C41" s="17"/>
       <c r="D41" s="17"/>
       <c r="E41" s="17" t="s">
-        <v>202</v>
+        <v>219</v>
       </c>
       <c r="F41" s="17" t="s">
-        <v>203</v>
+        <v>220</v>
       </c>
       <c r="G41" s="17" t="s">
-        <v>204</v>
+        <v>221</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="45" t="s">
-        <v>205</v>
-      </c>
-      <c r="B42" s="45"/>
-      <c r="C42" s="45"/>
-      <c r="D42" s="45"/>
-      <c r="E42" s="44" t="n">
-        <f aca="false">AVERAGE(B18:B29)*'Premissas Precept'!B7</f>
-        <v>27</v>
+      <c r="A42" s="46" t="s">
+        <v>222</v>
+      </c>
+      <c r="B42" s="46"/>
+      <c r="C42" s="46"/>
+      <c r="D42" s="46"/>
+      <c r="E42" s="45" t="n">
+        <f aca="false">AVERAGE(Z18:Z29)*'Premissas Precept'!B7</f>
+        <v>30.25</v>
       </c>
       <c r="F42" s="15" t="n">
         <f aca="false">'Premissas Precept'!B5</f>
@@ -5590,19 +5948,19 @@
       </c>
       <c r="G42" s="15" t="n">
         <f aca="false">E42*F42</f>
-        <v>26919</v>
+        <v>30159.25</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="45" t="s">
-        <v>206</v>
-      </c>
-      <c r="B43" s="45"/>
-      <c r="C43" s="45"/>
-      <c r="D43" s="45"/>
-      <c r="E43" s="44" t="n">
-        <f aca="false">AVERAGE(B18:B29)*(1-'Premissas Precept'!B7)</f>
-        <v>18</v>
+      <c r="A43" s="46" t="s">
+        <v>223</v>
+      </c>
+      <c r="B43" s="46"/>
+      <c r="C43" s="46"/>
+      <c r="D43" s="46"/>
+      <c r="E43" s="45" t="n">
+        <f aca="false">AVERAGE(Z18:Z29)*(1-'Premissas Precept'!B7)</f>
+        <v>20.1666666666667</v>
       </c>
       <c r="F43" s="15" t="n">
         <f aca="false">'Premissas Precept'!B6</f>
@@ -5610,229 +5968,249 @@
       </c>
       <c r="G43" s="15" t="n">
         <f aca="false">E43*F43</f>
-        <v>26946</v>
+        <v>30189.5</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="45" t="s">
-        <v>207</v>
-      </c>
-      <c r="B44" s="45"/>
-      <c r="C44" s="45"/>
-      <c r="D44" s="45"/>
-      <c r="E44" s="44" t="n">
+      <c r="A44" s="46" t="s">
+        <v>224</v>
+      </c>
+      <c r="B44" s="46"/>
+      <c r="C44" s="46"/>
+      <c r="D44" s="46"/>
+      <c r="E44" s="45" t="n">
+        <f aca="false">AVERAGE(Z18:Z29)*'Premissas Precept'!B89</f>
+        <v>50.4166666666667</v>
+      </c>
+      <c r="F44" s="15" t="n">
+        <f aca="false">'Premissas Precept'!B88</f>
+        <v>300</v>
+      </c>
+      <c r="G44" s="15" t="n">
+        <f aca="false">E44*F44</f>
+        <v>15125</v>
+      </c>
+    </row>
+    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A45" s="46" t="s">
+        <v>225</v>
+      </c>
+      <c r="B45" s="46"/>
+      <c r="C45" s="46"/>
+      <c r="D45" s="46"/>
+      <c r="E45" s="45" t="n">
         <f aca="false">AVERAGE(C18:C29)</f>
         <v>4.5</v>
       </c>
-      <c r="F44" s="15" t="n">
+      <c r="F45" s="15" t="n">
         <f aca="false">'Premissas Precept'!B9</f>
         <v>9997</v>
       </c>
-      <c r="G44" s="15" t="n">
-        <f aca="false">E44*F44</f>
+      <c r="G45" s="15" t="n">
+        <f aca="false">E45*F45</f>
         <v>44986.5</v>
       </c>
     </row>
-    <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="45" t="s">
-        <v>208</v>
-      </c>
-      <c r="B45" s="45"/>
-      <c r="C45" s="45"/>
-      <c r="D45" s="45"/>
-      <c r="E45" s="44" t="n">
+    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A46" s="46" t="s">
+        <v>226</v>
+      </c>
+      <c r="B46" s="46"/>
+      <c r="C46" s="46"/>
+      <c r="D46" s="46"/>
+      <c r="E46" s="45" t="n">
         <f aca="false">AVERAGE(E18:E29)</f>
         <v>5.33333333333333</v>
       </c>
-      <c r="F45" s="15" t="n">
+      <c r="F46" s="15" t="n">
         <f aca="false">'Premissas Precept'!B12</f>
         <v>4999.5</v>
       </c>
-      <c r="G45" s="15" t="n">
-        <f aca="false">E45*F45</f>
+      <c r="G46" s="15" t="n">
+        <f aca="false">E46*F46</f>
         <v>26664</v>
       </c>
     </row>
-    <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="42" t="s">
-        <v>209</v>
-      </c>
-      <c r="B46" s="42"/>
-      <c r="C46" s="42"/>
-      <c r="D46" s="42"/>
-      <c r="E46" s="44"/>
-      <c r="F46" s="15"/>
-      <c r="G46" s="28" t="n">
-        <f aca="false">SUM(G42:G45)</f>
-        <v>125515.5</v>
-      </c>
-    </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="45" t="s">
-        <v>210</v>
-      </c>
-      <c r="B47" s="45"/>
-      <c r="C47" s="45"/>
-      <c r="D47" s="45"/>
-      <c r="E47" s="44" t="n">
+      <c r="A47" s="43" t="s">
+        <v>227</v>
+      </c>
+      <c r="B47" s="43"/>
+      <c r="C47" s="43"/>
+      <c r="D47" s="43"/>
+      <c r="E47" s="45"/>
+      <c r="F47" s="15"/>
+      <c r="G47" s="28" t="n">
+        <f aca="false">SUM(G42:G46)</f>
+        <v>147124.25</v>
+      </c>
+    </row>
+    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A48" s="46" t="s">
+        <v>228</v>
+      </c>
+      <c r="B48" s="46"/>
+      <c r="C48" s="46"/>
+      <c r="D48" s="46"/>
+      <c r="E48" s="45" t="n">
         <f aca="false">AVERAGE(B18:B29)</f>
-        <v>45</v>
-      </c>
-      <c r="F47" s="15" t="n">
+        <v>57.6666666666667</v>
+      </c>
+      <c r="F48" s="15" t="n">
         <f aca="false">'Premissas Precept'!B15</f>
         <v>90</v>
       </c>
-      <c r="G47" s="15" t="n">
+      <c r="G48" s="15" t="n">
         <f aca="false">AVERAGE(M18:M29)</f>
-        <v>4050</v>
-      </c>
-    </row>
-    <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="45" t="s">
-        <v>211</v>
-      </c>
-      <c r="B48" s="45"/>
-      <c r="C48" s="45"/>
-      <c r="D48" s="45"/>
-      <c r="E48" s="44"/>
-      <c r="F48" s="23" t="n">
-        <f aca="false">G48/G46</f>
-        <v>0.186147023122443</v>
-      </c>
-      <c r="G48" s="15" t="n">
+        <v>6228</v>
+      </c>
+    </row>
+    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A49" s="46" t="s">
+        <v>229</v>
+      </c>
+      <c r="B49" s="46"/>
+      <c r="C49" s="46"/>
+      <c r="D49" s="46"/>
+      <c r="E49" s="45"/>
+      <c r="F49" s="23" t="n">
+        <f aca="false">G49/G47</f>
+        <v>0.187933713295811</v>
+      </c>
+      <c r="G49" s="15" t="n">
         <f aca="false">AVERAGE(L18:L29)</f>
-        <v>23364.3366807251</v>
-      </c>
-    </row>
-    <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="45" t="s">
-        <v>212</v>
-      </c>
-      <c r="B49" s="45"/>
-      <c r="C49" s="45"/>
-      <c r="D49" s="45"/>
-      <c r="E49" s="44"/>
-      <c r="F49" s="23" t="n">
+        <v>27649.6066183612</v>
+      </c>
+    </row>
+    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A50" s="46" t="s">
+        <v>230</v>
+      </c>
+      <c r="B50" s="46"/>
+      <c r="C50" s="46"/>
+      <c r="D50" s="46"/>
+      <c r="E50" s="45"/>
+      <c r="F50" s="23" t="n">
         <f aca="false">'Premissas Precept'!B16</f>
         <v>0.02</v>
       </c>
-      <c r="G49" s="15" t="n">
+      <c r="G50" s="15" t="n">
         <f aca="false">AVERAGE(N18:N29)</f>
-        <v>2510.31</v>
-      </c>
-    </row>
-    <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="45" t="s">
-        <v>213</v>
-      </c>
-      <c r="B50" s="45"/>
-      <c r="C50" s="45"/>
-      <c r="D50" s="45"/>
-      <c r="E50" s="44"/>
-      <c r="F50" s="23" t="n">
+        <v>2942.485</v>
+      </c>
+    </row>
+    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A51" s="46" t="s">
+        <v>231</v>
+      </c>
+      <c r="B51" s="46"/>
+      <c r="C51" s="46"/>
+      <c r="D51" s="46"/>
+      <c r="E51" s="45"/>
+      <c r="F51" s="23" t="n">
         <f aca="false">'Premissas Precept'!B17</f>
         <v>0.05</v>
       </c>
-      <c r="G50" s="15" t="n">
+      <c r="G51" s="15" t="n">
         <f aca="false">AVERAGE(O18:O29)</f>
         <v>3582.525</v>
       </c>
     </row>
-    <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="45" t="s">
-        <v>214</v>
-      </c>
-      <c r="B51" s="45"/>
-      <c r="C51" s="45"/>
-      <c r="D51" s="45"/>
-      <c r="E51" s="44"/>
-      <c r="F51" s="15"/>
-      <c r="G51" s="15" t="n">
+    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A52" s="46" t="s">
+        <v>232</v>
+      </c>
+      <c r="B52" s="46"/>
+      <c r="C52" s="46"/>
+      <c r="D52" s="46"/>
+      <c r="E52" s="45"/>
+      <c r="F52" s="15"/>
+      <c r="G52" s="15" t="n">
         <f aca="false">AVERAGE(Q18:Q29)</f>
         <v>3766.66666666667</v>
       </c>
     </row>
-    <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="45" t="s">
-        <v>215</v>
-      </c>
-      <c r="B52" s="45"/>
-      <c r="C52" s="45"/>
-      <c r="D52" s="45"/>
-      <c r="E52" s="44"/>
-      <c r="F52" s="23" t="n">
+    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A53" s="46" t="s">
+        <v>233</v>
+      </c>
+      <c r="B53" s="46"/>
+      <c r="C53" s="46"/>
+      <c r="D53" s="46"/>
+      <c r="E53" s="45"/>
+      <c r="F53" s="23" t="n">
         <f aca="false">'Premissas Precept'!B18</f>
         <v>0.35</v>
       </c>
-      <c r="G52" s="15" t="n">
+      <c r="G53" s="15" t="n">
         <f aca="false">AVERAGE(P18:P29)</f>
         <v>25077.675</v>
       </c>
     </row>
-    <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="42" t="s">
-        <v>216</v>
-      </c>
-      <c r="B53" s="42"/>
-      <c r="C53" s="42"/>
-      <c r="D53" s="42"/>
-      <c r="E53" s="44"/>
-      <c r="F53" s="23" t="n">
-        <f aca="false">G53/G46</f>
-        <v>0.496763454293627</v>
-      </c>
-      <c r="G53" s="28" t="n">
-        <f aca="false">SUM(G47:G52)</f>
-        <v>62351.5133473917</v>
-      </c>
-    </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="45" t="s">
-        <v>217</v>
-      </c>
-      <c r="B54" s="45"/>
-      <c r="C54" s="45"/>
-      <c r="D54" s="45"/>
-      <c r="E54" s="44"/>
+      <c r="A54" s="43" t="s">
+        <v>234</v>
+      </c>
+      <c r="B54" s="43"/>
+      <c r="C54" s="43"/>
+      <c r="D54" s="43"/>
+      <c r="E54" s="45"/>
       <c r="F54" s="23" t="n">
+        <f aca="false">G54/G47</f>
+        <v>0.470669915292876</v>
+      </c>
+      <c r="G54" s="28" t="n">
+        <f aca="false">SUM(G48:G53)</f>
+        <v>69246.9582850279</v>
+      </c>
+    </row>
+    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A55" s="46" t="s">
+        <v>235</v>
+      </c>
+      <c r="B55" s="46"/>
+      <c r="C55" s="46"/>
+      <c r="D55" s="46"/>
+      <c r="E55" s="45"/>
+      <c r="F55" s="23" t="n">
         <f aca="false">'Premissas Precept'!B48</f>
-        <v>0.21</v>
-      </c>
-      <c r="G54" s="15" t="n">
+        <v>0.245</v>
+      </c>
+      <c r="G55" s="15" t="n">
         <f aca="false">AVERAGE(T18:T29)</f>
-        <v>26358.255</v>
-      </c>
-    </row>
-    <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="45" t="s">
-        <v>218</v>
-      </c>
-      <c r="B55" s="45"/>
-      <c r="C55" s="45"/>
-      <c r="D55" s="45"/>
-      <c r="E55" s="44"/>
-      <c r="F55" s="15"/>
-      <c r="G55" s="15" t="n">
+        <v>36045.44125</v>
+      </c>
+    </row>
+    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A56" s="46" t="s">
+        <v>236</v>
+      </c>
+      <c r="B56" s="46"/>
+      <c r="C56" s="46"/>
+      <c r="D56" s="46"/>
+      <c r="E56" s="45"/>
+      <c r="F56" s="15"/>
+      <c r="G56" s="15" t="n">
         <f aca="false">'Premissas Precept'!B42</f>
         <v>12000</v>
       </c>
     </row>
-    <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="42" t="s">
-        <v>219</v>
-      </c>
-      <c r="B56" s="42"/>
-      <c r="C56" s="42"/>
-      <c r="D56" s="42"/>
-      <c r="E56" s="44"/>
-      <c r="F56" s="15"/>
-      <c r="G56" s="28" t="n">
-        <f aca="false">G54+G55</f>
-        <v>38358.255</v>
+    <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A57" s="43" t="s">
+        <v>237</v>
+      </c>
+      <c r="B57" s="43"/>
+      <c r="C57" s="43"/>
+      <c r="D57" s="43"/>
+      <c r="E57" s="45"/>
+      <c r="F57" s="15"/>
+      <c r="G57" s="28" t="n">
+        <f aca="false">G55+G56</f>
+        <v>48045.44125</v>
       </c>
     </row>
   </sheetData>
-  <mergeCells count="23">
+  <mergeCells count="24">
     <mergeCell ref="A34:B34"/>
     <mergeCell ref="C34:D34"/>
     <mergeCell ref="A35:B35"/>
@@ -5856,6 +6234,7 @@
     <mergeCell ref="A54:D54"/>
     <mergeCell ref="A55:D55"/>
     <mergeCell ref="A56:D56"/>
+    <mergeCell ref="A57:D57"/>
   </mergeCells>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.511811023622047" footer="0.511811023622047"/>
@@ -5883,726 +6262,726 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="46" t="s">
-        <v>220</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="A1" s="47" t="s">
+        <v>238</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="48" t="s">
-        <v>221</v>
+      <c r="A2" s="49" t="s">
+        <v>239</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>175</v>
+        <v>190</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="B5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="51" t="n">
+      <c r="A5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="52" t="n">
         <f aca="false">B5-C5-D5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="50" t="n">
+      <c r="F5" s="51" t="n">
         <f aca="false">'Premissas Precept'!B58</f>
         <v>102000</v>
       </c>
-      <c r="G5" s="52" t="n">
+      <c r="G5" s="53" t="n">
         <f aca="false">E5-F5</f>
         <v>-102000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="49" t="n">
+      <c r="A6" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="50" t="n">
+      <c r="B6" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I6</f>
-        <v>4788</v>
-      </c>
-      <c r="C6" s="50" t="n">
+        <v>5988</v>
+      </c>
+      <c r="C6" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R6</f>
-        <v>1197.9</v>
-      </c>
-      <c r="D6" s="50" t="n">
+        <v>1479.9</v>
+      </c>
+      <c r="D6" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U6</f>
         <v>12000</v>
       </c>
-      <c r="E6" s="51" t="n">
+      <c r="E6" s="52" t="n">
         <f aca="false">B6-C6-D6</f>
-        <v>-8409.9</v>
-      </c>
-      <c r="F6" s="50"/>
-      <c r="G6" s="52" t="n">
+        <v>-7491.9</v>
+      </c>
+      <c r="F6" s="51"/>
+      <c r="G6" s="53" t="n">
         <f aca="false">E6-F6</f>
-        <v>-8409.9</v>
+        <v>-7491.9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="n">
+      <c r="A7" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="50" t="n">
+      <c r="B7" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I7</f>
-        <v>7182</v>
-      </c>
-      <c r="C7" s="50" t="n">
+        <v>8982</v>
+      </c>
+      <c r="C7" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R7</f>
-        <v>1796.85</v>
-      </c>
-      <c r="D7" s="50" t="n">
+        <v>2219.85</v>
+      </c>
+      <c r="D7" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U7</f>
         <v>12000</v>
       </c>
-      <c r="E7" s="51" t="n">
+      <c r="E7" s="52" t="n">
         <f aca="false">B7-C7-D7</f>
-        <v>-6614.85</v>
-      </c>
-      <c r="F7" s="50"/>
-      <c r="G7" s="52" t="n">
+        <v>-5237.85</v>
+      </c>
+      <c r="F7" s="51"/>
+      <c r="G7" s="53" t="n">
         <f aca="false">E7-F7</f>
-        <v>-6614.85</v>
+        <v>-5237.85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="n">
+      <c r="A8" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="50" t="n">
+      <c r="B8" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I8</f>
-        <v>10773</v>
-      </c>
-      <c r="C8" s="50" t="n">
+        <v>13473</v>
+      </c>
+      <c r="C8" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R8</f>
-        <v>2695.275</v>
-      </c>
-      <c r="D8" s="50" t="n">
+        <v>3329.775</v>
+      </c>
+      <c r="D8" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U8</f>
         <v>12000</v>
       </c>
-      <c r="E8" s="51" t="n">
+      <c r="E8" s="52" t="n">
         <f aca="false">B8-C8-D8</f>
-        <v>-3922.275</v>
-      </c>
-      <c r="F8" s="50"/>
-      <c r="G8" s="52" t="n">
+        <v>-1856.775</v>
+      </c>
+      <c r="F8" s="51"/>
+      <c r="G8" s="53" t="n">
         <f aca="false">E8-F8</f>
-        <v>-3922.275</v>
+        <v>-1856.775</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="n">
+      <c r="A9" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="50" t="n">
+      <c r="B9" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I9</f>
-        <v>23164</v>
-      </c>
-      <c r="C9" s="50" t="n">
+        <v>24967</v>
+      </c>
+      <c r="C9" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R9</f>
-        <v>9642.5</v>
-      </c>
-      <c r="D9" s="50" t="n">
+        <v>10156.025</v>
+      </c>
+      <c r="D9" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U9</f>
-        <v>16864.44</v>
-      </c>
-      <c r="E9" s="51" t="n">
+        <v>18116.915</v>
+      </c>
+      <c r="E9" s="52" t="n">
         <f aca="false">B9-C9-D9</f>
-        <v>-3342.94</v>
-      </c>
-      <c r="F9" s="50"/>
-      <c r="G9" s="52" t="n">
+        <v>-3305.94</v>
+      </c>
+      <c r="F9" s="51"/>
+      <c r="G9" s="53" t="n">
         <f aca="false">E9-F9</f>
-        <v>-3342.94</v>
+        <v>-3305.94</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="n">
+      <c r="A10" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="50" t="n">
+      <c r="B10" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I10</f>
-        <v>26755</v>
-      </c>
-      <c r="C10" s="50" t="n">
+        <v>29458</v>
+      </c>
+      <c r="C10" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R10</f>
-        <v>10540.925</v>
-      </c>
-      <c r="D10" s="50" t="n">
+        <v>11265.95</v>
+      </c>
+      <c r="D10" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U10</f>
-        <v>17618.55</v>
-      </c>
-      <c r="E10" s="51" t="n">
+        <v>19217.21</v>
+      </c>
+      <c r="E10" s="52" t="n">
         <f aca="false">B10-C10-D10</f>
-        <v>-1404.475</v>
-      </c>
-      <c r="F10" s="50"/>
-      <c r="G10" s="52" t="n">
+        <v>-1025.16</v>
+      </c>
+      <c r="F10" s="51"/>
+      <c r="G10" s="53" t="n">
         <f aca="false">E10-F10</f>
-        <v>-1404.475</v>
+        <v>-1025.16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="n">
+      <c r="A11" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="50" t="n">
+      <c r="B11" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I11</f>
-        <v>34148.5</v>
-      </c>
-      <c r="C11" s="50" t="n">
+        <v>35954.5</v>
+      </c>
+      <c r="C11" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R11</f>
-        <v>14214.5875</v>
-      </c>
-      <c r="D11" s="50" t="n">
+        <v>14903.9810602404</v>
+      </c>
+      <c r="D11" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U11</f>
-        <v>19171.185</v>
-      </c>
-      <c r="E11" s="51" t="n">
+        <v>20808.8525</v>
+      </c>
+      <c r="E11" s="52" t="n">
         <f aca="false">B11-C11-D11</f>
-        <v>762.727500000001</v>
-      </c>
-      <c r="F11" s="50"/>
-      <c r="G11" s="52" t="n">
+        <v>241.666439759618</v>
+      </c>
+      <c r="F11" s="51"/>
+      <c r="G11" s="53" t="n">
         <f aca="false">E11-F11</f>
-        <v>762.727500000001</v>
+        <v>241.666439759618</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="n">
+      <c r="A12" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="50" t="n">
+      <c r="B12" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I12</f>
-        <v>37739.5</v>
-      </c>
-      <c r="C12" s="50" t="n">
+        <v>40445.5</v>
+      </c>
+      <c r="C12" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R12</f>
-        <v>15261.5044237224</v>
-      </c>
-      <c r="D12" s="50" t="n">
+        <v>16173.831793221</v>
+      </c>
+      <c r="D12" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U12</f>
-        <v>19925.295</v>
-      </c>
-      <c r="E12" s="51" t="n">
+        <v>21909.1475</v>
+      </c>
+      <c r="E12" s="52" t="n">
         <f aca="false">B12-C12-D12</f>
-        <v>2552.70057627762</v>
-      </c>
-      <c r="F12" s="50"/>
-      <c r="G12" s="52" t="n">
+        <v>2362.52070677902</v>
+      </c>
+      <c r="F12" s="51"/>
+      <c r="G12" s="53" t="n">
         <f aca="false">E12-F12</f>
-        <v>2552.70057627762</v>
+        <v>2362.52070677902</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="n">
+      <c r="A13" s="50" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="50" t="n">
+      <c r="B13" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I13</f>
-        <v>45133</v>
-      </c>
-      <c r="C13" s="50" t="n">
+        <v>46942</v>
+      </c>
+      <c r="C13" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R13</f>
-        <v>19095.3934624697</v>
-      </c>
-      <c r="D13" s="50" t="n">
+        <v>19881.1182183489</v>
+      </c>
+      <c r="D13" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U13</f>
-        <v>21477.93</v>
-      </c>
-      <c r="E13" s="51" t="n">
+        <v>23500.79</v>
+      </c>
+      <c r="E13" s="52" t="n">
         <f aca="false">B13-C13-D13</f>
-        <v>4559.67653753027</v>
-      </c>
-      <c r="F13" s="50"/>
-      <c r="G13" s="52" t="n">
+        <v>3560.09178165106</v>
+      </c>
+      <c r="F13" s="51"/>
+      <c r="G13" s="53" t="n">
         <f aca="false">E13-F13</f>
-        <v>4559.67653753027</v>
+        <v>3560.09178165106</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49" t="n">
+      <c r="A14" s="50" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="50" t="n">
+      <c r="B14" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I14</f>
-        <v>58721</v>
-      </c>
-      <c r="C14" s="50" t="n">
+        <v>61430</v>
+      </c>
+      <c r="C14" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R14</f>
-        <v>26572.6768144747</v>
-      </c>
-      <c r="D14" s="50" t="n">
+        <v>27581.4994035207</v>
+      </c>
+      <c r="D14" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U14</f>
-        <v>24331.41</v>
-      </c>
-      <c r="E14" s="51" t="n">
+        <v>27050.35</v>
+      </c>
+      <c r="E14" s="52" t="n">
         <f aca="false">B14-C14-D14</f>
-        <v>7816.91318552533</v>
-      </c>
-      <c r="F14" s="50"/>
-      <c r="G14" s="52" t="n">
+        <v>6798.15059647932</v>
+      </c>
+      <c r="F14" s="51"/>
+      <c r="G14" s="53" t="n">
         <f aca="false">E14-F14</f>
-        <v>7816.91318552533</v>
+        <v>6798.15059647932</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49" t="n">
+      <c r="A15" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="50" t="n">
+      <c r="B15" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I15</f>
-        <v>56117.5</v>
-      </c>
-      <c r="C15" s="50" t="n">
+        <v>59426.5</v>
+      </c>
+      <c r="C15" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R15</f>
-        <v>23999.2462452295</v>
-      </c>
-      <c r="D15" s="50" t="n">
+        <v>25142.1186014796</v>
+      </c>
+      <c r="D15" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U15</f>
-        <v>23784.675</v>
-      </c>
-      <c r="E15" s="51" t="n">
+        <v>26559.4925</v>
+      </c>
+      <c r="E15" s="52" t="n">
         <f aca="false">B15-C15-D15</f>
-        <v>8333.57875477045</v>
-      </c>
-      <c r="F15" s="50"/>
-      <c r="G15" s="52" t="n">
+        <v>7724.8888985204</v>
+      </c>
+      <c r="F15" s="51"/>
+      <c r="G15" s="53" t="n">
         <f aca="false">E15-F15</f>
-        <v>8333.57875477045</v>
+        <v>7724.8888985204</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="49" t="n">
+      <c r="A16" s="50" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="50" t="n">
+      <c r="B16" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I16</f>
-        <v>69705.5</v>
-      </c>
-      <c r="C16" s="50" t="n">
+        <v>73914.5</v>
+      </c>
+      <c r="C16" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R16</f>
-        <v>31505.2431779817</v>
-      </c>
-      <c r="D16" s="50" t="n">
+        <v>32956.1812920729</v>
+      </c>
+      <c r="D16" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U16</f>
-        <v>26638.155</v>
-      </c>
-      <c r="E16" s="51" t="n">
+        <v>30109.0525</v>
+      </c>
+      <c r="E16" s="52" t="n">
         <f aca="false">B16-C16-D16</f>
-        <v>11562.1018220183</v>
-      </c>
-      <c r="F16" s="50"/>
-      <c r="G16" s="52" t="n">
+        <v>10849.2662079271</v>
+      </c>
+      <c r="F16" s="51"/>
+      <c r="G16" s="53" t="n">
         <f aca="false">E16-F16</f>
-        <v>11562.1018220183</v>
+        <v>10849.2662079271</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="n">
+      <c r="A17" s="50" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="50" t="n">
+      <c r="B17" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I17</f>
-        <v>62102.5</v>
-      </c>
-      <c r="C17" s="50" t="n">
+        <v>66911.5</v>
+      </c>
+      <c r="C17" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R17</f>
-        <v>25834.2526632565</v>
-      </c>
-      <c r="D17" s="50" t="n">
+        <v>27417.831764404</v>
+      </c>
+      <c r="D17" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U17</f>
-        <v>25041.525</v>
-      </c>
-      <c r="E17" s="51" t="n">
+        <v>28393.3175</v>
+      </c>
+      <c r="E17" s="52" t="n">
         <f aca="false">B17-C17-D17</f>
-        <v>11226.7223367435</v>
-      </c>
-      <c r="F17" s="50"/>
-      <c r="G17" s="52" t="n">
+        <v>11100.3507355959</v>
+      </c>
+      <c r="F17" s="51"/>
+      <c r="G17" s="53" t="n">
         <f aca="false">E17-F17</f>
-        <v>11226.7223367435</v>
+        <v>11100.3507355959</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="n">
+      <c r="A18" s="50" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="50" t="n">
+      <c r="B18" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I18</f>
-        <v>100684</v>
-      </c>
-      <c r="C18" s="50" t="n">
+        <v>104896</v>
+      </c>
+      <c r="C18" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R18</f>
-        <v>49617.013039618</v>
-      </c>
-      <c r="D18" s="50" t="n">
+        <v>51415.5763411467</v>
+      </c>
+      <c r="D18" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U18</f>
-        <v>33143.64</v>
-      </c>
-      <c r="E18" s="51" t="n">
+        <v>37699.52</v>
+      </c>
+      <c r="E18" s="52" t="n">
         <f aca="false">B18-C18-D18</f>
-        <v>17923.346960382</v>
-      </c>
-      <c r="F18" s="50"/>
-      <c r="G18" s="52" t="n">
+        <v>15780.9036588533</v>
+      </c>
+      <c r="F18" s="51"/>
+      <c r="G18" s="53" t="n">
         <f aca="false">E18-F18</f>
-        <v>17923.346960382</v>
+        <v>15780.9036588533</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="n">
+      <c r="A19" s="50" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="50" t="n">
+      <c r="B19" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I19</f>
-        <v>103078</v>
-      </c>
-      <c r="C19" s="50" t="n">
+        <v>109387</v>
+      </c>
+      <c r="C19" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R19</f>
-        <v>50678.801891933</v>
-      </c>
-      <c r="D19" s="50" t="n">
+        <v>53122.0010044143</v>
+      </c>
+      <c r="D19" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U19</f>
-        <v>33646.38</v>
-      </c>
-      <c r="E19" s="51" t="n">
+        <v>38799.815</v>
+      </c>
+      <c r="E19" s="52" t="n">
         <f aca="false">B19-C19-D19</f>
-        <v>18752.818108067</v>
-      </c>
-      <c r="F19" s="50"/>
-      <c r="G19" s="52" t="n">
+        <v>17465.1839955858</v>
+      </c>
+      <c r="F19" s="51"/>
+      <c r="G19" s="53" t="n">
         <f aca="false">E19-F19</f>
-        <v>18752.818108067</v>
+        <v>17465.1839955858</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="49" t="n">
+      <c r="A20" s="50" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="50" t="n">
+      <c r="B20" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I20</f>
-        <v>110471.5</v>
-      </c>
-      <c r="C20" s="50" t="n">
+        <v>120374.5</v>
+      </c>
+      <c r="C20" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R20</f>
-        <v>54824.4000516759</v>
-      </c>
-      <c r="D20" s="50" t="n">
+        <v>58240.5998046273</v>
+      </c>
+      <c r="D20" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U20</f>
-        <v>35199.015</v>
-      </c>
-      <c r="E20" s="51" t="n">
+        <v>41491.7525</v>
+      </c>
+      <c r="E20" s="52" t="n">
         <f aca="false">B20-C20-D20</f>
-        <v>20448.0849483241</v>
-      </c>
-      <c r="F20" s="50"/>
-      <c r="G20" s="52" t="n">
+        <v>20642.1476953727</v>
+      </c>
+      <c r="F20" s="51"/>
+      <c r="G20" s="53" t="n">
         <f aca="false">E20-F20</f>
-        <v>20448.0849483241</v>
+        <v>20642.1476953727</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="n">
+      <c r="A21" s="50" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="50" t="n">
+      <c r="B21" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I21</f>
-        <v>112865.5</v>
-      </c>
-      <c r="C21" s="50" t="n">
+        <v>126362.5</v>
+      </c>
+      <c r="C21" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R21</f>
-        <v>55737.1828766041</v>
-      </c>
-      <c r="D21" s="50" t="n">
+        <v>60218.418732278</v>
+      </c>
+      <c r="D21" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U21</f>
-        <v>35701.755</v>
-      </c>
-      <c r="E21" s="51" t="n">
+        <v>42958.8125</v>
+      </c>
+      <c r="E21" s="52" t="n">
         <f aca="false">B21-C21-D21</f>
-        <v>21426.5621233959</v>
-      </c>
-      <c r="F21" s="50"/>
-      <c r="G21" s="52" t="n">
+        <v>23185.268767722</v>
+      </c>
+      <c r="F21" s="51"/>
+      <c r="G21" s="53" t="n">
         <f aca="false">E21-F21</f>
-        <v>21426.5621233959</v>
+        <v>23185.268767722</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="49" t="n">
+      <c r="A22" s="50" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="50" t="n">
+      <c r="B22" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I22</f>
-        <v>120259</v>
-      </c>
-      <c r="C22" s="50" t="n">
+        <v>135853</v>
+      </c>
+      <c r="C22" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R22</f>
-        <v>59916.8317975888</v>
-      </c>
-      <c r="D22" s="50" t="n">
+        <v>65015.4930566303</v>
+      </c>
+      <c r="D22" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U22</f>
-        <v>37254.39</v>
-      </c>
-      <c r="E22" s="51" t="n">
+        <v>45283.985</v>
+      </c>
+      <c r="E22" s="52" t="n">
         <f aca="false">B22-C22-D22</f>
-        <v>23087.7782024112</v>
-      </c>
-      <c r="F22" s="50"/>
-      <c r="G22" s="52" t="n">
+        <v>25553.5219433697</v>
+      </c>
+      <c r="F22" s="51"/>
+      <c r="G22" s="53" t="n">
         <f aca="false">E22-F22</f>
-        <v>23087.7782024112</v>
+        <v>25553.5219433697</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49" t="n">
+      <c r="A23" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="50" t="n">
+      <c r="B23" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I23</f>
-        <v>122653</v>
-      </c>
-      <c r="C23" s="50" t="n">
+        <v>141841</v>
+      </c>
+      <c r="C23" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R23</f>
-        <v>60848.7212746378</v>
-      </c>
-      <c r="D23" s="50" t="n">
+        <v>66978.0271432991</v>
+      </c>
+      <c r="D23" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U23</f>
-        <v>37757.13</v>
-      </c>
-      <c r="E23" s="51" t="n">
+        <v>46751.045</v>
+      </c>
+      <c r="E23" s="52" t="n">
         <f aca="false">B23-C23-D23</f>
-        <v>24047.1487253622</v>
-      </c>
-      <c r="F23" s="50"/>
-      <c r="G23" s="52" t="n">
+        <v>28111.9278567009</v>
+      </c>
+      <c r="F23" s="51"/>
+      <c r="G23" s="53" t="n">
         <f aca="false">E23-F23</f>
-        <v>24047.1487253622</v>
+        <v>28111.9278567009</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="49" t="n">
+      <c r="A24" s="50" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="50" t="n">
+      <c r="B24" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I24</f>
-        <v>135044</v>
-      </c>
-      <c r="C24" s="50" t="n">
+        <v>157826</v>
+      </c>
+      <c r="C24" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R24</f>
-        <v>68407.3617410183</v>
-      </c>
-      <c r="D24" s="50" t="n">
+        <v>75702.6201264222</v>
+      </c>
+      <c r="D24" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U24</f>
-        <v>40359.24</v>
-      </c>
-      <c r="E24" s="51" t="n">
+        <v>50667.37</v>
+      </c>
+      <c r="E24" s="52" t="n">
         <f aca="false">B24-C24-D24</f>
-        <v>26277.3982589817</v>
-      </c>
-      <c r="F24" s="50"/>
-      <c r="G24" s="52" t="n">
+        <v>31456.0098735778</v>
+      </c>
+      <c r="F24" s="51"/>
+      <c r="G24" s="53" t="n">
         <f aca="false">E24-F24</f>
-        <v>26277.3982589817</v>
+        <v>31456.0098735778</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="49" t="n">
+      <c r="A25" s="50" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="50" t="n">
+      <c r="B25" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I25</f>
-        <v>137438</v>
-      </c>
-      <c r="C25" s="50" t="n">
+        <v>163814</v>
+      </c>
+      <c r="C25" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R25</f>
-        <v>69293.6477053512</v>
-      </c>
-      <c r="D25" s="50" t="n">
+        <v>77638.6039045085</v>
+      </c>
+      <c r="D25" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U25</f>
-        <v>40861.98</v>
-      </c>
-      <c r="E25" s="51" t="n">
+        <v>52134.43</v>
+      </c>
+      <c r="E25" s="52" t="n">
         <f aca="false">B25-C25-D25</f>
-        <v>27282.3722946488</v>
-      </c>
-      <c r="F25" s="50"/>
-      <c r="G25" s="52" t="n">
+        <v>34040.9660954915</v>
+      </c>
+      <c r="F25" s="51"/>
+      <c r="G25" s="53" t="n">
         <f aca="false">E25-F25</f>
-        <v>27282.3722946488</v>
+        <v>34040.9660954915</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="49" t="n">
+      <c r="A26" s="50" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="50" t="n">
+      <c r="B26" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I26</f>
-        <v>139832</v>
-      </c>
-      <c r="C26" s="50" t="n">
+        <v>169802</v>
+      </c>
+      <c r="C26" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R26</f>
-        <v>70144.195380357</v>
-      </c>
-      <c r="D26" s="50" t="n">
+        <v>79545.9307607052</v>
+      </c>
+      <c r="D26" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U26</f>
-        <v>41364.72</v>
-      </c>
-      <c r="E26" s="51" t="n">
+        <v>53601.49</v>
+      </c>
+      <c r="E26" s="52" t="n">
         <f aca="false">B26-C26-D26</f>
-        <v>28323.084619643</v>
-      </c>
-      <c r="F26" s="50"/>
-      <c r="G26" s="52" t="n">
+        <v>36654.5792392948</v>
+      </c>
+      <c r="F26" s="51"/>
+      <c r="G26" s="53" t="n">
         <f aca="false">E26-F26</f>
-        <v>28323.084619643</v>
+        <v>36654.5792392948</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="49" t="n">
+      <c r="A27" s="50" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="50" t="n">
+      <c r="B27" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I27</f>
-        <v>142226</v>
-      </c>
-      <c r="C27" s="50" t="n">
+        <v>174293</v>
+      </c>
+      <c r="C27" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R27</f>
-        <v>70959.0161541562</v>
-      </c>
-      <c r="D27" s="50" t="n">
+        <v>80993.1172054434</v>
+      </c>
+      <c r="D27" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U27</f>
-        <v>41867.46</v>
-      </c>
-      <c r="E27" s="51" t="n">
+        <v>54701.785</v>
+      </c>
+      <c r="E27" s="52" t="n">
         <f aca="false">B27-C27-D27</f>
-        <v>29399.5238458438</v>
-      </c>
-      <c r="F27" s="50"/>
-      <c r="G27" s="52" t="n">
+        <v>38598.0977945566</v>
+      </c>
+      <c r="F27" s="51"/>
+      <c r="G27" s="53" t="n">
         <f aca="false">E27-F27</f>
-        <v>29399.5238458438</v>
+        <v>38598.0977945566</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="49" t="n">
+      <c r="A28" s="50" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="50" t="n">
+      <c r="B28" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I28</f>
-        <v>139620.5</v>
-      </c>
-      <c r="C28" s="50" t="n">
+        <v>178275.5</v>
+      </c>
+      <c r="C28" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R28</f>
-        <v>68507.3775253362</v>
-      </c>
-      <c r="D28" s="50" t="n">
+        <v>80340.192334091</v>
+      </c>
+      <c r="D28" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U28</f>
-        <v>41320.305</v>
-      </c>
-      <c r="E28" s="51" t="n">
+        <v>55677.4975</v>
+      </c>
+      <c r="E28" s="52" t="n">
         <f aca="false">B28-C28-D28</f>
-        <v>29792.8174746638</v>
-      </c>
-      <c r="F28" s="50"/>
-      <c r="G28" s="52" t="n">
+        <v>42257.810165909</v>
+      </c>
+      <c r="F28" s="51"/>
+      <c r="G28" s="53" t="n">
         <f aca="false">E28-F28</f>
-        <v>29792.8174746638</v>
+        <v>42257.810165909</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49" t="n">
+      <c r="A29" s="50" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="50" t="n">
+      <c r="B29" s="51" t="n">
         <f aca="false">'Projeção Mensal'!I29</f>
-        <v>142014.5</v>
-      </c>
-      <c r="C29" s="50" t="n">
+        <v>182766.5</v>
+      </c>
+      <c r="C29" s="51" t="n">
         <f aca="false">'Projeção Mensal'!R29</f>
-        <v>69283.6107304242</v>
-      </c>
-      <c r="D29" s="50" t="n">
+        <v>81752.9190067688</v>
+      </c>
+      <c r="D29" s="51" t="n">
         <f aca="false">'Projeção Mensal'!U29</f>
-        <v>41823.045</v>
-      </c>
-      <c r="E29" s="51" t="n">
+        <v>56777.7925</v>
+      </c>
+      <c r="E29" s="52" t="n">
         <f aca="false">B29-C29-D29</f>
-        <v>30907.8442695758</v>
-      </c>
-      <c r="F29" s="50"/>
-      <c r="G29" s="52" t="n">
+        <v>44235.7884932312</v>
+      </c>
+      <c r="F29" s="51"/>
+      <c r="G29" s="53" t="n">
         <f aca="false">E29-F29</f>
-        <v>30907.8442695758</v>
+        <v>44235.7884932312</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="53" t="s">
-        <v>179</v>
-      </c>
-      <c r="B30" s="52" t="n">
+      <c r="A30" s="54" t="s">
+        <v>196</v>
+      </c>
+      <c r="B30" s="53" t="n">
         <f aca="false">SUM(B5:B29)</f>
-        <v>1942515.5</v>
-      </c>
-      <c r="C30" s="52" t="n">
+        <v>2233383.5</v>
+      </c>
+      <c r="C30" s="53" t="n">
         <f aca="false">SUM(C5:C29)</f>
-        <v>930574.514455835</v>
-      </c>
-      <c r="D30" s="52" t="n">
+        <v>1023471.56155362</v>
+      </c>
+      <c r="D30" s="53" t="n">
         <f aca="false">SUM(D5:D29)</f>
-        <v>691152.225</v>
-      </c>
-      <c r="E30" s="52" t="n">
+        <v>828210.4225</v>
+      </c>
+      <c r="E30" s="53" t="n">
         <f aca="false">SUM(E5:E29)</f>
-        <v>320788.760544165</v>
-      </c>
-      <c r="F30" s="52" t="n">
+        <v>381701.515946378</v>
+      </c>
+      <c r="F30" s="53" t="n">
         <f aca="false">SUM(F5:F29)</f>
         <v>102000</v>
       </c>
-      <c r="G30" s="52" t="n">
+      <c r="G30" s="53" t="n">
         <f aca="false">SUM(G5:G29)</f>
-        <v>218788.760544165</v>
+        <v>279701.515946378</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="54" t="s">
-        <v>224</v>
+      <c r="A32" s="55" t="s">
+        <v>242</v>
       </c>
     </row>
   </sheetData>
@@ -6633,906 +7012,906 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
-      <c r="H1" s="47"/>
+      <c r="A1" s="47" t="s">
+        <v>243</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
+      <c r="H1" s="48"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="48" t="s">
-        <v>226</v>
+      <c r="A2" s="49" t="s">
+        <v>244</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="17" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="B4" s="17" t="s">
-        <v>162</v>
+        <v>177</v>
       </c>
       <c r="C4" s="17" t="s">
-        <v>171</v>
+        <v>186</v>
       </c>
       <c r="D4" s="17" t="s">
-        <v>174</v>
+        <v>189</v>
       </c>
       <c r="E4" s="17" t="s">
-        <v>186</v>
+        <v>203</v>
       </c>
       <c r="F4" s="17" t="s">
-        <v>223</v>
+        <v>241</v>
       </c>
       <c r="G4" s="17" t="s">
-        <v>227</v>
+        <v>245</v>
       </c>
       <c r="H4" s="17" t="s">
-        <v>228</v>
+        <v>246</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="B5" s="51" t="n">
+      <c r="A5" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="51" t="n">
+      <c r="C5" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="51" t="n">
+      <c r="D5" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="51" t="n">
+      <c r="E5" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F5</f>
         <v>102000</v>
       </c>
-      <c r="F5" s="51" t="n">
+      <c r="F5" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G5</f>
         <v>-102000</v>
       </c>
-      <c r="G5" s="52" t="n">
+      <c r="G5" s="53" t="n">
         <f aca="false">F5</f>
         <v>-102000</v>
       </c>
-      <c r="H5" s="55" t="str">
+      <c r="H5" s="56" t="str">
         <f aca="false">IF(G5&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="49" t="n">
+      <c r="A6" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="51" t="n">
+      <c r="B6" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B6</f>
-        <v>4788</v>
-      </c>
-      <c r="C6" s="51" t="n">
+        <v>5988</v>
+      </c>
+      <c r="C6" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C6</f>
-        <v>1197.9</v>
-      </c>
-      <c r="D6" s="51" t="n">
+        <v>1479.9</v>
+      </c>
+      <c r="D6" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D6</f>
         <v>12000</v>
       </c>
-      <c r="E6" s="51" t="n">
+      <c r="E6" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="51" t="n">
+      <c r="F6" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G6</f>
-        <v>-8409.9</v>
-      </c>
-      <c r="G6" s="52" t="n">
+        <v>-7491.9</v>
+      </c>
+      <c r="G6" s="53" t="n">
         <f aca="false">G5+F6</f>
-        <v>-110409.9</v>
-      </c>
-      <c r="H6" s="55" t="str">
+        <v>-109491.9</v>
+      </c>
+      <c r="H6" s="56" t="str">
         <f aca="false">IF(G6&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="49" t="n">
+      <c r="A7" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="51" t="n">
+      <c r="B7" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B7</f>
-        <v>7182</v>
-      </c>
-      <c r="C7" s="51" t="n">
+        <v>8982</v>
+      </c>
+      <c r="C7" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C7</f>
-        <v>1796.85</v>
-      </c>
-      <c r="D7" s="51" t="n">
+        <v>2219.85</v>
+      </c>
+      <c r="D7" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D7</f>
         <v>12000</v>
       </c>
-      <c r="E7" s="51" t="n">
+      <c r="E7" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="51" t="n">
+      <c r="F7" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G7</f>
-        <v>-6614.85</v>
-      </c>
-      <c r="G7" s="52" t="n">
+        <v>-5237.85</v>
+      </c>
+      <c r="G7" s="53" t="n">
         <f aca="false">G6+F7</f>
-        <v>-117024.75</v>
-      </c>
-      <c r="H7" s="55" t="str">
+        <v>-114729.75</v>
+      </c>
+      <c r="H7" s="56" t="str">
         <f aca="false">IF(G7&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="49" t="n">
+      <c r="A8" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="51" t="n">
+      <c r="B8" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B8</f>
-        <v>10773</v>
-      </c>
-      <c r="C8" s="51" t="n">
+        <v>13473</v>
+      </c>
+      <c r="C8" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C8</f>
-        <v>2695.275</v>
-      </c>
-      <c r="D8" s="51" t="n">
+        <v>3329.775</v>
+      </c>
+      <c r="D8" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D8</f>
         <v>12000</v>
       </c>
-      <c r="E8" s="51" t="n">
+      <c r="E8" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="51" t="n">
+      <c r="F8" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G8</f>
-        <v>-3922.275</v>
-      </c>
-      <c r="G8" s="52" t="n">
+        <v>-1856.775</v>
+      </c>
+      <c r="G8" s="53" t="n">
         <f aca="false">G7+F8</f>
-        <v>-120947.025</v>
-      </c>
-      <c r="H8" s="55" t="str">
+        <v>-116586.525</v>
+      </c>
+      <c r="H8" s="56" t="str">
         <f aca="false">IF(G8&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="49" t="n">
+      <c r="A9" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="51" t="n">
+      <c r="B9" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B9</f>
-        <v>23164</v>
-      </c>
-      <c r="C9" s="51" t="n">
+        <v>24967</v>
+      </c>
+      <c r="C9" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C9</f>
-        <v>9642.5</v>
-      </c>
-      <c r="D9" s="51" t="n">
+        <v>10156.025</v>
+      </c>
+      <c r="D9" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D9</f>
-        <v>16864.44</v>
-      </c>
-      <c r="E9" s="51" t="n">
+        <v>18116.915</v>
+      </c>
+      <c r="E9" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="51" t="n">
+      <c r="F9" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G9</f>
-        <v>-3342.94</v>
-      </c>
-      <c r="G9" s="52" t="n">
+        <v>-3305.94</v>
+      </c>
+      <c r="G9" s="53" t="n">
         <f aca="false">G8+F9</f>
-        <v>-124289.965</v>
-      </c>
-      <c r="H9" s="55" t="str">
+        <v>-119892.465</v>
+      </c>
+      <c r="H9" s="56" t="str">
         <f aca="false">IF(G9&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="49" t="n">
+      <c r="A10" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="51" t="n">
+      <c r="B10" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B10</f>
-        <v>26755</v>
-      </c>
-      <c r="C10" s="51" t="n">
+        <v>29458</v>
+      </c>
+      <c r="C10" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C10</f>
-        <v>10540.925</v>
-      </c>
-      <c r="D10" s="51" t="n">
+        <v>11265.95</v>
+      </c>
+      <c r="D10" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D10</f>
-        <v>17618.55</v>
-      </c>
-      <c r="E10" s="51" t="n">
+        <v>19217.21</v>
+      </c>
+      <c r="E10" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="51" t="n">
+      <c r="F10" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G10</f>
-        <v>-1404.475</v>
-      </c>
-      <c r="G10" s="52" t="n">
+        <v>-1025.16</v>
+      </c>
+      <c r="G10" s="53" t="n">
         <f aca="false">G9+F10</f>
-        <v>-125694.44</v>
-      </c>
-      <c r="H10" s="55" t="str">
+        <v>-120917.625</v>
+      </c>
+      <c r="H10" s="56" t="str">
         <f aca="false">IF(G10&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="n">
+      <c r="A11" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="51" t="n">
+      <c r="B11" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B11</f>
-        <v>34148.5</v>
-      </c>
-      <c r="C11" s="51" t="n">
+        <v>35954.5</v>
+      </c>
+      <c r="C11" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C11</f>
-        <v>14214.5875</v>
-      </c>
-      <c r="D11" s="51" t="n">
+        <v>14903.9810602404</v>
+      </c>
+      <c r="D11" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D11</f>
-        <v>19171.185</v>
-      </c>
-      <c r="E11" s="51" t="n">
+        <v>20808.8525</v>
+      </c>
+      <c r="E11" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="51" t="n">
+      <c r="F11" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G11</f>
-        <v>762.727500000001</v>
-      </c>
-      <c r="G11" s="52" t="n">
+        <v>241.666439759618</v>
+      </c>
+      <c r="G11" s="53" t="n">
         <f aca="false">G10+F11</f>
-        <v>-124931.7125</v>
-      </c>
-      <c r="H11" s="55" t="str">
+        <v>-120675.95856024</v>
+      </c>
+      <c r="H11" s="56" t="str">
         <f aca="false">IF(G11&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="n">
+      <c r="A12" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="51" t="n">
+      <c r="B12" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B12</f>
-        <v>37739.5</v>
-      </c>
-      <c r="C12" s="51" t="n">
+        <v>40445.5</v>
+      </c>
+      <c r="C12" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C12</f>
-        <v>15261.5044237224</v>
-      </c>
-      <c r="D12" s="51" t="n">
+        <v>16173.831793221</v>
+      </c>
+      <c r="D12" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D12</f>
-        <v>19925.295</v>
-      </c>
-      <c r="E12" s="51" t="n">
+        <v>21909.1475</v>
+      </c>
+      <c r="E12" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="51" t="n">
+      <c r="F12" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G12</f>
-        <v>2552.70057627762</v>
-      </c>
-      <c r="G12" s="52" t="n">
+        <v>2362.52070677902</v>
+      </c>
+      <c r="G12" s="53" t="n">
         <f aca="false">G11+F12</f>
-        <v>-122379.011923722</v>
-      </c>
-      <c r="H12" s="55" t="str">
+        <v>-118313.437853461</v>
+      </c>
+      <c r="H12" s="56" t="str">
         <f aca="false">IF(G12&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="n">
+      <c r="A13" s="50" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="51" t="n">
+      <c r="B13" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B13</f>
-        <v>45133</v>
-      </c>
-      <c r="C13" s="51" t="n">
+        <v>46942</v>
+      </c>
+      <c r="C13" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C13</f>
-        <v>19095.3934624697</v>
-      </c>
-      <c r="D13" s="51" t="n">
+        <v>19881.1182183489</v>
+      </c>
+      <c r="D13" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D13</f>
-        <v>21477.93</v>
-      </c>
-      <c r="E13" s="51" t="n">
+        <v>23500.79</v>
+      </c>
+      <c r="E13" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="51" t="n">
+      <c r="F13" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G13</f>
-        <v>4559.67653753027</v>
-      </c>
-      <c r="G13" s="52" t="n">
+        <v>3560.09178165106</v>
+      </c>
+      <c r="G13" s="53" t="n">
         <f aca="false">G12+F13</f>
-        <v>-117819.335386192</v>
-      </c>
-      <c r="H13" s="55" t="str">
+        <v>-114753.34607181</v>
+      </c>
+      <c r="H13" s="56" t="str">
         <f aca="false">IF(G13&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49" t="n">
+      <c r="A14" s="50" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="51" t="n">
+      <c r="B14" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B14</f>
-        <v>58721</v>
-      </c>
-      <c r="C14" s="51" t="n">
+        <v>61430</v>
+      </c>
+      <c r="C14" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C14</f>
-        <v>26572.6768144747</v>
-      </c>
-      <c r="D14" s="51" t="n">
+        <v>27581.4994035207</v>
+      </c>
+      <c r="D14" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D14</f>
-        <v>24331.41</v>
-      </c>
-      <c r="E14" s="51" t="n">
+        <v>27050.35</v>
+      </c>
+      <c r="E14" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="51" t="n">
+      <c r="F14" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G14</f>
-        <v>7816.91318552533</v>
-      </c>
-      <c r="G14" s="52" t="n">
+        <v>6798.15059647932</v>
+      </c>
+      <c r="G14" s="53" t="n">
         <f aca="false">G13+F14</f>
-        <v>-110002.422200667</v>
-      </c>
-      <c r="H14" s="55" t="str">
+        <v>-107955.195475331</v>
+      </c>
+      <c r="H14" s="56" t="str">
         <f aca="false">IF(G14&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49" t="n">
+      <c r="A15" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="51" t="n">
+      <c r="B15" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B15</f>
-        <v>56117.5</v>
-      </c>
-      <c r="C15" s="51" t="n">
+        <v>59426.5</v>
+      </c>
+      <c r="C15" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C15</f>
-        <v>23999.2462452295</v>
-      </c>
-      <c r="D15" s="51" t="n">
+        <v>25142.1186014796</v>
+      </c>
+      <c r="D15" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D15</f>
-        <v>23784.675</v>
-      </c>
-      <c r="E15" s="51" t="n">
+        <v>26559.4925</v>
+      </c>
+      <c r="E15" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="51" t="n">
+      <c r="F15" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G15</f>
-        <v>8333.57875477045</v>
-      </c>
-      <c r="G15" s="52" t="n">
+        <v>7724.8888985204</v>
+      </c>
+      <c r="G15" s="53" t="n">
         <f aca="false">G14+F15</f>
-        <v>-101668.843445896</v>
-      </c>
-      <c r="H15" s="55" t="str">
+        <v>-100230.306576811</v>
+      </c>
+      <c r="H15" s="56" t="str">
         <f aca="false">IF(G15&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="49" t="n">
+      <c r="A16" s="50" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="51" t="n">
+      <c r="B16" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B16</f>
-        <v>69705.5</v>
-      </c>
-      <c r="C16" s="51" t="n">
+        <v>73914.5</v>
+      </c>
+      <c r="C16" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C16</f>
-        <v>31505.2431779817</v>
-      </c>
-      <c r="D16" s="51" t="n">
+        <v>32956.1812920729</v>
+      </c>
+      <c r="D16" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D16</f>
-        <v>26638.155</v>
-      </c>
-      <c r="E16" s="51" t="n">
+        <v>30109.0525</v>
+      </c>
+      <c r="E16" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="51" t="n">
+      <c r="F16" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G16</f>
-        <v>11562.1018220183</v>
-      </c>
-      <c r="G16" s="52" t="n">
+        <v>10849.2662079271</v>
+      </c>
+      <c r="G16" s="53" t="n">
         <f aca="false">G15+F16</f>
-        <v>-90106.741623878</v>
-      </c>
-      <c r="H16" s="55" t="str">
+        <v>-89381.0403688835</v>
+      </c>
+      <c r="H16" s="56" t="str">
         <f aca="false">IF(G16&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="n">
+      <c r="A17" s="50" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="51" t="n">
+      <c r="B17" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B17</f>
-        <v>62102.5</v>
-      </c>
-      <c r="C17" s="51" t="n">
+        <v>66911.5</v>
+      </c>
+      <c r="C17" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C17</f>
-        <v>25834.2526632565</v>
-      </c>
-      <c r="D17" s="51" t="n">
+        <v>27417.831764404</v>
+      </c>
+      <c r="D17" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D17</f>
-        <v>25041.525</v>
-      </c>
-      <c r="E17" s="51" t="n">
+        <v>28393.3175</v>
+      </c>
+      <c r="E17" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="51" t="n">
+      <c r="F17" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G17</f>
-        <v>11226.7223367435</v>
-      </c>
-      <c r="G17" s="52" t="n">
+        <v>11100.3507355959</v>
+      </c>
+      <c r="G17" s="53" t="n">
         <f aca="false">G16+F17</f>
-        <v>-78880.0192871346</v>
-      </c>
-      <c r="H17" s="55" t="str">
+        <v>-78280.6896332875</v>
+      </c>
+      <c r="H17" s="56" t="str">
         <f aca="false">IF(G17&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="n">
+      <c r="A18" s="50" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="51" t="n">
+      <c r="B18" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B18</f>
-        <v>100684</v>
-      </c>
-      <c r="C18" s="51" t="n">
+        <v>104896</v>
+      </c>
+      <c r="C18" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C18</f>
-        <v>49617.013039618</v>
-      </c>
-      <c r="D18" s="51" t="n">
+        <v>51415.5763411467</v>
+      </c>
+      <c r="D18" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D18</f>
-        <v>33143.64</v>
-      </c>
-      <c r="E18" s="51" t="n">
+        <v>37699.52</v>
+      </c>
+      <c r="E18" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F18</f>
         <v>0</v>
       </c>
-      <c r="F18" s="51" t="n">
+      <c r="F18" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G18</f>
-        <v>17923.346960382</v>
-      </c>
-      <c r="G18" s="52" t="n">
+        <v>15780.9036588533</v>
+      </c>
+      <c r="G18" s="53" t="n">
         <f aca="false">G17+F18</f>
-        <v>-60956.6723267525</v>
-      </c>
-      <c r="H18" s="55" t="str">
+        <v>-62499.7859744343</v>
+      </c>
+      <c r="H18" s="56" t="str">
         <f aca="false">IF(G18&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="n">
+      <c r="A19" s="50" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="51" t="n">
+      <c r="B19" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B19</f>
-        <v>103078</v>
-      </c>
-      <c r="C19" s="51" t="n">
+        <v>109387</v>
+      </c>
+      <c r="C19" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C19</f>
-        <v>50678.801891933</v>
-      </c>
-      <c r="D19" s="51" t="n">
+        <v>53122.0010044143</v>
+      </c>
+      <c r="D19" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D19</f>
-        <v>33646.38</v>
-      </c>
-      <c r="E19" s="51" t="n">
+        <v>38799.815</v>
+      </c>
+      <c r="E19" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F19</f>
         <v>0</v>
       </c>
-      <c r="F19" s="51" t="n">
+      <c r="F19" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G19</f>
-        <v>18752.818108067</v>
-      </c>
-      <c r="G19" s="52" t="n">
+        <v>17465.1839955858</v>
+      </c>
+      <c r="G19" s="53" t="n">
         <f aca="false">G18+F19</f>
-        <v>-42203.8542186856</v>
-      </c>
-      <c r="H19" s="55" t="str">
+        <v>-45034.6019788485</v>
+      </c>
+      <c r="H19" s="56" t="str">
         <f aca="false">IF(G19&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="49" t="n">
+      <c r="A20" s="50" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="51" t="n">
+      <c r="B20" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B20</f>
-        <v>110471.5</v>
-      </c>
-      <c r="C20" s="51" t="n">
+        <v>120374.5</v>
+      </c>
+      <c r="C20" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C20</f>
-        <v>54824.4000516759</v>
-      </c>
-      <c r="D20" s="51" t="n">
+        <v>58240.5998046273</v>
+      </c>
+      <c r="D20" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D20</f>
-        <v>35199.015</v>
-      </c>
-      <c r="E20" s="51" t="n">
+        <v>41491.7525</v>
+      </c>
+      <c r="E20" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F20</f>
         <v>0</v>
       </c>
-      <c r="F20" s="51" t="n">
+      <c r="F20" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G20</f>
-        <v>20448.0849483241</v>
-      </c>
-      <c r="G20" s="52" t="n">
+        <v>20642.1476953727</v>
+      </c>
+      <c r="G20" s="53" t="n">
         <f aca="false">G19+F20</f>
-        <v>-21755.7692703615</v>
-      </c>
-      <c r="H20" s="55" t="str">
+        <v>-24392.4542834758</v>
+      </c>
+      <c r="H20" s="56" t="str">
         <f aca="false">IF(G20&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="n">
+      <c r="A21" s="50" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="51" t="n">
+      <c r="B21" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B21</f>
-        <v>112865.5</v>
-      </c>
-      <c r="C21" s="51" t="n">
+        <v>126362.5</v>
+      </c>
+      <c r="C21" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C21</f>
-        <v>55737.1828766041</v>
-      </c>
-      <c r="D21" s="51" t="n">
+        <v>60218.418732278</v>
+      </c>
+      <c r="D21" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D21</f>
-        <v>35701.755</v>
-      </c>
-      <c r="E21" s="51" t="n">
+        <v>42958.8125</v>
+      </c>
+      <c r="E21" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F21</f>
         <v>0</v>
       </c>
-      <c r="F21" s="51" t="n">
+      <c r="F21" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G21</f>
-        <v>21426.5621233959</v>
-      </c>
-      <c r="G21" s="52" t="n">
+        <v>23185.268767722</v>
+      </c>
+      <c r="G21" s="53" t="n">
         <f aca="false">G20+F21</f>
-        <v>-329.207146965571</v>
-      </c>
-      <c r="H21" s="55" t="str">
+        <v>-1207.18551575377</v>
+      </c>
+      <c r="H21" s="56" t="str">
         <f aca="false">IF(G21&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="49" t="n">
+      <c r="A22" s="50" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="51" t="n">
+      <c r="B22" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B22</f>
-        <v>120259</v>
-      </c>
-      <c r="C22" s="51" t="n">
+        <v>135853</v>
+      </c>
+      <c r="C22" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C22</f>
-        <v>59916.8317975888</v>
-      </c>
-      <c r="D22" s="51" t="n">
+        <v>65015.4930566303</v>
+      </c>
+      <c r="D22" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D22</f>
-        <v>37254.39</v>
-      </c>
-      <c r="E22" s="51" t="n">
+        <v>45283.985</v>
+      </c>
+      <c r="E22" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F22</f>
         <v>0</v>
       </c>
-      <c r="F22" s="51" t="n">
+      <c r="F22" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G22</f>
-        <v>23087.7782024112</v>
-      </c>
-      <c r="G22" s="52" t="n">
+        <v>25553.5219433697</v>
+      </c>
+      <c r="G22" s="53" t="n">
         <f aca="false">G21+F22</f>
-        <v>22758.5710554456</v>
-      </c>
-      <c r="H22" s="55" t="str">
+        <v>24346.3364276159</v>
+      </c>
+      <c r="H22" s="56" t="str">
         <f aca="false">IF(G22&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49" t="n">
+      <c r="A23" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="51" t="n">
+      <c r="B23" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B23</f>
-        <v>122653</v>
-      </c>
-      <c r="C23" s="51" t="n">
+        <v>141841</v>
+      </c>
+      <c r="C23" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C23</f>
-        <v>60848.7212746378</v>
-      </c>
-      <c r="D23" s="51" t="n">
+        <v>66978.0271432991</v>
+      </c>
+      <c r="D23" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D23</f>
-        <v>37757.13</v>
-      </c>
-      <c r="E23" s="51" t="n">
+        <v>46751.045</v>
+      </c>
+      <c r="E23" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F23</f>
         <v>0</v>
       </c>
-      <c r="F23" s="51" t="n">
+      <c r="F23" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G23</f>
-        <v>24047.1487253622</v>
-      </c>
-      <c r="G23" s="52" t="n">
+        <v>28111.9278567009</v>
+      </c>
+      <c r="G23" s="53" t="n">
         <f aca="false">G22+F23</f>
-        <v>46805.7197808079</v>
-      </c>
-      <c r="H23" s="55" t="str">
+        <v>52458.2642843168</v>
+      </c>
+      <c r="H23" s="56" t="str">
         <f aca="false">IF(G23&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="49" t="n">
+      <c r="A24" s="50" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="51" t="n">
+      <c r="B24" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B24</f>
-        <v>135044</v>
-      </c>
-      <c r="C24" s="51" t="n">
+        <v>157826</v>
+      </c>
+      <c r="C24" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C24</f>
-        <v>68407.3617410183</v>
-      </c>
-      <c r="D24" s="51" t="n">
+        <v>75702.6201264222</v>
+      </c>
+      <c r="D24" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D24</f>
-        <v>40359.24</v>
-      </c>
-      <c r="E24" s="51" t="n">
+        <v>50667.37</v>
+      </c>
+      <c r="E24" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F24</f>
         <v>0</v>
       </c>
-      <c r="F24" s="51" t="n">
+      <c r="F24" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G24</f>
-        <v>26277.3982589817</v>
-      </c>
-      <c r="G24" s="52" t="n">
+        <v>31456.0098735778</v>
+      </c>
+      <c r="G24" s="53" t="n">
         <f aca="false">G23+F24</f>
-        <v>73083.1180397896</v>
-      </c>
-      <c r="H24" s="55" t="str">
+        <v>83914.2741578947</v>
+      </c>
+      <c r="H24" s="56" t="str">
         <f aca="false">IF(G24&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="49" t="n">
+      <c r="A25" s="50" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="51" t="n">
+      <c r="B25" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B25</f>
-        <v>137438</v>
-      </c>
-      <c r="C25" s="51" t="n">
+        <v>163814</v>
+      </c>
+      <c r="C25" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C25</f>
-        <v>69293.6477053512</v>
-      </c>
-      <c r="D25" s="51" t="n">
+        <v>77638.6039045085</v>
+      </c>
+      <c r="D25" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D25</f>
-        <v>40861.98</v>
-      </c>
-      <c r="E25" s="51" t="n">
+        <v>52134.43</v>
+      </c>
+      <c r="E25" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F25</f>
         <v>0</v>
       </c>
-      <c r="F25" s="51" t="n">
+      <c r="F25" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G25</f>
-        <v>27282.3722946488</v>
-      </c>
-      <c r="G25" s="52" t="n">
+        <v>34040.9660954915</v>
+      </c>
+      <c r="G25" s="53" t="n">
         <f aca="false">G24+F25</f>
-        <v>100365.490334438</v>
-      </c>
-      <c r="H25" s="55" t="str">
+        <v>117955.240253386</v>
+      </c>
+      <c r="H25" s="56" t="str">
         <f aca="false">IF(G25&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="49" t="n">
+      <c r="A26" s="50" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="51" t="n">
+      <c r="B26" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B26</f>
-        <v>139832</v>
-      </c>
-      <c r="C26" s="51" t="n">
+        <v>169802</v>
+      </c>
+      <c r="C26" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C26</f>
-        <v>70144.195380357</v>
-      </c>
-      <c r="D26" s="51" t="n">
+        <v>79545.9307607052</v>
+      </c>
+      <c r="D26" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D26</f>
-        <v>41364.72</v>
-      </c>
-      <c r="E26" s="51" t="n">
+        <v>53601.49</v>
+      </c>
+      <c r="E26" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F26</f>
         <v>0</v>
       </c>
-      <c r="F26" s="51" t="n">
+      <c r="F26" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G26</f>
-        <v>28323.084619643</v>
-      </c>
-      <c r="G26" s="52" t="n">
+        <v>36654.5792392948</v>
+      </c>
+      <c r="G26" s="53" t="n">
         <f aca="false">G25+F26</f>
-        <v>128688.574954081</v>
-      </c>
-      <c r="H26" s="55" t="str">
+        <v>154609.819492681</v>
+      </c>
+      <c r="H26" s="56" t="str">
         <f aca="false">IF(G26&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="49" t="n">
+      <c r="A27" s="50" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="51" t="n">
+      <c r="B27" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B27</f>
-        <v>142226</v>
-      </c>
-      <c r="C27" s="51" t="n">
+        <v>174293</v>
+      </c>
+      <c r="C27" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C27</f>
-        <v>70959.0161541562</v>
-      </c>
-      <c r="D27" s="51" t="n">
+        <v>80993.1172054434</v>
+      </c>
+      <c r="D27" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D27</f>
-        <v>41867.46</v>
-      </c>
-      <c r="E27" s="51" t="n">
+        <v>54701.785</v>
+      </c>
+      <c r="E27" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F27</f>
         <v>0</v>
       </c>
-      <c r="F27" s="51" t="n">
+      <c r="F27" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G27</f>
-        <v>29399.5238458438</v>
-      </c>
-      <c r="G27" s="52" t="n">
+        <v>38598.0977945566</v>
+      </c>
+      <c r="G27" s="53" t="n">
         <f aca="false">G26+F27</f>
-        <v>158088.098799925</v>
-      </c>
-      <c r="H27" s="55" t="str">
+        <v>193207.917287238</v>
+      </c>
+      <c r="H27" s="56" t="str">
         <f aca="false">IF(G27&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="49" t="n">
+      <c r="A28" s="50" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="51" t="n">
+      <c r="B28" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B28</f>
-        <v>139620.5</v>
-      </c>
-      <c r="C28" s="51" t="n">
+        <v>178275.5</v>
+      </c>
+      <c r="C28" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C28</f>
-        <v>68507.3775253362</v>
-      </c>
-      <c r="D28" s="51" t="n">
+        <v>80340.192334091</v>
+      </c>
+      <c r="D28" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D28</f>
-        <v>41320.305</v>
-      </c>
-      <c r="E28" s="51" t="n">
+        <v>55677.4975</v>
+      </c>
+      <c r="E28" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F28</f>
         <v>0</v>
       </c>
-      <c r="F28" s="51" t="n">
+      <c r="F28" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G28</f>
-        <v>29792.8174746638</v>
-      </c>
-      <c r="G28" s="52" t="n">
+        <v>42257.810165909</v>
+      </c>
+      <c r="G28" s="53" t="n">
         <f aca="false">G27+F28</f>
-        <v>187880.916274589</v>
-      </c>
-      <c r="H28" s="55" t="str">
+        <v>235465.727453147</v>
+      </c>
+      <c r="H28" s="56" t="str">
         <f aca="false">IF(G28&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49" t="n">
+      <c r="A29" s="50" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="51" t="n">
+      <c r="B29" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!B29</f>
-        <v>142014.5</v>
-      </c>
-      <c r="C29" s="51" t="n">
+        <v>182766.5</v>
+      </c>
+      <c r="C29" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!C29</f>
-        <v>69283.6107304242</v>
-      </c>
-      <c r="D29" s="51" t="n">
+        <v>81752.9190067688</v>
+      </c>
+      <c r="D29" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!D29</f>
-        <v>41823.045</v>
-      </c>
-      <c r="E29" s="51" t="n">
+        <v>56777.7925</v>
+      </c>
+      <c r="E29" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!F29</f>
         <v>0</v>
       </c>
-      <c r="F29" s="51" t="n">
+      <c r="F29" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G29</f>
-        <v>30907.8442695758</v>
-      </c>
-      <c r="G29" s="52" t="n">
+        <v>44235.7884932312</v>
+      </c>
+      <c r="G29" s="53" t="n">
         <f aca="false">G28+F29</f>
-        <v>218788.760544165</v>
-      </c>
-      <c r="H29" s="55" t="str">
+        <v>279701.515946378</v>
+      </c>
+      <c r="H29" s="56" t="str">
         <f aca="false">IF(G29&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>229</v>
-      </c>
-      <c r="B31" s="47"/>
-      <c r="C31" s="47"/>
-      <c r="D31" s="47"/>
-      <c r="E31" s="47"/>
-      <c r="F31" s="47"/>
-      <c r="G31" s="47"/>
+        <v>247</v>
+      </c>
+      <c r="B31" s="48"/>
+      <c r="C31" s="48"/>
+      <c r="D31" s="48"/>
+      <c r="E31" s="48"/>
+      <c r="F31" s="48"/>
+      <c r="G31" s="48"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>230</v>
-      </c>
-      <c r="F32" s="56" t="n">
+        <v>248</v>
+      </c>
+      <c r="F32" s="57" t="n">
         <f aca="false">MAX(0,-MIN(G5:G29))</f>
-        <v>125694.44</v>
-      </c>
-      <c r="G32" s="57" t="s">
-        <v>231</v>
+        <v>120917.625</v>
+      </c>
+      <c r="G32" s="58" t="s">
+        <v>249</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="F33" s="58" t="n">
+        <v>250</v>
+      </c>
+      <c r="F33" s="59" t="n">
         <f aca="false">IFERROR(INDEX(A5:A29,MATCH("Sim",H5:H29,0)),"Não recupera")</f>
         <v>17</v>
       </c>
-      <c r="G33" s="57" t="s">
-        <v>233</v>
+      <c r="G33" s="58" t="s">
+        <v>251</v>
       </c>
     </row>
   </sheetData>
@@ -7570,877 +7949,877 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="46" t="s">
-        <v>234</v>
-      </c>
-      <c r="B1" s="47"/>
-      <c r="C1" s="47"/>
-      <c r="D1" s="47"/>
-      <c r="E1" s="47"/>
-      <c r="F1" s="47"/>
-      <c r="G1" s="47"/>
+      <c r="A1" s="47" t="s">
+        <v>252</v>
+      </c>
+      <c r="B1" s="48"/>
+      <c r="C1" s="48"/>
+      <c r="D1" s="48"/>
+      <c r="E1" s="48"/>
+      <c r="F1" s="48"/>
+      <c r="G1" s="48"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="48" t="s">
-        <v>235</v>
+      <c r="A2" s="49" t="s">
+        <v>253</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>236</v>
-      </c>
-      <c r="B4" s="47"/>
-      <c r="C4" s="47"/>
-      <c r="D4" s="47"/>
-      <c r="E4" s="47"/>
-      <c r="F4" s="47"/>
-      <c r="G4" s="47"/>
+        <v>254</v>
+      </c>
+      <c r="B4" s="48"/>
+      <c r="C4" s="48"/>
+      <c r="D4" s="48"/>
+      <c r="E4" s="48"/>
+      <c r="F4" s="48"/>
+      <c r="G4" s="48"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>237</v>
-      </c>
-      <c r="B5" s="59" t="n">
+        <v>255</v>
+      </c>
+      <c r="B5" s="60" t="n">
         <f aca="false">'Premissas Precept'!B64</f>
         <v>0.24</v>
       </c>
-      <c r="C5" s="57" t="s">
-        <v>238</v>
+      <c r="C5" s="58" t="s">
+        <v>256</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>239</v>
-      </c>
-      <c r="B6" s="60" t="s">
-        <v>240</v>
-      </c>
-      <c r="C6" s="57" t="s">
-        <v>241</v>
+        <v>257</v>
+      </c>
+      <c r="B6" s="61" t="s">
+        <v>258</v>
+      </c>
+      <c r="C6" s="58" t="s">
+        <v>259</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>242</v>
-      </c>
-      <c r="B7" s="61" t="n">
+        <v>260</v>
+      </c>
+      <c r="B7" s="62" t="n">
         <f aca="false">IF(B6="Mensal",(1+B5)^(1/12)-1,B5)</f>
         <v>0.0180875824835107</v>
       </c>
-      <c r="C7" s="57" t="s">
-        <v>243</v>
+      <c r="C7" s="58" t="s">
+        <v>261</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>244</v>
-      </c>
-      <c r="B9" s="47"/>
-      <c r="C9" s="47"/>
-      <c r="D9" s="47"/>
-      <c r="E9" s="47"/>
-      <c r="F9" s="47"/>
-      <c r="G9" s="47"/>
+        <v>262</v>
+      </c>
+      <c r="B9" s="48"/>
+      <c r="C9" s="48"/>
+      <c r="D9" s="48"/>
+      <c r="E9" s="48"/>
+      <c r="F9" s="48"/>
+      <c r="G9" s="48"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A10" s="17" t="s">
-        <v>222</v>
+        <v>240</v>
       </c>
       <c r="B10" s="17" t="s">
-        <v>245</v>
+        <v>263</v>
       </c>
       <c r="C10" s="17" t="s">
-        <v>246</v>
+        <v>264</v>
       </c>
       <c r="D10" s="17" t="s">
-        <v>247</v>
+        <v>265</v>
       </c>
       <c r="E10" s="17" t="s">
-        <v>248</v>
+        <v>266</v>
       </c>
       <c r="F10" s="17" t="s">
-        <v>249</v>
+        <v>267</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="49" t="n">
-        <v>0</v>
-      </c>
-      <c r="B11" s="51" t="n">
+      <c r="A11" s="50" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G5</f>
         <v>-102000</v>
       </c>
-      <c r="C11" s="62" t="n">
+      <c r="C11" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A11</f>
         <v>1</v>
       </c>
-      <c r="D11" s="51" t="n">
+      <c r="D11" s="52" t="n">
         <f aca="false">B11*C11</f>
         <v>-102000</v>
       </c>
-      <c r="E11" s="52" t="n">
+      <c r="E11" s="53" t="n">
         <f aca="false">D11</f>
         <v>-102000</v>
       </c>
-      <c r="F11" s="55" t="str">
+      <c r="F11" s="56" t="str">
         <f aca="false">IF(E11&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="49" t="n">
+      <c r="A12" s="50" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="51" t="n">
+      <c r="B12" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G6</f>
-        <v>-8409.9</v>
-      </c>
-      <c r="C12" s="62" t="n">
+        <v>-7491.9</v>
+      </c>
+      <c r="C12" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A12</f>
         <v>0.982233765744016</v>
       </c>
-      <c r="D12" s="51" t="n">
+      <c r="D12" s="52" t="n">
         <f aca="false">B12*C12</f>
-        <v>-8260.4877465306</v>
-      </c>
-      <c r="E12" s="52" t="n">
+        <v>-7358.79714957759</v>
+      </c>
+      <c r="E12" s="53" t="n">
         <f aca="false">E11+D12</f>
-        <v>-110260.487746531</v>
-      </c>
-      <c r="F12" s="55" t="str">
+        <v>-109358.797149578</v>
+      </c>
+      <c r="F12" s="56" t="str">
         <f aca="false">IF(E12&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="49" t="n">
+      <c r="A13" s="50" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="51" t="n">
+      <c r="B13" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G7</f>
-        <v>-6614.85</v>
-      </c>
-      <c r="C13" s="62" t="n">
+        <v>-5237.85</v>
+      </c>
+      <c r="C13" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A13</f>
         <v>0.96478317056767</v>
       </c>
-      <c r="D13" s="51" t="n">
+      <c r="D13" s="52" t="n">
         <f aca="false">B13*C13</f>
-        <v>-6381.89595582955</v>
-      </c>
-      <c r="E13" s="52" t="n">
+        <v>-5053.38952995787</v>
+      </c>
+      <c r="E13" s="53" t="n">
         <f aca="false">E12+D13</f>
-        <v>-116642.38370236</v>
-      </c>
-      <c r="F13" s="55" t="str">
+        <v>-114412.186679535</v>
+      </c>
+      <c r="F13" s="56" t="str">
         <f aca="false">IF(E13&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="49" t="n">
+      <c r="A14" s="50" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="51" t="n">
+      <c r="B14" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G8</f>
-        <v>-3922.275</v>
-      </c>
-      <c r="C14" s="62" t="n">
+        <v>-1856.775</v>
+      </c>
+      <c r="C14" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A14</f>
         <v>0.947642606753134</v>
       </c>
-      <c r="D14" s="51" t="n">
+      <c r="D14" s="52" t="n">
         <f aca="false">B14*C14</f>
-        <v>-3716.91490540265</v>
-      </c>
-      <c r="E14" s="52" t="n">
+        <v>-1759.55910115405</v>
+      </c>
+      <c r="E14" s="53" t="n">
         <f aca="false">E13+D14</f>
-        <v>-120359.298607763</v>
-      </c>
-      <c r="F14" s="55" t="str">
+        <v>-116171.74578069</v>
+      </c>
+      <c r="F14" s="56" t="str">
         <f aca="false">IF(E14&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="49" t="n">
+      <c r="A15" s="50" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="51" t="n">
+      <c r="B15" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G9</f>
-        <v>-3342.94</v>
-      </c>
-      <c r="C15" s="62" t="n">
+        <v>-3305.94</v>
+      </c>
+      <c r="C15" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A15</f>
         <v>0.930806566210606</v>
       </c>
-      <c r="D15" s="51" t="n">
+      <c r="D15" s="52" t="n">
         <f aca="false">B15*C15</f>
-        <v>-3111.63050244808</v>
-      </c>
-      <c r="E15" s="52" t="n">
+        <v>-3077.19065949829</v>
+      </c>
+      <c r="E15" s="53" t="n">
         <f aca="false">E14+D15</f>
-        <v>-123470.929110211</v>
-      </c>
-      <c r="F15" s="55" t="str">
+        <v>-119248.936440188</v>
+      </c>
+      <c r="F15" s="56" t="str">
         <f aca="false">IF(E15&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="49" t="n">
+      <c r="A16" s="50" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="51" t="n">
+      <c r="B16" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G10</f>
-        <v>-1404.475</v>
-      </c>
-      <c r="C16" s="62" t="n">
+        <v>-1025.16</v>
+      </c>
+      <c r="C16" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A16</f>
         <v>0.9142696387083</v>
       </c>
-      <c r="D16" s="51" t="n">
+      <c r="D16" s="52" t="n">
         <f aca="false">B16*C16</f>
-        <v>-1284.06885082484</v>
-      </c>
-      <c r="E16" s="52" t="n">
+        <v>-937.272662818197</v>
+      </c>
+      <c r="E16" s="53" t="n">
         <f aca="false">E15+D16</f>
-        <v>-124754.997961036</v>
-      </c>
-      <c r="F16" s="55" t="str">
+        <v>-120186.209103006</v>
+      </c>
+      <c r="F16" s="56" t="str">
         <f aca="false">IF(E16&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="49" t="n">
+      <c r="A17" s="50" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="51" t="n">
+      <c r="B17" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G11</f>
-        <v>762.727500000001</v>
-      </c>
-      <c r="C17" s="62" t="n">
+        <v>241.666439759618</v>
+      </c>
+      <c r="C17" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A17</f>
         <v>0.898026510133874</v>
       </c>
-      <c r="D17" s="51" t="n">
+      <c r="D17" s="52" t="n">
         <f aca="false">B17*C17</f>
-        <v>684.949515008135</v>
-      </c>
-      <c r="E17" s="52" t="n">
+        <v>217.022869513808</v>
+      </c>
+      <c r="E17" s="53" t="n">
         <f aca="false">E16+D17</f>
-        <v>-124070.048446028</v>
-      </c>
-      <c r="F17" s="55" t="str">
+        <v>-119969.186233492</v>
+      </c>
+      <c r="F17" s="56" t="str">
         <f aca="false">IF(E17&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="49" t="n">
+      <c r="A18" s="50" t="n">
         <v>7</v>
       </c>
-      <c r="B18" s="51" t="n">
+      <c r="B18" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G12</f>
-        <v>2552.70057627762</v>
-      </c>
-      <c r="C18" s="62" t="n">
+        <v>2362.52070677902</v>
+      </c>
+      <c r="C18" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A18</f>
         <v>0.882071960786752</v>
       </c>
-      <c r="D18" s="51" t="n">
+      <c r="D18" s="52" t="n">
         <f aca="false">B18*C18</f>
-        <v>2251.66560261867</v>
-      </c>
-      <c r="E18" s="52" t="n">
+        <v>2083.91327222787</v>
+      </c>
+      <c r="E18" s="53" t="n">
         <f aca="false">E17+D18</f>
-        <v>-121818.382843409</v>
-      </c>
-      <c r="F18" s="55" t="str">
+        <v>-117885.272961264</v>
+      </c>
+      <c r="F18" s="56" t="str">
         <f aca="false">IF(E18&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="49" t="n">
+      <c r="A19" s="50" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="51" t="n">
+      <c r="B19" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G13</f>
-        <v>4559.67653753027</v>
-      </c>
-      <c r="C19" s="62" t="n">
+        <v>3560.09178165106</v>
+      </c>
+      <c r="C19" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A19</f>
         <v>0.866400863700779</v>
       </c>
-      <c r="D19" s="51" t="n">
+      <c r="D19" s="52" t="n">
         <f aca="false">B19*C19</f>
-        <v>3950.5076903124</v>
-      </c>
-      <c r="E19" s="52" t="n">
+        <v>3084.46659447652</v>
+      </c>
+      <c r="E19" s="53" t="n">
         <f aca="false">E18+D19</f>
-        <v>-117867.875153097</v>
-      </c>
-      <c r="F19" s="55" t="str">
+        <v>-114800.806366788</v>
+      </c>
+      <c r="F19" s="56" t="str">
         <f aca="false">IF(E19&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="49" t="n">
+      <c r="A20" s="50" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="51" t="n">
+      <c r="B20" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G14</f>
-        <v>7816.91318552533</v>
-      </c>
-      <c r="C20" s="62" t="n">
+        <v>6798.15059647932</v>
+      </c>
+      <c r="C20" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A20</f>
         <v>0.851008182996684</v>
       </c>
-      <c r="D20" s="51" t="n">
+      <c r="D20" s="52" t="n">
         <f aca="false">B20*C20</f>
-        <v>6652.25708665673</v>
-      </c>
-      <c r="E20" s="52" t="n">
+        <v>5785.28178684769</v>
+      </c>
+      <c r="E20" s="53" t="n">
         <f aca="false">E19+D20</f>
-        <v>-111215.61806644</v>
-      </c>
-      <c r="F20" s="55" t="str">
+        <v>-109015.52457994</v>
+      </c>
+      <c r="F20" s="56" t="str">
         <f aca="false">IF(E20&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="49" t="n">
+      <c r="A21" s="50" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="51" t="n">
+      <c r="B21" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G15</f>
-        <v>8333.57875477045</v>
-      </c>
-      <c r="C21" s="62" t="n">
+        <v>7724.8888985204</v>
+      </c>
+      <c r="C21" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A21</f>
         <v>0.835888972263805</v>
       </c>
-      <c r="D21" s="51" t="n">
+      <c r="D21" s="52" t="n">
         <f aca="false">B21*C21</f>
-        <v>6965.94658060456</v>
-      </c>
-      <c r="E21" s="52" t="n">
+        <v>6457.1494422363</v>
+      </c>
+      <c r="E21" s="53" t="n">
         <f aca="false">E20+D21</f>
-        <v>-104249.671485835</v>
-      </c>
-      <c r="F21" s="55" t="str">
+        <v>-102558.375137704</v>
+      </c>
+      <c r="F21" s="56" t="str">
         <f aca="false">IF(E21&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="49" t="n">
+      <c r="A22" s="50" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="51" t="n">
+      <c r="B22" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G16</f>
-        <v>11562.1018220183</v>
-      </c>
-      <c r="C22" s="62" t="n">
+        <v>10849.2662079271</v>
+      </c>
+      <c r="C22" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A22</f>
         <v>0.821038372970573</v>
       </c>
-      <c r="D22" s="51" t="n">
+      <c r="D22" s="52" t="n">
         <f aca="false">B22*C22</f>
-        <v>9492.92926807002</v>
-      </c>
-      <c r="E22" s="52" t="n">
+        <v>8907.66387528111</v>
+      </c>
+      <c r="E22" s="53" t="n">
         <f aca="false">E21+D22</f>
-        <v>-94756.7422177652</v>
-      </c>
-      <c r="F22" s="55" t="str">
+        <v>-93650.7112624227</v>
+      </c>
+      <c r="F22" s="56" t="str">
         <f aca="false">IF(E22&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="49" t="n">
+      <c r="A23" s="50" t="n">
         <v>12</v>
       </c>
-      <c r="B23" s="51" t="n">
+      <c r="B23" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G17</f>
-        <v>11226.7223367435</v>
-      </c>
-      <c r="C23" s="62" t="n">
+        <v>11100.3507355959</v>
+      </c>
+      <c r="C23" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A23</f>
         <v>0.806451612903225</v>
       </c>
-      <c r="D23" s="51" t="n">
+      <c r="D23" s="52" t="n">
         <f aca="false">B23*C23</f>
-        <v>9053.80833608344</v>
-      </c>
-      <c r="E23" s="52" t="n">
+        <v>8951.89575451286</v>
+      </c>
+      <c r="E23" s="53" t="n">
         <f aca="false">E22+D23</f>
-        <v>-85702.9338816818</v>
-      </c>
-      <c r="F23" s="55" t="str">
+        <v>-84698.8155079098</v>
+      </c>
+      <c r="F23" s="56" t="str">
         <f aca="false">IF(E23&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="49" t="n">
+      <c r="A24" s="50" t="n">
         <v>13</v>
       </c>
-      <c r="B24" s="51" t="n">
+      <c r="B24" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G18</f>
-        <v>17923.346960382</v>
-      </c>
-      <c r="C24" s="62" t="n">
+        <v>15780.9036588533</v>
+      </c>
+      <c r="C24" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A24</f>
         <v>0.79212400463227</v>
       </c>
-      <c r="D24" s="51" t="n">
+      <c r="D24" s="52" t="n">
         <f aca="false">B24*C24</f>
-        <v>14197.5133706714</v>
-      </c>
-      <c r="E24" s="52" t="n">
+        <v>12500.4326029669</v>
+      </c>
+      <c r="E24" s="53" t="n">
         <f aca="false">E23+D24</f>
-        <v>-71505.4205110103</v>
-      </c>
-      <c r="F24" s="55" t="str">
+        <v>-72198.382904943</v>
+      </c>
+      <c r="F24" s="56" t="str">
         <f aca="false">IF(E24&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="49" t="n">
+      <c r="A25" s="50" t="n">
         <v>14</v>
       </c>
-      <c r="B25" s="51" t="n">
+      <c r="B25" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G19</f>
-        <v>18752.818108067</v>
-      </c>
-      <c r="C25" s="62" t="n">
+        <v>17465.1839955858</v>
+      </c>
+      <c r="C25" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A25</f>
         <v>0.778050944006185</v>
       </c>
-      <c r="D25" s="51" t="n">
+      <c r="D25" s="52" t="n">
         <f aca="false">B25*C25</f>
-        <v>14590.6478317578</v>
-      </c>
-      <c r="E25" s="52" t="n">
+        <v>13588.8028950072</v>
+      </c>
+      <c r="E25" s="53" t="n">
         <f aca="false">E24+D25</f>
-        <v>-56914.7726792525</v>
-      </c>
-      <c r="F25" s="55" t="str">
+        <v>-58609.5800099357</v>
+      </c>
+      <c r="F25" s="56" t="str">
         <f aca="false">IF(E25&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="49" t="n">
+      <c r="A26" s="50" t="n">
         <v>15</v>
       </c>
-      <c r="B26" s="51" t="n">
+      <c r="B26" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G20</f>
-        <v>20448.0849483241</v>
-      </c>
-      <c r="C26" s="62" t="n">
+        <v>20642.1476953727</v>
+      </c>
+      <c r="C26" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A26</f>
         <v>0.764227908671882</v>
       </c>
-      <c r="D26" s="51" t="n">
+      <c r="D26" s="52" t="n">
         <f aca="false">B26*C26</f>
-        <v>15626.9971964027</v>
-      </c>
-      <c r="E26" s="52" t="n">
+        <v>15775.3053637308</v>
+      </c>
+      <c r="E26" s="53" t="n">
         <f aca="false">E25+D26</f>
-        <v>-41287.7754828498</v>
-      </c>
-      <c r="F26" s="55" t="str">
+        <v>-42834.274646205</v>
+      </c>
+      <c r="F26" s="56" t="str">
         <f aca="false">IF(E26&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="49" t="n">
+      <c r="A27" s="50" t="n">
         <v>16</v>
       </c>
-      <c r="B27" s="51" t="n">
+      <c r="B27" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G21</f>
-        <v>21426.5621233959</v>
-      </c>
-      <c r="C27" s="62" t="n">
+        <v>23185.268767722</v>
+      </c>
+      <c r="C27" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A27</f>
         <v>0.750650456621456</v>
       </c>
-      <c r="D27" s="51" t="n">
+      <c r="D27" s="52" t="n">
         <f aca="false">B27*C27</f>
-        <v>16083.8586417551</v>
-      </c>
-      <c r="E27" s="52" t="n">
+        <v>17404.0325873817</v>
+      </c>
+      <c r="E27" s="53" t="n">
         <f aca="false">E26+D27</f>
-        <v>-25203.9168410947</v>
-      </c>
-      <c r="F27" s="55" t="str">
+        <v>-25430.2420588232</v>
+      </c>
+      <c r="F27" s="56" t="str">
         <f aca="false">IF(E27&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="49" t="n">
+      <c r="A28" s="50" t="n">
         <v>17</v>
       </c>
-      <c r="B28" s="51" t="n">
+      <c r="B28" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G22</f>
-        <v>23087.7782024112</v>
-      </c>
-      <c r="C28" s="62" t="n">
+        <v>25553.5219433697</v>
+      </c>
+      <c r="C28" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A28</f>
         <v>0.737314224764758</v>
       </c>
-      <c r="D28" s="51" t="n">
+      <c r="D28" s="52" t="n">
         <f aca="false">B28*C28</f>
-        <v>17022.9472868515</v>
-      </c>
-      <c r="E28" s="52" t="n">
+        <v>18840.9752216848</v>
+      </c>
+      <c r="E28" s="53" t="n">
         <f aca="false">E27+D28</f>
-        <v>-8180.96955424323</v>
-      </c>
-      <c r="F28" s="55" t="str">
+        <v>-6589.2668371384</v>
+      </c>
+      <c r="F28" s="56" t="str">
         <f aca="false">IF(E28&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="49" t="n">
+      <c r="A29" s="50" t="n">
         <v>18</v>
       </c>
-      <c r="B29" s="51" t="n">
+      <c r="B29" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G23</f>
-        <v>24047.1487253622</v>
-      </c>
-      <c r="C29" s="62" t="n">
+        <v>28111.9278567009</v>
+      </c>
+      <c r="C29" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A29</f>
         <v>0.724214927527318</v>
       </c>
-      <c r="D29" s="51" t="n">
+      <c r="D29" s="52" t="n">
         <f aca="false">B29*C29</f>
-        <v>17415.3040713768</v>
-      </c>
-      <c r="E29" s="52" t="n">
+        <v>20359.0777953938</v>
+      </c>
+      <c r="E29" s="53" t="n">
         <f aca="false">E28+D29</f>
-        <v>9234.33451713362</v>
-      </c>
-      <c r="F29" s="55" t="str">
+        <v>13769.8109582554</v>
+      </c>
+      <c r="F29" s="56" t="str">
         <f aca="false">IF(E29&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="49" t="n">
+      <c r="A30" s="50" t="n">
         <v>19</v>
       </c>
-      <c r="B30" s="51" t="n">
+      <c r="B30" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G24</f>
-        <v>26277.3982589817</v>
-      </c>
-      <c r="C30" s="62" t="n">
+        <v>31456.0098735778</v>
+      </c>
+      <c r="C30" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A30</f>
         <v>0.711348355473187</v>
       </c>
-      <c r="D30" s="51" t="n">
+      <c r="D30" s="52" t="n">
         <f aca="false">B30*C30</f>
-        <v>18692.3840376406</v>
-      </c>
-      <c r="E30" s="52" t="n">
+        <v>22376.1808933179</v>
+      </c>
+      <c r="E30" s="53" t="n">
         <f aca="false">E29+D30</f>
-        <v>27926.7185547742</v>
-      </c>
-      <c r="F30" s="55" t="str">
+        <v>36145.9918515734</v>
+      </c>
+      <c r="F30" s="56" t="str">
         <f aca="false">IF(E30&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="49" t="n">
+      <c r="A31" s="50" t="n">
         <v>20</v>
       </c>
-      <c r="B31" s="51" t="n">
+      <c r="B31" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G25</f>
-        <v>27282.3722946488</v>
-      </c>
-      <c r="C31" s="62" t="n">
+        <v>34040.9660954915</v>
+      </c>
+      <c r="C31" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A31</f>
         <v>0.698710373952241</v>
       </c>
-      <c r="D31" s="51" t="n">
+      <c r="D31" s="52" t="n">
         <f aca="false">B31*C31</f>
-        <v>19062.4765482983</v>
-      </c>
-      <c r="E31" s="52" t="n">
+        <v>23784.7761502764</v>
+      </c>
+      <c r="E31" s="53" t="n">
         <f aca="false">E30+D31</f>
-        <v>46989.1951030726</v>
-      </c>
-      <c r="F31" s="55" t="str">
+        <v>59930.7680018498</v>
+      </c>
+      <c r="F31" s="56" t="str">
         <f aca="false">IF(E31&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="49" t="n">
+      <c r="A32" s="50" t="n">
         <v>21</v>
       </c>
-      <c r="B32" s="51" t="n">
+      <c r="B32" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G26</f>
-        <v>28323.084619643</v>
-      </c>
-      <c r="C32" s="62" t="n">
+        <v>36654.5792392948</v>
+      </c>
+      <c r="C32" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A32</f>
         <v>0.686296921771519</v>
       </c>
-      <c r="D32" s="51" t="n">
+      <c r="D32" s="52" t="n">
         <f aca="false">B32*C32</f>
-        <v>19438.0457895353</v>
-      </c>
-      <c r="E32" s="52" t="n">
+        <v>25155.9249007583</v>
+      </c>
+      <c r="E32" s="53" t="n">
         <f aca="false">E31+D32</f>
-        <v>66427.2408926079</v>
-      </c>
-      <c r="F32" s="55" t="str">
+        <v>85086.6929026081</v>
+      </c>
+      <c r="F32" s="56" t="str">
         <f aca="false">IF(E32&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="49" t="n">
+      <c r="A33" s="50" t="n">
         <v>22</v>
       </c>
-      <c r="B33" s="51" t="n">
+      <c r="B33" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G27</f>
-        <v>29399.5238458438</v>
-      </c>
-      <c r="C33" s="62" t="n">
+        <v>38598.0977945566</v>
+      </c>
+      <c r="C33" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A33</f>
         <v>0.674104009890165</v>
       </c>
-      <c r="D33" s="51" t="n">
+      <c r="D33" s="52" t="n">
         <f aca="false">B33*C33</f>
-        <v>19818.3369133448</v>
-      </c>
-      <c r="E33" s="52" t="n">
+        <v>26019.1324974433</v>
+      </c>
+      <c r="E33" s="53" t="n">
         <f aca="false">E32+D33</f>
-        <v>86245.5778059527</v>
-      </c>
-      <c r="F33" s="55" t="str">
+        <v>111105.825400051</v>
+      </c>
+      <c r="F33" s="56" t="str">
         <f aca="false">IF(E33&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="49" t="n">
+      <c r="A34" s="50" t="n">
         <v>23</v>
       </c>
-      <c r="B34" s="51" t="n">
+      <c r="B34" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G28</f>
-        <v>29792.8174746638</v>
-      </c>
-      <c r="C34" s="62" t="n">
+        <v>42257.810165909</v>
+      </c>
+      <c r="C34" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A34</f>
         <v>0.662127720137558</v>
       </c>
-      <c r="D34" s="51" t="n">
+      <c r="D34" s="52" t="n">
         <f aca="false">B34*C34</f>
-        <v>19726.6503109735</v>
-      </c>
-      <c r="E34" s="52" t="n">
+        <v>27980.067503159</v>
+      </c>
+      <c r="E34" s="53" t="n">
         <f aca="false">E33+D34</f>
-        <v>105972.228116926</v>
-      </c>
-      <c r="F34" s="55" t="str">
+        <v>139085.89290321</v>
+      </c>
+      <c r="F34" s="56" t="str">
         <f aca="false">IF(E34&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="49" t="n">
+      <c r="A35" s="50" t="n">
         <v>24</v>
       </c>
-      <c r="B35" s="51" t="n">
+      <c r="B35" s="52" t="n">
         <f aca="false">'Fluxo de Caixa'!G29</f>
-        <v>30907.8442695758</v>
-      </c>
-      <c r="C35" s="62" t="n">
+        <v>44235.7884932312</v>
+      </c>
+      <c r="C35" s="63" t="n">
         <f aca="false">1/(1+$B$7)^A35</f>
         <v>0.650364203954214</v>
       </c>
-      <c r="D35" s="51" t="n">
+      <c r="D35" s="52" t="n">
         <f aca="false">B35*C35</f>
-        <v>20101.3555343235</v>
-      </c>
-      <c r="E35" s="52" t="n">
+        <v>28769.3733696873</v>
+      </c>
+      <c r="E35" s="53" t="n">
         <f aca="false">E34+D35</f>
-        <v>126073.58365125</v>
-      </c>
-      <c r="F35" s="55" t="str">
+        <v>167855.266272898</v>
+      </c>
+      <c r="F35" s="56" t="str">
         <f aca="false">IF(E35&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>250</v>
-      </c>
-      <c r="B37" s="47"/>
-      <c r="C37" s="47"/>
-      <c r="D37" s="47"/>
-      <c r="E37" s="47"/>
-      <c r="F37" s="47"/>
-      <c r="G37" s="47"/>
+        <v>268</v>
+      </c>
+      <c r="B37" s="48"/>
+      <c r="C37" s="48"/>
+      <c r="D37" s="48"/>
+      <c r="E37" s="48"/>
+      <c r="F37" s="48"/>
+      <c r="G37" s="48"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>251</v>
-      </c>
-      <c r="B38" s="63" t="n">
+        <v>269</v>
+      </c>
+      <c r="B38" s="64" t="n">
         <f aca="false">SUM(D11:D35)</f>
-        <v>126073.58365125</v>
-      </c>
-      <c r="C38" s="64" t="str">
+        <v>167855.266272898</v>
+      </c>
+      <c r="C38" s="65" t="str">
         <f aca="false">IF(B38&gt;0,"VIÁVEL: o projeto gera mais do que a taxa exigida",IF(B38&lt;0,"INVIÁVEL: o projeto rende menos que a taxa exigida","EQUILÍBRIO: rende exatamente a taxa exigida"))</f>
         <v>VIÁVEL: o projeto gera mais do que a taxa exigida</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>252</v>
-      </c>
-      <c r="B39" s="65" t="n">
+        <v>270</v>
+      </c>
+      <c r="B39" s="66" t="n">
         <f aca="false">IFERROR(IRR(B11:B35),"Não calculável")</f>
-        <v>0.0615783311983349</v>
-      </c>
-      <c r="C39" s="64" t="str">
+        <v>0.0704388506259977</v>
+      </c>
+      <c r="C39" s="65" t="str">
         <f aca="false">IF(ISNUMBER(B39),IF(B39&gt;B7,"VIÁVEL: TIR maior que a taxa de desconto","INVIÁVEL: TIR menor ou igual à taxa de desconto"),"Sem TIR: o fluxo precisa ter valores negativos E positivos")</f>
         <v>VIÁVEL: TIR maior que a taxa de desconto</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>253</v>
-      </c>
-      <c r="B40" s="65" t="n">
+        <v>271</v>
+      </c>
+      <c r="B40" s="66" t="n">
         <f aca="false">IF(ISNUMBER(B39),IF(B6="Mensal",(1+B39)^12-1,B39),"Não calculável")</f>
-        <v>1.04844610560403</v>
-      </c>
-      <c r="C40" s="64" t="str">
+        <v>1.26330121466574</v>
+      </c>
+      <c r="C40" s="65" t="str">
         <f aca="false">"Compare com a taxa anual de "&amp;ROUND(B5*100,2)&amp;"%"</f>
         <v>Compare com a taxa anual de 24%</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>254</v>
-      </c>
-      <c r="B41" s="63" t="n">
+        <v>272</v>
+      </c>
+      <c r="B41" s="64" t="n">
         <f aca="false">'Fluxo de Caixa'!F5</f>
         <v>102000</v>
       </c>
-      <c r="C41" s="64" t="str">
+      <c r="C41" s="65" t="str">
         <f aca="false">IF(B41=0,"Atenção: informe o investimento no período 0 da aba Fluxo de Caixa","")</f>
         <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B42" s="65" t="n">
+        <v>273</v>
+      </c>
+      <c r="B42" s="66" t="n">
         <f aca="false">IF(B41=0,"-",B38/B41)</f>
-        <v>1.23601552599264</v>
-      </c>
-      <c r="C42" s="64" t="str">
+        <v>1.64563986542057</v>
+      </c>
+      <c r="C42" s="65" t="str">
         <f aca="false">"Para cada R$ 100 de investimento inicial, o projeto gera R$ "&amp;IF(ISNUMBER(B42),ROUND(B42*100,2),"-")&amp;" de VPL acima da taxa exigida"</f>
-        <v>Para cada R$ 100 de investimento inicial, o projeto gera R$ 123.6 de VPL acima da taxa exigida</v>
+        <v>Para cada R$ 100 de investimento inicial, o projeto gera R$ 164.56 de VPL acima da taxa exigida</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>232</v>
-      </c>
-      <c r="B43" s="66" t="n">
+        <v>250</v>
+      </c>
+      <c r="B43" s="67" t="n">
         <f aca="false">'Necessidade de Caixa e Payback'!F33</f>
         <v>17</v>
       </c>
-      <c r="C43" s="64" t="str">
+      <c r="C43" s="65" t="str">
         <f aca="false">"Período em que o saldo acumulado (sem descontar) fica positivo"</f>
         <v>Período em que o saldo acumulado (sem descontar) fica positivo</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>256</v>
-      </c>
-      <c r="B44" s="66" t="n">
+        <v>274</v>
+      </c>
+      <c r="B44" s="67" t="n">
         <f aca="false">IFERROR(INDEX(A11:A35,MATCH("Sim",F11:F35,0)),"Não recupera")</f>
         <v>18</v>
       </c>
-      <c r="C44" s="64" t="str">
+      <c r="C44" s="65" t="str">
         <f aca="false">"Período em que o VP acumulado fica positivo"</f>
         <v>Período em que o VP acumulado fica positivo</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B45" s="63" t="n">
+        <v>275</v>
+      </c>
+      <c r="B45" s="64" t="n">
         <f aca="false">'Necessidade de Caixa e Payback'!F32</f>
-        <v>125694.44</v>
-      </c>
-      <c r="C45" s="64" t="str">
+        <v>120917.625</v>
+      </c>
+      <c r="C45" s="65" t="str">
         <f aca="false">"Dinheiro que os sócios precisam ter para cobrir o pior momento"</f>
         <v>Dinheiro que os sócios precisam ter para cobrir o pior momento</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>258</v>
-      </c>
-      <c r="B47" s="47"/>
-      <c r="C47" s="47"/>
-      <c r="D47" s="47"/>
-      <c r="E47" s="47"/>
-      <c r="F47" s="47"/>
-      <c r="G47" s="47"/>
+        <v>276</v>
+      </c>
+      <c r="B47" s="48"/>
+      <c r="C47" s="48"/>
+      <c r="D47" s="48"/>
+      <c r="E47" s="48"/>
+      <c r="F47" s="48"/>
+      <c r="G47" s="48"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="67" t="s">
-        <v>259</v>
+      <c r="A48" s="68" t="s">
+        <v>277</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="67" t="s">
-        <v>260</v>
+      <c r="A49" s="68" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="67" t="s">
-        <v>261</v>
+      <c r="A50" s="68" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="67" t="s">
-        <v>262</v>
+      <c r="A51" s="68" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="67" t="s">
-        <v>263</v>
+      <c r="A52" s="68" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="67" t="s">
-        <v>264</v>
+      <c r="A53" s="68" t="s">
+        <v>282</v>
       </c>
     </row>
   </sheetData>

--- a/precept-financeiro/Memoria_de_Calculo_Precept.xlsx
+++ b/precept-financeiro/Memoria_de_Calculo_Precept.xlsx
@@ -223,7 +223,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="297" uniqueCount="283">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="298" uniqueCount="284">
   <si>
     <t xml:space="preserve">PLANILHA DE ANÁLISE FINANCEIRA – VPL, TIR E PAYBACK</t>
   </si>
@@ -342,28 +342,31 @@
     <t xml:space="preserve">Média ponderada dos dois planos.</t>
   </si>
   <si>
-    <t xml:space="preserve">Precept Sprint – imersão de 7 dias (R$, à vista)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preço definido pelo grupo: planejamento estratégico e tático em 7 dias imersivos. No ano 2, também vendido para escritórios fora da base Core (4 a 5 por mês), no modelo das imersões da G4.</t>
+    <t xml:space="preserve">Precept Sprint – planejamento de 7 dias (R$ por imersão)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Preço definido pelo grupo: planejamento estratégico e tático em 7 dias imersivos. Recebido no mês da venda (Pix ou cartão). No ano 2, também vendido para escritórios fora da base Core (4 a 5 por mês), no modelo das imersões da G4.</t>
   </si>
   <si>
     <t xml:space="preserve">Precept Scale – implementação (R$ por projeto)</t>
   </si>
   <si>
-    <t xml:space="preserve">Preço proposto para o início da operação: 3× o Sprint e ~R$ 5 mil/mês por 6 meses, abaixo de consultorias de gestão para PMEs (R$ 8–15 mil/mês). Cerca de 1% a 3% do faturamento anual de um escritório de R$ 1–4 mi.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcelas do Scale (meses de projeto)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Decisão do grupo: 6 parcelas, 1 pilar implementado por mês.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcela mensal do Scale (R$)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Preço do projeto ÷ número de parcelas.</t>
+    <t xml:space="preserve">Preço proposto para o início da operação: 3× o Sprint, equivalente a ~R$ 5 mil por mês de entrega, abaixo de consultorias de gestão para PMEs (R$ 8–15 mil/mês). Cerca de 1% a 3% do faturamento anual de um escritório de R$ 1–4 mi. Recebido no mês da venda (Pix ou cartão).</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Duração da implementação do Scale (meses)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Entrega em 6 meses, 1 pilar implementado por mês. O pagamento não depende da duração.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Recebimento do Sprint e do Scale</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Mês da venda</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Valor cheio no mês da venda: Pix à vista ou cartão parcelado pelo cliente, com a operadora antecipando o valor para a Precept.</t>
   </si>
   <si>
     <t xml:space="preserve">2. DESPESAS VARIÁVEIS</t>
@@ -378,7 +381,7 @@
     <t xml:space="preserve">Meio de pagamento – Pix, boleto e cartão (% da venda)</t>
   </si>
   <si>
-    <t xml:space="preserve">Asaas: Pix e boleto R$ 1,99 por cobrança; cartão à vista 2,99% + R$ 0,49 (asaas.com/precos-e-taxas). Média ponderada ≈ 2%.</t>
+    <t xml:space="preserve">Asaas: Pix e boleto R$ 1,99 por cobrança; cartão à vista 2,99% + R$ 0,49; parcelado em 2 a 6x 3,49% + R$ 0,49, mais a antecipação (asaas.com/precos-e-taxas). Média ponderada ≈ 2%, supondo a maioria dos pagamentos via Pix ou boleto.</t>
   </si>
   <si>
     <t xml:space="preserve">Comissão de parceiros (% da receita de Sprint e Scale)</t>
@@ -390,7 +393,7 @@
     <t xml:space="preserve">Especialistas na entrega (% da receita de Sprint e Scale)</t>
   </si>
   <si>
-    <t xml:space="preserve">Gestores e empresários experientes pagos por projeto: é o know-how que o pitch apresenta como diferencial.</t>
+    <t xml:space="preserve">Gestores e empresários experientes pagos por projeto: é o know-how que o pitch apresenta como diferencial. Lançado no mês da venda, junto com a receita (a despesa variável acompanha a venda, como pede a ficha).</t>
   </si>
   <si>
     <t xml:space="preserve">Deslocamento por Sprint (R$)</t>
@@ -399,10 +402,10 @@
     <t xml:space="preserve">Transporte e alimentação nos 7 dias de imersão na Grande SP.</t>
   </si>
   <si>
-    <t xml:space="preserve">Deslocamento por mês de Scale ativo (R$)</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Visitas mensais de acompanhamento no escritório do cliente.</t>
+    <t xml:space="preserve">Deslocamento por Scale vendido (R$)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">6 visitas mensais de acompanhamento no escritório do cliente (R$ 200 cada), lançadas no mês da venda.</t>
   </si>
   <si>
     <t xml:space="preserve">3. SIMPLES NACIONAL – ANEXO V (LC 123/2006)</t>
@@ -516,7 +519,7 @@
     <t xml:space="preserve">Retirada por sócio (% da receita bruta do mês)</t>
   </si>
   <si>
-    <t xml:space="preserve">Calibrado: maior % que mantém o break-even no mês 6 (faixa viável de ~3,0% a ~3,6% por sócio, com licenças e Core como base).</t>
+    <t xml:space="preserve">Mantém o break-even no mês 6, com todos os meses seguintes positivos (faixa viável de ~3,1% a ~4,1% por sócio). Igual para os 7 sócios.</t>
   </si>
   <si>
     <t xml:space="preserve">Mês em que a retirada começa</t>
@@ -741,10 +744,10 @@
     <t xml:space="preserve">Sprints vendidos</t>
   </si>
   <si>
-    <t xml:space="preserve">Scales iniciados</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Parcelas de Scale ativas</t>
+    <t xml:space="preserve">Scales vendidos</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Scales em execução (6 meses)</t>
   </si>
   <si>
     <t xml:space="preserve">Receita Core (R$)</t>
@@ -903,7 +906,7 @@
     <t xml:space="preserve">Sprint – imersão de 7 dias</t>
   </si>
   <si>
-    <t xml:space="preserve">Scale – parcelas mensais</t>
+    <t xml:space="preserve">Scale – implementação de 6 meses</t>
   </si>
   <si>
     <t xml:space="preserve">TOTAL DA RECEITA MENSAL (A)</t>
@@ -1285,7 +1288,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="69">
+  <cellXfs count="70">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -1351,6 +1354,10 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="167" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
+      <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="7" fillId="3" borderId="1" xfId="0" applyFont="true" applyBorder="true" applyAlignment="true" applyProtection="false">
       <alignment horizontal="general" vertical="center" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -2132,117 +2139,116 @@
       <c r="A12" s="11" t="s">
         <v>45</v>
       </c>
-      <c r="B12" s="15" t="n">
-        <f aca="false">B10/B11</f>
-        <v>4999.5</v>
+      <c r="B12" s="17" t="s">
+        <v>46</v>
       </c>
       <c r="C12" s="13" t="s">
-        <v>46</v>
+        <v>47</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A14" s="9" t="s">
-        <v>47</v>
+        <v>48</v>
       </c>
       <c r="B14" s="10"/>
       <c r="C14" s="10"/>
     </row>
     <row r="15" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A15" s="11" t="s">
-        <v>48</v>
+        <v>49</v>
       </c>
       <c r="B15" s="12" t="n">
         <v>90</v>
       </c>
       <c r="C15" s="13" t="s">
-        <v>49</v>
-      </c>
-    </row>
-    <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>50</v>
+      </c>
+    </row>
+    <row r="16" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A16" s="11" t="s">
-        <v>50</v>
+        <v>51</v>
       </c>
       <c r="B16" s="14" t="n">
         <v>0.02</v>
       </c>
       <c r="C16" s="13" t="s">
-        <v>51</v>
+        <v>52</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A17" s="11" t="s">
-        <v>52</v>
+        <v>53</v>
       </c>
       <c r="B17" s="14" t="n">
         <v>0.05</v>
       </c>
       <c r="C17" s="13" t="s">
-        <v>53</v>
-      </c>
-    </row>
-    <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+        <v>54</v>
+      </c>
+    </row>
+    <row r="18" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A18" s="11" t="s">
-        <v>54</v>
+        <v>55</v>
       </c>
       <c r="B18" s="14" t="n">
         <v>0.35</v>
       </c>
       <c r="C18" s="13" t="s">
-        <v>55</v>
+        <v>56</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A19" s="11" t="s">
-        <v>56</v>
+        <v>57</v>
       </c>
       <c r="B19" s="12" t="n">
         <v>600</v>
       </c>
       <c r="C19" s="13" t="s">
-        <v>57</v>
+        <v>58</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A20" s="11" t="s">
-        <v>58</v>
+        <v>59</v>
       </c>
       <c r="B20" s="12" t="n">
-        <v>200</v>
+        <v>1200</v>
       </c>
       <c r="C20" s="13" t="s">
-        <v>59</v>
+        <v>60</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A22" s="9" t="s">
-        <v>60</v>
+        <v>61</v>
       </c>
       <c r="B22" s="10"/>
       <c r="C22" s="10"/>
       <c r="D22" s="10"/>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="17" t="s">
-        <v>61</v>
-      </c>
-      <c r="B23" s="17" t="s">
+      <c r="A23" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="C23" s="17" t="s">
+      <c r="B23" s="18" t="s">
         <v>63</v>
       </c>
-      <c r="D23" s="17" t="s">
+      <c r="C23" s="18" t="s">
         <v>64</v>
       </c>
+      <c r="D23" s="18" t="s">
+        <v>65</v>
+      </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="18" t="s">
-        <v>65</v>
+      <c r="A24" s="19" t="s">
+        <v>66</v>
       </c>
       <c r="B24" s="12" t="n">
         <v>0</v>
       </c>
-      <c r="C24" s="19" t="n">
+      <c r="C24" s="20" t="n">
         <v>0.155</v>
       </c>
       <c r="D24" s="12" t="n">
@@ -2250,13 +2256,13 @@
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="18" t="s">
-        <v>66</v>
+      <c r="A25" s="19" t="s">
+        <v>67</v>
       </c>
       <c r="B25" s="12" t="n">
         <v>180000.01</v>
       </c>
-      <c r="C25" s="19" t="n">
+      <c r="C25" s="20" t="n">
         <v>0.18</v>
       </c>
       <c r="D25" s="12" t="n">
@@ -2264,13 +2270,13 @@
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="18" t="s">
-        <v>67</v>
+      <c r="A26" s="19" t="s">
+        <v>68</v>
       </c>
       <c r="B26" s="12" t="n">
         <v>360000.01</v>
       </c>
-      <c r="C26" s="19" t="n">
+      <c r="C26" s="20" t="n">
         <v>0.195</v>
       </c>
       <c r="D26" s="12" t="n">
@@ -2278,13 +2284,13 @@
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="18" t="s">
-        <v>68</v>
+      <c r="A27" s="19" t="s">
+        <v>69</v>
       </c>
       <c r="B27" s="12" t="n">
         <v>720000.01</v>
       </c>
-      <c r="C27" s="19" t="n">
+      <c r="C27" s="20" t="n">
         <v>0.205</v>
       </c>
       <c r="D27" s="12" t="n">
@@ -2292,13 +2298,13 @@
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="18" t="s">
-        <v>69</v>
+      <c r="A28" s="19" t="s">
+        <v>70</v>
       </c>
       <c r="B28" s="12" t="n">
         <v>1800000.01</v>
       </c>
-      <c r="C28" s="19" t="n">
+      <c r="C28" s="20" t="n">
         <v>0.23</v>
       </c>
       <c r="D28" s="12" t="n">
@@ -2306,13 +2312,13 @@
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="18" t="s">
-        <v>70</v>
+      <c r="A29" s="19" t="s">
+        <v>71</v>
       </c>
       <c r="B29" s="12" t="n">
         <v>3600000.01</v>
       </c>
-      <c r="C29" s="19" t="n">
+      <c r="C29" s="20" t="n">
         <v>0.305</v>
       </c>
       <c r="D29" s="12" t="n">
@@ -2320,614 +2326,614 @@
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="20" t="s">
-        <v>71</v>
+      <c r="A30" s="21" t="s">
+        <v>72</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A32" s="9" t="s">
-        <v>72</v>
+        <v>73</v>
       </c>
       <c r="B32" s="10"/>
       <c r="C32" s="10"/>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A33" s="11" t="s">
-        <v>73</v>
+        <v>74</v>
       </c>
       <c r="B33" s="12" t="n">
         <v>150</v>
       </c>
       <c r="C33" s="13" t="s">
-        <v>74</v>
+        <v>75</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A34" s="11" t="s">
-        <v>75</v>
+        <v>76</v>
       </c>
       <c r="B34" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C34" s="13" t="s">
-        <v>76</v>
+        <v>77</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A35" s="11" t="s">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="B35" s="12" t="n">
         <v>400</v>
       </c>
       <c r="C35" s="13" t="s">
-        <v>78</v>
+        <v>79</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A36" s="11" t="s">
-        <v>79</v>
+        <v>80</v>
       </c>
       <c r="B36" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C36" s="13" t="s">
-        <v>80</v>
+        <v>81</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A37" s="11" t="s">
-        <v>81</v>
+        <v>82</v>
       </c>
       <c r="B37" s="12" t="n">
         <v>200</v>
       </c>
       <c r="C37" s="13" t="s">
-        <v>82</v>
+        <v>83</v>
       </c>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A38" s="11" t="s">
-        <v>83</v>
+        <v>84</v>
       </c>
       <c r="B38" s="12" t="n">
         <v>3500</v>
       </c>
       <c r="C38" s="13" t="s">
-        <v>84</v>
+        <v>85</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A39" s="11" t="s">
-        <v>85</v>
+        <v>86</v>
       </c>
       <c r="B39" s="12" t="n">
         <v>1500</v>
       </c>
       <c r="C39" s="13" t="s">
-        <v>86</v>
+        <v>87</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A40" s="11" t="s">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="B40" s="12" t="n">
         <v>5000</v>
       </c>
       <c r="C40" s="13" t="s">
-        <v>88</v>
+        <v>89</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A41" s="11" t="s">
-        <v>89</v>
+        <v>90</v>
       </c>
       <c r="B41" s="12" t="n">
         <v>1250</v>
       </c>
       <c r="C41" s="13" t="s">
-        <v>90</v>
+        <v>91</v>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="21" t="s">
-        <v>91</v>
-      </c>
-      <c r="B42" s="22" t="n">
+      <c r="A42" s="22" t="s">
+        <v>92</v>
+      </c>
+      <c r="B42" s="23" t="n">
         <f aca="false">SUM(B33:B41)</f>
         <v>12000</v>
       </c>
       <c r="C42" s="13" t="s">
-        <v>92</v>
+        <v>93</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A44" s="9" t="s">
-        <v>93</v>
+        <v>94</v>
       </c>
       <c r="B44" s="10"/>
       <c r="C44" s="10"/>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A45" s="11" t="s">
-        <v>94</v>
+        <v>95</v>
       </c>
       <c r="B45" s="16" t="n">
         <v>7</v>
       </c>
       <c r="C45" s="13" t="s">
-        <v>95</v>
+        <v>96</v>
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A46" s="11" t="s">
-        <v>96</v>
+        <v>97</v>
       </c>
       <c r="B46" s="14" t="n">
         <v>0.035</v>
       </c>
       <c r="C46" s="13" t="s">
-        <v>97</v>
+        <v>98</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A47" s="11" t="s">
-        <v>98</v>
+        <v>99</v>
       </c>
       <c r="B47" s="16" t="n">
         <v>4</v>
       </c>
       <c r="C47" s="13" t="s">
-        <v>99</v>
+        <v>100</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A48" s="11" t="s">
-        <v>100</v>
-      </c>
-      <c r="B48" s="23" t="n">
+        <v>101</v>
+      </c>
+      <c r="B48" s="24" t="n">
         <f aca="false">B45*B46</f>
         <v>0.245</v>
       </c>
       <c r="C48" s="13" t="s">
-        <v>101</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A50" s="9" t="s">
-        <v>102</v>
+        <v>103</v>
       </c>
       <c r="B50" s="10"/>
       <c r="C50" s="10"/>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A51" s="11" t="s">
-        <v>103</v>
+        <v>104</v>
       </c>
       <c r="B51" s="12" t="n">
         <v>12000</v>
       </c>
       <c r="C51" s="13" t="s">
-        <v>104</v>
+        <v>105</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A52" s="11" t="s">
-        <v>105</v>
+        <v>106</v>
       </c>
       <c r="B52" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C52" s="13" t="s">
-        <v>106</v>
+        <v>107</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A53" s="11" t="s">
-        <v>107</v>
+        <v>108</v>
       </c>
       <c r="B53" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C53" s="13" t="s">
-        <v>108</v>
+        <v>109</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A54" s="11" t="s">
-        <v>109</v>
+        <v>110</v>
       </c>
       <c r="B54" s="12" t="n">
         <v>2500</v>
       </c>
       <c r="C54" s="13" t="s">
-        <v>110</v>
+        <v>111</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A55" s="11" t="s">
-        <v>111</v>
+        <v>112</v>
       </c>
       <c r="B55" s="12" t="n">
         <v>0</v>
       </c>
       <c r="C55" s="13" t="s">
-        <v>112</v>
+        <v>113</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A56" s="11" t="s">
-        <v>113</v>
+        <v>114</v>
       </c>
       <c r="B56" s="12" t="n">
         <v>57000</v>
       </c>
       <c r="C56" s="13" t="s">
-        <v>114</v>
+        <v>115</v>
       </c>
     </row>
     <row r="57" customFormat="false" ht="22.35" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A57" s="11" t="s">
-        <v>115</v>
+        <v>116</v>
       </c>
       <c r="B57" s="12" t="n">
         <v>30500</v>
       </c>
       <c r="C57" s="13" t="s">
-        <v>116</v>
+        <v>117</v>
       </c>
     </row>
     <row r="58" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A58" s="21" t="s">
-        <v>117</v>
-      </c>
-      <c r="B58" s="22" t="n">
+      <c r="A58" s="22" t="s">
+        <v>118</v>
+      </c>
+      <c r="B58" s="23" t="n">
         <f aca="false">SUM(B51:B57)</f>
         <v>102000</v>
       </c>
       <c r="C58" s="13" t="s">
-        <v>118</v>
+        <v>119</v>
       </c>
     </row>
     <row r="59" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A59" s="11" t="s">
-        <v>119</v>
+        <v>120</v>
       </c>
       <c r="B59" s="12" t="n">
         <v>150000</v>
       </c>
       <c r="C59" s="13" t="s">
-        <v>120</v>
+        <v>121</v>
       </c>
     </row>
     <row r="61" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A61" s="9" t="s">
-        <v>121</v>
+        <v>122</v>
       </c>
       <c r="B61" s="10"/>
       <c r="C61" s="10"/>
     </row>
     <row r="62" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A62" s="11" t="s">
-        <v>122</v>
-      </c>
-      <c r="B62" s="24" t="n">
+        <v>123</v>
+      </c>
+      <c r="B62" s="25" t="n">
         <v>0.1365</v>
       </c>
       <c r="C62" s="13" t="s">
-        <v>123</v>
+        <v>124</v>
       </c>
     </row>
     <row r="63" customFormat="false" ht="32.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A63" s="11" t="s">
-        <v>124</v>
-      </c>
-      <c r="B63" s="24" t="n">
+        <v>125</v>
+      </c>
+      <c r="B63" s="25" t="n">
         <v>0.1035</v>
       </c>
       <c r="C63" s="13" t="s">
-        <v>125</v>
+        <v>126</v>
       </c>
     </row>
     <row r="64" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A64" s="21" t="s">
-        <v>126</v>
-      </c>
-      <c r="B64" s="25" t="n">
+      <c r="A64" s="22" t="s">
+        <v>127</v>
+      </c>
+      <c r="B64" s="26" t="n">
         <f aca="false">B62+B63</f>
         <v>0.24</v>
       </c>
       <c r="C64" s="13" t="s">
-        <v>127</v>
+        <v>128</v>
       </c>
     </row>
     <row r="66" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A66" s="9" t="s">
-        <v>128</v>
+        <v>129</v>
       </c>
       <c r="B66" s="10"/>
       <c r="C66" s="10"/>
     </row>
     <row r="67" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A67" s="21" t="s">
-        <v>129</v>
-      </c>
-      <c r="B67" s="26" t="n">
+      <c r="A67" s="22" t="s">
+        <v>130</v>
+      </c>
+      <c r="B67" s="27" t="n">
         <f aca="false">(B59-B58)/B42</f>
         <v>4</v>
       </c>
       <c r="C67" s="13" t="s">
-        <v>130</v>
+        <v>131</v>
       </c>
     </row>
     <row r="68" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A68" s="21" t="s">
-        <v>131</v>
-      </c>
-      <c r="B68" s="27" t="n">
+      <c r="A68" s="22" t="s">
+        <v>132</v>
+      </c>
+      <c r="B68" s="28" t="n">
         <f aca="false">IFERROR(INDEX('Projeção Mensal'!A6:A29,MATCH("Sim",'Projeção Mensal'!X6:X29,0)),"Não atinge")</f>
         <v>6</v>
       </c>
       <c r="C68" s="13" t="s">
-        <v>132</v>
+        <v>133</v>
       </c>
     </row>
     <row r="69" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A69" s="21" t="s">
-        <v>133</v>
-      </c>
-      <c r="B69" s="28" t="n">
+      <c r="A69" s="22" t="s">
+        <v>134</v>
+      </c>
+      <c r="B69" s="29" t="n">
         <f aca="false">'Necessidade de Caixa e Payback'!F32</f>
         <v>120917.625</v>
       </c>
       <c r="C69" s="13" t="s">
-        <v>134</v>
+        <v>135</v>
       </c>
     </row>
     <row r="70" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A70" s="21" t="s">
-        <v>135</v>
-      </c>
-      <c r="B70" s="28" t="n">
+      <c r="A70" s="22" t="s">
+        <v>136</v>
+      </c>
+      <c r="B70" s="29" t="n">
         <f aca="false">B59-B69</f>
         <v>29082.375</v>
       </c>
       <c r="C70" s="13" t="s">
-        <v>136</v>
+        <v>137</v>
       </c>
     </row>
     <row r="71" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A71" s="21" t="s">
-        <v>137</v>
-      </c>
-      <c r="B71" s="28" t="n">
+      <c r="A71" s="22" t="s">
+        <v>138</v>
+      </c>
+      <c r="B71" s="29" t="n">
         <f aca="false">'VPL e TIR'!B38</f>
-        <v>167855.266272898</v>
+        <v>172527.17474949</v>
       </c>
       <c r="C71" s="13" t="s">
-        <v>138</v>
+        <v>139</v>
       </c>
     </row>
     <row r="72" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A72" s="21" t="s">
-        <v>139</v>
-      </c>
-      <c r="B72" s="29" t="n">
+      <c r="A72" s="22" t="s">
+        <v>140</v>
+      </c>
+      <c r="B72" s="30" t="n">
         <f aca="false">'VPL e TIR'!B40</f>
-        <v>1.26330121466574</v>
+        <v>1.31180138851585</v>
       </c>
       <c r="C72" s="13" t="s">
-        <v>140</v>
+        <v>141</v>
       </c>
     </row>
     <row r="73" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A73" s="21" t="s">
-        <v>141</v>
-      </c>
-      <c r="B73" s="30" t="n">
+      <c r="A73" s="22" t="s">
+        <v>142</v>
+      </c>
+      <c r="B73" s="31" t="n">
         <f aca="false">'VPL e TIR'!B43</f>
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="C73" s="13" t="s">
-        <v>142</v>
+        <v>143</v>
       </c>
     </row>
     <row r="74" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A74" s="21" t="s">
-        <v>143</v>
-      </c>
-      <c r="B74" s="30" t="n">
+      <c r="A74" s="22" t="s">
+        <v>144</v>
+      </c>
+      <c r="B74" s="31" t="n">
         <f aca="false">'VPL e TIR'!B44</f>
         <v>18</v>
       </c>
       <c r="C74" s="13" t="s">
-        <v>144</v>
+        <v>145</v>
       </c>
     </row>
     <row r="75" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A75" s="21" t="s">
-        <v>145</v>
-      </c>
-      <c r="B75" s="28" t="n">
+      <c r="A75" s="22" t="s">
+        <v>146</v>
+      </c>
+      <c r="B75" s="29" t="n">
         <f aca="false">AVERAGE('Projeção Mensal'!W18:W29)</f>
-        <v>5149.34875</v>
+        <v>5178.5125</v>
       </c>
       <c r="C75" s="13" t="s">
-        <v>146</v>
+        <v>147</v>
       </c>
     </row>
     <row r="77" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A77" s="9" t="s">
-        <v>147</v>
+        <v>148</v>
       </c>
       <c r="B77" s="10"/>
       <c r="C77" s="10"/>
     </row>
     <row r="78" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A78" s="17" t="s">
-        <v>148</v>
-      </c>
-      <c r="B78" s="17" t="s">
+      <c r="A78" s="18" t="s">
         <v>149</v>
       </c>
-      <c r="C78" s="17" t="s">
+      <c r="B78" s="18" t="s">
         <v>150</v>
       </c>
+      <c r="C78" s="18" t="s">
+        <v>151</v>
+      </c>
     </row>
     <row r="79" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A79" s="31" t="n">
+      <c r="A79" s="32" t="n">
         <v>0.2</v>
       </c>
       <c r="B79" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A79)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>182484.377767326</v>
-      </c>
-      <c r="C79" s="32" t="str">
+        <v>187211.829922097</v>
+      </c>
+      <c r="C79" s="33" t="str">
         <f aca="false">IF(B79&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
         <v>Viável a esta taxa</v>
       </c>
     </row>
     <row r="80" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A80" s="31" t="n">
+      <c r="A80" s="32" t="n">
         <v>0.24</v>
       </c>
       <c r="B80" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A80)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>167855.266272898</v>
-      </c>
-      <c r="C80" s="32" t="str">
+        <v>172527.17474949</v>
+      </c>
+      <c r="C80" s="33" t="str">
         <f aca="false">IF(B80&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
         <v>Viável a esta taxa</v>
       </c>
     </row>
     <row r="81" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A81" s="31" t="n">
+      <c r="A81" s="32" t="n">
         <v>0.27</v>
       </c>
       <c r="B81" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A81)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>157668.32220101</v>
-      </c>
-      <c r="C81" s="32" t="str">
+        <v>162298.642705966</v>
+      </c>
+      <c r="C81" s="33" t="str">
         <f aca="false">IF(B81&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
         <v>Viável a esta taxa</v>
       </c>
     </row>
     <row r="82" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A82" s="31" t="n">
+      <c r="A82" s="32" t="n">
         <v>0.29</v>
       </c>
       <c r="B82" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A82)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>151219.258293713</v>
-      </c>
-      <c r="C82" s="32" t="str">
+        <v>155821.946695353</v>
+      </c>
+      <c r="C82" s="33" t="str">
         <f aca="false">IF(B82&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
         <v>Viável a esta taxa</v>
       </c>
     </row>
     <row r="83" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A83" s="31" t="n">
+      <c r="A83" s="32" t="n">
         <v>0.33</v>
       </c>
       <c r="B83" s="15" t="n">
         <f aca="false">'Fluxo de Caixa'!$G$5+NPV((1+A83)^(1/12)-1,'Fluxo de Caixa'!$G$6:$G$29)</f>
-        <v>139075.399922297</v>
-      </c>
-      <c r="C83" s="32" t="str">
+        <v>143623.164560387</v>
+      </c>
+      <c r="C83" s="33" t="str">
         <f aca="false">IF(B83&gt;0,"Viável a esta taxa","Inviável a esta taxa")</f>
         <v>Viável a esta taxa</v>
       </c>
     </row>
     <row r="84" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A84" s="20" t="s">
-        <v>151</v>
+      <c r="A84" s="21" t="s">
+        <v>152</v>
       </c>
     </row>
     <row r="86" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A86" s="9" t="s">
-        <v>152</v>
+        <v>153</v>
       </c>
       <c r="B86" s="10"/>
       <c r="C86" s="10"/>
     </row>
     <row r="87" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A87" s="11" t="s">
-        <v>153</v>
+        <v>154</v>
       </c>
       <c r="B87" s="16" t="n">
         <v>5</v>
       </c>
       <c r="C87" s="13" t="s">
-        <v>154</v>
+        <v>155</v>
       </c>
     </row>
     <row r="88" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A88" s="11" t="s">
-        <v>155</v>
+        <v>156</v>
       </c>
       <c r="B88" s="12" t="n">
         <v>300</v>
       </c>
       <c r="C88" s="13" t="s">
-        <v>156</v>
+        <v>157</v>
       </c>
     </row>
     <row r="89" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A89" s="11" t="s">
-        <v>157</v>
-      </c>
-      <c r="B89" s="33" t="n">
+        <v>158</v>
+      </c>
+      <c r="B89" s="34" t="n">
         <v>1</v>
       </c>
       <c r="C89" s="13" t="s">
-        <v>158</v>
+        <v>159</v>
       </c>
     </row>
     <row r="90" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A90" s="11" t="s">
-        <v>159</v>
+        <v>160</v>
       </c>
       <c r="B90" s="12" t="n">
         <v>18</v>
       </c>
       <c r="C90" s="13" t="s">
-        <v>160</v>
+        <v>161</v>
       </c>
     </row>
     <row r="91" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A91" s="11" t="s">
-        <v>161</v>
+        <v>162</v>
       </c>
       <c r="B91" s="16" t="n">
         <v>1</v>
       </c>
       <c r="C91" s="13" t="s">
-        <v>162</v>
+        <v>163</v>
       </c>
     </row>
     <row r="92" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A92" s="11" t="s">
-        <v>163</v>
+        <v>164</v>
       </c>
       <c r="B92" s="16" t="n">
         <v>3</v>
       </c>
       <c r="C92" s="13" t="s">
-        <v>164</v>
+        <v>165</v>
       </c>
     </row>
     <row r="93" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A93" s="11" t="s">
-        <v>165</v>
+        <v>166</v>
       </c>
       <c r="B93" s="15" t="n">
         <f aca="false">B8+B88*B89</f>
         <v>1497</v>
       </c>
       <c r="C93" s="13" t="s">
-        <v>166</v>
+        <v>167</v>
       </c>
     </row>
   </sheetData>
@@ -2972,7 +2978,7 @@
   <sheetData>
     <row r="1" customFormat="false" ht="21.75" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A1" s="6" t="s">
-        <v>167</v>
+        <v>168</v>
       </c>
       <c r="B1" s="7"/>
       <c r="C1" s="7"/>
@@ -3002,103 +3008,103 @@
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="8" t="s">
-        <v>168</v>
+        <v>169</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>169</v>
-      </c>
-      <c r="B4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>170</v>
       </c>
-      <c r="C4" s="17" t="s">
+      <c r="B4" s="18" t="s">
         <v>171</v>
       </c>
-      <c r="D4" s="17" t="s">
+      <c r="C4" s="18" t="s">
         <v>172</v>
       </c>
-      <c r="E4" s="17" t="s">
+      <c r="D4" s="18" t="s">
         <v>173</v>
       </c>
-      <c r="F4" s="17" t="s">
+      <c r="E4" s="18" t="s">
         <v>174</v>
       </c>
-      <c r="G4" s="17" t="s">
+      <c r="F4" s="18" t="s">
         <v>175</v>
       </c>
-      <c r="H4" s="17" t="s">
+      <c r="G4" s="18" t="s">
         <v>176</v>
       </c>
-      <c r="I4" s="17" t="s">
+      <c r="H4" s="18" t="s">
         <v>177</v>
       </c>
-      <c r="J4" s="17" t="s">
+      <c r="I4" s="18" t="s">
         <v>178</v>
       </c>
-      <c r="K4" s="17" t="s">
+      <c r="J4" s="18" t="s">
         <v>179</v>
       </c>
-      <c r="L4" s="17" t="s">
+      <c r="K4" s="18" t="s">
         <v>180</v>
       </c>
-      <c r="M4" s="17" t="s">
+      <c r="L4" s="18" t="s">
         <v>181</v>
       </c>
-      <c r="N4" s="17" t="s">
+      <c r="M4" s="18" t="s">
         <v>182</v>
       </c>
-      <c r="O4" s="17" t="s">
+      <c r="N4" s="18" t="s">
         <v>183</v>
       </c>
-      <c r="P4" s="17" t="s">
+      <c r="O4" s="18" t="s">
         <v>184</v>
       </c>
-      <c r="Q4" s="17" t="s">
+      <c r="P4" s="18" t="s">
         <v>185</v>
       </c>
-      <c r="R4" s="17" t="s">
+      <c r="Q4" s="18" t="s">
         <v>186</v>
       </c>
-      <c r="S4" s="17" t="s">
+      <c r="R4" s="18" t="s">
         <v>187</v>
       </c>
-      <c r="T4" s="17" t="s">
+      <c r="S4" s="18" t="s">
         <v>188</v>
       </c>
-      <c r="U4" s="17" t="s">
+      <c r="T4" s="18" t="s">
         <v>189</v>
       </c>
-      <c r="V4" s="17" t="s">
+      <c r="U4" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="W4" s="17" t="s">
+      <c r="V4" s="18" t="s">
         <v>191</v>
       </c>
-      <c r="X4" s="17" t="s">
+      <c r="W4" s="18" t="s">
         <v>192</v>
       </c>
-      <c r="Y4" s="17" t="s">
+      <c r="X4" s="18" t="s">
         <v>193</v>
       </c>
-      <c r="Z4" s="17" t="s">
+      <c r="Y4" s="18" t="s">
         <v>194</v>
       </c>
+      <c r="Z4" s="18" t="s">
+        <v>195</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="34" t="n">
-        <v>0</v>
-      </c>
-      <c r="B5" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="35" t="n">
+      <c r="A5" s="35" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="36" t="n">
         <v>0</v>
       </c>
       <c r="F5" s="15" t="n">
@@ -3116,7 +3122,7 @@
       <c r="J5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="K5" s="32"/>
+      <c r="K5" s="33"/>
       <c r="L5" s="15" t="n">
         <v>0</v>
       </c>
@@ -3153,30 +3159,30 @@
       <c r="W5" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="X5" s="36" t="s">
-        <v>195</v>
-      </c>
-      <c r="Y5" s="35" t="n">
-        <v>0</v>
-      </c>
-      <c r="Z5" s="35" t="n">
+      <c r="X5" s="37" t="s">
+        <v>196</v>
+      </c>
+      <c r="Y5" s="36" t="n">
+        <v>0</v>
+      </c>
+      <c r="Z5" s="36" t="n">
         <v>0</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="34" t="n">
+      <c r="A6" s="35" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="37" t="n">
+      <c r="B6" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="C6" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D6" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="38" t="n">
+      <c r="C6" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D6" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A6-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A6)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
@@ -3189,10 +3195,10 @@
         <v>0</v>
       </c>
       <c r="H6" s="15" t="n">
-        <f aca="false">E6*'Premissas Precept'!$B$12</f>
-        <v>0</v>
-      </c>
-      <c r="I6" s="22" t="n">
+        <f aca="false">D6*'Premissas Precept'!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="I6" s="23" t="n">
         <f aca="false">F6+G6+H6</f>
         <v>5988</v>
       </c>
@@ -3200,7 +3206,7 @@
         <f aca="false">I6*12</f>
         <v>71856</v>
       </c>
-      <c r="K6" s="39" t="n">
+      <c r="K6" s="40" t="n">
         <f aca="false">IF(J6&lt;=0,'Premissas Precept'!$C$24,(J6*LOOKUP(J6,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J6,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J6)</f>
         <v>0.155</v>
       </c>
@@ -3225,10 +3231,10 @@
         <v>0</v>
       </c>
       <c r="Q6" s="15" t="n">
-        <f aca="false">C6*'Premissas Precept'!$B$19+E6*'Premissas Precept'!$B$20</f>
-        <v>0</v>
-      </c>
-      <c r="R6" s="22" t="n">
+        <f aca="false">C6*'Premissas Precept'!$B$19+D6*'Premissas Precept'!$B$20</f>
+        <v>0</v>
+      </c>
+      <c r="R6" s="23" t="n">
         <f aca="false">SUM(L6:Q6)</f>
         <v>1479.9</v>
       </c>
@@ -3240,11 +3246,11 @@
         <f aca="false">IF(A6&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I6,0)</f>
         <v>0</v>
       </c>
-      <c r="U6" s="22" t="n">
+      <c r="U6" s="23" t="n">
         <f aca="false">S6+T6</f>
         <v>12000</v>
       </c>
-      <c r="V6" s="22" t="n">
+      <c r="V6" s="23" t="n">
         <f aca="false">I6-R6-U6</f>
         <v>-7491.9</v>
       </c>
@@ -3252,33 +3258,33 @@
         <f aca="false">T6/'Premissas Precept'!$B$45</f>
         <v>0</v>
       </c>
-      <c r="X6" s="36" t="str">
+      <c r="X6" s="37" t="str">
         <f aca="false">IF(V6&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
-      <c r="Y6" s="38" t="n">
+      <c r="Y6" s="39" t="n">
         <f aca="false">C6*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A6-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A6)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
-      <c r="Z6" s="38" t="n">
+      <c r="Z6" s="39" t="n">
         <f aca="false">MAX(0,B6-Y6)</f>
         <v>4</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="34" t="n">
+      <c r="A7" s="35" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="37" t="n">
+      <c r="B7" s="38" t="n">
         <v>6</v>
       </c>
-      <c r="C7" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D7" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="38" t="n">
+      <c r="C7" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D7" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A7-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A7)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
@@ -3291,10 +3297,10 @@
         <v>0</v>
       </c>
       <c r="H7" s="15" t="n">
-        <f aca="false">E7*'Premissas Precept'!$B$12</f>
-        <v>0</v>
-      </c>
-      <c r="I7" s="22" t="n">
+        <f aca="false">D7*'Premissas Precept'!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="I7" s="23" t="n">
         <f aca="false">F7+G7+H7</f>
         <v>8982</v>
       </c>
@@ -3302,7 +3308,7 @@
         <f aca="false">AVERAGE(I$6:I6)*12</f>
         <v>71856</v>
       </c>
-      <c r="K7" s="39" t="n">
+      <c r="K7" s="40" t="n">
         <f aca="false">IF(J7&lt;=0,'Premissas Precept'!$C$24,(J7*LOOKUP(J7,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J7,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J7)</f>
         <v>0.155</v>
       </c>
@@ -3327,10 +3333,10 @@
         <v>0</v>
       </c>
       <c r="Q7" s="15" t="n">
-        <f aca="false">C7*'Premissas Precept'!$B$19+E7*'Premissas Precept'!$B$20</f>
-        <v>0</v>
-      </c>
-      <c r="R7" s="22" t="n">
+        <f aca="false">C7*'Premissas Precept'!$B$19+D7*'Premissas Precept'!$B$20</f>
+        <v>0</v>
+      </c>
+      <c r="R7" s="23" t="n">
         <f aca="false">SUM(L7:Q7)</f>
         <v>2219.85</v>
       </c>
@@ -3342,11 +3348,11 @@
         <f aca="false">IF(A7&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I7,0)</f>
         <v>0</v>
       </c>
-      <c r="U7" s="22" t="n">
+      <c r="U7" s="23" t="n">
         <f aca="false">S7+T7</f>
         <v>12000</v>
       </c>
-      <c r="V7" s="22" t="n">
+      <c r="V7" s="23" t="n">
         <f aca="false">I7-R7-U7</f>
         <v>-5237.85</v>
       </c>
@@ -3354,33 +3360,33 @@
         <f aca="false">T7/'Premissas Precept'!$B$45</f>
         <v>0</v>
       </c>
-      <c r="X7" s="36" t="str">
+      <c r="X7" s="37" t="str">
         <f aca="false">IF(V7&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
-      <c r="Y7" s="38" t="n">
+      <c r="Y7" s="39" t="n">
         <f aca="false">C7*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A7-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A7)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
-      <c r="Z7" s="38" t="n">
+      <c r="Z7" s="39" t="n">
         <f aca="false">MAX(0,B7-Y7)</f>
         <v>6</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="34" t="n">
+      <c r="A8" s="35" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="37" t="n">
+      <c r="B8" s="38" t="n">
         <v>9</v>
       </c>
-      <c r="C8" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="D8" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="38" t="n">
+      <c r="C8" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="D8" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A8-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A8)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
@@ -3393,10 +3399,10 @@
         <v>0</v>
       </c>
       <c r="H8" s="15" t="n">
-        <f aca="false">E8*'Premissas Precept'!$B$12</f>
-        <v>0</v>
-      </c>
-      <c r="I8" s="22" t="n">
+        <f aca="false">D8*'Premissas Precept'!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="I8" s="23" t="n">
         <f aca="false">F8+G8+H8</f>
         <v>13473</v>
       </c>
@@ -3404,7 +3410,7 @@
         <f aca="false">AVERAGE(I$6:I7)*12</f>
         <v>89820</v>
       </c>
-      <c r="K8" s="39" t="n">
+      <c r="K8" s="40" t="n">
         <f aca="false">IF(J8&lt;=0,'Premissas Precept'!$C$24,(J8*LOOKUP(J8,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J8,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J8)</f>
         <v>0.155</v>
       </c>
@@ -3429,10 +3435,10 @@
         <v>0</v>
       </c>
       <c r="Q8" s="15" t="n">
-        <f aca="false">C8*'Premissas Precept'!$B$19+E8*'Premissas Precept'!$B$20</f>
-        <v>0</v>
-      </c>
-      <c r="R8" s="22" t="n">
+        <f aca="false">C8*'Premissas Precept'!$B$19+D8*'Premissas Precept'!$B$20</f>
+        <v>0</v>
+      </c>
+      <c r="R8" s="23" t="n">
         <f aca="false">SUM(L8:Q8)</f>
         <v>3329.775</v>
       </c>
@@ -3444,11 +3450,11 @@
         <f aca="false">IF(A8&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I8,0)</f>
         <v>0</v>
       </c>
-      <c r="U8" s="22" t="n">
+      <c r="U8" s="23" t="n">
         <f aca="false">S8+T8</f>
         <v>12000</v>
       </c>
-      <c r="V8" s="22" t="n">
+      <c r="V8" s="23" t="n">
         <f aca="false">I8-R8-U8</f>
         <v>-1856.775</v>
       </c>
@@ -3456,33 +3462,33 @@
         <f aca="false">T8/'Premissas Precept'!$B$45</f>
         <v>0</v>
       </c>
-      <c r="X8" s="36" t="str">
+      <c r="X8" s="37" t="str">
         <f aca="false">IF(V8&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
-      <c r="Y8" s="38" t="n">
+      <c r="Y8" s="39" t="n">
         <f aca="false">C8*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A8-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A8)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
-      <c r="Z8" s="38" t="n">
+      <c r="Z8" s="39" t="n">
         <f aca="false">MAX(0,B8-Y8)</f>
         <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="34" t="n">
+      <c r="A9" s="35" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="37" t="n">
+      <c r="B9" s="38" t="n">
         <v>11</v>
       </c>
-      <c r="C9" s="37" t="n">
+      <c r="C9" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="D9" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="38" t="n">
+      <c r="D9" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A9-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A9)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
@@ -3495,10 +3501,10 @@
         <v>9997</v>
       </c>
       <c r="H9" s="15" t="n">
-        <f aca="false">E9*'Premissas Precept'!$B$12</f>
-        <v>0</v>
-      </c>
-      <c r="I9" s="22" t="n">
+        <f aca="false">D9*'Premissas Precept'!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="I9" s="23" t="n">
         <f aca="false">F9+G9+H9</f>
         <v>24967</v>
       </c>
@@ -3506,7 +3512,7 @@
         <f aca="false">AVERAGE(I$6:I8)*12</f>
         <v>113772</v>
       </c>
-      <c r="K9" s="39" t="n">
+      <c r="K9" s="40" t="n">
         <f aca="false">IF(J9&lt;=0,'Premissas Precept'!$C$24,(J9*LOOKUP(J9,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J9,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J9)</f>
         <v>0.155</v>
       </c>
@@ -3531,10 +3537,10 @@
         <v>3498.95</v>
       </c>
       <c r="Q9" s="15" t="n">
-        <f aca="false">C9*'Premissas Precept'!$B$19+E9*'Premissas Precept'!$B$20</f>
+        <f aca="false">C9*'Premissas Precept'!$B$19+D9*'Premissas Precept'!$B$20</f>
         <v>600</v>
       </c>
-      <c r="R9" s="22" t="n">
+      <c r="R9" s="23" t="n">
         <f aca="false">SUM(L9:Q9)</f>
         <v>10156.025</v>
       </c>
@@ -3546,11 +3552,11 @@
         <f aca="false">IF(A9&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I9,0)</f>
         <v>6116.915</v>
       </c>
-      <c r="U9" s="22" t="n">
+      <c r="U9" s="23" t="n">
         <f aca="false">S9+T9</f>
         <v>18116.915</v>
       </c>
-      <c r="V9" s="22" t="n">
+      <c r="V9" s="23" t="n">
         <f aca="false">I9-R9-U9</f>
         <v>-3305.94</v>
       </c>
@@ -3558,33 +3564,33 @@
         <f aca="false">T9/'Premissas Precept'!$B$45</f>
         <v>873.845</v>
       </c>
-      <c r="X9" s="36" t="str">
+      <c r="X9" s="37" t="str">
         <f aca="false">IF(V9&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
-      <c r="Y9" s="38" t="n">
+      <c r="Y9" s="39" t="n">
         <f aca="false">C9*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A9-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A9)*$D$6:$D$29)</f>
         <v>1</v>
       </c>
-      <c r="Z9" s="38" t="n">
+      <c r="Z9" s="39" t="n">
         <f aca="false">MAX(0,B9-Y9)</f>
         <v>10</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="34" t="n">
+      <c r="A10" s="35" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="37" t="n">
+      <c r="B10" s="38" t="n">
         <v>14</v>
       </c>
-      <c r="C10" s="37" t="n">
+      <c r="C10" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="D10" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="38" t="n">
+      <c r="D10" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A10-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A10)*$D$6:$D$29)</f>
         <v>0</v>
       </c>
@@ -3597,10 +3603,10 @@
         <v>9997</v>
       </c>
       <c r="H10" s="15" t="n">
-        <f aca="false">E10*'Premissas Precept'!$B$12</f>
-        <v>0</v>
-      </c>
-      <c r="I10" s="22" t="n">
+        <f aca="false">D10*'Premissas Precept'!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="I10" s="23" t="n">
         <f aca="false">F10+G10+H10</f>
         <v>29458</v>
       </c>
@@ -3608,7 +3614,7 @@
         <f aca="false">AVERAGE(I$6:I9)*12</f>
         <v>160230</v>
       </c>
-      <c r="K10" s="39" t="n">
+      <c r="K10" s="40" t="n">
         <f aca="false">IF(J10&lt;=0,'Premissas Precept'!$C$24,(J10*LOOKUP(J10,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J10,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J10)</f>
         <v>0.155</v>
       </c>
@@ -3633,10 +3639,10 @@
         <v>3498.95</v>
       </c>
       <c r="Q10" s="15" t="n">
-        <f aca="false">C10*'Premissas Precept'!$B$19+E10*'Premissas Precept'!$B$20</f>
+        <f aca="false">C10*'Premissas Precept'!$B$19+D10*'Premissas Precept'!$B$20</f>
         <v>600</v>
       </c>
-      <c r="R10" s="22" t="n">
+      <c r="R10" s="23" t="n">
         <f aca="false">SUM(L10:Q10)</f>
         <v>11265.95</v>
       </c>
@@ -3648,11 +3654,11 @@
         <f aca="false">IF(A10&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I10,0)</f>
         <v>7217.21</v>
       </c>
-      <c r="U10" s="22" t="n">
+      <c r="U10" s="23" t="n">
         <f aca="false">S10+T10</f>
         <v>19217.21</v>
       </c>
-      <c r="V10" s="22" t="n">
+      <c r="V10" s="23" t="n">
         <f aca="false">I10-R10-U10</f>
         <v>-1025.16</v>
       </c>
@@ -3660,33 +3666,33 @@
         <f aca="false">T10/'Premissas Precept'!$B$45</f>
         <v>1031.03</v>
       </c>
-      <c r="X10" s="36" t="str">
+      <c r="X10" s="37" t="str">
         <f aca="false">IF(V10&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
-      <c r="Y10" s="38" t="n">
+      <c r="Y10" s="39" t="n">
         <f aca="false">C10*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A10-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A10)*$D$6:$D$29)</f>
         <v>1</v>
       </c>
-      <c r="Z10" s="38" t="n">
+      <c r="Z10" s="39" t="n">
         <f aca="false">MAX(0,B10-Y10)</f>
         <v>13</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="34" t="n">
+      <c r="A11" s="35" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="37" t="n">
+      <c r="B11" s="38" t="n">
         <v>16</v>
       </c>
-      <c r="C11" s="37" t="n">
+      <c r="C11" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="D11" s="37" t="n">
+      <c r="D11" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E11" s="38" t="n">
+      <c r="E11" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A11-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A11)*$D$6:$D$29)</f>
         <v>1</v>
       </c>
@@ -3699,24 +3705,24 @@
         <v>9997</v>
       </c>
       <c r="H11" s="15" t="n">
-        <f aca="false">E11*'Premissas Precept'!$B$12</f>
-        <v>4999.5</v>
-      </c>
-      <c r="I11" s="22" t="n">
+        <f aca="false">D11*'Premissas Precept'!$B$10</f>
+        <v>29997</v>
+      </c>
+      <c r="I11" s="23" t="n">
         <f aca="false">F11+G11+H11</f>
-        <v>35954.5</v>
+        <v>60952</v>
       </c>
       <c r="J11" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I10)*12</f>
         <v>198883.2</v>
       </c>
-      <c r="K11" s="39" t="n">
+      <c r="K11" s="40" t="n">
         <f aca="false">IF(J11&lt;=0,'Premissas Precept'!$C$24,(J11*LOOKUP(J11,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J11,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J11)</f>
         <v>0.157373654486653</v>
       </c>
       <c r="L11" s="15" t="n">
         <f aca="false">I11*K11</f>
-        <v>5658.29106024038</v>
+        <v>9592.2389882705</v>
       </c>
       <c r="M11" s="15" t="n">
         <f aca="false">B11*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -3724,23 +3730,23 @@
       </c>
       <c r="N11" s="15" t="n">
         <f aca="false">I11*'Premissas Precept'!$B$16</f>
-        <v>719.09</v>
+        <v>1219.04</v>
       </c>
       <c r="O11" s="15" t="n">
         <f aca="false">(G11+H11)*'Premissas Precept'!$B$17</f>
-        <v>749.825</v>
+        <v>1999.7</v>
       </c>
       <c r="P11" s="15" t="n">
         <f aca="false">(G11+H11)*'Premissas Precept'!$B$18</f>
-        <v>5248.775</v>
+        <v>13997.9</v>
       </c>
       <c r="Q11" s="15" t="n">
-        <f aca="false">C11*'Premissas Precept'!$B$19+E11*'Premissas Precept'!$B$20</f>
-        <v>800</v>
-      </c>
-      <c r="R11" s="22" t="n">
+        <f aca="false">C11*'Premissas Precept'!$B$19+D11*'Premissas Precept'!$B$20</f>
+        <v>1800</v>
+      </c>
+      <c r="R11" s="23" t="n">
         <f aca="false">SUM(L11:Q11)</f>
-        <v>14903.9810602404</v>
+        <v>30336.8789882705</v>
       </c>
       <c r="S11" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3748,47 +3754,47 @@
       </c>
       <c r="T11" s="15" t="n">
         <f aca="false">IF(A11&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I11,0)</f>
-        <v>8808.8525</v>
-      </c>
-      <c r="U11" s="22" t="n">
+        <v>14933.24</v>
+      </c>
+      <c r="U11" s="23" t="n">
         <f aca="false">S11+T11</f>
-        <v>20808.8525</v>
-      </c>
-      <c r="V11" s="22" t="n">
+        <v>26933.24</v>
+      </c>
+      <c r="V11" s="23" t="n">
         <f aca="false">I11-R11-U11</f>
-        <v>241.666439759618</v>
+        <v>3681.8810117295</v>
       </c>
       <c r="W11" s="15" t="n">
         <f aca="false">T11/'Premissas Precept'!$B$45</f>
-        <v>1258.4075</v>
-      </c>
-      <c r="X11" s="36" t="str">
+        <v>2133.32</v>
+      </c>
+      <c r="X11" s="37" t="str">
         <f aca="false">IF(V11&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y11" s="38" t="n">
+      <c r="Y11" s="39" t="n">
         <f aca="false">C11*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A11-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A11)*$D$6:$D$29)</f>
         <v>2</v>
       </c>
-      <c r="Z11" s="38" t="n">
+      <c r="Z11" s="39" t="n">
         <f aca="false">MAX(0,B11-Y11)</f>
         <v>14</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="34" t="n">
+      <c r="A12" s="35" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="37" t="n">
+      <c r="B12" s="38" t="n">
         <v>19</v>
       </c>
-      <c r="C12" s="37" t="n">
+      <c r="C12" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="D12" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="38" t="n">
+      <c r="D12" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A12-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A12)*$D$6:$D$29)</f>
         <v>1</v>
       </c>
@@ -3801,24 +3807,24 @@
         <v>9997</v>
       </c>
       <c r="H12" s="15" t="n">
-        <f aca="false">E12*'Premissas Precept'!$B$12</f>
-        <v>4999.5</v>
-      </c>
-      <c r="I12" s="22" t="n">
+        <f aca="false">D12*'Premissas Precept'!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="I12" s="23" t="n">
         <f aca="false">F12+G12+H12</f>
-        <v>40445.5</v>
+        <v>35446</v>
       </c>
       <c r="J12" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I11)*12</f>
-        <v>237645</v>
-      </c>
-      <c r="K12" s="39" t="n">
+        <v>287640</v>
+      </c>
+      <c r="K12" s="40" t="n">
         <f aca="false">IF(J12&lt;=0,'Premissas Precept'!$C$24,(J12*LOOKUP(J12,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J12,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J12)</f>
-        <v>0.161064192387805</v>
+        <v>0.164355444305382</v>
       </c>
       <c r="L12" s="15" t="n">
         <f aca="false">I12*K12</f>
-        <v>6514.32179322098</v>
+        <v>5825.74307884856</v>
       </c>
       <c r="M12" s="15" t="n">
         <f aca="false">B12*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -3826,23 +3832,23 @@
       </c>
       <c r="N12" s="15" t="n">
         <f aca="false">I12*'Premissas Precept'!$B$16</f>
-        <v>808.91</v>
+        <v>708.92</v>
       </c>
       <c r="O12" s="15" t="n">
         <f aca="false">(G12+H12)*'Premissas Precept'!$B$17</f>
-        <v>749.825</v>
+        <v>499.85</v>
       </c>
       <c r="P12" s="15" t="n">
         <f aca="false">(G12+H12)*'Premissas Precept'!$B$18</f>
-        <v>5248.775</v>
+        <v>3498.95</v>
       </c>
       <c r="Q12" s="15" t="n">
-        <f aca="false">C12*'Premissas Precept'!$B$19+E12*'Premissas Precept'!$B$20</f>
-        <v>800</v>
-      </c>
-      <c r="R12" s="22" t="n">
+        <f aca="false">C12*'Premissas Precept'!$B$19+D12*'Premissas Precept'!$B$20</f>
+        <v>600</v>
+      </c>
+      <c r="R12" s="23" t="n">
         <f aca="false">SUM(L12:Q12)</f>
-        <v>16173.831793221</v>
+        <v>13185.4630788486</v>
       </c>
       <c r="S12" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3850,47 +3856,47 @@
       </c>
       <c r="T12" s="15" t="n">
         <f aca="false">IF(A12&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I12,0)</f>
-        <v>9909.1475</v>
-      </c>
-      <c r="U12" s="22" t="n">
+        <v>8684.27</v>
+      </c>
+      <c r="U12" s="23" t="n">
         <f aca="false">S12+T12</f>
-        <v>21909.1475</v>
-      </c>
-      <c r="V12" s="22" t="n">
+        <v>20684.27</v>
+      </c>
+      <c r="V12" s="23" t="n">
         <f aca="false">I12-R12-U12</f>
-        <v>2362.52070677902</v>
+        <v>1576.26692115144</v>
       </c>
       <c r="W12" s="15" t="n">
         <f aca="false">T12/'Premissas Precept'!$B$45</f>
-        <v>1415.5925</v>
-      </c>
-      <c r="X12" s="36" t="str">
+        <v>1240.61</v>
+      </c>
+      <c r="X12" s="37" t="str">
         <f aca="false">IF(V12&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y12" s="38" t="n">
+      <c r="Y12" s="39" t="n">
         <f aca="false">C12*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A12-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A12)*$D$6:$D$29)</f>
         <v>2</v>
       </c>
-      <c r="Z12" s="38" t="n">
+      <c r="Z12" s="39" t="n">
         <f aca="false">MAX(0,B12-Y12)</f>
         <v>17</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="34" t="n">
+      <c r="A13" s="35" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="37" t="n">
+      <c r="B13" s="38" t="n">
         <v>21</v>
       </c>
-      <c r="C13" s="37" t="n">
+      <c r="C13" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="D13" s="37" t="n">
+      <c r="D13" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E13" s="38" t="n">
+      <c r="E13" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A13-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A13)*$D$6:$D$29)</f>
         <v>2</v>
       </c>
@@ -3903,24 +3909,24 @@
         <v>9997</v>
       </c>
       <c r="H13" s="15" t="n">
-        <f aca="false">E13*'Premissas Precept'!$B$12</f>
-        <v>9999</v>
-      </c>
-      <c r="I13" s="22" t="n">
+        <f aca="false">D13*'Premissas Precept'!$B$10</f>
+        <v>29997</v>
+      </c>
+      <c r="I13" s="23" t="n">
         <f aca="false">F13+G13+H13</f>
-        <v>46942</v>
+        <v>66940</v>
       </c>
       <c r="J13" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I12)*12</f>
-        <v>273030.857142857</v>
-      </c>
-      <c r="K13" s="39" t="n">
+        <v>307313.142857143</v>
+      </c>
+      <c r="K13" s="40" t="n">
         <f aca="false">IF(J13&lt;=0,'Premissas Precept'!$C$24,(J13*LOOKUP(J13,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J13,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J13)</f>
-        <v>0.16351834643494</v>
+        <v>0.165356955585554</v>
       </c>
       <c r="L13" s="15" t="n">
         <f aca="false">I13*K13</f>
-        <v>7675.87821834895</v>
+        <v>11068.994606897</v>
       </c>
       <c r="M13" s="15" t="n">
         <f aca="false">B13*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -3928,23 +3934,23 @@
       </c>
       <c r="N13" s="15" t="n">
         <f aca="false">I13*'Premissas Precept'!$B$16</f>
-        <v>938.84</v>
+        <v>1338.8</v>
       </c>
       <c r="O13" s="15" t="n">
         <f aca="false">(G13+H13)*'Premissas Precept'!$B$17</f>
-        <v>999.8</v>
+        <v>1999.7</v>
       </c>
       <c r="P13" s="15" t="n">
         <f aca="false">(G13+H13)*'Premissas Precept'!$B$18</f>
-        <v>6998.6</v>
+        <v>13997.9</v>
       </c>
       <c r="Q13" s="15" t="n">
-        <f aca="false">C13*'Premissas Precept'!$B$19+E13*'Premissas Precept'!$B$20</f>
-        <v>1000</v>
-      </c>
-      <c r="R13" s="22" t="n">
+        <f aca="false">C13*'Premissas Precept'!$B$19+D13*'Premissas Precept'!$B$20</f>
+        <v>1800</v>
+      </c>
+      <c r="R13" s="23" t="n">
         <f aca="false">SUM(L13:Q13)</f>
-        <v>19881.1182183489</v>
+        <v>32473.394606897</v>
       </c>
       <c r="S13" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -3952,47 +3958,47 @@
       </c>
       <c r="T13" s="15" t="n">
         <f aca="false">IF(A13&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I13,0)</f>
-        <v>11500.79</v>
-      </c>
-      <c r="U13" s="22" t="n">
+        <v>16400.3</v>
+      </c>
+      <c r="U13" s="23" t="n">
         <f aca="false">S13+T13</f>
-        <v>23500.79</v>
-      </c>
-      <c r="V13" s="22" t="n">
+        <v>28400.3</v>
+      </c>
+      <c r="V13" s="23" t="n">
         <f aca="false">I13-R13-U13</f>
-        <v>3560.09178165106</v>
+        <v>6066.30539310299</v>
       </c>
       <c r="W13" s="15" t="n">
         <f aca="false">T13/'Premissas Precept'!$B$45</f>
-        <v>1642.97</v>
-      </c>
-      <c r="X13" s="36" t="str">
+        <v>2342.9</v>
+      </c>
+      <c r="X13" s="37" t="str">
         <f aca="false">IF(V13&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y13" s="38" t="n">
+      <c r="Y13" s="39" t="n">
         <f aca="false">C13*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A13-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A13)*$D$6:$D$29)</f>
         <v>3</v>
       </c>
-      <c r="Z13" s="38" t="n">
+      <c r="Z13" s="39" t="n">
         <f aca="false">MAX(0,B13-Y13)</f>
         <v>18</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A14" s="34" t="n">
+      <c r="A14" s="35" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="37" t="n">
+      <c r="B14" s="38" t="n">
         <v>24</v>
       </c>
-      <c r="C14" s="37" t="n">
+      <c r="C14" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="D14" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E14" s="38" t="n">
+      <c r="D14" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E14" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A14-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A14)*$D$6:$D$29)</f>
         <v>2</v>
       </c>
@@ -4005,24 +4011,24 @@
         <v>19994</v>
       </c>
       <c r="H14" s="15" t="n">
-        <f aca="false">E14*'Premissas Precept'!$B$12</f>
-        <v>9999</v>
-      </c>
-      <c r="I14" s="22" t="n">
+        <f aca="false">D14*'Premissas Precept'!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="I14" s="23" t="n">
         <f aca="false">F14+G14+H14</f>
-        <v>61430</v>
+        <v>51431</v>
       </c>
       <c r="J14" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I13)*12</f>
-        <v>309315</v>
-      </c>
-      <c r="K14" s="39" t="n">
+        <v>369309</v>
+      </c>
+      <c r="K14" s="40" t="n">
         <f aca="false">IF(J14&lt;=0,'Premissas Precept'!$C$24,(J14*LOOKUP(J14,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J14,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J14)</f>
-        <v>0.165451723970709</v>
+        <v>0.168193179695052</v>
       </c>
       <c r="L14" s="15" t="n">
         <f aca="false">I14*K14</f>
-        <v>10163.6994035207</v>
+        <v>8650.34342489623</v>
       </c>
       <c r="M14" s="15" t="n">
         <f aca="false">B14*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -4030,23 +4036,23 @@
       </c>
       <c r="N14" s="15" t="n">
         <f aca="false">I14*'Premissas Precept'!$B$16</f>
-        <v>1228.6</v>
+        <v>1028.62</v>
       </c>
       <c r="O14" s="15" t="n">
         <f aca="false">(G14+H14)*'Premissas Precept'!$B$17</f>
-        <v>1499.65</v>
+        <v>999.7</v>
       </c>
       <c r="P14" s="15" t="n">
         <f aca="false">(G14+H14)*'Premissas Precept'!$B$18</f>
-        <v>10497.55</v>
+        <v>6997.9</v>
       </c>
       <c r="Q14" s="15" t="n">
-        <f aca="false">C14*'Premissas Precept'!$B$19+E14*'Premissas Precept'!$B$20</f>
-        <v>1600</v>
-      </c>
-      <c r="R14" s="22" t="n">
+        <f aca="false">C14*'Premissas Precept'!$B$19+D14*'Premissas Precept'!$B$20</f>
+        <v>1200</v>
+      </c>
+      <c r="R14" s="23" t="n">
         <f aca="false">SUM(L14:Q14)</f>
-        <v>27581.4994035207</v>
+        <v>21468.5634248962</v>
       </c>
       <c r="S14" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4054,47 +4060,47 @@
       </c>
       <c r="T14" s="15" t="n">
         <f aca="false">IF(A14&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I14,0)</f>
-        <v>15050.35</v>
-      </c>
-      <c r="U14" s="22" t="n">
+        <v>12600.595</v>
+      </c>
+      <c r="U14" s="23" t="n">
         <f aca="false">S14+T14</f>
-        <v>27050.35</v>
-      </c>
-      <c r="V14" s="22" t="n">
+        <v>24600.595</v>
+      </c>
+      <c r="V14" s="23" t="n">
         <f aca="false">I14-R14-U14</f>
-        <v>6798.15059647932</v>
+        <v>5361.84157510377</v>
       </c>
       <c r="W14" s="15" t="n">
         <f aca="false">T14/'Premissas Precept'!$B$45</f>
-        <v>2150.05</v>
-      </c>
-      <c r="X14" s="36" t="str">
+        <v>1800.085</v>
+      </c>
+      <c r="X14" s="37" t="str">
         <f aca="false">IF(V14&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y14" s="38" t="n">
+      <c r="Y14" s="39" t="n">
         <f aca="false">C14*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A14-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A14)*$D$6:$D$29)</f>
         <v>3</v>
       </c>
-      <c r="Z14" s="38" t="n">
+      <c r="Z14" s="39" t="n">
         <f aca="false">MAX(0,B14-Y14)</f>
         <v>21</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A15" s="34" t="n">
+      <c r="A15" s="35" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="37" t="n">
+      <c r="B15" s="38" t="n">
         <v>26</v>
       </c>
-      <c r="C15" s="37" t="n">
+      <c r="C15" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="D15" s="37" t="n">
+      <c r="D15" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E15" s="38" t="n">
+      <c r="E15" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A15-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A15)*$D$6:$D$29)</f>
         <v>3</v>
       </c>
@@ -4107,24 +4113,24 @@
         <v>9997</v>
       </c>
       <c r="H15" s="15" t="n">
-        <f aca="false">E15*'Premissas Precept'!$B$12</f>
-        <v>14998.5</v>
-      </c>
-      <c r="I15" s="22" t="n">
+        <f aca="false">D15*'Premissas Precept'!$B$10</f>
+        <v>29997</v>
+      </c>
+      <c r="I15" s="23" t="n">
         <f aca="false">F15+G15+H15</f>
-        <v>59426.5</v>
+        <v>74425</v>
       </c>
       <c r="J15" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I14)*12</f>
-        <v>356853.333333333</v>
-      </c>
-      <c r="K15" s="39" t="n">
+        <v>396849.333333333</v>
+      </c>
+      <c r="K15" s="40" t="n">
         <f aca="false">IF(J15&lt;=0,'Premissas Precept'!$C$24,(J15*LOOKUP(J15,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J15,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J15)</f>
-        <v>0.167389777312808</v>
+        <v>0.170053504772592</v>
       </c>
       <c r="L15" s="15" t="n">
         <f aca="false">I15*K15</f>
-        <v>9947.3886014796</v>
+        <v>12656.2320927002</v>
       </c>
       <c r="M15" s="15" t="n">
         <f aca="false">B15*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -4132,23 +4138,23 @@
       </c>
       <c r="N15" s="15" t="n">
         <f aca="false">I15*'Premissas Precept'!$B$16</f>
-        <v>1188.53</v>
+        <v>1488.5</v>
       </c>
       <c r="O15" s="15" t="n">
         <f aca="false">(G15+H15)*'Premissas Precept'!$B$17</f>
-        <v>1249.775</v>
+        <v>1999.7</v>
       </c>
       <c r="P15" s="15" t="n">
         <f aca="false">(G15+H15)*'Premissas Precept'!$B$18</f>
-        <v>8748.425</v>
+        <v>13997.9</v>
       </c>
       <c r="Q15" s="15" t="n">
-        <f aca="false">C15*'Premissas Precept'!$B$19+E15*'Premissas Precept'!$B$20</f>
-        <v>1200</v>
-      </c>
-      <c r="R15" s="22" t="n">
+        <f aca="false">C15*'Premissas Precept'!$B$19+D15*'Premissas Precept'!$B$20</f>
+        <v>1800</v>
+      </c>
+      <c r="R15" s="23" t="n">
         <f aca="false">SUM(L15:Q15)</f>
-        <v>25142.1186014796</v>
+        <v>34750.3320927002</v>
       </c>
       <c r="S15" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4156,47 +4162,47 @@
       </c>
       <c r="T15" s="15" t="n">
         <f aca="false">IF(A15&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I15,0)</f>
-        <v>14559.4925</v>
-      </c>
-      <c r="U15" s="22" t="n">
+        <v>18234.125</v>
+      </c>
+      <c r="U15" s="23" t="n">
         <f aca="false">S15+T15</f>
-        <v>26559.4925</v>
-      </c>
-      <c r="V15" s="22" t="n">
+        <v>30234.125</v>
+      </c>
+      <c r="V15" s="23" t="n">
         <f aca="false">I15-R15-U15</f>
-        <v>7724.8888985204</v>
+        <v>9440.54290729983</v>
       </c>
       <c r="W15" s="15" t="n">
         <f aca="false">T15/'Premissas Precept'!$B$45</f>
-        <v>2079.9275</v>
-      </c>
-      <c r="X15" s="36" t="str">
+        <v>2604.875</v>
+      </c>
+      <c r="X15" s="37" t="str">
         <f aca="false">IF(V15&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y15" s="38" t="n">
+      <c r="Y15" s="39" t="n">
         <f aca="false">C15*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A15-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A15)*$D$6:$D$29)</f>
         <v>3</v>
       </c>
-      <c r="Z15" s="38" t="n">
+      <c r="Z15" s="39" t="n">
         <f aca="false">MAX(0,B15-Y15)</f>
         <v>23</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A16" s="34" t="n">
+      <c r="A16" s="35" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="37" t="n">
+      <c r="B16" s="38" t="n">
         <v>29</v>
       </c>
-      <c r="C16" s="37" t="n">
+      <c r="C16" s="38" t="n">
         <v>2</v>
       </c>
-      <c r="D16" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E16" s="38" t="n">
+      <c r="D16" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E16" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A16-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A16)*$D$6:$D$29)</f>
         <v>3</v>
       </c>
@@ -4209,24 +4215,24 @@
         <v>19994</v>
       </c>
       <c r="H16" s="15" t="n">
-        <f aca="false">E16*'Premissas Precept'!$B$12</f>
-        <v>14998.5</v>
-      </c>
-      <c r="I16" s="22" t="n">
+        <f aca="false">D16*'Premissas Precept'!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="I16" s="23" t="n">
         <f aca="false">F16+G16+H16</f>
-        <v>73914.5</v>
+        <v>58916</v>
       </c>
       <c r="J16" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I15)*12</f>
-        <v>392479.8</v>
-      </c>
-      <c r="K16" s="39" t="n">
+        <v>446474.4</v>
+      </c>
+      <c r="K16" s="40" t="n">
         <f aca="false">IF(J16&lt;=0,'Premissas Precept'!$C$24,(J16*LOOKUP(J16,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J16,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J16)</f>
-        <v>0.169775771899598</v>
+        <v>0.172826276265784</v>
       </c>
       <c r="L16" s="15" t="n">
         <f aca="false">I16*K16</f>
-        <v>12548.8912920729</v>
+        <v>10182.2328924749</v>
       </c>
       <c r="M16" s="15" t="n">
         <f aca="false">B16*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -4234,23 +4240,23 @@
       </c>
       <c r="N16" s="15" t="n">
         <f aca="false">I16*'Premissas Precept'!$B$16</f>
-        <v>1478.29</v>
+        <v>1178.32</v>
       </c>
       <c r="O16" s="15" t="n">
         <f aca="false">(G16+H16)*'Premissas Precept'!$B$17</f>
-        <v>1749.625</v>
+        <v>999.7</v>
       </c>
       <c r="P16" s="15" t="n">
         <f aca="false">(G16+H16)*'Premissas Precept'!$B$18</f>
-        <v>12247.375</v>
+        <v>6997.9</v>
       </c>
       <c r="Q16" s="15" t="n">
-        <f aca="false">C16*'Premissas Precept'!$B$19+E16*'Premissas Precept'!$B$20</f>
-        <v>1800</v>
-      </c>
-      <c r="R16" s="22" t="n">
+        <f aca="false">C16*'Premissas Precept'!$B$19+D16*'Premissas Precept'!$B$20</f>
+        <v>1200</v>
+      </c>
+      <c r="R16" s="23" t="n">
         <f aca="false">SUM(L16:Q16)</f>
-        <v>32956.1812920729</v>
+        <v>23690.1528924749</v>
       </c>
       <c r="S16" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4258,47 +4264,47 @@
       </c>
       <c r="T16" s="15" t="n">
         <f aca="false">IF(A16&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I16,0)</f>
-        <v>18109.0525</v>
-      </c>
-      <c r="U16" s="22" t="n">
+        <v>14434.42</v>
+      </c>
+      <c r="U16" s="23" t="n">
         <f aca="false">S16+T16</f>
-        <v>30109.0525</v>
-      </c>
-      <c r="V16" s="22" t="n">
+        <v>26434.42</v>
+      </c>
+      <c r="V16" s="23" t="n">
         <f aca="false">I16-R16-U16</f>
-        <v>10849.2662079271</v>
+        <v>8791.42710752508</v>
       </c>
       <c r="W16" s="15" t="n">
         <f aca="false">T16/'Premissas Precept'!$B$45</f>
-        <v>2587.0075</v>
-      </c>
-      <c r="X16" s="36" t="str">
+        <v>2062.06</v>
+      </c>
+      <c r="X16" s="37" t="str">
         <f aca="false">IF(V16&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y16" s="38" t="n">
+      <c r="Y16" s="39" t="n">
         <f aca="false">C16*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A16-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A16)*$D$6:$D$29)</f>
         <v>3</v>
       </c>
-      <c r="Z16" s="38" t="n">
+      <c r="Z16" s="39" t="n">
         <f aca="false">MAX(0,B16-Y16)</f>
         <v>26</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A17" s="34" t="n">
+      <c r="A17" s="35" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="37" t="n">
+      <c r="B17" s="38" t="n">
         <v>31</v>
       </c>
-      <c r="C17" s="37" t="n">
+      <c r="C17" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="D17" s="37" t="n">
+      <c r="D17" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E17" s="38" t="n">
+      <c r="E17" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A17-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A17)*$D$6:$D$29)</f>
         <v>3</v>
       </c>
@@ -4311,24 +4317,24 @@
         <v>9997</v>
       </c>
       <c r="H17" s="15" t="n">
-        <f aca="false">E17*'Premissas Precept'!$B$12</f>
-        <v>14998.5</v>
-      </c>
-      <c r="I17" s="22" t="n">
+        <f aca="false">D17*'Premissas Precept'!$B$10</f>
+        <v>29997</v>
+      </c>
+      <c r="I17" s="23" t="n">
         <f aca="false">F17+G17+H17</f>
-        <v>66911.5</v>
+        <v>81910</v>
       </c>
       <c r="J17" s="15" t="n">
         <f aca="false">AVERAGE(I$6:I16)*12</f>
-        <v>437433.818181818</v>
-      </c>
-      <c r="K17" s="39" t="n">
+        <v>470157.818181818</v>
+      </c>
+      <c r="K17" s="40" t="n">
         <f aca="false">IF(J17&lt;=0,'Premissas Precept'!$C$24,(J17*LOOKUP(J17,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J17,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J17)</f>
-        <v>0.172368004967816</v>
+        <v>0.173943240722264</v>
       </c>
       <c r="L17" s="15" t="n">
         <f aca="false">I17*K17</f>
-        <v>11533.401764404</v>
+        <v>14247.6908475607</v>
       </c>
       <c r="M17" s="15" t="n">
         <f aca="false">B17*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -4336,23 +4342,23 @@
       </c>
       <c r="N17" s="15" t="n">
         <f aca="false">I17*'Premissas Precept'!$B$16</f>
-        <v>1338.23</v>
+        <v>1638.2</v>
       </c>
       <c r="O17" s="15" t="n">
         <f aca="false">(G17+H17)*'Premissas Precept'!$B$17</f>
-        <v>1249.775</v>
+        <v>1999.7</v>
       </c>
       <c r="P17" s="15" t="n">
         <f aca="false">(G17+H17)*'Premissas Precept'!$B$18</f>
-        <v>8748.425</v>
+        <v>13997.9</v>
       </c>
       <c r="Q17" s="15" t="n">
-        <f aca="false">C17*'Premissas Precept'!$B$19+E17*'Premissas Precept'!$B$20</f>
-        <v>1200</v>
-      </c>
-      <c r="R17" s="22" t="n">
+        <f aca="false">C17*'Premissas Precept'!$B$19+D17*'Premissas Precept'!$B$20</f>
+        <v>1800</v>
+      </c>
+      <c r="R17" s="23" t="n">
         <f aca="false">SUM(L17:Q17)</f>
-        <v>27417.831764404</v>
+        <v>37031.4908475607</v>
       </c>
       <c r="S17" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4360,47 +4366,47 @@
       </c>
       <c r="T17" s="15" t="n">
         <f aca="false">IF(A17&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I17,0)</f>
-        <v>16393.3175</v>
-      </c>
-      <c r="U17" s="22" t="n">
+        <v>20067.95</v>
+      </c>
+      <c r="U17" s="23" t="n">
         <f aca="false">S17+T17</f>
-        <v>28393.3175</v>
-      </c>
-      <c r="V17" s="22" t="n">
+        <v>32067.95</v>
+      </c>
+      <c r="V17" s="23" t="n">
         <f aca="false">I17-R17-U17</f>
-        <v>11100.3507355959</v>
+        <v>12810.5591524393</v>
       </c>
       <c r="W17" s="15" t="n">
         <f aca="false">T17/'Premissas Precept'!$B$45</f>
-        <v>2341.9025</v>
-      </c>
-      <c r="X17" s="36" t="str">
+        <v>2866.85</v>
+      </c>
+      <c r="X17" s="37" t="str">
         <f aca="false">IF(V17&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y17" s="38" t="n">
+      <c r="Y17" s="39" t="n">
         <f aca="false">C17*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A17-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A17)*$D$6:$D$29)</f>
         <v>3</v>
       </c>
-      <c r="Z17" s="38" t="n">
+      <c r="Z17" s="39" t="n">
         <f aca="false">MAX(0,B17-Y17)</f>
         <v>28</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A18" s="34" t="n">
+      <c r="A18" s="35" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="37" t="n">
+      <c r="B18" s="38" t="n">
         <v>36</v>
       </c>
-      <c r="C18" s="37" t="n">
+      <c r="C18" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="D18" s="37" t="n">
+      <c r="D18" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E18" s="38" t="n">
+      <c r="E18" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A18-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A18)*$D$6:$D$29)</f>
         <v>4</v>
       </c>
@@ -4413,24 +4419,24 @@
         <v>39988</v>
       </c>
       <c r="H18" s="15" t="n">
-        <f aca="false">E18*'Premissas Precept'!$B$12</f>
-        <v>19998</v>
-      </c>
-      <c r="I18" s="22" t="n">
+        <f aca="false">D18*'Premissas Precept'!$B$10</f>
+        <v>29997</v>
+      </c>
+      <c r="I18" s="23" t="n">
         <f aca="false">F18+G18+H18</f>
-        <v>104896</v>
+        <v>114895</v>
       </c>
       <c r="J18" s="15" t="n">
         <f aca="false">SUM(I6:I17)</f>
-        <v>467892.5</v>
-      </c>
-      <c r="K18" s="39" t="n">
+        <v>512888</v>
+      </c>
+      <c r="K18" s="40" t="n">
         <f aca="false">IF(J18&lt;=0,'Premissas Precept'!$C$24,(J18*LOOKUP(J18,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J18,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J18)</f>
-        <v>0.173841293673226</v>
+        <v>0.175697540203709</v>
       </c>
       <c r="L18" s="15" t="n">
         <f aca="false">I18*K18</f>
-        <v>18235.2563411467</v>
+        <v>20186.7688817052</v>
       </c>
       <c r="M18" s="15" t="n">
         <f aca="false">B18*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -4438,23 +4444,23 @@
       </c>
       <c r="N18" s="15" t="n">
         <f aca="false">I18*'Premissas Precept'!$B$16</f>
-        <v>2097.92</v>
+        <v>2297.9</v>
       </c>
       <c r="O18" s="15" t="n">
         <f aca="false">(G18+H18)*'Premissas Precept'!$B$17</f>
-        <v>2999.3</v>
+        <v>3499.25</v>
       </c>
       <c r="P18" s="15" t="n">
         <f aca="false">(G18+H18)*'Premissas Precept'!$B$18</f>
-        <v>20995.1</v>
+        <v>24494.75</v>
       </c>
       <c r="Q18" s="15" t="n">
-        <f aca="false">C18*'Premissas Precept'!$B$19+E18*'Premissas Precept'!$B$20</f>
-        <v>3200</v>
-      </c>
-      <c r="R18" s="22" t="n">
+        <f aca="false">C18*'Premissas Precept'!$B$19+D18*'Premissas Precept'!$B$20</f>
+        <v>3600</v>
+      </c>
+      <c r="R18" s="23" t="n">
         <f aca="false">SUM(L18:Q18)</f>
-        <v>51415.5763411467</v>
+        <v>57966.6688817052</v>
       </c>
       <c r="S18" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4462,47 +4468,47 @@
       </c>
       <c r="T18" s="15" t="n">
         <f aca="false">IF(A18&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I18,0)</f>
-        <v>25699.52</v>
-      </c>
-      <c r="U18" s="22" t="n">
+        <v>28149.275</v>
+      </c>
+      <c r="U18" s="23" t="n">
         <f aca="false">S18+T18</f>
-        <v>37699.52</v>
-      </c>
-      <c r="V18" s="22" t="n">
+        <v>40149.275</v>
+      </c>
+      <c r="V18" s="23" t="n">
         <f aca="false">I18-R18-U18</f>
-        <v>15780.9036588533</v>
+        <v>16779.0561182948</v>
       </c>
       <c r="W18" s="15" t="n">
         <f aca="false">T18/'Premissas Precept'!$B$45</f>
-        <v>3671.36</v>
-      </c>
-      <c r="X18" s="36" t="str">
+        <v>4021.325</v>
+      </c>
+      <c r="X18" s="37" t="str">
         <f aca="false">IF(V18&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y18" s="38" t="n">
+      <c r="Y18" s="39" t="n">
         <f aca="false">C18*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A18-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A18)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
-      <c r="Z18" s="38" t="n">
+      <c r="Z18" s="39" t="n">
         <f aca="false">MAX(0,B18-Y18)</f>
         <v>30</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A19" s="34" t="n">
+      <c r="A19" s="35" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="37" t="n">
+      <c r="B19" s="38" t="n">
         <v>40</v>
       </c>
-      <c r="C19" s="37" t="n">
+      <c r="C19" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="D19" s="37" t="n">
+      <c r="D19" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E19" s="38" t="n">
+      <c r="E19" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A19-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A19)*$D$6:$D$29)</f>
         <v>4</v>
       </c>
@@ -4515,24 +4521,24 @@
         <v>39988</v>
       </c>
       <c r="H19" s="15" t="n">
-        <f aca="false">E19*'Premissas Precept'!$B$12</f>
-        <v>19998</v>
-      </c>
-      <c r="I19" s="22" t="n">
+        <f aca="false">D19*'Premissas Precept'!$B$10</f>
+        <v>29997</v>
+      </c>
+      <c r="I19" s="23" t="n">
         <f aca="false">F19+G19+H19</f>
-        <v>109387</v>
+        <v>119386</v>
       </c>
       <c r="J19" s="15" t="n">
         <f aca="false">SUM(I7:I18)</f>
-        <v>566800.5</v>
-      </c>
-      <c r="K19" s="39" t="n">
+        <v>621795</v>
+      </c>
+      <c r="K19" s="40" t="n">
         <f aca="false">IF(J19&lt;=0,'Premissas Precept'!$C$24,(J19*LOOKUP(J19,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J19,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J19)</f>
-        <v>0.177533536932307</v>
+        <v>0.179078353798278</v>
       </c>
       <c r="L19" s="15" t="n">
         <f aca="false">I19*K19</f>
-        <v>19419.8610044143</v>
+        <v>21379.4483465612</v>
       </c>
       <c r="M19" s="15" t="n">
         <f aca="false">B19*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -4540,23 +4546,23 @@
       </c>
       <c r="N19" s="15" t="n">
         <f aca="false">I19*'Premissas Precept'!$B$16</f>
-        <v>2187.74</v>
+        <v>2387.72</v>
       </c>
       <c r="O19" s="15" t="n">
         <f aca="false">(G19+H19)*'Premissas Precept'!$B$17</f>
-        <v>2999.3</v>
+        <v>3499.25</v>
       </c>
       <c r="P19" s="15" t="n">
         <f aca="false">(G19+H19)*'Premissas Precept'!$B$18</f>
-        <v>20995.1</v>
+        <v>24494.75</v>
       </c>
       <c r="Q19" s="15" t="n">
-        <f aca="false">C19*'Premissas Precept'!$B$19+E19*'Premissas Precept'!$B$20</f>
-        <v>3200</v>
-      </c>
-      <c r="R19" s="22" t="n">
+        <f aca="false">C19*'Premissas Precept'!$B$19+D19*'Premissas Precept'!$B$20</f>
+        <v>3600</v>
+      </c>
+      <c r="R19" s="23" t="n">
         <f aca="false">SUM(L19:Q19)</f>
-        <v>53122.0010044143</v>
+        <v>59681.1683465612</v>
       </c>
       <c r="S19" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4564,47 +4570,47 @@
       </c>
       <c r="T19" s="15" t="n">
         <f aca="false">IF(A19&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I19,0)</f>
-        <v>26799.815</v>
-      </c>
-      <c r="U19" s="22" t="n">
+        <v>29249.57</v>
+      </c>
+      <c r="U19" s="23" t="n">
         <f aca="false">S19+T19</f>
-        <v>38799.815</v>
-      </c>
-      <c r="V19" s="22" t="n">
+        <v>41249.57</v>
+      </c>
+      <c r="V19" s="23" t="n">
         <f aca="false">I19-R19-U19</f>
-        <v>17465.1839955858</v>
+        <v>18455.2616534388</v>
       </c>
       <c r="W19" s="15" t="n">
         <f aca="false">T19/'Premissas Precept'!$B$45</f>
-        <v>3828.545</v>
-      </c>
-      <c r="X19" s="36" t="str">
+        <v>4178.51</v>
+      </c>
+      <c r="X19" s="37" t="str">
         <f aca="false">IF(V19&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y19" s="38" t="n">
+      <c r="Y19" s="39" t="n">
         <f aca="false">C19*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A19-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A19)*$D$6:$D$29)</f>
         <v>7</v>
       </c>
-      <c r="Z19" s="38" t="n">
+      <c r="Z19" s="39" t="n">
         <f aca="false">MAX(0,B19-Y19)</f>
         <v>33</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A20" s="34" t="n">
+      <c r="A20" s="35" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="37" t="n">
+      <c r="B20" s="38" t="n">
         <v>44</v>
       </c>
-      <c r="C20" s="37" t="n">
+      <c r="C20" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="D20" s="37" t="n">
+      <c r="D20" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E20" s="38" t="n">
+      <c r="E20" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A20-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A20)*$D$6:$D$29)</f>
         <v>5</v>
       </c>
@@ -4617,24 +4623,24 @@
         <v>39988</v>
       </c>
       <c r="H20" s="15" t="n">
-        <f aca="false">E20*'Premissas Precept'!$B$12</f>
-        <v>24997.5</v>
-      </c>
-      <c r="I20" s="22" t="n">
+        <f aca="false">D20*'Premissas Precept'!$B$10</f>
+        <v>29997</v>
+      </c>
+      <c r="I20" s="23" t="n">
         <f aca="false">F20+G20+H20</f>
-        <v>120374.5</v>
+        <v>125374</v>
       </c>
       <c r="J20" s="15" t="n">
         <f aca="false">SUM(I8:I19)</f>
-        <v>667205.5</v>
-      </c>
-      <c r="K20" s="39" t="n">
+        <v>732199</v>
+      </c>
+      <c r="K20" s="40" t="n">
         <f aca="false">IF(J20&lt;=0,'Premissas Precept'!$C$24,(J20*LOOKUP(J20,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J20,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J20)</f>
-        <v>0.180161992819304</v>
+        <v>0.181645693315615</v>
       </c>
       <c r="L20" s="15" t="n">
         <f aca="false">I20*K20</f>
-        <v>21686.9098046273</v>
+        <v>22773.6471537519</v>
       </c>
       <c r="M20" s="15" t="n">
         <f aca="false">B20*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -4642,23 +4648,23 @@
       </c>
       <c r="N20" s="15" t="n">
         <f aca="false">I20*'Premissas Precept'!$B$16</f>
-        <v>2407.49</v>
+        <v>2507.48</v>
       </c>
       <c r="O20" s="15" t="n">
         <f aca="false">(G20+H20)*'Premissas Precept'!$B$17</f>
-        <v>3249.275</v>
+        <v>3499.25</v>
       </c>
       <c r="P20" s="15" t="n">
         <f aca="false">(G20+H20)*'Premissas Precept'!$B$18</f>
-        <v>22744.925</v>
+        <v>24494.75</v>
       </c>
       <c r="Q20" s="15" t="n">
-        <f aca="false">C20*'Premissas Precept'!$B$19+E20*'Premissas Precept'!$B$20</f>
-        <v>3400</v>
-      </c>
-      <c r="R20" s="22" t="n">
+        <f aca="false">C20*'Premissas Precept'!$B$19+D20*'Premissas Precept'!$B$20</f>
+        <v>3600</v>
+      </c>
+      <c r="R20" s="23" t="n">
         <f aca="false">SUM(L20:Q20)</f>
-        <v>58240.5998046273</v>
+        <v>61627.1271537519</v>
       </c>
       <c r="S20" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4666,47 +4672,47 @@
       </c>
       <c r="T20" s="15" t="n">
         <f aca="false">IF(A20&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I20,0)</f>
-        <v>29491.7525</v>
-      </c>
-      <c r="U20" s="22" t="n">
+        <v>30716.63</v>
+      </c>
+      <c r="U20" s="23" t="n">
         <f aca="false">S20+T20</f>
-        <v>41491.7525</v>
-      </c>
-      <c r="V20" s="22" t="n">
+        <v>42716.63</v>
+      </c>
+      <c r="V20" s="23" t="n">
         <f aca="false">I20-R20-U20</f>
-        <v>20642.1476953727</v>
+        <v>21030.2428462481</v>
       </c>
       <c r="W20" s="15" t="n">
         <f aca="false">T20/'Premissas Precept'!$B$45</f>
-        <v>4213.1075</v>
-      </c>
-      <c r="X20" s="36" t="str">
+        <v>4388.09</v>
+      </c>
+      <c r="X20" s="37" t="str">
         <f aca="false">IF(V20&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y20" s="38" t="n">
+      <c r="Y20" s="39" t="n">
         <f aca="false">C20*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A20-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A20)*$D$6:$D$29)</f>
         <v>7</v>
       </c>
-      <c r="Z20" s="38" t="n">
+      <c r="Z20" s="39" t="n">
         <f aca="false">MAX(0,B20-Y20)</f>
         <v>37</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A21" s="34" t="n">
+      <c r="A21" s="35" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="37" t="n">
+      <c r="B21" s="38" t="n">
         <v>48</v>
       </c>
-      <c r="C21" s="37" t="n">
+      <c r="C21" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="D21" s="37" t="n">
+      <c r="D21" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E21" s="38" t="n">
+      <c r="E21" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A21-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A21)*$D$6:$D$29)</f>
         <v>5</v>
       </c>
@@ -4719,24 +4725,24 @@
         <v>39988</v>
       </c>
       <c r="H21" s="15" t="n">
-        <f aca="false">E21*'Premissas Precept'!$B$12</f>
-        <v>24997.5</v>
-      </c>
-      <c r="I21" s="22" t="n">
+        <f aca="false">D21*'Premissas Precept'!$B$10</f>
+        <v>29997</v>
+      </c>
+      <c r="I21" s="23" t="n">
         <f aca="false">F21+G21+H21</f>
-        <v>126362.5</v>
+        <v>131362</v>
       </c>
       <c r="J21" s="15" t="n">
         <f aca="false">SUM(I9:I20)</f>
-        <v>774107</v>
-      </c>
-      <c r="K21" s="39" t="n">
+        <v>844100</v>
+      </c>
+      <c r="K21" s="40" t="n">
         <f aca="false">IF(J21&lt;=0,'Premissas Precept'!$C$24,(J21*LOOKUP(J21,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J21,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J21)</f>
-        <v>0.182910030525496</v>
+        <v>0.184741736761047</v>
       </c>
       <c r="L21" s="15" t="n">
         <f aca="false">I21*K21</f>
-        <v>23112.968732278</v>
+        <v>24268.0440244047</v>
       </c>
       <c r="M21" s="15" t="n">
         <f aca="false">B21*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -4744,23 +4750,23 @@
       </c>
       <c r="N21" s="15" t="n">
         <f aca="false">I21*'Premissas Precept'!$B$16</f>
-        <v>2527.25</v>
+        <v>2627.24</v>
       </c>
       <c r="O21" s="15" t="n">
         <f aca="false">(G21+H21)*'Premissas Precept'!$B$17</f>
-        <v>3249.275</v>
+        <v>3499.25</v>
       </c>
       <c r="P21" s="15" t="n">
         <f aca="false">(G21+H21)*'Premissas Precept'!$B$18</f>
-        <v>22744.925</v>
+        <v>24494.75</v>
       </c>
       <c r="Q21" s="15" t="n">
-        <f aca="false">C21*'Premissas Precept'!$B$19+E21*'Premissas Precept'!$B$20</f>
-        <v>3400</v>
-      </c>
-      <c r="R21" s="22" t="n">
+        <f aca="false">C21*'Premissas Precept'!$B$19+D21*'Premissas Precept'!$B$20</f>
+        <v>3600</v>
+      </c>
+      <c r="R21" s="23" t="n">
         <f aca="false">SUM(L21:Q21)</f>
-        <v>60218.418732278</v>
+        <v>63673.2840244047</v>
       </c>
       <c r="S21" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4768,47 +4774,47 @@
       </c>
       <c r="T21" s="15" t="n">
         <f aca="false">IF(A21&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I21,0)</f>
-        <v>30958.8125</v>
-      </c>
-      <c r="U21" s="22" t="n">
+        <v>32183.69</v>
+      </c>
+      <c r="U21" s="23" t="n">
         <f aca="false">S21+T21</f>
-        <v>42958.8125</v>
-      </c>
-      <c r="V21" s="22" t="n">
+        <v>44183.69</v>
+      </c>
+      <c r="V21" s="23" t="n">
         <f aca="false">I21-R21-U21</f>
-        <v>23185.268767722</v>
+        <v>23505.0259755953</v>
       </c>
       <c r="W21" s="15" t="n">
         <f aca="false">T21/'Premissas Precept'!$B$45</f>
-        <v>4422.6875</v>
-      </c>
-      <c r="X21" s="36" t="str">
+        <v>4597.67</v>
+      </c>
+      <c r="X21" s="37" t="str">
         <f aca="false">IF(V21&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y21" s="38" t="n">
+      <c r="Y21" s="39" t="n">
         <f aca="false">C21*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A21-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A21)*$D$6:$D$29)</f>
         <v>7</v>
       </c>
-      <c r="Z21" s="38" t="n">
+      <c r="Z21" s="39" t="n">
         <f aca="false">MAX(0,B21-Y21)</f>
         <v>41</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A22" s="34" t="n">
+      <c r="A22" s="35" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="37" t="n">
+      <c r="B22" s="38" t="n">
         <v>51</v>
       </c>
-      <c r="C22" s="37" t="n">
+      <c r="C22" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="D22" s="37" t="n">
+      <c r="D22" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E22" s="38" t="n">
+      <c r="E22" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A22-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A22)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
@@ -4821,24 +4827,24 @@
         <v>39988</v>
       </c>
       <c r="H22" s="15" t="n">
-        <f aca="false">E22*'Premissas Precept'!$B$12</f>
+        <f aca="false">D22*'Premissas Precept'!$B$10</f>
         <v>29997</v>
       </c>
-      <c r="I22" s="22" t="n">
+      <c r="I22" s="23" t="n">
         <f aca="false">F22+G22+H22</f>
         <v>135853</v>
       </c>
       <c r="J22" s="15" t="n">
         <f aca="false">SUM(I10:I21)</f>
-        <v>875502.5</v>
-      </c>
-      <c r="K22" s="39" t="n">
+        <v>950495</v>
+      </c>
+      <c r="K22" s="40" t="n">
         <f aca="false">IF(J22&lt;=0,'Premissas Precept'!$C$24,(J22*LOOKUP(J22,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J22,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J22)</f>
-        <v>0.185468359599202</v>
+        <v>0.187009374062988</v>
       </c>
       <c r="L22" s="15" t="n">
         <f aca="false">I22*K22</f>
-        <v>25196.4330566303</v>
+        <v>25405.7844945791</v>
       </c>
       <c r="M22" s="15" t="n">
         <f aca="false">B22*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -4857,12 +4863,12 @@
         <v>24494.75</v>
       </c>
       <c r="Q22" s="15" t="n">
-        <f aca="false">C22*'Premissas Precept'!$B$19+E22*'Premissas Precept'!$B$20</f>
+        <f aca="false">C22*'Premissas Precept'!$B$19+D22*'Premissas Precept'!$B$20</f>
         <v>3600</v>
       </c>
-      <c r="R22" s="22" t="n">
+      <c r="R22" s="23" t="n">
         <f aca="false">SUM(L22:Q22)</f>
-        <v>65015.4930566303</v>
+        <v>65224.8444945791</v>
       </c>
       <c r="S22" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4872,45 +4878,45 @@
         <f aca="false">IF(A22&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I22,0)</f>
         <v>33283.985</v>
       </c>
-      <c r="U22" s="22" t="n">
+      <c r="U22" s="23" t="n">
         <f aca="false">S22+T22</f>
         <v>45283.985</v>
       </c>
-      <c r="V22" s="22" t="n">
+      <c r="V22" s="23" t="n">
         <f aca="false">I22-R22-U22</f>
-        <v>25553.5219433697</v>
+        <v>25344.1705054209</v>
       </c>
       <c r="W22" s="15" t="n">
         <f aca="false">T22/'Premissas Precept'!$B$45</f>
         <v>4754.855</v>
       </c>
-      <c r="X22" s="36" t="str">
+      <c r="X22" s="37" t="str">
         <f aca="false">IF(V22&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y22" s="38" t="n">
+      <c r="Y22" s="39" t="n">
         <f aca="false">C22*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A22-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A22)*$D$6:$D$29)</f>
         <v>7</v>
       </c>
-      <c r="Z22" s="38" t="n">
+      <c r="Z22" s="39" t="n">
         <f aca="false">MAX(0,B22-Y22)</f>
         <v>44</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A23" s="34" t="n">
+      <c r="A23" s="35" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="37" t="n">
+      <c r="B23" s="38" t="n">
         <v>55</v>
       </c>
-      <c r="C23" s="37" t="n">
+      <c r="C23" s="38" t="n">
         <v>4</v>
       </c>
-      <c r="D23" s="37" t="n">
+      <c r="D23" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E23" s="38" t="n">
+      <c r="E23" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A23-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A23)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
@@ -4923,24 +4929,24 @@
         <v>39988</v>
       </c>
       <c r="H23" s="15" t="n">
-        <f aca="false">E23*'Premissas Precept'!$B$12</f>
+        <f aca="false">D23*'Premissas Precept'!$B$10</f>
         <v>29997</v>
       </c>
-      <c r="I23" s="22" t="n">
+      <c r="I23" s="23" t="n">
         <f aca="false">F23+G23+H23</f>
         <v>141841</v>
       </c>
       <c r="J23" s="15" t="n">
         <f aca="false">SUM(I11:I22)</f>
-        <v>981897.5</v>
-      </c>
-      <c r="K23" s="39" t="n">
+        <v>1056890</v>
+      </c>
+      <c r="K23" s="40" t="n">
         <f aca="false">IF(J23&lt;=0,'Premissas Precept'!$C$24,(J23*LOOKUP(J23,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J23,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J23)</f>
-        <v>0.187584740260567</v>
+        <v>0.188820454351919</v>
       </c>
       <c r="L23" s="15" t="n">
         <f aca="false">I23*K23</f>
-        <v>26607.2071432991</v>
+        <v>26782.4820657306</v>
       </c>
       <c r="M23" s="15" t="n">
         <f aca="false">B23*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -4959,12 +4965,12 @@
         <v>24494.75</v>
       </c>
       <c r="Q23" s="15" t="n">
-        <f aca="false">C23*'Premissas Precept'!$B$19+E23*'Premissas Precept'!$B$20</f>
+        <f aca="false">C23*'Premissas Precept'!$B$19+D23*'Premissas Precept'!$B$20</f>
         <v>3600</v>
       </c>
-      <c r="R23" s="22" t="n">
+      <c r="R23" s="23" t="n">
         <f aca="false">SUM(L23:Q23)</f>
-        <v>66978.0271432991</v>
+        <v>67153.3020657306</v>
       </c>
       <c r="S23" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -4974,45 +4980,45 @@
         <f aca="false">IF(A23&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I23,0)</f>
         <v>34751.045</v>
       </c>
-      <c r="U23" s="22" t="n">
+      <c r="U23" s="23" t="n">
         <f aca="false">S23+T23</f>
         <v>46751.045</v>
       </c>
-      <c r="V23" s="22" t="n">
+      <c r="V23" s="23" t="n">
         <f aca="false">I23-R23-U23</f>
-        <v>28111.9278567009</v>
+        <v>27936.6529342694</v>
       </c>
       <c r="W23" s="15" t="n">
         <f aca="false">T23/'Premissas Precept'!$B$45</f>
         <v>4964.435</v>
       </c>
-      <c r="X23" s="36" t="str">
+      <c r="X23" s="37" t="str">
         <f aca="false">IF(V23&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y23" s="38" t="n">
+      <c r="Y23" s="39" t="n">
         <f aca="false">C23*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A23-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A23)*$D$6:$D$29)</f>
         <v>7</v>
       </c>
-      <c r="Z23" s="38" t="n">
+      <c r="Z23" s="39" t="n">
         <f aca="false">MAX(0,B23-Y23)</f>
         <v>48</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A24" s="34" t="n">
+      <c r="A24" s="35" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="37" t="n">
+      <c r="B24" s="38" t="n">
         <v>60</v>
       </c>
-      <c r="C24" s="37" t="n">
+      <c r="C24" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="D24" s="37" t="n">
+      <c r="D24" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E24" s="38" t="n">
+      <c r="E24" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A24-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A24)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
@@ -5025,24 +5031,24 @@
         <v>49985</v>
       </c>
       <c r="H24" s="15" t="n">
-        <f aca="false">E24*'Premissas Precept'!$B$12</f>
+        <f aca="false">D24*'Premissas Precept'!$B$10</f>
         <v>29997</v>
       </c>
-      <c r="I24" s="22" t="n">
+      <c r="I24" s="23" t="n">
         <f aca="false">F24+G24+H24</f>
         <v>157826</v>
       </c>
       <c r="J24" s="15" t="n">
         <f aca="false">SUM(I12:I23)</f>
-        <v>1087784</v>
-      </c>
-      <c r="K24" s="39" t="n">
+        <v>1137779</v>
+      </c>
+      <c r="K24" s="40" t="n">
         <f aca="false">IF(J24&lt;=0,'Premissas Precept'!$C$24,(J24*LOOKUP(J24,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J24,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J24)</f>
-        <v>0.189279967346459</v>
+        <v>0.189970719269735</v>
       </c>
       <c r="L24" s="15" t="n">
         <f aca="false">I24*K24</f>
-        <v>29873.3001264222</v>
+        <v>29982.3187394652</v>
       </c>
       <c r="M24" s="15" t="n">
         <f aca="false">B24*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -5061,12 +5067,12 @@
         <v>27993.7</v>
       </c>
       <c r="Q24" s="15" t="n">
-        <f aca="false">C24*'Premissas Precept'!$B$19+E24*'Premissas Precept'!$B$20</f>
+        <f aca="false">C24*'Premissas Precept'!$B$19+D24*'Premissas Precept'!$B$20</f>
         <v>4200</v>
       </c>
-      <c r="R24" s="22" t="n">
+      <c r="R24" s="23" t="n">
         <f aca="false">SUM(L24:Q24)</f>
-        <v>75702.6201264222</v>
+        <v>75811.6387394652</v>
       </c>
       <c r="S24" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5076,45 +5082,45 @@
         <f aca="false">IF(A24&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I24,0)</f>
         <v>38667.37</v>
       </c>
-      <c r="U24" s="22" t="n">
+      <c r="U24" s="23" t="n">
         <f aca="false">S24+T24</f>
         <v>50667.37</v>
       </c>
-      <c r="V24" s="22" t="n">
+      <c r="V24" s="23" t="n">
         <f aca="false">I24-R24-U24</f>
-        <v>31456.0098735778</v>
+        <v>31346.9912605348</v>
       </c>
       <c r="W24" s="15" t="n">
         <f aca="false">T24/'Premissas Precept'!$B$45</f>
         <v>5523.91</v>
       </c>
-      <c r="X24" s="36" t="str">
+      <c r="X24" s="37" t="str">
         <f aca="false">IF(V24&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y24" s="38" t="n">
+      <c r="Y24" s="39" t="n">
         <f aca="false">C24*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A24-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A24)*$D$6:$D$29)</f>
         <v>8</v>
       </c>
-      <c r="Z24" s="38" t="n">
+      <c r="Z24" s="39" t="n">
         <f aca="false">MAX(0,B24-Y24)</f>
         <v>52</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A25" s="34" t="n">
+      <c r="A25" s="35" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="37" t="n">
+      <c r="B25" s="38" t="n">
         <v>64</v>
       </c>
-      <c r="C25" s="37" t="n">
+      <c r="C25" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="D25" s="37" t="n">
+      <c r="D25" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E25" s="38" t="n">
+      <c r="E25" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A25-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A25)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
@@ -5127,24 +5133,24 @@
         <v>49985</v>
       </c>
       <c r="H25" s="15" t="n">
-        <f aca="false">E25*'Premissas Precept'!$B$12</f>
+        <f aca="false">D25*'Premissas Precept'!$B$10</f>
         <v>29997</v>
       </c>
-      <c r="I25" s="22" t="n">
+      <c r="I25" s="23" t="n">
         <f aca="false">F25+G25+H25</f>
         <v>163814</v>
       </c>
       <c r="J25" s="15" t="n">
         <f aca="false">SUM(I13:I24)</f>
-        <v>1205164.5</v>
-      </c>
-      <c r="K25" s="39" t="n">
+        <v>1260159</v>
+      </c>
+      <c r="K25" s="40" t="n">
         <f aca="false">IF(J25&lt;=0,'Premissas Precept'!$C$24,(J25*LOOKUP(J25,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J25,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J25)</f>
-        <v>0.190811065626311</v>
+        <v>0.191430283797521</v>
       </c>
       <c r="L25" s="15" t="n">
         <f aca="false">I25*K25</f>
-        <v>31257.5239045085</v>
+        <v>31358.9605100071</v>
       </c>
       <c r="M25" s="15" t="n">
         <f aca="false">B25*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -5163,12 +5169,12 @@
         <v>27993.7</v>
       </c>
       <c r="Q25" s="15" t="n">
-        <f aca="false">C25*'Premissas Precept'!$B$19+E25*'Premissas Precept'!$B$20</f>
+        <f aca="false">C25*'Premissas Precept'!$B$19+D25*'Premissas Precept'!$B$20</f>
         <v>4200</v>
       </c>
-      <c r="R25" s="22" t="n">
+      <c r="R25" s="23" t="n">
         <f aca="false">SUM(L25:Q25)</f>
-        <v>77638.6039045085</v>
+        <v>77740.0405100071</v>
       </c>
       <c r="S25" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5178,45 +5184,45 @@
         <f aca="false">IF(A25&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I25,0)</f>
         <v>40134.43</v>
       </c>
-      <c r="U25" s="22" t="n">
+      <c r="U25" s="23" t="n">
         <f aca="false">S25+T25</f>
         <v>52134.43</v>
       </c>
-      <c r="V25" s="22" t="n">
+      <c r="V25" s="23" t="n">
         <f aca="false">I25-R25-U25</f>
-        <v>34040.9660954915</v>
+        <v>33939.5294899929</v>
       </c>
       <c r="W25" s="15" t="n">
         <f aca="false">T25/'Premissas Precept'!$B$45</f>
         <v>5733.49</v>
       </c>
-      <c r="X25" s="36" t="str">
+      <c r="X25" s="37" t="str">
         <f aca="false">IF(V25&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y25" s="38" t="n">
+      <c r="Y25" s="39" t="n">
         <f aca="false">C25*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A25-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A25)*$D$6:$D$29)</f>
         <v>8</v>
       </c>
-      <c r="Z25" s="38" t="n">
+      <c r="Z25" s="39" t="n">
         <f aca="false">MAX(0,B25-Y25)</f>
         <v>56</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A26" s="34" t="n">
+      <c r="A26" s="35" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="37" t="n">
+      <c r="B26" s="38" t="n">
         <v>68</v>
       </c>
-      <c r="C26" s="37" t="n">
+      <c r="C26" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="D26" s="37" t="n">
+      <c r="D26" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E26" s="38" t="n">
+      <c r="E26" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A26-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A26)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
@@ -5229,24 +5235,24 @@
         <v>49985</v>
       </c>
       <c r="H26" s="15" t="n">
-        <f aca="false">E26*'Premissas Precept'!$B$12</f>
+        <f aca="false">D26*'Premissas Precept'!$B$10</f>
         <v>29997</v>
       </c>
-      <c r="I26" s="22" t="n">
+      <c r="I26" s="23" t="n">
         <f aca="false">F26+G26+H26</f>
         <v>169802</v>
       </c>
       <c r="J26" s="15" t="n">
         <f aca="false">SUM(I14:I25)</f>
-        <v>1322036.5</v>
-      </c>
-      <c r="K26" s="39" t="n">
+        <v>1357033</v>
+      </c>
+      <c r="K26" s="40" t="n">
         <f aca="false">IF(J26&lt;=0,'Premissas Precept'!$C$24,(J26*LOOKUP(J26,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J26,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J26)</f>
-        <v>0.192065410069994</v>
+        <v>0.19239897998059</v>
       </c>
       <c r="L26" s="15" t="n">
         <f aca="false">I26*K26</f>
-        <v>32613.0907607052</v>
+        <v>32669.7315986641</v>
       </c>
       <c r="M26" s="15" t="n">
         <f aca="false">B26*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -5265,12 +5271,12 @@
         <v>27993.7</v>
       </c>
       <c r="Q26" s="15" t="n">
-        <f aca="false">C26*'Premissas Precept'!$B$19+E26*'Premissas Precept'!$B$20</f>
+        <f aca="false">C26*'Premissas Precept'!$B$19+D26*'Premissas Precept'!$B$20</f>
         <v>4200</v>
       </c>
-      <c r="R26" s="22" t="n">
+      <c r="R26" s="23" t="n">
         <f aca="false">SUM(L26:Q26)</f>
-        <v>79545.9307607052</v>
+        <v>79602.5715986641</v>
       </c>
       <c r="S26" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5280,45 +5286,45 @@
         <f aca="false">IF(A26&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I26,0)</f>
         <v>41601.49</v>
       </c>
-      <c r="U26" s="22" t="n">
+      <c r="U26" s="23" t="n">
         <f aca="false">S26+T26</f>
         <v>53601.49</v>
       </c>
-      <c r="V26" s="22" t="n">
+      <c r="V26" s="23" t="n">
         <f aca="false">I26-R26-U26</f>
-        <v>36654.5792392948</v>
+        <v>36597.9384013359</v>
       </c>
       <c r="W26" s="15" t="n">
         <f aca="false">T26/'Premissas Precept'!$B$45</f>
         <v>5943.07</v>
       </c>
-      <c r="X26" s="36" t="str">
+      <c r="X26" s="37" t="str">
         <f aca="false">IF(V26&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y26" s="38" t="n">
+      <c r="Y26" s="39" t="n">
         <f aca="false">C26*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A26-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A26)*$D$6:$D$29)</f>
         <v>8</v>
       </c>
-      <c r="Z26" s="38" t="n">
+      <c r="Z26" s="39" t="n">
         <f aca="false">MAX(0,B26-Y26)</f>
         <v>60</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A27" s="34" t="n">
+      <c r="A27" s="35" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="37" t="n">
+      <c r="B27" s="38" t="n">
         <v>71</v>
       </c>
-      <c r="C27" s="37" t="n">
+      <c r="C27" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="D27" s="37" t="n">
+      <c r="D27" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E27" s="38" t="n">
+      <c r="E27" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A27-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A27)*$D$6:$D$29)</f>
         <v>6</v>
       </c>
@@ -5331,24 +5337,24 @@
         <v>49985</v>
       </c>
       <c r="H27" s="15" t="n">
-        <f aca="false">E27*'Premissas Precept'!$B$12</f>
+        <f aca="false">D27*'Premissas Precept'!$B$10</f>
         <v>29997</v>
       </c>
-      <c r="I27" s="22" t="n">
+      <c r="I27" s="23" t="n">
         <f aca="false">F27+G27+H27</f>
         <v>174293</v>
       </c>
       <c r="J27" s="15" t="n">
         <f aca="false">SUM(I15:I26)</f>
-        <v>1430408.5</v>
-      </c>
-      <c r="K27" s="39" t="n">
+        <v>1475404</v>
+      </c>
+      <c r="K27" s="40" t="n">
         <f aca="false">IF(J27&lt;=0,'Premissas Precept'!$C$24,(J27*LOOKUP(J27,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J27,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J27)</f>
-        <v>0.193045373052523</v>
+        <v>0.19340995415493</v>
       </c>
       <c r="L27" s="15" t="n">
         <f aca="false">I27*K27</f>
-        <v>33646.4572054434</v>
+        <v>33710.0011395252</v>
       </c>
       <c r="M27" s="15" t="n">
         <f aca="false">B27*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -5367,12 +5373,12 @@
         <v>27993.7</v>
       </c>
       <c r="Q27" s="15" t="n">
-        <f aca="false">C27*'Premissas Precept'!$B$19+E27*'Premissas Precept'!$B$20</f>
+        <f aca="false">C27*'Premissas Precept'!$B$19+D27*'Premissas Precept'!$B$20</f>
         <v>4200</v>
       </c>
-      <c r="R27" s="22" t="n">
+      <c r="R27" s="23" t="n">
         <f aca="false">SUM(L27:Q27)</f>
-        <v>80993.1172054434</v>
+        <v>81056.6611395252</v>
       </c>
       <c r="S27" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5382,45 +5388,45 @@
         <f aca="false">IF(A27&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I27,0)</f>
         <v>42701.785</v>
       </c>
-      <c r="U27" s="22" t="n">
+      <c r="U27" s="23" t="n">
         <f aca="false">S27+T27</f>
         <v>54701.785</v>
       </c>
-      <c r="V27" s="22" t="n">
+      <c r="V27" s="23" t="n">
         <f aca="false">I27-R27-U27</f>
-        <v>38598.0977945566</v>
+        <v>38534.5538604748</v>
       </c>
       <c r="W27" s="15" t="n">
         <f aca="false">T27/'Premissas Precept'!$B$45</f>
         <v>6100.255</v>
       </c>
-      <c r="X27" s="36" t="str">
+      <c r="X27" s="37" t="str">
         <f aca="false">IF(V27&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y27" s="38" t="n">
+      <c r="Y27" s="39" t="n">
         <f aca="false">C27*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A27-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A27)*$D$6:$D$29)</f>
         <v>8</v>
       </c>
-      <c r="Z27" s="38" t="n">
+      <c r="Z27" s="39" t="n">
         <f aca="false">MAX(0,B27-Y27)</f>
         <v>63</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A28" s="34" t="n">
+      <c r="A28" s="35" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="37" t="n">
+      <c r="B28" s="38" t="n">
         <v>76</v>
       </c>
-      <c r="C28" s="37" t="n">
+      <c r="C28" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="D28" s="37" t="n">
-        <v>0</v>
-      </c>
-      <c r="E28" s="38" t="n">
+      <c r="D28" s="38" t="n">
+        <v>0</v>
+      </c>
+      <c r="E28" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A28-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A28)*$D$6:$D$29)</f>
         <v>5</v>
       </c>
@@ -5433,24 +5439,24 @@
         <v>49985</v>
       </c>
       <c r="H28" s="15" t="n">
-        <f aca="false">E28*'Premissas Precept'!$B$12</f>
-        <v>24997.5</v>
-      </c>
-      <c r="I28" s="22" t="n">
+        <f aca="false">D28*'Premissas Precept'!$B$10</f>
+        <v>0</v>
+      </c>
+      <c r="I28" s="23" t="n">
         <f aca="false">F28+G28+H28</f>
-        <v>178275.5</v>
+        <v>153278</v>
       </c>
       <c r="J28" s="15" t="n">
         <f aca="false">SUM(I16:I27)</f>
-        <v>1545275</v>
-      </c>
-      <c r="K28" s="39" t="n">
+        <v>1575272</v>
+      </c>
+      <c r="K28" s="40" t="n">
         <f aca="false">IF(J28&lt;=0,'Premissas Precept'!$C$24,(J28*LOOKUP(J28,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J28,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J28)</f>
-        <v>0.193934008509812</v>
+        <v>0.194144731830439</v>
       </c>
       <c r="L28" s="15" t="n">
         <f aca="false">I28*K28</f>
-        <v>34573.682334091</v>
+        <v>29758.1162055061</v>
       </c>
       <c r="M28" s="15" t="n">
         <f aca="false">B28*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -5458,23 +5464,23 @@
       </c>
       <c r="N28" s="15" t="n">
         <f aca="false">I28*'Premissas Precept'!$B$16</f>
-        <v>3565.51</v>
+        <v>3065.56</v>
       </c>
       <c r="O28" s="15" t="n">
         <f aca="false">(G28+H28)*'Premissas Precept'!$B$17</f>
-        <v>3749.125</v>
+        <v>2499.25</v>
       </c>
       <c r="P28" s="15" t="n">
         <f aca="false">(G28+H28)*'Premissas Precept'!$B$18</f>
-        <v>26243.875</v>
+        <v>17494.75</v>
       </c>
       <c r="Q28" s="15" t="n">
-        <f aca="false">C28*'Premissas Precept'!$B$19+E28*'Premissas Precept'!$B$20</f>
-        <v>4000</v>
-      </c>
-      <c r="R28" s="22" t="n">
+        <f aca="false">C28*'Premissas Precept'!$B$19+D28*'Premissas Precept'!$B$20</f>
+        <v>3000</v>
+      </c>
+      <c r="R28" s="23" t="n">
         <f aca="false">SUM(L28:Q28)</f>
-        <v>80340.192334091</v>
+        <v>64025.6762055061</v>
       </c>
       <c r="S28" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5482,47 +5488,47 @@
       </c>
       <c r="T28" s="15" t="n">
         <f aca="false">IF(A28&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I28,0)</f>
-        <v>43677.4975</v>
-      </c>
-      <c r="U28" s="22" t="n">
+        <v>37553.11</v>
+      </c>
+      <c r="U28" s="23" t="n">
         <f aca="false">S28+T28</f>
-        <v>55677.4975</v>
-      </c>
-      <c r="V28" s="22" t="n">
+        <v>49553.11</v>
+      </c>
+      <c r="V28" s="23" t="n">
         <f aca="false">I28-R28-U28</f>
-        <v>42257.810165909</v>
+        <v>39699.2137944939</v>
       </c>
       <c r="W28" s="15" t="n">
         <f aca="false">T28/'Premissas Precept'!$B$45</f>
-        <v>6239.6425</v>
-      </c>
-      <c r="X28" s="36" t="str">
+        <v>5364.73</v>
+      </c>
+      <c r="X28" s="37" t="str">
         <f aca="false">IF(V28&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y28" s="38" t="n">
+      <c r="Y28" s="39" t="n">
         <f aca="false">C28*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A28-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A28)*$D$6:$D$29)</f>
         <v>7</v>
       </c>
-      <c r="Z28" s="38" t="n">
+      <c r="Z28" s="39" t="n">
         <f aca="false">MAX(0,B28-Y28)</f>
         <v>69</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A29" s="34" t="n">
+      <c r="A29" s="35" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="37" t="n">
+      <c r="B29" s="38" t="n">
         <v>79</v>
       </c>
-      <c r="C29" s="37" t="n">
+      <c r="C29" s="38" t="n">
         <v>5</v>
       </c>
-      <c r="D29" s="37" t="n">
+      <c r="D29" s="38" t="n">
         <v>1</v>
       </c>
-      <c r="E29" s="38" t="n">
+      <c r="E29" s="39" t="n">
         <f aca="false">SUMPRODUCT(($A$6:$A$29&gt;A29-'Premissas Precept'!$B$11)*($A$6:$A$29&lt;=A29)*$D$6:$D$29)</f>
         <v>5</v>
       </c>
@@ -5535,24 +5541,24 @@
         <v>49985</v>
       </c>
       <c r="H29" s="15" t="n">
-        <f aca="false">E29*'Premissas Precept'!$B$12</f>
-        <v>24997.5</v>
-      </c>
-      <c r="I29" s="22" t="n">
+        <f aca="false">D29*'Premissas Precept'!$B$10</f>
+        <v>29997</v>
+      </c>
+      <c r="I29" s="23" t="n">
         <f aca="false">F29+G29+H29</f>
-        <v>182766.5</v>
+        <v>187766</v>
       </c>
       <c r="J29" s="15" t="n">
         <f aca="false">SUM(I17:I28)</f>
-        <v>1649636</v>
-      </c>
-      <c r="K29" s="39" t="n">
+        <v>1669634</v>
+      </c>
+      <c r="K29" s="40" t="n">
         <f aca="false">IF(J29&lt;=0,'Premissas Precept'!$C$24,(J29*LOOKUP(J29,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$C$24:$C$29)-LOOKUP(J29,'Premissas Precept'!$B$24:$B$29,'Premissas Precept'!$D$24:$D$29))/J29)</f>
-        <v>0.194634076850893</v>
+        <v>0.194758234439404</v>
       </c>
       <c r="L29" s="15" t="n">
         <f aca="false">I29*K29</f>
-        <v>35572.5890067688</v>
+        <v>36568.9746477491</v>
       </c>
       <c r="M29" s="15" t="n">
         <f aca="false">B29*('Premissas Precept'!$B$15+'Premissas Precept'!$B$89*'Premissas Precept'!$B$90)</f>
@@ -5560,23 +5566,23 @@
       </c>
       <c r="N29" s="15" t="n">
         <f aca="false">I29*'Premissas Precept'!$B$16</f>
-        <v>3655.33</v>
+        <v>3755.32</v>
       </c>
       <c r="O29" s="15" t="n">
         <f aca="false">(G29+H29)*'Premissas Precept'!$B$17</f>
-        <v>3749.125</v>
+        <v>3999.1</v>
       </c>
       <c r="P29" s="15" t="n">
         <f aca="false">(G29+H29)*'Premissas Precept'!$B$18</f>
-        <v>26243.875</v>
+        <v>27993.7</v>
       </c>
       <c r="Q29" s="15" t="n">
-        <f aca="false">C29*'Premissas Precept'!$B$19+E29*'Premissas Precept'!$B$20</f>
-        <v>4000</v>
-      </c>
-      <c r="R29" s="22" t="n">
+        <f aca="false">C29*'Premissas Precept'!$B$19+D29*'Premissas Precept'!$B$20</f>
+        <v>4200</v>
+      </c>
+      <c r="R29" s="23" t="n">
         <f aca="false">SUM(L29:Q29)</f>
-        <v>81752.9190067688</v>
+        <v>85049.0946477491</v>
       </c>
       <c r="S29" s="15" t="n">
         <f aca="false">'Premissas Precept'!$B$42</f>
@@ -5584,177 +5590,177 @@
       </c>
       <c r="T29" s="15" t="n">
         <f aca="false">IF(A29&gt;='Premissas Precept'!$B$47,'Premissas Precept'!$B$48*I29,0)</f>
-        <v>44777.7925</v>
-      </c>
-      <c r="U29" s="22" t="n">
+        <v>46002.67</v>
+      </c>
+      <c r="U29" s="23" t="n">
         <f aca="false">S29+T29</f>
-        <v>56777.7925</v>
-      </c>
-      <c r="V29" s="22" t="n">
+        <v>58002.67</v>
+      </c>
+      <c r="V29" s="23" t="n">
         <f aca="false">I29-R29-U29</f>
-        <v>44235.7884932312</v>
+        <v>44714.2353522509</v>
       </c>
       <c r="W29" s="15" t="n">
         <f aca="false">T29/'Premissas Precept'!$B$45</f>
-        <v>6396.8275</v>
-      </c>
-      <c r="X29" s="36" t="str">
+        <v>6571.81</v>
+      </c>
+      <c r="X29" s="37" t="str">
         <f aca="false">IF(V29&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
-      <c r="Y29" s="38" t="n">
+      <c r="Y29" s="39" t="n">
         <f aca="false">C29*'Premissas Precept'!$B$91+SUMPRODUCT(($A$6:$A$29&gt;A29-'Premissas Precept'!$B$92)*($A$6:$A$29&lt;=A29)*$D$6:$D$29)</f>
         <v>7</v>
       </c>
-      <c r="Z29" s="38" t="n">
+      <c r="Z29" s="39" t="n">
         <f aca="false">MAX(0,B29-Y29)</f>
         <v>72</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A30" s="40" t="s">
-        <v>196</v>
-      </c>
-      <c r="B30" s="41" t="n">
+      <c r="A30" s="41" t="s">
+        <v>197</v>
+      </c>
+      <c r="B30" s="42" t="n">
         <f aca="false">SUM(B6:B29)</f>
         <v>902</v>
       </c>
-      <c r="C30" s="41" t="n">
+      <c r="C30" s="42" t="n">
         <f aca="false">SUM(C6:C29)</f>
         <v>65</v>
       </c>
-      <c r="D30" s="41" t="n">
+      <c r="D30" s="42" t="n">
         <f aca="false">SUM(D6:D29)</f>
         <v>15</v>
       </c>
-      <c r="E30" s="32"/>
-      <c r="F30" s="22" t="n">
+      <c r="E30" s="33"/>
+      <c r="F30" s="23" t="n">
         <f aca="false">SUM(F6:F29)</f>
         <v>1188618</v>
       </c>
-      <c r="G30" s="22" t="n">
+      <c r="G30" s="23" t="n">
         <f aca="false">SUM(G6:G29)</f>
         <v>649805</v>
       </c>
-      <c r="H30" s="22" t="n">
+      <c r="H30" s="23" t="n">
         <f aca="false">SUM(H6:H29)</f>
-        <v>394960.5</v>
-      </c>
-      <c r="I30" s="22" t="n">
+        <v>449955</v>
+      </c>
+      <c r="I30" s="23" t="n">
         <f aca="false">SUM(I6:I29)</f>
-        <v>2233383.5</v>
-      </c>
-      <c r="J30" s="32"/>
-      <c r="K30" s="32"/>
-      <c r="L30" s="22" t="n">
+        <v>2288378</v>
+      </c>
+      <c r="J30" s="33"/>
+      <c r="K30" s="33"/>
+      <c r="L30" s="23" t="n">
         <f aca="false">SUM(L6:L29)</f>
-        <v>408681.691553622</v>
-      </c>
-      <c r="M30" s="22" t="n">
+        <v>419912.293739298</v>
+      </c>
+      <c r="M30" s="23" t="n">
         <f aca="false">SUM(M6:M29)</f>
         <v>97416</v>
       </c>
-      <c r="N30" s="22" t="n">
+      <c r="N30" s="23" t="n">
         <f aca="false">SUM(N6:N29)</f>
-        <v>44667.67</v>
-      </c>
-      <c r="O30" s="22" t="n">
+        <v>45767.56</v>
+      </c>
+      <c r="O30" s="23" t="n">
         <f aca="false">SUM(O6:O29)</f>
-        <v>52238.275</v>
-      </c>
-      <c r="P30" s="22" t="n">
+        <v>54988</v>
+      </c>
+      <c r="P30" s="23" t="n">
         <f aca="false">SUM(P6:P29)</f>
-        <v>365667.925</v>
-      </c>
-      <c r="Q30" s="22" t="n">
+        <v>384916</v>
+      </c>
+      <c r="Q30" s="23" t="n">
         <f aca="false">SUM(Q6:Q29)</f>
-        <v>54800</v>
-      </c>
-      <c r="R30" s="22" t="n">
+        <v>57000</v>
+      </c>
+      <c r="R30" s="23" t="n">
         <f aca="false">SUM(R6:R29)</f>
-        <v>1023471.56155362</v>
-      </c>
-      <c r="S30" s="22" t="n">
+        <v>1059999.8537393</v>
+      </c>
+      <c r="S30" s="23" t="n">
         <f aca="false">SUM(S6:S29)</f>
         <v>288000</v>
       </c>
-      <c r="T30" s="22" t="n">
+      <c r="T30" s="23" t="n">
         <f aca="false">SUM(T6:T29)</f>
-        <v>540210.4225</v>
-      </c>
-      <c r="U30" s="22" t="n">
+        <v>553684.075</v>
+      </c>
+      <c r="U30" s="23" t="n">
         <f aca="false">SUM(U6:U29)</f>
-        <v>828210.4225</v>
-      </c>
-      <c r="V30" s="22" t="n">
+        <v>841684.075</v>
+      </c>
+      <c r="V30" s="23" t="n">
         <f aca="false">SUM(V6:V29)</f>
-        <v>381701.515946378</v>
-      </c>
-      <c r="W30" s="22" t="n">
+        <v>386694.071260702</v>
+      </c>
+      <c r="W30" s="23" t="n">
         <f aca="false">SUM(W6:W29)</f>
-        <v>77172.9175</v>
-      </c>
-      <c r="X30" s="32"/>
-      <c r="Y30" s="41" t="n">
+        <v>79097.725</v>
+      </c>
+      <c r="X30" s="33"/>
+      <c r="Y30" s="42" t="n">
         <f aca="false">SUM(Y6:Y29)</f>
         <v>108</v>
       </c>
-      <c r="Z30" s="41" t="n">
+      <c r="Z30" s="42" t="n">
         <f aca="false">SUM(Z6:Z29)</f>
         <v>794</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A32" s="42" t="s">
-        <v>197</v>
+      <c r="A32" s="43" t="s">
+        <v>198</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="42" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="17" t="s">
-        <v>198</v>
-      </c>
-      <c r="B33" s="17"/>
-      <c r="C33" s="17" t="s">
+      <c r="A33" s="18" t="s">
         <v>199</v>
       </c>
-      <c r="D33" s="17"/>
-      <c r="E33" s="17" t="s">
+      <c r="B33" s="18"/>
+      <c r="C33" s="18" t="s">
         <v>200</v>
       </c>
-      <c r="F33" s="17" t="s">
+      <c r="D33" s="18"/>
+      <c r="E33" s="18" t="s">
         <v>201</v>
       </c>
-      <c r="G33" s="17" t="s">
+      <c r="F33" s="18" t="s">
         <v>202</v>
       </c>
-      <c r="H33" s="17" t="s">
+      <c r="G33" s="18" t="s">
         <v>203</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="H33" s="18" t="s">
         <v>204</v>
       </c>
-      <c r="J33" s="17" t="s">
+      <c r="I33" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="K33" s="17" t="s">
+      <c r="J33" s="18" t="s">
         <v>206</v>
       </c>
-      <c r="L33" s="17" t="s">
+      <c r="K33" s="18" t="s">
         <v>207</v>
       </c>
-      <c r="M33" s="17" t="s">
+      <c r="L33" s="18" t="s">
         <v>208</v>
       </c>
+      <c r="M33" s="18" t="s">
+        <v>209</v>
+      </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A34" s="43" t="s">
-        <v>209</v>
-      </c>
-      <c r="B34" s="43"/>
-      <c r="C34" s="44" t="s">
+      <c r="A34" s="44" t="s">
         <v>210</v>
       </c>
-      <c r="D34" s="44"/>
+      <c r="B34" s="44"/>
+      <c r="C34" s="45" t="s">
+        <v>211</v>
+      </c>
+      <c r="D34" s="45"/>
       <c r="E34" s="15" t="n">
         <v>0</v>
       </c>
@@ -5764,181 +5770,181 @@
       <c r="G34" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="H34" s="28" t="n">
+      <c r="H34" s="29" t="n">
         <f aca="false">'Premissas Precept'!B58</f>
         <v>102000</v>
       </c>
-      <c r="I34" s="32"/>
-      <c r="J34" s="32"/>
-      <c r="K34" s="32"/>
-      <c r="L34" s="32"/>
-      <c r="M34" s="32"/>
+      <c r="I34" s="33"/>
+      <c r="J34" s="33"/>
+      <c r="K34" s="33"/>
+      <c r="L34" s="33"/>
+      <c r="M34" s="33"/>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A35" s="43" t="s">
-        <v>211</v>
-      </c>
-      <c r="B35" s="43"/>
-      <c r="C35" s="44" t="s">
+      <c r="A35" s="44" t="s">
         <v>212</v>
       </c>
-      <c r="D35" s="44"/>
-      <c r="E35" s="28" t="n">
+      <c r="B35" s="44"/>
+      <c r="C35" s="45" t="s">
+        <v>213</v>
+      </c>
+      <c r="D35" s="45"/>
+      <c r="E35" s="29" t="n">
         <f aca="false">AVERAGE(I6:I11)</f>
-        <v>19803.75</v>
-      </c>
-      <c r="F35" s="28" t="n">
+        <v>23970</v>
+      </c>
+      <c r="F35" s="29" t="n">
         <f aca="false">AVERAGE(R6:R11)</f>
-        <v>7225.91351004006</v>
-      </c>
-      <c r="G35" s="28" t="n">
+        <v>9798.06316471175</v>
+      </c>
+      <c r="G35" s="29" t="n">
         <f aca="false">AVERAGE(U6:U11)</f>
-        <v>15690.49625</v>
+        <v>16711.2275</v>
       </c>
       <c r="H35" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I35" s="23" t="n">
+      <c r="I35" s="24" t="n">
         <f aca="false">F35/E35</f>
-        <v>0.364876021462605</v>
+        <v>0.408763586345922</v>
       </c>
       <c r="J35" s="15" t="n">
         <f aca="false">E35-F35-G35</f>
-        <v>-3112.65976004007</v>
-      </c>
-      <c r="K35" s="45" t="n">
+        <v>-2539.29066471175</v>
+      </c>
+      <c r="K35" s="46" t="n">
         <f aca="false">AVERAGE(B6:B11)</f>
         <v>10</v>
       </c>
-      <c r="L35" s="35" t="n">
+      <c r="L35" s="36" t="n">
         <f aca="false">SUM(C6:C11)</f>
         <v>3</v>
       </c>
-      <c r="M35" s="35" t="n">
+      <c r="M35" s="36" t="n">
         <f aca="false">SUM(D6:D11)</f>
         <v>1</v>
       </c>
     </row>
     <row r="36" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A36" s="43" t="s">
-        <v>213</v>
-      </c>
-      <c r="B36" s="43"/>
-      <c r="C36" s="44" t="s">
+      <c r="A36" s="44" t="s">
         <v>214</v>
       </c>
-      <c r="D36" s="44"/>
-      <c r="E36" s="28" t="n">
+      <c r="B36" s="44"/>
+      <c r="C36" s="45" t="s">
+        <v>215</v>
+      </c>
+      <c r="D36" s="45"/>
+      <c r="E36" s="29" t="n">
         <f aca="false">AVERAGE(I12:I17)</f>
-        <v>58178.3333333333</v>
-      </c>
-      <c r="F36" s="28" t="n">
+        <v>61511.3333333333</v>
+      </c>
+      <c r="F36" s="29" t="n">
         <f aca="false">AVERAGE(R12:R17)</f>
-        <v>24858.7635121745</v>
-      </c>
-      <c r="G36" s="28" t="n">
+        <v>27099.8994905629</v>
+      </c>
+      <c r="G36" s="29" t="n">
         <f aca="false">AVERAGE(U12:U17)</f>
-        <v>26253.6916666667</v>
+        <v>27070.2766666667</v>
       </c>
       <c r="H36" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I36" s="23" t="n">
+      <c r="I36" s="24" t="n">
         <f aca="false">F36/E36</f>
-        <v>0.427285590492013</v>
+        <v>0.440567583598084</v>
       </c>
       <c r="J36" s="15" t="n">
         <f aca="false">E36-F36-G36</f>
-        <v>7065.87815449215</v>
-      </c>
-      <c r="K36" s="45" t="n">
+        <v>7341.15717610375</v>
+      </c>
+      <c r="K36" s="46" t="n">
         <f aca="false">AVERAGE(B12:B17)</f>
         <v>25</v>
       </c>
-      <c r="L36" s="35" t="n">
+      <c r="L36" s="36" t="n">
         <f aca="false">SUM(C12:C17)</f>
         <v>8</v>
       </c>
-      <c r="M36" s="35" t="n">
+      <c r="M36" s="36" t="n">
         <f aca="false">SUM(D12:D17)</f>
         <v>3</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A37" s="43" t="s">
-        <v>215</v>
-      </c>
-      <c r="B37" s="43"/>
-      <c r="C37" s="44" t="s">
+      <c r="A37" s="44" t="s">
         <v>216</v>
       </c>
-      <c r="D37" s="44"/>
-      <c r="E37" s="28" t="n">
+      <c r="B37" s="44"/>
+      <c r="C37" s="45" t="s">
+        <v>217</v>
+      </c>
+      <c r="D37" s="45"/>
+      <c r="E37" s="29" t="n">
         <f aca="false">AVERAGE(I18:I29)</f>
-        <v>147124.25</v>
-      </c>
-      <c r="F37" s="28" t="n">
+        <v>147957.5</v>
+      </c>
+      <c r="F37" s="29" t="n">
         <f aca="false">AVERAGE(R18:R29)</f>
-        <v>69246.9582850279</v>
-      </c>
-      <c r="G37" s="28" t="n">
+        <v>69884.3398173041</v>
+      </c>
+      <c r="G37" s="29" t="n">
         <f aca="false">AVERAGE(U18:U29)</f>
-        <v>48045.44125</v>
+        <v>48249.5875</v>
       </c>
       <c r="H37" s="15" t="n">
         <v>0</v>
       </c>
-      <c r="I37" s="23" t="n">
+      <c r="I37" s="24" t="n">
         <f aca="false">F37/E37</f>
-        <v>0.470669915292876</v>
+        <v>0.472327119729004</v>
       </c>
       <c r="J37" s="15" t="n">
         <f aca="false">E37-F37-G37</f>
-        <v>29831.8504649721</v>
-      </c>
-      <c r="K37" s="45" t="n">
+        <v>29823.5726826959</v>
+      </c>
+      <c r="K37" s="46" t="n">
         <f aca="false">AVERAGE(B18:B29)</f>
         <v>57.6666666666667</v>
       </c>
-      <c r="L37" s="35" t="n">
+      <c r="L37" s="36" t="n">
         <f aca="false">SUM(C18:C29)</f>
         <v>54</v>
       </c>
-      <c r="M37" s="35" t="n">
+      <c r="M37" s="36" t="n">
         <f aca="false">SUM(D18:D29)</f>
         <v>11</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A40" s="42" t="s">
-        <v>217</v>
+      <c r="A40" s="43" t="s">
+        <v>218</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="30" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A41" s="17" t="s">
-        <v>218</v>
-      </c>
-      <c r="B41" s="17"/>
-      <c r="C41" s="17"/>
-      <c r="D41" s="17"/>
-      <c r="E41" s="17" t="s">
+      <c r="A41" s="18" t="s">
         <v>219</v>
       </c>
-      <c r="F41" s="17" t="s">
+      <c r="B41" s="18"/>
+      <c r="C41" s="18"/>
+      <c r="D41" s="18"/>
+      <c r="E41" s="18" t="s">
         <v>220</v>
       </c>
-      <c r="G41" s="17" t="s">
+      <c r="F41" s="18" t="s">
         <v>221</v>
       </c>
+      <c r="G41" s="18" t="s">
+        <v>222</v>
+      </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A42" s="46" t="s">
-        <v>222</v>
-      </c>
-      <c r="B42" s="46"/>
-      <c r="C42" s="46"/>
-      <c r="D42" s="46"/>
-      <c r="E42" s="45" t="n">
+      <c r="A42" s="47" t="s">
+        <v>223</v>
+      </c>
+      <c r="B42" s="47"/>
+      <c r="C42" s="47"/>
+      <c r="D42" s="47"/>
+      <c r="E42" s="46" t="n">
         <f aca="false">AVERAGE(Z18:Z29)*'Premissas Precept'!B7</f>
         <v>30.25</v>
       </c>
@@ -5952,13 +5958,13 @@
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A43" s="46" t="s">
-        <v>223</v>
-      </c>
-      <c r="B43" s="46"/>
-      <c r="C43" s="46"/>
-      <c r="D43" s="46"/>
-      <c r="E43" s="45" t="n">
+      <c r="A43" s="47" t="s">
+        <v>224</v>
+      </c>
+      <c r="B43" s="47"/>
+      <c r="C43" s="47"/>
+      <c r="D43" s="47"/>
+      <c r="E43" s="46" t="n">
         <f aca="false">AVERAGE(Z18:Z29)*(1-'Premissas Precept'!B7)</f>
         <v>20.1666666666667</v>
       </c>
@@ -5972,13 +5978,13 @@
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A44" s="46" t="s">
-        <v>224</v>
-      </c>
-      <c r="B44" s="46"/>
-      <c r="C44" s="46"/>
-      <c r="D44" s="46"/>
-      <c r="E44" s="45" t="n">
+      <c r="A44" s="47" t="s">
+        <v>225</v>
+      </c>
+      <c r="B44" s="47"/>
+      <c r="C44" s="47"/>
+      <c r="D44" s="47"/>
+      <c r="E44" s="46" t="n">
         <f aca="false">AVERAGE(Z18:Z29)*'Premissas Precept'!B89</f>
         <v>50.4166666666667</v>
       </c>
@@ -5992,13 +5998,13 @@
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A45" s="46" t="s">
-        <v>225</v>
-      </c>
-      <c r="B45" s="46"/>
-      <c r="C45" s="46"/>
-      <c r="D45" s="46"/>
-      <c r="E45" s="45" t="n">
+      <c r="A45" s="47" t="s">
+        <v>226</v>
+      </c>
+      <c r="B45" s="47"/>
+      <c r="C45" s="47"/>
+      <c r="D45" s="47"/>
+      <c r="E45" s="46" t="n">
         <f aca="false">AVERAGE(C18:C29)</f>
         <v>4.5</v>
       </c>
@@ -6012,47 +6018,47 @@
       </c>
     </row>
     <row r="46" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A46" s="46" t="s">
-        <v>226</v>
-      </c>
-      <c r="B46" s="46"/>
-      <c r="C46" s="46"/>
-      <c r="D46" s="46"/>
-      <c r="E46" s="45" t="n">
-        <f aca="false">AVERAGE(E18:E29)</f>
-        <v>5.33333333333333</v>
+      <c r="A46" s="47" t="s">
+        <v>227</v>
+      </c>
+      <c r="B46" s="47"/>
+      <c r="C46" s="47"/>
+      <c r="D46" s="47"/>
+      <c r="E46" s="46" t="n">
+        <f aca="false">AVERAGE(D18:D29)</f>
+        <v>0.916666666666667</v>
       </c>
       <c r="F46" s="15" t="n">
-        <f aca="false">'Premissas Precept'!B12</f>
-        <v>4999.5</v>
+        <f aca="false">'Premissas Precept'!B10</f>
+        <v>29997</v>
       </c>
       <c r="G46" s="15" t="n">
         <f aca="false">E46*F46</f>
-        <v>26664</v>
+        <v>27497.25</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A47" s="43" t="s">
-        <v>227</v>
-      </c>
-      <c r="B47" s="43"/>
-      <c r="C47" s="43"/>
-      <c r="D47" s="43"/>
-      <c r="E47" s="45"/>
+      <c r="A47" s="44" t="s">
+        <v>228</v>
+      </c>
+      <c r="B47" s="44"/>
+      <c r="C47" s="44"/>
+      <c r="D47" s="44"/>
+      <c r="E47" s="46"/>
       <c r="F47" s="15"/>
-      <c r="G47" s="28" t="n">
+      <c r="G47" s="29" t="n">
         <f aca="false">SUM(G42:G46)</f>
-        <v>147124.25</v>
+        <v>147957.5</v>
       </c>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A48" s="46" t="s">
-        <v>228</v>
-      </c>
-      <c r="B48" s="46"/>
-      <c r="C48" s="46"/>
-      <c r="D48" s="46"/>
-      <c r="E48" s="45" t="n">
+      <c r="A48" s="47" t="s">
+        <v>229</v>
+      </c>
+      <c r="B48" s="47"/>
+      <c r="C48" s="47"/>
+      <c r="D48" s="47"/>
+      <c r="E48" s="46" t="n">
         <f aca="false">AVERAGE(B18:B29)</f>
         <v>57.6666666666667</v>
       </c>
@@ -6066,129 +6072,129 @@
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A49" s="46" t="s">
-        <v>229</v>
-      </c>
-      <c r="B49" s="46"/>
-      <c r="C49" s="46"/>
-      <c r="D49" s="46"/>
-      <c r="E49" s="45"/>
-      <c r="F49" s="23" t="n">
+      <c r="A49" s="47" t="s">
+        <v>230</v>
+      </c>
+      <c r="B49" s="47"/>
+      <c r="C49" s="47"/>
+      <c r="D49" s="47"/>
+      <c r="E49" s="46"/>
+      <c r="F49" s="24" t="n">
         <f aca="false">G49/G47</f>
-        <v>0.187933713295811</v>
+        <v>0.188592601370692</v>
       </c>
       <c r="G49" s="15" t="n">
         <f aca="false">AVERAGE(L18:L29)</f>
-        <v>27649.6066183612</v>
+        <v>27903.6898173041</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A50" s="46" t="s">
-        <v>230</v>
-      </c>
-      <c r="B50" s="46"/>
-      <c r="C50" s="46"/>
-      <c r="D50" s="46"/>
-      <c r="E50" s="45"/>
-      <c r="F50" s="23" t="n">
+      <c r="A50" s="47" t="s">
+        <v>231</v>
+      </c>
+      <c r="B50" s="47"/>
+      <c r="C50" s="47"/>
+      <c r="D50" s="47"/>
+      <c r="E50" s="46"/>
+      <c r="F50" s="24" t="n">
         <f aca="false">'Premissas Precept'!B16</f>
         <v>0.02</v>
       </c>
       <c r="G50" s="15" t="n">
         <f aca="false">AVERAGE(N18:N29)</f>
-        <v>2942.485</v>
+        <v>2959.15</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A51" s="46" t="s">
-        <v>231</v>
-      </c>
-      <c r="B51" s="46"/>
-      <c r="C51" s="46"/>
-      <c r="D51" s="46"/>
-      <c r="E51" s="45"/>
-      <c r="F51" s="23" t="n">
+      <c r="A51" s="47" t="s">
+        <v>232</v>
+      </c>
+      <c r="B51" s="47"/>
+      <c r="C51" s="47"/>
+      <c r="D51" s="47"/>
+      <c r="E51" s="46"/>
+      <c r="F51" s="24" t="n">
         <f aca="false">'Premissas Precept'!B17</f>
         <v>0.05</v>
       </c>
       <c r="G51" s="15" t="n">
         <f aca="false">AVERAGE(O18:O29)</f>
-        <v>3582.525</v>
+        <v>3624.1875</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A52" s="46" t="s">
-        <v>232</v>
-      </c>
-      <c r="B52" s="46"/>
-      <c r="C52" s="46"/>
-      <c r="D52" s="46"/>
-      <c r="E52" s="45"/>
+      <c r="A52" s="47" t="s">
+        <v>233</v>
+      </c>
+      <c r="B52" s="47"/>
+      <c r="C52" s="47"/>
+      <c r="D52" s="47"/>
+      <c r="E52" s="46"/>
       <c r="F52" s="15"/>
       <c r="G52" s="15" t="n">
         <f aca="false">AVERAGE(Q18:Q29)</f>
-        <v>3766.66666666667</v>
+        <v>3800</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A53" s="46" t="s">
-        <v>233</v>
-      </c>
-      <c r="B53" s="46"/>
-      <c r="C53" s="46"/>
-      <c r="D53" s="46"/>
-      <c r="E53" s="45"/>
-      <c r="F53" s="23" t="n">
+      <c r="A53" s="47" t="s">
+        <v>234</v>
+      </c>
+      <c r="B53" s="47"/>
+      <c r="C53" s="47"/>
+      <c r="D53" s="47"/>
+      <c r="E53" s="46"/>
+      <c r="F53" s="24" t="n">
         <f aca="false">'Premissas Precept'!B18</f>
         <v>0.35</v>
       </c>
       <c r="G53" s="15" t="n">
         <f aca="false">AVERAGE(P18:P29)</f>
-        <v>25077.675</v>
+        <v>25369.3125</v>
       </c>
     </row>
     <row r="54" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A54" s="43" t="s">
-        <v>234</v>
-      </c>
-      <c r="B54" s="43"/>
-      <c r="C54" s="43"/>
-      <c r="D54" s="43"/>
-      <c r="E54" s="45"/>
-      <c r="F54" s="23" t="n">
+      <c r="A54" s="44" t="s">
+        <v>235</v>
+      </c>
+      <c r="B54" s="44"/>
+      <c r="C54" s="44"/>
+      <c r="D54" s="44"/>
+      <c r="E54" s="46"/>
+      <c r="F54" s="24" t="n">
         <f aca="false">G54/G47</f>
-        <v>0.470669915292876</v>
-      </c>
-      <c r="G54" s="28" t="n">
+        <v>0.472327119729004</v>
+      </c>
+      <c r="G54" s="29" t="n">
         <f aca="false">SUM(G48:G53)</f>
-        <v>69246.9582850279</v>
+        <v>69884.3398173041</v>
       </c>
     </row>
     <row r="55" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A55" s="46" t="s">
-        <v>235</v>
-      </c>
-      <c r="B55" s="46"/>
-      <c r="C55" s="46"/>
-      <c r="D55" s="46"/>
-      <c r="E55" s="45"/>
-      <c r="F55" s="23" t="n">
+      <c r="A55" s="47" t="s">
+        <v>236</v>
+      </c>
+      <c r="B55" s="47"/>
+      <c r="C55" s="47"/>
+      <c r="D55" s="47"/>
+      <c r="E55" s="46"/>
+      <c r="F55" s="24" t="n">
         <f aca="false">'Premissas Precept'!B48</f>
         <v>0.245</v>
       </c>
       <c r="G55" s="15" t="n">
         <f aca="false">AVERAGE(T18:T29)</f>
-        <v>36045.44125</v>
+        <v>36249.5875</v>
       </c>
     </row>
     <row r="56" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A56" s="46" t="s">
-        <v>236</v>
-      </c>
-      <c r="B56" s="46"/>
-      <c r="C56" s="46"/>
-      <c r="D56" s="46"/>
-      <c r="E56" s="45"/>
+      <c r="A56" s="47" t="s">
+        <v>237</v>
+      </c>
+      <c r="B56" s="47"/>
+      <c r="C56" s="47"/>
+      <c r="D56" s="47"/>
+      <c r="E56" s="46"/>
       <c r="F56" s="15"/>
       <c r="G56" s="15" t="n">
         <f aca="false">'Premissas Precept'!B42</f>
@@ -6196,17 +6202,17 @@
       </c>
     </row>
     <row r="57" customFormat="false" ht="15" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A57" s="43" t="s">
-        <v>237</v>
-      </c>
-      <c r="B57" s="43"/>
-      <c r="C57" s="43"/>
-      <c r="D57" s="43"/>
-      <c r="E57" s="45"/>
+      <c r="A57" s="44" t="s">
+        <v>238</v>
+      </c>
+      <c r="B57" s="44"/>
+      <c r="C57" s="44"/>
+      <c r="D57" s="44"/>
+      <c r="E57" s="46"/>
       <c r="F57" s="15"/>
-      <c r="G57" s="28" t="n">
+      <c r="G57" s="29" t="n">
         <f aca="false">G55+G56</f>
-        <v>48045.44125</v>
+        <v>48249.5875</v>
       </c>
     </row>
   </sheetData>
@@ -6262,726 +6268,726 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>238</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="A1" s="48" t="s">
+        <v>239</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
-        <v>239</v>
+      <c r="A2" s="50" t="s">
+        <v>240</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="E4" s="17" t="s">
+      <c r="A4" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="B4" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="18" t="s">
         <v>190</v>
       </c>
-      <c r="F4" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="G4" s="17" t="s">
-        <v>241</v>
+      <c r="E4" s="18" t="s">
+        <v>191</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="G4" s="18" t="s">
+        <v>242</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="B5" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="C5" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="D5" s="51" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="52" t="n">
+      <c r="A5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="C5" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="D5" s="52" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="53" t="n">
         <f aca="false">B5-C5-D5</f>
         <v>0</v>
       </c>
-      <c r="F5" s="51" t="n">
+      <c r="F5" s="52" t="n">
         <f aca="false">'Premissas Precept'!B58</f>
         <v>102000</v>
       </c>
-      <c r="G5" s="53" t="n">
+      <c r="G5" s="54" t="n">
         <f aca="false">E5-F5</f>
         <v>-102000</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="50" t="n">
+      <c r="A6" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="51" t="n">
+      <c r="B6" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I6</f>
         <v>5988</v>
       </c>
-      <c r="C6" s="51" t="n">
+      <c r="C6" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R6</f>
         <v>1479.9</v>
       </c>
-      <c r="D6" s="51" t="n">
+      <c r="D6" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U6</f>
         <v>12000</v>
       </c>
-      <c r="E6" s="52" t="n">
+      <c r="E6" s="53" t="n">
         <f aca="false">B6-C6-D6</f>
         <v>-7491.9</v>
       </c>
-      <c r="F6" s="51"/>
-      <c r="G6" s="53" t="n">
+      <c r="F6" s="52"/>
+      <c r="G6" s="54" t="n">
         <f aca="false">E6-F6</f>
         <v>-7491.9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="50" t="n">
+      <c r="A7" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="51" t="n">
+      <c r="B7" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I7</f>
         <v>8982</v>
       </c>
-      <c r="C7" s="51" t="n">
+      <c r="C7" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R7</f>
         <v>2219.85</v>
       </c>
-      <c r="D7" s="51" t="n">
+      <c r="D7" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U7</f>
         <v>12000</v>
       </c>
-      <c r="E7" s="52" t="n">
+      <c r="E7" s="53" t="n">
         <f aca="false">B7-C7-D7</f>
         <v>-5237.85</v>
       </c>
-      <c r="F7" s="51"/>
-      <c r="G7" s="53" t="n">
+      <c r="F7" s="52"/>
+      <c r="G7" s="54" t="n">
         <f aca="false">E7-F7</f>
         <v>-5237.85</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="50" t="n">
+      <c r="A8" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="51" t="n">
+      <c r="B8" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I8</f>
         <v>13473</v>
       </c>
-      <c r="C8" s="51" t="n">
+      <c r="C8" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R8</f>
         <v>3329.775</v>
       </c>
-      <c r="D8" s="51" t="n">
+      <c r="D8" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U8</f>
         <v>12000</v>
       </c>
-      <c r="E8" s="52" t="n">
+      <c r="E8" s="53" t="n">
         <f aca="false">B8-C8-D8</f>
         <v>-1856.775</v>
       </c>
-      <c r="F8" s="51"/>
-      <c r="G8" s="53" t="n">
+      <c r="F8" s="52"/>
+      <c r="G8" s="54" t="n">
         <f aca="false">E8-F8</f>
         <v>-1856.775</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="50" t="n">
+      <c r="A9" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="51" t="n">
+      <c r="B9" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I9</f>
         <v>24967</v>
       </c>
-      <c r="C9" s="51" t="n">
+      <c r="C9" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R9</f>
         <v>10156.025</v>
       </c>
-      <c r="D9" s="51" t="n">
+      <c r="D9" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U9</f>
         <v>18116.915</v>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="53" t="n">
         <f aca="false">B9-C9-D9</f>
         <v>-3305.94</v>
       </c>
-      <c r="F9" s="51"/>
-      <c r="G9" s="53" t="n">
+      <c r="F9" s="52"/>
+      <c r="G9" s="54" t="n">
         <f aca="false">E9-F9</f>
         <v>-3305.94</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="50" t="n">
+      <c r="A10" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="51" t="n">
+      <c r="B10" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I10</f>
         <v>29458</v>
       </c>
-      <c r="C10" s="51" t="n">
+      <c r="C10" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R10</f>
         <v>11265.95</v>
       </c>
-      <c r="D10" s="51" t="n">
+      <c r="D10" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U10</f>
         <v>19217.21</v>
       </c>
-      <c r="E10" s="52" t="n">
+      <c r="E10" s="53" t="n">
         <f aca="false">B10-C10-D10</f>
         <v>-1025.16</v>
       </c>
-      <c r="F10" s="51"/>
-      <c r="G10" s="53" t="n">
+      <c r="F10" s="52"/>
+      <c r="G10" s="54" t="n">
         <f aca="false">E10-F10</f>
         <v>-1025.16</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="50" t="n">
+      <c r="A11" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="51" t="n">
+      <c r="B11" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I11</f>
-        <v>35954.5</v>
-      </c>
-      <c r="C11" s="51" t="n">
+        <v>60952</v>
+      </c>
+      <c r="C11" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R11</f>
-        <v>14903.9810602404</v>
-      </c>
-      <c r="D11" s="51" t="n">
+        <v>30336.8789882705</v>
+      </c>
+      <c r="D11" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U11</f>
-        <v>20808.8525</v>
-      </c>
-      <c r="E11" s="52" t="n">
+        <v>26933.24</v>
+      </c>
+      <c r="E11" s="53" t="n">
         <f aca="false">B11-C11-D11</f>
-        <v>241.666439759618</v>
-      </c>
-      <c r="F11" s="51"/>
-      <c r="G11" s="53" t="n">
+        <v>3681.8810117295</v>
+      </c>
+      <c r="F11" s="52"/>
+      <c r="G11" s="54" t="n">
         <f aca="false">E11-F11</f>
-        <v>241.666439759618</v>
+        <v>3681.8810117295</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="50" t="n">
+      <c r="A12" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="51" t="n">
+      <c r="B12" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I12</f>
-        <v>40445.5</v>
-      </c>
-      <c r="C12" s="51" t="n">
+        <v>35446</v>
+      </c>
+      <c r="C12" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R12</f>
-        <v>16173.831793221</v>
-      </c>
-      <c r="D12" s="51" t="n">
+        <v>13185.4630788486</v>
+      </c>
+      <c r="D12" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U12</f>
-        <v>21909.1475</v>
-      </c>
-      <c r="E12" s="52" t="n">
+        <v>20684.27</v>
+      </c>
+      <c r="E12" s="53" t="n">
         <f aca="false">B12-C12-D12</f>
-        <v>2362.52070677902</v>
-      </c>
-      <c r="F12" s="51"/>
-      <c r="G12" s="53" t="n">
+        <v>1576.26692115144</v>
+      </c>
+      <c r="F12" s="52"/>
+      <c r="G12" s="54" t="n">
         <f aca="false">E12-F12</f>
-        <v>2362.52070677902</v>
+        <v>1576.26692115144</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="50" t="n">
+      <c r="A13" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="51" t="n">
+      <c r="B13" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I13</f>
-        <v>46942</v>
-      </c>
-      <c r="C13" s="51" t="n">
+        <v>66940</v>
+      </c>
+      <c r="C13" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R13</f>
-        <v>19881.1182183489</v>
-      </c>
-      <c r="D13" s="51" t="n">
+        <v>32473.394606897</v>
+      </c>
+      <c r="D13" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U13</f>
-        <v>23500.79</v>
-      </c>
-      <c r="E13" s="52" t="n">
+        <v>28400.3</v>
+      </c>
+      <c r="E13" s="53" t="n">
         <f aca="false">B13-C13-D13</f>
-        <v>3560.09178165106</v>
-      </c>
-      <c r="F13" s="51"/>
-      <c r="G13" s="53" t="n">
+        <v>6066.30539310299</v>
+      </c>
+      <c r="F13" s="52"/>
+      <c r="G13" s="54" t="n">
         <f aca="false">E13-F13</f>
-        <v>3560.09178165106</v>
+        <v>6066.30539310299</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="50" t="n">
+      <c r="A14" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="51" t="n">
+      <c r="B14" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I14</f>
-        <v>61430</v>
-      </c>
-      <c r="C14" s="51" t="n">
+        <v>51431</v>
+      </c>
+      <c r="C14" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R14</f>
-        <v>27581.4994035207</v>
-      </c>
-      <c r="D14" s="51" t="n">
+        <v>21468.5634248962</v>
+      </c>
+      <c r="D14" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U14</f>
-        <v>27050.35</v>
-      </c>
-      <c r="E14" s="52" t="n">
+        <v>24600.595</v>
+      </c>
+      <c r="E14" s="53" t="n">
         <f aca="false">B14-C14-D14</f>
-        <v>6798.15059647932</v>
-      </c>
-      <c r="F14" s="51"/>
-      <c r="G14" s="53" t="n">
+        <v>5361.84157510377</v>
+      </c>
+      <c r="F14" s="52"/>
+      <c r="G14" s="54" t="n">
         <f aca="false">E14-F14</f>
-        <v>6798.15059647932</v>
+        <v>5361.84157510377</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="50" t="n">
+      <c r="A15" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="51" t="n">
+      <c r="B15" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I15</f>
-        <v>59426.5</v>
-      </c>
-      <c r="C15" s="51" t="n">
+        <v>74425</v>
+      </c>
+      <c r="C15" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R15</f>
-        <v>25142.1186014796</v>
-      </c>
-      <c r="D15" s="51" t="n">
+        <v>34750.3320927002</v>
+      </c>
+      <c r="D15" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U15</f>
-        <v>26559.4925</v>
-      </c>
-      <c r="E15" s="52" t="n">
+        <v>30234.125</v>
+      </c>
+      <c r="E15" s="53" t="n">
         <f aca="false">B15-C15-D15</f>
-        <v>7724.8888985204</v>
-      </c>
-      <c r="F15" s="51"/>
-      <c r="G15" s="53" t="n">
+        <v>9440.54290729983</v>
+      </c>
+      <c r="F15" s="52"/>
+      <c r="G15" s="54" t="n">
         <f aca="false">E15-F15</f>
-        <v>7724.8888985204</v>
+        <v>9440.54290729983</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="50" t="n">
+      <c r="A16" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="51" t="n">
+      <c r="B16" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I16</f>
-        <v>73914.5</v>
-      </c>
-      <c r="C16" s="51" t="n">
+        <v>58916</v>
+      </c>
+      <c r="C16" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R16</f>
-        <v>32956.1812920729</v>
-      </c>
-      <c r="D16" s="51" t="n">
+        <v>23690.1528924749</v>
+      </c>
+      <c r="D16" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U16</f>
-        <v>30109.0525</v>
-      </c>
-      <c r="E16" s="52" t="n">
+        <v>26434.42</v>
+      </c>
+      <c r="E16" s="53" t="n">
         <f aca="false">B16-C16-D16</f>
-        <v>10849.2662079271</v>
-      </c>
-      <c r="F16" s="51"/>
-      <c r="G16" s="53" t="n">
+        <v>8791.42710752508</v>
+      </c>
+      <c r="F16" s="52"/>
+      <c r="G16" s="54" t="n">
         <f aca="false">E16-F16</f>
-        <v>10849.2662079271</v>
+        <v>8791.42710752508</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="50" t="n">
+      <c r="A17" s="51" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="51" t="n">
+      <c r="B17" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I17</f>
-        <v>66911.5</v>
-      </c>
-      <c r="C17" s="51" t="n">
+        <v>81910</v>
+      </c>
+      <c r="C17" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R17</f>
-        <v>27417.831764404</v>
-      </c>
-      <c r="D17" s="51" t="n">
+        <v>37031.4908475607</v>
+      </c>
+      <c r="D17" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U17</f>
-        <v>28393.3175</v>
-      </c>
-      <c r="E17" s="52" t="n">
+        <v>32067.95</v>
+      </c>
+      <c r="E17" s="53" t="n">
         <f aca="false">B17-C17-D17</f>
-        <v>11100.3507355959</v>
-      </c>
-      <c r="F17" s="51"/>
-      <c r="G17" s="53" t="n">
+        <v>12810.5591524393</v>
+      </c>
+      <c r="F17" s="52"/>
+      <c r="G17" s="54" t="n">
         <f aca="false">E17-F17</f>
-        <v>11100.3507355959</v>
+        <v>12810.5591524393</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="50" t="n">
+      <c r="A18" s="51" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="51" t="n">
+      <c r="B18" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I18</f>
-        <v>104896</v>
-      </c>
-      <c r="C18" s="51" t="n">
+        <v>114895</v>
+      </c>
+      <c r="C18" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R18</f>
-        <v>51415.5763411467</v>
-      </c>
-      <c r="D18" s="51" t="n">
+        <v>57966.6688817052</v>
+      </c>
+      <c r="D18" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U18</f>
-        <v>37699.52</v>
-      </c>
-      <c r="E18" s="52" t="n">
+        <v>40149.275</v>
+      </c>
+      <c r="E18" s="53" t="n">
         <f aca="false">B18-C18-D18</f>
-        <v>15780.9036588533</v>
-      </c>
-      <c r="F18" s="51"/>
-      <c r="G18" s="53" t="n">
+        <v>16779.0561182948</v>
+      </c>
+      <c r="F18" s="52"/>
+      <c r="G18" s="54" t="n">
         <f aca="false">E18-F18</f>
-        <v>15780.9036588533</v>
+        <v>16779.0561182948</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="50" t="n">
+      <c r="A19" s="51" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="51" t="n">
+      <c r="B19" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I19</f>
-        <v>109387</v>
-      </c>
-      <c r="C19" s="51" t="n">
+        <v>119386</v>
+      </c>
+      <c r="C19" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R19</f>
-        <v>53122.0010044143</v>
-      </c>
-      <c r="D19" s="51" t="n">
+        <v>59681.1683465612</v>
+      </c>
+      <c r="D19" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U19</f>
-        <v>38799.815</v>
-      </c>
-      <c r="E19" s="52" t="n">
+        <v>41249.57</v>
+      </c>
+      <c r="E19" s="53" t="n">
         <f aca="false">B19-C19-D19</f>
-        <v>17465.1839955858</v>
-      </c>
-      <c r="F19" s="51"/>
-      <c r="G19" s="53" t="n">
+        <v>18455.2616534388</v>
+      </c>
+      <c r="F19" s="52"/>
+      <c r="G19" s="54" t="n">
         <f aca="false">E19-F19</f>
-        <v>17465.1839955858</v>
+        <v>18455.2616534388</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="50" t="n">
+      <c r="A20" s="51" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="51" t="n">
+      <c r="B20" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I20</f>
-        <v>120374.5</v>
-      </c>
-      <c r="C20" s="51" t="n">
+        <v>125374</v>
+      </c>
+      <c r="C20" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R20</f>
-        <v>58240.5998046273</v>
-      </c>
-      <c r="D20" s="51" t="n">
+        <v>61627.1271537519</v>
+      </c>
+      <c r="D20" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U20</f>
-        <v>41491.7525</v>
-      </c>
-      <c r="E20" s="52" t="n">
+        <v>42716.63</v>
+      </c>
+      <c r="E20" s="53" t="n">
         <f aca="false">B20-C20-D20</f>
-        <v>20642.1476953727</v>
-      </c>
-      <c r="F20" s="51"/>
-      <c r="G20" s="53" t="n">
+        <v>21030.2428462481</v>
+      </c>
+      <c r="F20" s="52"/>
+      <c r="G20" s="54" t="n">
         <f aca="false">E20-F20</f>
-        <v>20642.1476953727</v>
+        <v>21030.2428462481</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="50" t="n">
+      <c r="A21" s="51" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="51" t="n">
+      <c r="B21" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I21</f>
-        <v>126362.5</v>
-      </c>
-      <c r="C21" s="51" t="n">
+        <v>131362</v>
+      </c>
+      <c r="C21" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R21</f>
-        <v>60218.418732278</v>
-      </c>
-      <c r="D21" s="51" t="n">
+        <v>63673.2840244047</v>
+      </c>
+      <c r="D21" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U21</f>
-        <v>42958.8125</v>
-      </c>
-      <c r="E21" s="52" t="n">
+        <v>44183.69</v>
+      </c>
+      <c r="E21" s="53" t="n">
         <f aca="false">B21-C21-D21</f>
-        <v>23185.268767722</v>
-      </c>
-      <c r="F21" s="51"/>
-      <c r="G21" s="53" t="n">
+        <v>23505.0259755953</v>
+      </c>
+      <c r="F21" s="52"/>
+      <c r="G21" s="54" t="n">
         <f aca="false">E21-F21</f>
-        <v>23185.268767722</v>
+        <v>23505.0259755953</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="50" t="n">
+      <c r="A22" s="51" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="51" t="n">
+      <c r="B22" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I22</f>
         <v>135853</v>
       </c>
-      <c r="C22" s="51" t="n">
+      <c r="C22" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R22</f>
-        <v>65015.4930566303</v>
-      </c>
-      <c r="D22" s="51" t="n">
+        <v>65224.8444945791</v>
+      </c>
+      <c r="D22" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U22</f>
         <v>45283.985</v>
       </c>
-      <c r="E22" s="52" t="n">
+      <c r="E22" s="53" t="n">
         <f aca="false">B22-C22-D22</f>
-        <v>25553.5219433697</v>
-      </c>
-      <c r="F22" s="51"/>
-      <c r="G22" s="53" t="n">
+        <v>25344.1705054209</v>
+      </c>
+      <c r="F22" s="52"/>
+      <c r="G22" s="54" t="n">
         <f aca="false">E22-F22</f>
-        <v>25553.5219433697</v>
+        <v>25344.1705054209</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="50" t="n">
+      <c r="A23" s="51" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="51" t="n">
+      <c r="B23" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I23</f>
         <v>141841</v>
       </c>
-      <c r="C23" s="51" t="n">
+      <c r="C23" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R23</f>
-        <v>66978.0271432991</v>
-      </c>
-      <c r="D23" s="51" t="n">
+        <v>67153.3020657306</v>
+      </c>
+      <c r="D23" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U23</f>
         <v>46751.045</v>
       </c>
-      <c r="E23" s="52" t="n">
+      <c r="E23" s="53" t="n">
         <f aca="false">B23-C23-D23</f>
-        <v>28111.9278567009</v>
-      </c>
-      <c r="F23" s="51"/>
-      <c r="G23" s="53" t="n">
+        <v>27936.6529342694</v>
+      </c>
+      <c r="F23" s="52"/>
+      <c r="G23" s="54" t="n">
         <f aca="false">E23-F23</f>
-        <v>28111.9278567009</v>
+        <v>27936.6529342694</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="50" t="n">
+      <c r="A24" s="51" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="51" t="n">
+      <c r="B24" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I24</f>
         <v>157826</v>
       </c>
-      <c r="C24" s="51" t="n">
+      <c r="C24" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R24</f>
-        <v>75702.6201264222</v>
-      </c>
-      <c r="D24" s="51" t="n">
+        <v>75811.6387394652</v>
+      </c>
+      <c r="D24" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U24</f>
         <v>50667.37</v>
       </c>
-      <c r="E24" s="52" t="n">
+      <c r="E24" s="53" t="n">
         <f aca="false">B24-C24-D24</f>
-        <v>31456.0098735778</v>
-      </c>
-      <c r="F24" s="51"/>
-      <c r="G24" s="53" t="n">
+        <v>31346.9912605348</v>
+      </c>
+      <c r="F24" s="52"/>
+      <c r="G24" s="54" t="n">
         <f aca="false">E24-F24</f>
-        <v>31456.0098735778</v>
+        <v>31346.9912605348</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="50" t="n">
+      <c r="A25" s="51" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="51" t="n">
+      <c r="B25" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I25</f>
         <v>163814</v>
       </c>
-      <c r="C25" s="51" t="n">
+      <c r="C25" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R25</f>
-        <v>77638.6039045085</v>
-      </c>
-      <c r="D25" s="51" t="n">
+        <v>77740.0405100071</v>
+      </c>
+      <c r="D25" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U25</f>
         <v>52134.43</v>
       </c>
-      <c r="E25" s="52" t="n">
+      <c r="E25" s="53" t="n">
         <f aca="false">B25-C25-D25</f>
-        <v>34040.9660954915</v>
-      </c>
-      <c r="F25" s="51"/>
-      <c r="G25" s="53" t="n">
+        <v>33939.5294899929</v>
+      </c>
+      <c r="F25" s="52"/>
+      <c r="G25" s="54" t="n">
         <f aca="false">E25-F25</f>
-        <v>34040.9660954915</v>
+        <v>33939.5294899929</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="50" t="n">
+      <c r="A26" s="51" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="51" t="n">
+      <c r="B26" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I26</f>
         <v>169802</v>
       </c>
-      <c r="C26" s="51" t="n">
+      <c r="C26" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R26</f>
-        <v>79545.9307607052</v>
-      </c>
-      <c r="D26" s="51" t="n">
+        <v>79602.5715986641</v>
+      </c>
+      <c r="D26" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U26</f>
         <v>53601.49</v>
       </c>
-      <c r="E26" s="52" t="n">
+      <c r="E26" s="53" t="n">
         <f aca="false">B26-C26-D26</f>
-        <v>36654.5792392948</v>
-      </c>
-      <c r="F26" s="51"/>
-      <c r="G26" s="53" t="n">
+        <v>36597.9384013359</v>
+      </c>
+      <c r="F26" s="52"/>
+      <c r="G26" s="54" t="n">
         <f aca="false">E26-F26</f>
-        <v>36654.5792392948</v>
+        <v>36597.9384013359</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="50" t="n">
+      <c r="A27" s="51" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="51" t="n">
+      <c r="B27" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I27</f>
         <v>174293</v>
       </c>
-      <c r="C27" s="51" t="n">
+      <c r="C27" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R27</f>
-        <v>80993.1172054434</v>
-      </c>
-      <c r="D27" s="51" t="n">
+        <v>81056.6611395252</v>
+      </c>
+      <c r="D27" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U27</f>
         <v>54701.785</v>
       </c>
-      <c r="E27" s="52" t="n">
+      <c r="E27" s="53" t="n">
         <f aca="false">B27-C27-D27</f>
-        <v>38598.0977945566</v>
-      </c>
-      <c r="F27" s="51"/>
-      <c r="G27" s="53" t="n">
+        <v>38534.5538604748</v>
+      </c>
+      <c r="F27" s="52"/>
+      <c r="G27" s="54" t="n">
         <f aca="false">E27-F27</f>
-        <v>38598.0977945566</v>
+        <v>38534.5538604748</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="n">
+      <c r="A28" s="51" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="51" t="n">
+      <c r="B28" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I28</f>
-        <v>178275.5</v>
-      </c>
-      <c r="C28" s="51" t="n">
+        <v>153278</v>
+      </c>
+      <c r="C28" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R28</f>
-        <v>80340.192334091</v>
-      </c>
-      <c r="D28" s="51" t="n">
+        <v>64025.6762055061</v>
+      </c>
+      <c r="D28" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U28</f>
-        <v>55677.4975</v>
-      </c>
-      <c r="E28" s="52" t="n">
+        <v>49553.11</v>
+      </c>
+      <c r="E28" s="53" t="n">
         <f aca="false">B28-C28-D28</f>
-        <v>42257.810165909</v>
-      </c>
-      <c r="F28" s="51"/>
-      <c r="G28" s="53" t="n">
+        <v>39699.2137944939</v>
+      </c>
+      <c r="F28" s="52"/>
+      <c r="G28" s="54" t="n">
         <f aca="false">E28-F28</f>
-        <v>42257.810165909</v>
+        <v>39699.2137944939</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="50" t="n">
+      <c r="A29" s="51" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="51" t="n">
+      <c r="B29" s="52" t="n">
         <f aca="false">'Projeção Mensal'!I29</f>
-        <v>182766.5</v>
-      </c>
-      <c r="C29" s="51" t="n">
+        <v>187766</v>
+      </c>
+      <c r="C29" s="52" t="n">
         <f aca="false">'Projeção Mensal'!R29</f>
-        <v>81752.9190067688</v>
-      </c>
-      <c r="D29" s="51" t="n">
+        <v>85049.0946477491</v>
+      </c>
+      <c r="D29" s="52" t="n">
         <f aca="false">'Projeção Mensal'!U29</f>
-        <v>56777.7925</v>
-      </c>
-      <c r="E29" s="52" t="n">
+        <v>58002.67</v>
+      </c>
+      <c r="E29" s="53" t="n">
         <f aca="false">B29-C29-D29</f>
-        <v>44235.7884932312</v>
-      </c>
-      <c r="F29" s="51"/>
-      <c r="G29" s="53" t="n">
+        <v>44714.2353522509</v>
+      </c>
+      <c r="F29" s="52"/>
+      <c r="G29" s="54" t="n">
         <f aca="false">E29-F29</f>
-        <v>44235.7884932312</v>
+        <v>44714.2353522509</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="54" t="s">
-        <v>196</v>
-      </c>
-      <c r="B30" s="53" t="n">
+      <c r="A30" s="55" t="s">
+        <v>197</v>
+      </c>
+      <c r="B30" s="54" t="n">
         <f aca="false">SUM(B5:B29)</f>
-        <v>2233383.5</v>
-      </c>
-      <c r="C30" s="53" t="n">
+        <v>2288378</v>
+      </c>
+      <c r="C30" s="54" t="n">
         <f aca="false">SUM(C5:C29)</f>
-        <v>1023471.56155362</v>
-      </c>
-      <c r="D30" s="53" t="n">
+        <v>1059999.8537393</v>
+      </c>
+      <c r="D30" s="54" t="n">
         <f aca="false">SUM(D5:D29)</f>
-        <v>828210.4225</v>
-      </c>
-      <c r="E30" s="53" t="n">
+        <v>841684.075</v>
+      </c>
+      <c r="E30" s="54" t="n">
         <f aca="false">SUM(E5:E29)</f>
-        <v>381701.515946378</v>
-      </c>
-      <c r="F30" s="53" t="n">
+        <v>386694.071260702</v>
+      </c>
+      <c r="F30" s="54" t="n">
         <f aca="false">SUM(F5:F29)</f>
         <v>102000</v>
       </c>
-      <c r="G30" s="53" t="n">
+      <c r="G30" s="54" t="n">
         <f aca="false">SUM(G5:G29)</f>
-        <v>279701.515946378</v>
+        <v>284694.071260702</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="55" t="s">
-        <v>242</v>
+      <c r="A32" s="56" t="s">
+        <v>243</v>
       </c>
     </row>
   </sheetData>
@@ -7012,906 +7018,906 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>243</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
-      <c r="H1" s="48"/>
+      <c r="A1" s="48" t="s">
+        <v>244</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
+      <c r="H1" s="49"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
-        <v>244</v>
+      <c r="A2" s="50" t="s">
+        <v>245</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A4" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="B4" s="17" t="s">
-        <v>177</v>
-      </c>
-      <c r="C4" s="17" t="s">
-        <v>186</v>
-      </c>
-      <c r="D4" s="17" t="s">
-        <v>189</v>
-      </c>
-      <c r="E4" s="17" t="s">
-        <v>203</v>
-      </c>
-      <c r="F4" s="17" t="s">
+      <c r="A4" s="18" t="s">
         <v>241</v>
       </c>
-      <c r="G4" s="17" t="s">
-        <v>245</v>
-      </c>
-      <c r="H4" s="17" t="s">
+      <c r="B4" s="18" t="s">
+        <v>178</v>
+      </c>
+      <c r="C4" s="18" t="s">
+        <v>187</v>
+      </c>
+      <c r="D4" s="18" t="s">
+        <v>190</v>
+      </c>
+      <c r="E4" s="18" t="s">
+        <v>204</v>
+      </c>
+      <c r="F4" s="18" t="s">
+        <v>242</v>
+      </c>
+      <c r="G4" s="18" t="s">
         <v>246</v>
       </c>
+      <c r="H4" s="18" t="s">
+        <v>247</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A5" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="B5" s="52" t="n">
+      <c r="A5" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="B5" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B5</f>
         <v>0</v>
       </c>
-      <c r="C5" s="52" t="n">
+      <c r="C5" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C5</f>
         <v>0</v>
       </c>
-      <c r="D5" s="52" t="n">
+      <c r="D5" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D5</f>
         <v>0</v>
       </c>
-      <c r="E5" s="52" t="n">
+      <c r="E5" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F5</f>
         <v>102000</v>
       </c>
-      <c r="F5" s="52" t="n">
+      <c r="F5" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G5</f>
         <v>-102000</v>
       </c>
-      <c r="G5" s="53" t="n">
+      <c r="G5" s="54" t="n">
         <f aca="false">F5</f>
         <v>-102000</v>
       </c>
-      <c r="H5" s="56" t="str">
+      <c r="H5" s="57" t="str">
         <f aca="false">IF(G5&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A6" s="50" t="n">
+      <c r="A6" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B6" s="52" t="n">
+      <c r="B6" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B6</f>
         <v>5988</v>
       </c>
-      <c r="C6" s="52" t="n">
+      <c r="C6" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C6</f>
         <v>1479.9</v>
       </c>
-      <c r="D6" s="52" t="n">
+      <c r="D6" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D6</f>
         <v>12000</v>
       </c>
-      <c r="E6" s="52" t="n">
+      <c r="E6" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F6</f>
         <v>0</v>
       </c>
-      <c r="F6" s="52" t="n">
+      <c r="F6" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G6</f>
         <v>-7491.9</v>
       </c>
-      <c r="G6" s="53" t="n">
+      <c r="G6" s="54" t="n">
         <f aca="false">G5+F6</f>
         <v>-109491.9</v>
       </c>
-      <c r="H6" s="56" t="str">
+      <c r="H6" s="57" t="str">
         <f aca="false">IF(G6&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A7" s="50" t="n">
+      <c r="A7" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B7" s="52" t="n">
+      <c r="B7" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B7</f>
         <v>8982</v>
       </c>
-      <c r="C7" s="52" t="n">
+      <c r="C7" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C7</f>
         <v>2219.85</v>
       </c>
-      <c r="D7" s="52" t="n">
+      <c r="D7" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D7</f>
         <v>12000</v>
       </c>
-      <c r="E7" s="52" t="n">
+      <c r="E7" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F7</f>
         <v>0</v>
       </c>
-      <c r="F7" s="52" t="n">
+      <c r="F7" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G7</f>
         <v>-5237.85</v>
       </c>
-      <c r="G7" s="53" t="n">
+      <c r="G7" s="54" t="n">
         <f aca="false">G6+F7</f>
         <v>-114729.75</v>
       </c>
-      <c r="H7" s="56" t="str">
+      <c r="H7" s="57" t="str">
         <f aca="false">IF(G7&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A8" s="50" t="n">
+      <c r="A8" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B8" s="52" t="n">
+      <c r="B8" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B8</f>
         <v>13473</v>
       </c>
-      <c r="C8" s="52" t="n">
+      <c r="C8" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C8</f>
         <v>3329.775</v>
       </c>
-      <c r="D8" s="52" t="n">
+      <c r="D8" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D8</f>
         <v>12000</v>
       </c>
-      <c r="E8" s="52" t="n">
+      <c r="E8" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F8</f>
         <v>0</v>
       </c>
-      <c r="F8" s="52" t="n">
+      <c r="F8" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G8</f>
         <v>-1856.775</v>
       </c>
-      <c r="G8" s="53" t="n">
+      <c r="G8" s="54" t="n">
         <f aca="false">G7+F8</f>
         <v>-116586.525</v>
       </c>
-      <c r="H8" s="56" t="str">
+      <c r="H8" s="57" t="str">
         <f aca="false">IF(G8&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A9" s="50" t="n">
+      <c r="A9" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B9" s="52" t="n">
+      <c r="B9" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B9</f>
         <v>24967</v>
       </c>
-      <c r="C9" s="52" t="n">
+      <c r="C9" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C9</f>
         <v>10156.025</v>
       </c>
-      <c r="D9" s="52" t="n">
+      <c r="D9" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D9</f>
         <v>18116.915</v>
       </c>
-      <c r="E9" s="52" t="n">
+      <c r="E9" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F9</f>
         <v>0</v>
       </c>
-      <c r="F9" s="52" t="n">
+      <c r="F9" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G9</f>
         <v>-3305.94</v>
       </c>
-      <c r="G9" s="53" t="n">
+      <c r="G9" s="54" t="n">
         <f aca="false">G8+F9</f>
         <v>-119892.465</v>
       </c>
-      <c r="H9" s="56" t="str">
+      <c r="H9" s="57" t="str">
         <f aca="false">IF(G9&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="50" t="n">
+      <c r="A10" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B10" s="52" t="n">
+      <c r="B10" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B10</f>
         <v>29458</v>
       </c>
-      <c r="C10" s="52" t="n">
+      <c r="C10" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C10</f>
         <v>11265.95</v>
       </c>
-      <c r="D10" s="52" t="n">
+      <c r="D10" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D10</f>
         <v>19217.21</v>
       </c>
-      <c r="E10" s="52" t="n">
+      <c r="E10" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F10</f>
         <v>0</v>
       </c>
-      <c r="F10" s="52" t="n">
+      <c r="F10" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G10</f>
         <v>-1025.16</v>
       </c>
-      <c r="G10" s="53" t="n">
+      <c r="G10" s="54" t="n">
         <f aca="false">G9+F10</f>
         <v>-120917.625</v>
       </c>
-      <c r="H10" s="56" t="str">
+      <c r="H10" s="57" t="str">
         <f aca="false">IF(G10&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="50" t="n">
+      <c r="A11" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B11" s="52" t="n">
+      <c r="B11" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B11</f>
-        <v>35954.5</v>
-      </c>
-      <c r="C11" s="52" t="n">
+        <v>60952</v>
+      </c>
+      <c r="C11" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C11</f>
-        <v>14903.9810602404</v>
-      </c>
-      <c r="D11" s="52" t="n">
+        <v>30336.8789882705</v>
+      </c>
+      <c r="D11" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D11</f>
-        <v>20808.8525</v>
-      </c>
-      <c r="E11" s="52" t="n">
+        <v>26933.24</v>
+      </c>
+      <c r="E11" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F11</f>
         <v>0</v>
       </c>
-      <c r="F11" s="52" t="n">
+      <c r="F11" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G11</f>
-        <v>241.666439759618</v>
-      </c>
-      <c r="G11" s="53" t="n">
+        <v>3681.8810117295</v>
+      </c>
+      <c r="G11" s="54" t="n">
         <f aca="false">G10+F11</f>
-        <v>-120675.95856024</v>
-      </c>
-      <c r="H11" s="56" t="str">
+        <v>-117235.743988271</v>
+      </c>
+      <c r="H11" s="57" t="str">
         <f aca="false">IF(G11&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="50" t="n">
+      <c r="A12" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B12" s="52" t="n">
+      <c r="B12" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B12</f>
-        <v>40445.5</v>
-      </c>
-      <c r="C12" s="52" t="n">
+        <v>35446</v>
+      </c>
+      <c r="C12" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C12</f>
-        <v>16173.831793221</v>
-      </c>
-      <c r="D12" s="52" t="n">
+        <v>13185.4630788486</v>
+      </c>
+      <c r="D12" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D12</f>
-        <v>21909.1475</v>
-      </c>
-      <c r="E12" s="52" t="n">
+        <v>20684.27</v>
+      </c>
+      <c r="E12" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F12</f>
         <v>0</v>
       </c>
-      <c r="F12" s="52" t="n">
+      <c r="F12" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G12</f>
-        <v>2362.52070677902</v>
-      </c>
-      <c r="G12" s="53" t="n">
+        <v>1576.26692115144</v>
+      </c>
+      <c r="G12" s="54" t="n">
         <f aca="false">G11+F12</f>
-        <v>-118313.437853461</v>
-      </c>
-      <c r="H12" s="56" t="str">
+        <v>-115659.477067119</v>
+      </c>
+      <c r="H12" s="57" t="str">
         <f aca="false">IF(G12&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="50" t="n">
+      <c r="A13" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="B13" s="52" t="n">
+      <c r="B13" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B13</f>
-        <v>46942</v>
-      </c>
-      <c r="C13" s="52" t="n">
+        <v>66940</v>
+      </c>
+      <c r="C13" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C13</f>
-        <v>19881.1182183489</v>
-      </c>
-      <c r="D13" s="52" t="n">
+        <v>32473.394606897</v>
+      </c>
+      <c r="D13" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D13</f>
-        <v>23500.79</v>
-      </c>
-      <c r="E13" s="52" t="n">
+        <v>28400.3</v>
+      </c>
+      <c r="E13" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F13</f>
         <v>0</v>
       </c>
-      <c r="F13" s="52" t="n">
+      <c r="F13" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G13</f>
-        <v>3560.09178165106</v>
-      </c>
-      <c r="G13" s="53" t="n">
+        <v>6066.30539310299</v>
+      </c>
+      <c r="G13" s="54" t="n">
         <f aca="false">G12+F13</f>
-        <v>-114753.34607181</v>
-      </c>
-      <c r="H13" s="56" t="str">
+        <v>-109593.171674016</v>
+      </c>
+      <c r="H13" s="57" t="str">
         <f aca="false">IF(G13&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="50" t="n">
+      <c r="A14" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B14" s="52" t="n">
+      <c r="B14" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B14</f>
-        <v>61430</v>
-      </c>
-      <c r="C14" s="52" t="n">
+        <v>51431</v>
+      </c>
+      <c r="C14" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C14</f>
-        <v>27581.4994035207</v>
-      </c>
-      <c r="D14" s="52" t="n">
+        <v>21468.5634248962</v>
+      </c>
+      <c r="D14" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D14</f>
-        <v>27050.35</v>
-      </c>
-      <c r="E14" s="52" t="n">
+        <v>24600.595</v>
+      </c>
+      <c r="E14" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F14</f>
         <v>0</v>
       </c>
-      <c r="F14" s="52" t="n">
+      <c r="F14" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G14</f>
-        <v>6798.15059647932</v>
-      </c>
-      <c r="G14" s="53" t="n">
+        <v>5361.84157510377</v>
+      </c>
+      <c r="G14" s="54" t="n">
         <f aca="false">G13+F14</f>
-        <v>-107955.195475331</v>
-      </c>
-      <c r="H14" s="56" t="str">
+        <v>-104231.330098912</v>
+      </c>
+      <c r="H14" s="57" t="str">
         <f aca="false">IF(G14&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="50" t="n">
+      <c r="A15" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="B15" s="52" t="n">
+      <c r="B15" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B15</f>
-        <v>59426.5</v>
-      </c>
-      <c r="C15" s="52" t="n">
+        <v>74425</v>
+      </c>
+      <c r="C15" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C15</f>
-        <v>25142.1186014796</v>
-      </c>
-      <c r="D15" s="52" t="n">
+        <v>34750.3320927002</v>
+      </c>
+      <c r="D15" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D15</f>
-        <v>26559.4925</v>
-      </c>
-      <c r="E15" s="52" t="n">
+        <v>30234.125</v>
+      </c>
+      <c r="E15" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F15</f>
         <v>0</v>
       </c>
-      <c r="F15" s="52" t="n">
+      <c r="F15" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G15</f>
-        <v>7724.8888985204</v>
-      </c>
-      <c r="G15" s="53" t="n">
+        <v>9440.54290729983</v>
+      </c>
+      <c r="G15" s="54" t="n">
         <f aca="false">G14+F15</f>
-        <v>-100230.306576811</v>
-      </c>
-      <c r="H15" s="56" t="str">
+        <v>-94790.7871916125</v>
+      </c>
+      <c r="H15" s="57" t="str">
         <f aca="false">IF(G15&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="50" t="n">
+      <c r="A16" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="B16" s="52" t="n">
+      <c r="B16" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B16</f>
-        <v>73914.5</v>
-      </c>
-      <c r="C16" s="52" t="n">
+        <v>58916</v>
+      </c>
+      <c r="C16" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C16</f>
-        <v>32956.1812920729</v>
-      </c>
-      <c r="D16" s="52" t="n">
+        <v>23690.1528924749</v>
+      </c>
+      <c r="D16" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D16</f>
-        <v>30109.0525</v>
-      </c>
-      <c r="E16" s="52" t="n">
+        <v>26434.42</v>
+      </c>
+      <c r="E16" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F16</f>
         <v>0</v>
       </c>
-      <c r="F16" s="52" t="n">
+      <c r="F16" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G16</f>
-        <v>10849.2662079271</v>
-      </c>
-      <c r="G16" s="53" t="n">
+        <v>8791.42710752508</v>
+      </c>
+      <c r="G16" s="54" t="n">
         <f aca="false">G15+F16</f>
-        <v>-89381.0403688835</v>
-      </c>
-      <c r="H16" s="56" t="str">
+        <v>-85999.3600840874</v>
+      </c>
+      <c r="H16" s="57" t="str">
         <f aca="false">IF(G16&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="50" t="n">
+      <c r="A17" s="51" t="n">
         <v>12</v>
       </c>
-      <c r="B17" s="52" t="n">
+      <c r="B17" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B17</f>
-        <v>66911.5</v>
-      </c>
-      <c r="C17" s="52" t="n">
+        <v>81910</v>
+      </c>
+      <c r="C17" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C17</f>
-        <v>27417.831764404</v>
-      </c>
-      <c r="D17" s="52" t="n">
+        <v>37031.4908475607</v>
+      </c>
+      <c r="D17" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D17</f>
-        <v>28393.3175</v>
-      </c>
-      <c r="E17" s="52" t="n">
+        <v>32067.95</v>
+      </c>
+      <c r="E17" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F17</f>
         <v>0</v>
       </c>
-      <c r="F17" s="52" t="n">
+      <c r="F17" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G17</f>
-        <v>11100.3507355959</v>
-      </c>
-      <c r="G17" s="53" t="n">
+        <v>12810.5591524393</v>
+      </c>
+      <c r="G17" s="54" t="n">
         <f aca="false">G16+F17</f>
-        <v>-78280.6896332875</v>
-      </c>
-      <c r="H17" s="56" t="str">
+        <v>-73188.8009316481</v>
+      </c>
+      <c r="H17" s="57" t="str">
         <f aca="false">IF(G17&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="50" t="n">
+      <c r="A18" s="51" t="n">
         <v>13</v>
       </c>
-      <c r="B18" s="52" t="n">
+      <c r="B18" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B18</f>
-        <v>104896</v>
-      </c>
-      <c r="C18" s="52" t="n">
+        <v>114895</v>
+      </c>
+      <c r="C18" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C18</f>
-        <v>51415.5763411467</v>
-      </c>
-      <c r="D18" s="52" t="n">
+        <v>57966.6688817052</v>
+      </c>
+      <c r="D18" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D18</f>
-        <v>37699.52</v>
-      </c>
-      <c r="E18" s="52" t="n">
+        <v>40149.275</v>
+      </c>
+      <c r="E18" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F18</f>
         <v>0</v>
       </c>
-      <c r="F18" s="52" t="n">
+      <c r="F18" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G18</f>
-        <v>15780.9036588533</v>
-      </c>
-      <c r="G18" s="53" t="n">
+        <v>16779.0561182948</v>
+      </c>
+      <c r="G18" s="54" t="n">
         <f aca="false">G17+F18</f>
-        <v>-62499.7859744343</v>
-      </c>
-      <c r="H18" s="56" t="str">
+        <v>-56409.7448133532</v>
+      </c>
+      <c r="H18" s="57" t="str">
         <f aca="false">IF(G18&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="50" t="n">
+      <c r="A19" s="51" t="n">
         <v>14</v>
       </c>
-      <c r="B19" s="52" t="n">
+      <c r="B19" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B19</f>
-        <v>109387</v>
-      </c>
-      <c r="C19" s="52" t="n">
+        <v>119386</v>
+      </c>
+      <c r="C19" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C19</f>
-        <v>53122.0010044143</v>
-      </c>
-      <c r="D19" s="52" t="n">
+        <v>59681.1683465612</v>
+      </c>
+      <c r="D19" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D19</f>
-        <v>38799.815</v>
-      </c>
-      <c r="E19" s="52" t="n">
+        <v>41249.57</v>
+      </c>
+      <c r="E19" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F19</f>
         <v>0</v>
       </c>
-      <c r="F19" s="52" t="n">
+      <c r="F19" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G19</f>
-        <v>17465.1839955858</v>
-      </c>
-      <c r="G19" s="53" t="n">
+        <v>18455.2616534388</v>
+      </c>
+      <c r="G19" s="54" t="n">
         <f aca="false">G18+F19</f>
-        <v>-45034.6019788485</v>
-      </c>
-      <c r="H19" s="56" t="str">
+        <v>-37954.4831599144</v>
+      </c>
+      <c r="H19" s="57" t="str">
         <f aca="false">IF(G19&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="50" t="n">
+      <c r="A20" s="51" t="n">
         <v>15</v>
       </c>
-      <c r="B20" s="52" t="n">
+      <c r="B20" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B20</f>
-        <v>120374.5</v>
-      </c>
-      <c r="C20" s="52" t="n">
+        <v>125374</v>
+      </c>
+      <c r="C20" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C20</f>
-        <v>58240.5998046273</v>
-      </c>
-      <c r="D20" s="52" t="n">
+        <v>61627.1271537519</v>
+      </c>
+      <c r="D20" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D20</f>
-        <v>41491.7525</v>
-      </c>
-      <c r="E20" s="52" t="n">
+        <v>42716.63</v>
+      </c>
+      <c r="E20" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F20</f>
         <v>0</v>
       </c>
-      <c r="F20" s="52" t="n">
+      <c r="F20" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G20</f>
-        <v>20642.1476953727</v>
-      </c>
-      <c r="G20" s="53" t="n">
+        <v>21030.2428462481</v>
+      </c>
+      <c r="G20" s="54" t="n">
         <f aca="false">G19+F20</f>
-        <v>-24392.4542834758</v>
-      </c>
-      <c r="H20" s="56" t="str">
+        <v>-16924.2403136663</v>
+      </c>
+      <c r="H20" s="57" t="str">
         <f aca="false">IF(G20&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="50" t="n">
+      <c r="A21" s="51" t="n">
         <v>16</v>
       </c>
-      <c r="B21" s="52" t="n">
+      <c r="B21" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B21</f>
-        <v>126362.5</v>
-      </c>
-      <c r="C21" s="52" t="n">
+        <v>131362</v>
+      </c>
+      <c r="C21" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C21</f>
-        <v>60218.418732278</v>
-      </c>
-      <c r="D21" s="52" t="n">
+        <v>63673.2840244047</v>
+      </c>
+      <c r="D21" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D21</f>
-        <v>42958.8125</v>
-      </c>
-      <c r="E21" s="52" t="n">
+        <v>44183.69</v>
+      </c>
+      <c r="E21" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F21</f>
         <v>0</v>
       </c>
-      <c r="F21" s="52" t="n">
+      <c r="F21" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G21</f>
-        <v>23185.268767722</v>
-      </c>
-      <c r="G21" s="53" t="n">
+        <v>23505.0259755953</v>
+      </c>
+      <c r="G21" s="54" t="n">
         <f aca="false">G20+F21</f>
-        <v>-1207.18551575377</v>
-      </c>
-      <c r="H21" s="56" t="str">
+        <v>6580.78566192901</v>
+      </c>
+      <c r="H21" s="57" t="str">
         <f aca="false">IF(G21&gt;=0,"Sim","Não")</f>
-        <v>Não</v>
+        <v>Sim</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="50" t="n">
+      <c r="A22" s="51" t="n">
         <v>17</v>
       </c>
-      <c r="B22" s="52" t="n">
+      <c r="B22" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B22</f>
         <v>135853</v>
       </c>
-      <c r="C22" s="52" t="n">
+      <c r="C22" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C22</f>
-        <v>65015.4930566303</v>
-      </c>
-      <c r="D22" s="52" t="n">
+        <v>65224.8444945791</v>
+      </c>
+      <c r="D22" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D22</f>
         <v>45283.985</v>
       </c>
-      <c r="E22" s="52" t="n">
+      <c r="E22" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F22</f>
         <v>0</v>
       </c>
-      <c r="F22" s="52" t="n">
+      <c r="F22" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G22</f>
-        <v>25553.5219433697</v>
-      </c>
-      <c r="G22" s="53" t="n">
+        <v>25344.1705054209</v>
+      </c>
+      <c r="G22" s="54" t="n">
         <f aca="false">G21+F22</f>
-        <v>24346.3364276159</v>
-      </c>
-      <c r="H22" s="56" t="str">
+        <v>31924.9561673499</v>
+      </c>
+      <c r="H22" s="57" t="str">
         <f aca="false">IF(G22&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="50" t="n">
+      <c r="A23" s="51" t="n">
         <v>18</v>
       </c>
-      <c r="B23" s="52" t="n">
+      <c r="B23" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B23</f>
         <v>141841</v>
       </c>
-      <c r="C23" s="52" t="n">
+      <c r="C23" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C23</f>
-        <v>66978.0271432991</v>
-      </c>
-      <c r="D23" s="52" t="n">
+        <v>67153.3020657306</v>
+      </c>
+      <c r="D23" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D23</f>
         <v>46751.045</v>
       </c>
-      <c r="E23" s="52" t="n">
+      <c r="E23" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F23</f>
         <v>0</v>
       </c>
-      <c r="F23" s="52" t="n">
+      <c r="F23" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G23</f>
-        <v>28111.9278567009</v>
-      </c>
-      <c r="G23" s="53" t="n">
+        <v>27936.6529342694</v>
+      </c>
+      <c r="G23" s="54" t="n">
         <f aca="false">G22+F23</f>
-        <v>52458.2642843168</v>
-      </c>
-      <c r="H23" s="56" t="str">
+        <v>59861.6091016193</v>
+      </c>
+      <c r="H23" s="57" t="str">
         <f aca="false">IF(G23&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="50" t="n">
+      <c r="A24" s="51" t="n">
         <v>19</v>
       </c>
-      <c r="B24" s="52" t="n">
+      <c r="B24" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B24</f>
         <v>157826</v>
       </c>
-      <c r="C24" s="52" t="n">
+      <c r="C24" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C24</f>
-        <v>75702.6201264222</v>
-      </c>
-      <c r="D24" s="52" t="n">
+        <v>75811.6387394652</v>
+      </c>
+      <c r="D24" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D24</f>
         <v>50667.37</v>
       </c>
-      <c r="E24" s="52" t="n">
+      <c r="E24" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F24</f>
         <v>0</v>
       </c>
-      <c r="F24" s="52" t="n">
+      <c r="F24" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G24</f>
-        <v>31456.0098735778</v>
-      </c>
-      <c r="G24" s="53" t="n">
+        <v>31346.9912605348</v>
+      </c>
+      <c r="G24" s="54" t="n">
         <f aca="false">G23+F24</f>
-        <v>83914.2741578947</v>
-      </c>
-      <c r="H24" s="56" t="str">
+        <v>91208.6003621541</v>
+      </c>
+      <c r="H24" s="57" t="str">
         <f aca="false">IF(G24&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="50" t="n">
+      <c r="A25" s="51" t="n">
         <v>20</v>
       </c>
-      <c r="B25" s="52" t="n">
+      <c r="B25" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B25</f>
         <v>163814</v>
       </c>
-      <c r="C25" s="52" t="n">
+      <c r="C25" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C25</f>
-        <v>77638.6039045085</v>
-      </c>
-      <c r="D25" s="52" t="n">
+        <v>77740.0405100071</v>
+      </c>
+      <c r="D25" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D25</f>
         <v>52134.43</v>
       </c>
-      <c r="E25" s="52" t="n">
+      <c r="E25" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F25</f>
         <v>0</v>
       </c>
-      <c r="F25" s="52" t="n">
+      <c r="F25" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G25</f>
-        <v>34040.9660954915</v>
-      </c>
-      <c r="G25" s="53" t="n">
+        <v>33939.5294899929</v>
+      </c>
+      <c r="G25" s="54" t="n">
         <f aca="false">G24+F25</f>
-        <v>117955.240253386</v>
-      </c>
-      <c r="H25" s="56" t="str">
+        <v>125148.129852147</v>
+      </c>
+      <c r="H25" s="57" t="str">
         <f aca="false">IF(G25&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="50" t="n">
+      <c r="A26" s="51" t="n">
         <v>21</v>
       </c>
-      <c r="B26" s="52" t="n">
+      <c r="B26" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B26</f>
         <v>169802</v>
       </c>
-      <c r="C26" s="52" t="n">
+      <c r="C26" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C26</f>
-        <v>79545.9307607052</v>
-      </c>
-      <c r="D26" s="52" t="n">
+        <v>79602.5715986641</v>
+      </c>
+      <c r="D26" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D26</f>
         <v>53601.49</v>
       </c>
-      <c r="E26" s="52" t="n">
+      <c r="E26" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F26</f>
         <v>0</v>
       </c>
-      <c r="F26" s="52" t="n">
+      <c r="F26" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G26</f>
-        <v>36654.5792392948</v>
-      </c>
-      <c r="G26" s="53" t="n">
+        <v>36597.9384013359</v>
+      </c>
+      <c r="G26" s="54" t="n">
         <f aca="false">G25+F26</f>
-        <v>154609.819492681</v>
-      </c>
-      <c r="H26" s="56" t="str">
+        <v>161746.068253483</v>
+      </c>
+      <c r="H26" s="57" t="str">
         <f aca="false">IF(G26&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="50" t="n">
+      <c r="A27" s="51" t="n">
         <v>22</v>
       </c>
-      <c r="B27" s="52" t="n">
+      <c r="B27" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B27</f>
         <v>174293</v>
       </c>
-      <c r="C27" s="52" t="n">
+      <c r="C27" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C27</f>
-        <v>80993.1172054434</v>
-      </c>
-      <c r="D27" s="52" t="n">
+        <v>81056.6611395252</v>
+      </c>
+      <c r="D27" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D27</f>
         <v>54701.785</v>
       </c>
-      <c r="E27" s="52" t="n">
+      <c r="E27" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F27</f>
         <v>0</v>
       </c>
-      <c r="F27" s="52" t="n">
+      <c r="F27" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G27</f>
-        <v>38598.0977945566</v>
-      </c>
-      <c r="G27" s="53" t="n">
+        <v>38534.5538604748</v>
+      </c>
+      <c r="G27" s="54" t="n">
         <f aca="false">G26+F27</f>
-        <v>193207.917287238</v>
-      </c>
-      <c r="H27" s="56" t="str">
+        <v>200280.622113958</v>
+      </c>
+      <c r="H27" s="57" t="str">
         <f aca="false">IF(G27&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="n">
+      <c r="A28" s="51" t="n">
         <v>23</v>
       </c>
-      <c r="B28" s="52" t="n">
+      <c r="B28" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B28</f>
-        <v>178275.5</v>
-      </c>
-      <c r="C28" s="52" t="n">
+        <v>153278</v>
+      </c>
+      <c r="C28" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C28</f>
-        <v>80340.192334091</v>
-      </c>
-      <c r="D28" s="52" t="n">
+        <v>64025.6762055061</v>
+      </c>
+      <c r="D28" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D28</f>
-        <v>55677.4975</v>
-      </c>
-      <c r="E28" s="52" t="n">
+        <v>49553.11</v>
+      </c>
+      <c r="E28" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F28</f>
         <v>0</v>
       </c>
-      <c r="F28" s="52" t="n">
+      <c r="F28" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G28</f>
-        <v>42257.810165909</v>
-      </c>
-      <c r="G28" s="53" t="n">
+        <v>39699.2137944939</v>
+      </c>
+      <c r="G28" s="54" t="n">
         <f aca="false">G27+F28</f>
-        <v>235465.727453147</v>
-      </c>
-      <c r="H28" s="56" t="str">
+        <v>239979.835908452</v>
+      </c>
+      <c r="H28" s="57" t="str">
         <f aca="false">IF(G28&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="50" t="n">
+      <c r="A29" s="51" t="n">
         <v>24</v>
       </c>
-      <c r="B29" s="52" t="n">
+      <c r="B29" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!B29</f>
-        <v>182766.5</v>
-      </c>
-      <c r="C29" s="52" t="n">
+        <v>187766</v>
+      </c>
+      <c r="C29" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!C29</f>
-        <v>81752.9190067688</v>
-      </c>
-      <c r="D29" s="52" t="n">
+        <v>85049.0946477491</v>
+      </c>
+      <c r="D29" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!D29</f>
-        <v>56777.7925</v>
-      </c>
-      <c r="E29" s="52" t="n">
+        <v>58002.67</v>
+      </c>
+      <c r="E29" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!F29</f>
         <v>0</v>
       </c>
-      <c r="F29" s="52" t="n">
+      <c r="F29" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G29</f>
-        <v>44235.7884932312</v>
-      </c>
-      <c r="G29" s="53" t="n">
+        <v>44714.2353522509</v>
+      </c>
+      <c r="G29" s="54" t="n">
         <f aca="false">G28+F29</f>
-        <v>279701.515946378</v>
-      </c>
-      <c r="H29" s="56" t="str">
+        <v>284694.071260702</v>
+      </c>
+      <c r="H29" s="57" t="str">
         <f aca="false">IF(G29&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A31" s="4" t="s">
-        <v>247</v>
-      </c>
-      <c r="B31" s="48"/>
-      <c r="C31" s="48"/>
-      <c r="D31" s="48"/>
-      <c r="E31" s="48"/>
-      <c r="F31" s="48"/>
-      <c r="G31" s="48"/>
+        <v>248</v>
+      </c>
+      <c r="B31" s="49"/>
+      <c r="C31" s="49"/>
+      <c r="D31" s="49"/>
+      <c r="E31" s="49"/>
+      <c r="F31" s="49"/>
+      <c r="G31" s="49"/>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A32" s="3" t="s">
-        <v>248</v>
-      </c>
-      <c r="F32" s="57" t="n">
+        <v>249</v>
+      </c>
+      <c r="F32" s="58" t="n">
         <f aca="false">MAX(0,-MIN(G5:G29))</f>
         <v>120917.625</v>
       </c>
-      <c r="G32" s="58" t="s">
-        <v>249</v>
+      <c r="G32" s="59" t="s">
+        <v>250</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A33" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="F33" s="59" t="n">
+        <v>251</v>
+      </c>
+      <c r="F33" s="60" t="n">
         <f aca="false">IFERROR(INDEX(A5:A29,MATCH("Sim",H5:H29,0)),"Não recupera")</f>
-        <v>17</v>
-      </c>
-      <c r="G33" s="58" t="s">
-        <v>251</v>
+        <v>16</v>
+      </c>
+      <c r="G33" s="59" t="s">
+        <v>252</v>
       </c>
     </row>
   </sheetData>
@@ -7949,877 +7955,877 @@
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="17.25" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A1" s="47" t="s">
-        <v>252</v>
-      </c>
-      <c r="B1" s="48"/>
-      <c r="C1" s="48"/>
-      <c r="D1" s="48"/>
-      <c r="E1" s="48"/>
-      <c r="F1" s="48"/>
-      <c r="G1" s="48"/>
+      <c r="A1" s="48" t="s">
+        <v>253</v>
+      </c>
+      <c r="B1" s="49"/>
+      <c r="C1" s="49"/>
+      <c r="D1" s="49"/>
+      <c r="E1" s="49"/>
+      <c r="F1" s="49"/>
+      <c r="G1" s="49"/>
     </row>
     <row r="2" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A2" s="49" t="s">
-        <v>253</v>
+      <c r="A2" s="50" t="s">
+        <v>254</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A4" s="4" t="s">
-        <v>254</v>
-      </c>
-      <c r="B4" s="48"/>
-      <c r="C4" s="48"/>
-      <c r="D4" s="48"/>
-      <c r="E4" s="48"/>
-      <c r="F4" s="48"/>
-      <c r="G4" s="48"/>
+        <v>255</v>
+      </c>
+      <c r="B4" s="49"/>
+      <c r="C4" s="49"/>
+      <c r="D4" s="49"/>
+      <c r="E4" s="49"/>
+      <c r="F4" s="49"/>
+      <c r="G4" s="49"/>
     </row>
     <row r="5" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A5" s="3" t="s">
-        <v>255</v>
-      </c>
-      <c r="B5" s="60" t="n">
+        <v>256</v>
+      </c>
+      <c r="B5" s="61" t="n">
         <f aca="false">'Premissas Precept'!B64</f>
         <v>0.24</v>
       </c>
-      <c r="C5" s="58" t="s">
-        <v>256</v>
+      <c r="C5" s="59" t="s">
+        <v>257</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A6" s="3" t="s">
-        <v>257</v>
-      </c>
-      <c r="B6" s="61" t="s">
         <v>258</v>
       </c>
-      <c r="C6" s="58" t="s">
+      <c r="B6" s="62" t="s">
         <v>259</v>
+      </c>
+      <c r="C6" s="59" t="s">
+        <v>260</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A7" s="3" t="s">
-        <v>260</v>
-      </c>
-      <c r="B7" s="62" t="n">
+        <v>261</v>
+      </c>
+      <c r="B7" s="63" t="n">
         <f aca="false">IF(B6="Mensal",(1+B5)^(1/12)-1,B5)</f>
         <v>0.0180875824835107</v>
       </c>
-      <c r="C7" s="58" t="s">
-        <v>261</v>
+      <c r="C7" s="59" t="s">
+        <v>262</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A9" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="B9" s="48"/>
-      <c r="C9" s="48"/>
-      <c r="D9" s="48"/>
-      <c r="E9" s="48"/>
-      <c r="F9" s="48"/>
-      <c r="G9" s="48"/>
+        <v>263</v>
+      </c>
+      <c r="B9" s="49"/>
+      <c r="C9" s="49"/>
+      <c r="D9" s="49"/>
+      <c r="E9" s="49"/>
+      <c r="F9" s="49"/>
+      <c r="G9" s="49"/>
     </row>
     <row r="10" customFormat="false" ht="31.5" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A10" s="17" t="s">
-        <v>240</v>
-      </c>
-      <c r="B10" s="17" t="s">
-        <v>263</v>
-      </c>
-      <c r="C10" s="17" t="s">
+      <c r="A10" s="18" t="s">
+        <v>241</v>
+      </c>
+      <c r="B10" s="18" t="s">
         <v>264</v>
       </c>
-      <c r="D10" s="17" t="s">
+      <c r="C10" s="18" t="s">
         <v>265</v>
       </c>
-      <c r="E10" s="17" t="s">
+      <c r="D10" s="18" t="s">
         <v>266</v>
       </c>
-      <c r="F10" s="17" t="s">
+      <c r="E10" s="18" t="s">
         <v>267</v>
       </c>
+      <c r="F10" s="18" t="s">
+        <v>268</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A11" s="50" t="n">
-        <v>0</v>
-      </c>
-      <c r="B11" s="52" t="n">
+      <c r="A11" s="51" t="n">
+        <v>0</v>
+      </c>
+      <c r="B11" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G5</f>
         <v>-102000</v>
       </c>
-      <c r="C11" s="63" t="n">
+      <c r="C11" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A11</f>
         <v>1</v>
       </c>
-      <c r="D11" s="52" t="n">
+      <c r="D11" s="53" t="n">
         <f aca="false">B11*C11</f>
         <v>-102000</v>
       </c>
-      <c r="E11" s="53" t="n">
+      <c r="E11" s="54" t="n">
         <f aca="false">D11</f>
         <v>-102000</v>
       </c>
-      <c r="F11" s="56" t="str">
+      <c r="F11" s="57" t="str">
         <f aca="false">IF(E11&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A12" s="50" t="n">
+      <c r="A12" s="51" t="n">
         <v>1</v>
       </c>
-      <c r="B12" s="52" t="n">
+      <c r="B12" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G6</f>
         <v>-7491.9</v>
       </c>
-      <c r="C12" s="63" t="n">
+      <c r="C12" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A12</f>
         <v>0.982233765744016</v>
       </c>
-      <c r="D12" s="52" t="n">
+      <c r="D12" s="53" t="n">
         <f aca="false">B12*C12</f>
         <v>-7358.79714957759</v>
       </c>
-      <c r="E12" s="53" t="n">
+      <c r="E12" s="54" t="n">
         <f aca="false">E11+D12</f>
         <v>-109358.797149578</v>
       </c>
-      <c r="F12" s="56" t="str">
+      <c r="F12" s="57" t="str">
         <f aca="false">IF(E12&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A13" s="50" t="n">
+      <c r="A13" s="51" t="n">
         <v>2</v>
       </c>
-      <c r="B13" s="52" t="n">
+      <c r="B13" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G7</f>
         <v>-5237.85</v>
       </c>
-      <c r="C13" s="63" t="n">
+      <c r="C13" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A13</f>
         <v>0.96478317056767</v>
       </c>
-      <c r="D13" s="52" t="n">
+      <c r="D13" s="53" t="n">
         <f aca="false">B13*C13</f>
         <v>-5053.38952995787</v>
       </c>
-      <c r="E13" s="53" t="n">
+      <c r="E13" s="54" t="n">
         <f aca="false">E12+D13</f>
         <v>-114412.186679535</v>
       </c>
-      <c r="F13" s="56" t="str">
+      <c r="F13" s="57" t="str">
         <f aca="false">IF(E13&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="14" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A14" s="50" t="n">
+      <c r="A14" s="51" t="n">
         <v>3</v>
       </c>
-      <c r="B14" s="52" t="n">
+      <c r="B14" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G8</f>
         <v>-1856.775</v>
       </c>
-      <c r="C14" s="63" t="n">
+      <c r="C14" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A14</f>
         <v>0.947642606753134</v>
       </c>
-      <c r="D14" s="52" t="n">
+      <c r="D14" s="53" t="n">
         <f aca="false">B14*C14</f>
         <v>-1759.55910115405</v>
       </c>
-      <c r="E14" s="53" t="n">
+      <c r="E14" s="54" t="n">
         <f aca="false">E13+D14</f>
         <v>-116171.74578069</v>
       </c>
-      <c r="F14" s="56" t="str">
+      <c r="F14" s="57" t="str">
         <f aca="false">IF(E14&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="15" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A15" s="50" t="n">
+      <c r="A15" s="51" t="n">
         <v>4</v>
       </c>
-      <c r="B15" s="52" t="n">
+      <c r="B15" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G9</f>
         <v>-3305.94</v>
       </c>
-      <c r="C15" s="63" t="n">
+      <c r="C15" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A15</f>
         <v>0.930806566210606</v>
       </c>
-      <c r="D15" s="52" t="n">
+      <c r="D15" s="53" t="n">
         <f aca="false">B15*C15</f>
         <v>-3077.19065949829</v>
       </c>
-      <c r="E15" s="53" t="n">
+      <c r="E15" s="54" t="n">
         <f aca="false">E14+D15</f>
         <v>-119248.936440188</v>
       </c>
-      <c r="F15" s="56" t="str">
+      <c r="F15" s="57" t="str">
         <f aca="false">IF(E15&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="16" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A16" s="50" t="n">
+      <c r="A16" s="51" t="n">
         <v>5</v>
       </c>
-      <c r="B16" s="52" t="n">
+      <c r="B16" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G10</f>
         <v>-1025.16</v>
       </c>
-      <c r="C16" s="63" t="n">
+      <c r="C16" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A16</f>
         <v>0.9142696387083</v>
       </c>
-      <c r="D16" s="52" t="n">
+      <c r="D16" s="53" t="n">
         <f aca="false">B16*C16</f>
         <v>-937.272662818197</v>
       </c>
-      <c r="E16" s="53" t="n">
+      <c r="E16" s="54" t="n">
         <f aca="false">E15+D16</f>
         <v>-120186.209103006</v>
       </c>
-      <c r="F16" s="56" t="str">
+      <c r="F16" s="57" t="str">
         <f aca="false">IF(E16&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="17" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A17" s="50" t="n">
+      <c r="A17" s="51" t="n">
         <v>6</v>
       </c>
-      <c r="B17" s="52" t="n">
+      <c r="B17" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G11</f>
-        <v>241.666439759618</v>
-      </c>
-      <c r="C17" s="63" t="n">
+        <v>3681.8810117295</v>
+      </c>
+      <c r="C17" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A17</f>
         <v>0.898026510133874</v>
       </c>
-      <c r="D17" s="52" t="n">
+      <c r="D17" s="53" t="n">
         <f aca="false">B17*C17</f>
-        <v>217.022869513808</v>
-      </c>
-      <c r="E17" s="53" t="n">
+        <v>3306.42675569162</v>
+      </c>
+      <c r="E17" s="54" t="n">
         <f aca="false">E16+D17</f>
-        <v>-119969.186233492</v>
-      </c>
-      <c r="F17" s="56" t="str">
+        <v>-116879.782347314</v>
+      </c>
+      <c r="F17" s="57" t="str">
         <f aca="false">IF(E17&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="18" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A18" s="50" t="n">
+      <c r="A18" s="51" t="n">
         <v>7</v>
       </c>
-      <c r="B18" s="52" t="n">
+      <c r="B18" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G12</f>
-        <v>2362.52070677902</v>
-      </c>
-      <c r="C18" s="63" t="n">
+        <v>1576.26692115144</v>
+      </c>
+      <c r="C18" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A18</f>
         <v>0.882071960786752</v>
       </c>
-      <c r="D18" s="52" t="n">
+      <c r="D18" s="53" t="n">
         <f aca="false">B18*C18</f>
-        <v>2083.91327222787</v>
-      </c>
-      <c r="E18" s="53" t="n">
+        <v>1390.38085386335</v>
+      </c>
+      <c r="E18" s="54" t="n">
         <f aca="false">E17+D18</f>
-        <v>-117885.272961264</v>
-      </c>
-      <c r="F18" s="56" t="str">
+        <v>-115489.401493451</v>
+      </c>
+      <c r="F18" s="57" t="str">
         <f aca="false">IF(E18&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="19" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A19" s="50" t="n">
+      <c r="A19" s="51" t="n">
         <v>8</v>
       </c>
-      <c r="B19" s="52" t="n">
+      <c r="B19" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G13</f>
-        <v>3560.09178165106</v>
-      </c>
-      <c r="C19" s="63" t="n">
+        <v>6066.30539310299</v>
+      </c>
+      <c r="C19" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A19</f>
         <v>0.866400863700779</v>
       </c>
-      <c r="D19" s="52" t="n">
+      <c r="D19" s="53" t="n">
         <f aca="false">B19*C19</f>
-        <v>3084.46659447652</v>
-      </c>
-      <c r="E19" s="53" t="n">
+        <v>5255.85223205712</v>
+      </c>
+      <c r="E19" s="54" t="n">
         <f aca="false">E18+D19</f>
-        <v>-114800.806366788</v>
-      </c>
-      <c r="F19" s="56" t="str">
+        <v>-110233.549261394</v>
+      </c>
+      <c r="F19" s="57" t="str">
         <f aca="false">IF(E19&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="20" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A20" s="50" t="n">
+      <c r="A20" s="51" t="n">
         <v>9</v>
       </c>
-      <c r="B20" s="52" t="n">
+      <c r="B20" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G14</f>
-        <v>6798.15059647932</v>
-      </c>
-      <c r="C20" s="63" t="n">
+        <v>5361.84157510377</v>
+      </c>
+      <c r="C20" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A20</f>
         <v>0.851008182996684</v>
       </c>
-      <c r="D20" s="52" t="n">
+      <c r="D20" s="53" t="n">
         <f aca="false">B20*C20</f>
-        <v>5785.28178684769</v>
-      </c>
-      <c r="E20" s="53" t="n">
+        <v>4562.97105634514</v>
+      </c>
+      <c r="E20" s="54" t="n">
         <f aca="false">E19+D20</f>
-        <v>-109015.52457994</v>
-      </c>
-      <c r="F20" s="56" t="str">
+        <v>-105670.578205049</v>
+      </c>
+      <c r="F20" s="57" t="str">
         <f aca="false">IF(E20&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="21" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A21" s="50" t="n">
+      <c r="A21" s="51" t="n">
         <v>10</v>
       </c>
-      <c r="B21" s="52" t="n">
+      <c r="B21" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G15</f>
-        <v>7724.8888985204</v>
-      </c>
-      <c r="C21" s="63" t="n">
+        <v>9440.54290729983</v>
+      </c>
+      <c r="C21" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A21</f>
         <v>0.835888972263805</v>
       </c>
-      <c r="D21" s="52" t="n">
+      <c r="D21" s="53" t="n">
         <f aca="false">B21*C21</f>
-        <v>6457.1494422363</v>
-      </c>
-      <c r="E21" s="53" t="n">
+        <v>7891.24570839521</v>
+      </c>
+      <c r="E21" s="54" t="n">
         <f aca="false">E20+D21</f>
-        <v>-102558.375137704</v>
-      </c>
-      <c r="F21" s="56" t="str">
+        <v>-97779.3324966536</v>
+      </c>
+      <c r="F21" s="57" t="str">
         <f aca="false">IF(E21&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="22" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A22" s="50" t="n">
+      <c r="A22" s="51" t="n">
         <v>11</v>
       </c>
-      <c r="B22" s="52" t="n">
+      <c r="B22" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G16</f>
-        <v>10849.2662079271</v>
-      </c>
-      <c r="C22" s="63" t="n">
+        <v>8791.42710752508</v>
+      </c>
+      <c r="C22" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A22</f>
         <v>0.821038372970573</v>
       </c>
-      <c r="D22" s="52" t="n">
+      <c r="D22" s="53" t="n">
         <f aca="false">B22*C22</f>
-        <v>8907.66387528111</v>
-      </c>
-      <c r="E22" s="53" t="n">
+        <v>7218.09900845178</v>
+      </c>
+      <c r="E22" s="54" t="n">
         <f aca="false">E21+D22</f>
-        <v>-93650.7112624227</v>
-      </c>
-      <c r="F22" s="56" t="str">
+        <v>-90561.2334882018</v>
+      </c>
+      <c r="F22" s="57" t="str">
         <f aca="false">IF(E22&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="23" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A23" s="50" t="n">
+      <c r="A23" s="51" t="n">
         <v>12</v>
       </c>
-      <c r="B23" s="52" t="n">
+      <c r="B23" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G17</f>
-        <v>11100.3507355959</v>
-      </c>
-      <c r="C23" s="63" t="n">
+        <v>12810.5591524393</v>
+      </c>
+      <c r="C23" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A23</f>
         <v>0.806451612903225</v>
       </c>
-      <c r="D23" s="52" t="n">
+      <c r="D23" s="53" t="n">
         <f aca="false">B23*C23</f>
-        <v>8951.89575451286</v>
-      </c>
-      <c r="E23" s="53" t="n">
+        <v>10331.0960906769</v>
+      </c>
+      <c r="E23" s="54" t="n">
         <f aca="false">E22+D23</f>
-        <v>-84698.8155079098</v>
-      </c>
-      <c r="F23" s="56" t="str">
+        <v>-80230.1373975249</v>
+      </c>
+      <c r="F23" s="57" t="str">
         <f aca="false">IF(E23&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="24" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A24" s="50" t="n">
+      <c r="A24" s="51" t="n">
         <v>13</v>
       </c>
-      <c r="B24" s="52" t="n">
+      <c r="B24" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G18</f>
-        <v>15780.9036588533</v>
-      </c>
-      <c r="C24" s="63" t="n">
+        <v>16779.0561182948</v>
+      </c>
+      <c r="C24" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A24</f>
         <v>0.79212400463227</v>
       </c>
-      <c r="D24" s="52" t="n">
+      <c r="D24" s="53" t="n">
         <f aca="false">B24*C24</f>
-        <v>12500.4326029669</v>
-      </c>
-      <c r="E24" s="53" t="n">
+        <v>13291.0931263733</v>
+      </c>
+      <c r="E24" s="54" t="n">
         <f aca="false">E23+D24</f>
-        <v>-72198.382904943</v>
-      </c>
-      <c r="F24" s="56" t="str">
+        <v>-66939.0442711516</v>
+      </c>
+      <c r="F24" s="57" t="str">
         <f aca="false">IF(E24&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="25" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A25" s="50" t="n">
+      <c r="A25" s="51" t="n">
         <v>14</v>
       </c>
-      <c r="B25" s="52" t="n">
+      <c r="B25" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G19</f>
-        <v>17465.1839955858</v>
-      </c>
-      <c r="C25" s="63" t="n">
+        <v>18455.2616534388</v>
+      </c>
+      <c r="C25" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A25</f>
         <v>0.778050944006185</v>
       </c>
-      <c r="D25" s="52" t="n">
+      <c r="D25" s="53" t="n">
         <f aca="false">B25*C25</f>
-        <v>13588.8028950072</v>
-      </c>
-      <c r="E25" s="53" t="n">
+        <v>14359.1337513392</v>
+      </c>
+      <c r="E25" s="54" t="n">
         <f aca="false">E24+D25</f>
-        <v>-58609.5800099357</v>
-      </c>
-      <c r="F25" s="56" t="str">
+        <v>-52579.9105198124</v>
+      </c>
+      <c r="F25" s="57" t="str">
         <f aca="false">IF(E25&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="26" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A26" s="50" t="n">
+      <c r="A26" s="51" t="n">
         <v>15</v>
       </c>
-      <c r="B26" s="52" t="n">
+      <c r="B26" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G20</f>
-        <v>20642.1476953727</v>
-      </c>
-      <c r="C26" s="63" t="n">
+        <v>21030.2428462481</v>
+      </c>
+      <c r="C26" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A26</f>
         <v>0.764227908671882</v>
       </c>
-      <c r="D26" s="52" t="n">
+      <c r="D26" s="53" t="n">
         <f aca="false">B26*C26</f>
-        <v>15775.3053637308</v>
-      </c>
-      <c r="E26" s="53" t="n">
+        <v>16071.89850925</v>
+      </c>
+      <c r="E26" s="54" t="n">
         <f aca="false">E25+D26</f>
-        <v>-42834.274646205</v>
-      </c>
-      <c r="F26" s="56" t="str">
+        <v>-36508.0120105624</v>
+      </c>
+      <c r="F26" s="57" t="str">
         <f aca="false">IF(E26&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="27" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A27" s="50" t="n">
+      <c r="A27" s="51" t="n">
         <v>16</v>
       </c>
-      <c r="B27" s="52" t="n">
+      <c r="B27" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G21</f>
-        <v>23185.268767722</v>
-      </c>
-      <c r="C27" s="63" t="n">
+        <v>23505.0259755953</v>
+      </c>
+      <c r="C27" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A27</f>
         <v>0.750650456621456</v>
       </c>
-      <c r="D27" s="52" t="n">
+      <c r="D27" s="53" t="n">
         <f aca="false">B27*C27</f>
-        <v>17404.0325873817</v>
-      </c>
-      <c r="E27" s="53" t="n">
+        <v>17644.0584814798</v>
+      </c>
+      <c r="E27" s="54" t="n">
         <f aca="false">E26+D27</f>
-        <v>-25430.2420588232</v>
-      </c>
-      <c r="F27" s="56" t="str">
+        <v>-18863.9535290826</v>
+      </c>
+      <c r="F27" s="57" t="str">
         <f aca="false">IF(E27&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="28" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A28" s="50" t="n">
+      <c r="A28" s="51" t="n">
         <v>17</v>
       </c>
-      <c r="B28" s="52" t="n">
+      <c r="B28" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G22</f>
-        <v>25553.5219433697</v>
-      </c>
-      <c r="C28" s="63" t="n">
+        <v>25344.1705054209</v>
+      </c>
+      <c r="C28" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A28</f>
         <v>0.737314224764758</v>
       </c>
-      <c r="D28" s="52" t="n">
+      <c r="D28" s="53" t="n">
         <f aca="false">B28*C28</f>
-        <v>18840.9752216848</v>
-      </c>
-      <c r="E28" s="53" t="n">
+        <v>18686.6174285102</v>
+      </c>
+      <c r="E28" s="54" t="n">
         <f aca="false">E27+D28</f>
-        <v>-6589.2668371384</v>
-      </c>
-      <c r="F28" s="56" t="str">
+        <v>-177.336100572378</v>
+      </c>
+      <c r="F28" s="57" t="str">
         <f aca="false">IF(E28&gt;=0,"Sim","Não")</f>
         <v>Não</v>
       </c>
     </row>
     <row r="29" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A29" s="50" t="n">
+      <c r="A29" s="51" t="n">
         <v>18</v>
       </c>
-      <c r="B29" s="52" t="n">
+      <c r="B29" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G23</f>
-        <v>28111.9278567009</v>
-      </c>
-      <c r="C29" s="63" t="n">
+        <v>27936.6529342694</v>
+      </c>
+      <c r="C29" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A29</f>
         <v>0.724214927527318</v>
       </c>
-      <c r="D29" s="52" t="n">
+      <c r="D29" s="53" t="n">
         <f aca="false">B29*C29</f>
-        <v>20359.0777953938</v>
-      </c>
-      <c r="E29" s="53" t="n">
+        <v>20232.1410801477</v>
+      </c>
+      <c r="E29" s="54" t="n">
         <f aca="false">E28+D29</f>
-        <v>13769.8109582554</v>
-      </c>
-      <c r="F29" s="56" t="str">
+        <v>20054.8049795754</v>
+      </c>
+      <c r="F29" s="57" t="str">
         <f aca="false">IF(E29&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="30" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A30" s="50" t="n">
+      <c r="A30" s="51" t="n">
         <v>19</v>
       </c>
-      <c r="B30" s="52" t="n">
+      <c r="B30" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G24</f>
-        <v>31456.0098735778</v>
-      </c>
-      <c r="C30" s="63" t="n">
+        <v>31346.9912605348</v>
+      </c>
+      <c r="C30" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A30</f>
         <v>0.711348355473187</v>
       </c>
-      <c r="D30" s="52" t="n">
+      <c r="D30" s="53" t="n">
         <f aca="false">B30*C30</f>
-        <v>22376.1808933179</v>
-      </c>
-      <c r="E30" s="53" t="n">
+        <v>22298.6306822138</v>
+      </c>
+      <c r="E30" s="54" t="n">
         <f aca="false">E29+D30</f>
-        <v>36145.9918515734</v>
-      </c>
-      <c r="F30" s="56" t="str">
+        <v>42353.4356617891</v>
+      </c>
+      <c r="F30" s="57" t="str">
         <f aca="false">IF(E30&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="31" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A31" s="50" t="n">
+      <c r="A31" s="51" t="n">
         <v>20</v>
       </c>
-      <c r="B31" s="52" t="n">
+      <c r="B31" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G25</f>
-        <v>34040.9660954915</v>
-      </c>
-      <c r="C31" s="63" t="n">
+        <v>33939.5294899929</v>
+      </c>
+      <c r="C31" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A31</f>
         <v>0.698710373952241</v>
       </c>
-      <c r="D31" s="52" t="n">
+      <c r="D31" s="53" t="n">
         <f aca="false">B31*C31</f>
-        <v>23784.7761502764</v>
-      </c>
-      <c r="E31" s="53" t="n">
+        <v>23713.9013417161</v>
+      </c>
+      <c r="E31" s="54" t="n">
         <f aca="false">E30+D31</f>
-        <v>59930.7680018498</v>
-      </c>
-      <c r="F31" s="56" t="str">
+        <v>66067.3370035052</v>
+      </c>
+      <c r="F31" s="57" t="str">
         <f aca="false">IF(E31&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="32" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A32" s="50" t="n">
+      <c r="A32" s="51" t="n">
         <v>21</v>
       </c>
-      <c r="B32" s="52" t="n">
+      <c r="B32" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G26</f>
-        <v>36654.5792392948</v>
-      </c>
-      <c r="C32" s="63" t="n">
+        <v>36597.9384013359</v>
+      </c>
+      <c r="C32" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A32</f>
         <v>0.686296921771519</v>
       </c>
-      <c r="D32" s="52" t="n">
+      <c r="D32" s="53" t="n">
         <f aca="false">B32*C32</f>
-        <v>25155.9249007583</v>
-      </c>
-      <c r="E32" s="53" t="n">
+        <v>25117.0524680205</v>
+      </c>
+      <c r="E32" s="54" t="n">
         <f aca="false">E31+D32</f>
-        <v>85086.6929026081</v>
-      </c>
-      <c r="F32" s="56" t="str">
+        <v>91184.3894715257</v>
+      </c>
+      <c r="F32" s="57" t="str">
         <f aca="false">IF(E32&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="33" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A33" s="50" t="n">
+      <c r="A33" s="51" t="n">
         <v>22</v>
       </c>
-      <c r="B33" s="52" t="n">
+      <c r="B33" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G27</f>
-        <v>38598.0977945566</v>
-      </c>
-      <c r="C33" s="63" t="n">
+        <v>38534.5538604748</v>
+      </c>
+      <c r="C33" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A33</f>
         <v>0.674104009890165</v>
       </c>
-      <c r="D33" s="52" t="n">
+      <c r="D33" s="53" t="n">
         <f aca="false">B33*C33</f>
-        <v>26019.1324974433</v>
-      </c>
-      <c r="E33" s="53" t="n">
+        <v>25976.2972766746</v>
+      </c>
+      <c r="E33" s="54" t="n">
         <f aca="false">E32+D33</f>
-        <v>111105.825400051</v>
-      </c>
-      <c r="F33" s="56" t="str">
+        <v>117160.6867482</v>
+      </c>
+      <c r="F33" s="57" t="str">
         <f aca="false">IF(E33&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="34" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A34" s="50" t="n">
+      <c r="A34" s="51" t="n">
         <v>23</v>
       </c>
-      <c r="B34" s="52" t="n">
+      <c r="B34" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G28</f>
-        <v>42257.810165909</v>
-      </c>
-      <c r="C34" s="63" t="n">
+        <v>39699.2137944939</v>
+      </c>
+      <c r="C34" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A34</f>
         <v>0.662127720137558</v>
       </c>
-      <c r="D34" s="52" t="n">
+      <c r="D34" s="53" t="n">
         <f aca="false">B34*C34</f>
-        <v>27980.067503159</v>
-      </c>
-      <c r="E34" s="53" t="n">
+        <v>26285.9499210018</v>
+      </c>
+      <c r="E34" s="54" t="n">
         <f aca="false">E33+D34</f>
-        <v>139085.89290321</v>
-      </c>
-      <c r="F34" s="56" t="str">
+        <v>143446.636669202</v>
+      </c>
+      <c r="F34" s="57" t="str">
         <f aca="false">IF(E34&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="35" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A35" s="50" t="n">
+      <c r="A35" s="51" t="n">
         <v>24</v>
       </c>
-      <c r="B35" s="52" t="n">
+      <c r="B35" s="53" t="n">
         <f aca="false">'Fluxo de Caixa'!G29</f>
-        <v>44235.7884932312</v>
-      </c>
-      <c r="C35" s="63" t="n">
+        <v>44714.2353522509</v>
+      </c>
+      <c r="C35" s="64" t="n">
         <f aca="false">1/(1+$B$7)^A35</f>
         <v>0.650364203954214</v>
       </c>
-      <c r="D35" s="52" t="n">
+      <c r="D35" s="53" t="n">
         <f aca="false">B35*C35</f>
-        <v>28769.3733696873</v>
-      </c>
-      <c r="E35" s="53" t="n">
+        <v>29080.538080288</v>
+      </c>
+      <c r="E35" s="54" t="n">
         <f aca="false">E34+D35</f>
-        <v>167855.266272898</v>
-      </c>
-      <c r="F35" s="56" t="str">
+        <v>172527.17474949</v>
+      </c>
+      <c r="F35" s="57" t="str">
         <f aca="false">IF(E35&gt;=0,"Sim","Não")</f>
         <v>Sim</v>
       </c>
     </row>
     <row r="37" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A37" s="4" t="s">
-        <v>268</v>
-      </c>
-      <c r="B37" s="48"/>
-      <c r="C37" s="48"/>
-      <c r="D37" s="48"/>
-      <c r="E37" s="48"/>
-      <c r="F37" s="48"/>
-      <c r="G37" s="48"/>
+        <v>269</v>
+      </c>
+      <c r="B37" s="49"/>
+      <c r="C37" s="49"/>
+      <c r="D37" s="49"/>
+      <c r="E37" s="49"/>
+      <c r="F37" s="49"/>
+      <c r="G37" s="49"/>
     </row>
     <row r="38" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A38" s="3" t="s">
-        <v>269</v>
-      </c>
-      <c r="B38" s="64" t="n">
+        <v>270</v>
+      </c>
+      <c r="B38" s="65" t="n">
         <f aca="false">SUM(D11:D35)</f>
-        <v>167855.266272898</v>
-      </c>
-      <c r="C38" s="65" t="str">
+        <v>172527.17474949</v>
+      </c>
+      <c r="C38" s="66" t="str">
         <f aca="false">IF(B38&gt;0,"VIÁVEL: o projeto gera mais do que a taxa exigida",IF(B38&lt;0,"INVIÁVEL: o projeto rende menos que a taxa exigida","EQUILÍBRIO: rende exatamente a taxa exigida"))</f>
         <v>VIÁVEL: o projeto gera mais do que a taxa exigida</v>
       </c>
     </row>
     <row r="39" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A39" s="3" t="s">
-        <v>270</v>
-      </c>
-      <c r="B39" s="66" t="n">
+        <v>271</v>
+      </c>
+      <c r="B39" s="67" t="n">
         <f aca="false">IFERROR(IRR(B11:B35),"Não calculável")</f>
-        <v>0.0704388506259977</v>
-      </c>
-      <c r="C39" s="65" t="str">
+        <v>0.0723318613275063</v>
+      </c>
+      <c r="C39" s="66" t="str">
         <f aca="false">IF(ISNUMBER(B39),IF(B39&gt;B7,"VIÁVEL: TIR maior que a taxa de desconto","INVIÁVEL: TIR menor ou igual à taxa de desconto"),"Sem TIR: o fluxo precisa ter valores negativos E positivos")</f>
         <v>VIÁVEL: TIR maior que a taxa de desconto</v>
       </c>
     </row>
     <row r="40" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A40" s="3" t="s">
-        <v>271</v>
-      </c>
-      <c r="B40" s="66" t="n">
+        <v>272</v>
+      </c>
+      <c r="B40" s="67" t="n">
         <f aca="false">IF(ISNUMBER(B39),IF(B6="Mensal",(1+B39)^12-1,B39),"Não calculável")</f>
-        <v>1.26330121466574</v>
-      </c>
-      <c r="C40" s="65" t="str">
+        <v>1.31180138851585</v>
+      </c>
+      <c r="C40" s="66" t="str">
         <f aca="false">"Compare com a taxa anual de "&amp;ROUND(B5*100,2)&amp;"%"</f>
         <v>Compare com a taxa anual de 24%</v>
       </c>
     </row>
     <row r="41" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A41" s="3" t="s">
-        <v>272</v>
-      </c>
-      <c r="B41" s="64" t="n">
+        <v>273</v>
+      </c>
+      <c r="B41" s="65" t="n">
         <f aca="false">'Fluxo de Caixa'!F5</f>
         <v>102000</v>
       </c>
-      <c r="C41" s="65" t="str">
+      <c r="C41" s="66" t="str">
         <f aca="false">IF(B41=0,"Atenção: informe o investimento no período 0 da aba Fluxo de Caixa","")</f>
         <v/>
       </c>
     </row>
     <row r="42" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A42" s="3" t="s">
-        <v>273</v>
-      </c>
-      <c r="B42" s="66" t="n">
+        <v>274</v>
+      </c>
+      <c r="B42" s="67" t="n">
         <f aca="false">IF(B41=0,"-",B38/B41)</f>
-        <v>1.64563986542057</v>
-      </c>
-      <c r="C42" s="65" t="str">
+        <v>1.69144288970088</v>
+      </c>
+      <c r="C42" s="66" t="str">
         <f aca="false">"Para cada R$ 100 de investimento inicial, o projeto gera R$ "&amp;IF(ISNUMBER(B42),ROUND(B42*100,2),"-")&amp;" de VPL acima da taxa exigida"</f>
-        <v>Para cada R$ 100 de investimento inicial, o projeto gera R$ 164.56 de VPL acima da taxa exigida</v>
+        <v>Para cada R$ 100 de investimento inicial, o projeto gera R$ 169.14 de VPL acima da taxa exigida</v>
       </c>
     </row>
     <row r="43" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A43" s="3" t="s">
-        <v>250</v>
-      </c>
-      <c r="B43" s="67" t="n">
+        <v>251</v>
+      </c>
+      <c r="B43" s="68" t="n">
         <f aca="false">'Necessidade de Caixa e Payback'!F33</f>
-        <v>17</v>
-      </c>
-      <c r="C43" s="65" t="str">
+        <v>16</v>
+      </c>
+      <c r="C43" s="66" t="str">
         <f aca="false">"Período em que o saldo acumulado (sem descontar) fica positivo"</f>
         <v>Período em que o saldo acumulado (sem descontar) fica positivo</v>
       </c>
     </row>
     <row r="44" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A44" s="3" t="s">
-        <v>274</v>
-      </c>
-      <c r="B44" s="67" t="n">
+        <v>275</v>
+      </c>
+      <c r="B44" s="68" t="n">
         <f aca="false">IFERROR(INDEX(A11:A35,MATCH("Sim",F11:F35,0)),"Não recupera")</f>
         <v>18</v>
       </c>
-      <c r="C44" s="65" t="str">
+      <c r="C44" s="66" t="str">
         <f aca="false">"Período em que o VP acumulado fica positivo"</f>
         <v>Período em que o VP acumulado fica positivo</v>
       </c>
     </row>
     <row r="45" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A45" s="3" t="s">
-        <v>275</v>
-      </c>
-      <c r="B45" s="64" t="n">
+        <v>276</v>
+      </c>
+      <c r="B45" s="65" t="n">
         <f aca="false">'Necessidade de Caixa e Payback'!F32</f>
         <v>120917.625</v>
       </c>
-      <c r="C45" s="65" t="str">
+      <c r="C45" s="66" t="str">
         <f aca="false">"Dinheiro que os sócios precisam ter para cobrir o pior momento"</f>
         <v>Dinheiro que os sócios precisam ter para cobrir o pior momento</v>
       </c>
     </row>
     <row r="47" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
       <c r="A47" s="4" t="s">
-        <v>276</v>
-      </c>
-      <c r="B47" s="48"/>
-      <c r="C47" s="48"/>
-      <c r="D47" s="48"/>
-      <c r="E47" s="48"/>
-      <c r="F47" s="48"/>
-      <c r="G47" s="48"/>
+        <v>277</v>
+      </c>
+      <c r="B47" s="49"/>
+      <c r="C47" s="49"/>
+      <c r="D47" s="49"/>
+      <c r="E47" s="49"/>
+      <c r="F47" s="49"/>
+      <c r="G47" s="49"/>
     </row>
     <row r="48" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A48" s="68" t="s">
-        <v>277</v>
+      <c r="A48" s="69" t="s">
+        <v>278</v>
       </c>
     </row>
     <row r="49" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A49" s="68" t="s">
-        <v>278</v>
+      <c r="A49" s="69" t="s">
+        <v>279</v>
       </c>
     </row>
     <row r="50" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A50" s="68" t="s">
-        <v>279</v>
+      <c r="A50" s="69" t="s">
+        <v>280</v>
       </c>
     </row>
     <row r="51" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A51" s="68" t="s">
-        <v>280</v>
+      <c r="A51" s="69" t="s">
+        <v>281</v>
       </c>
     </row>
     <row r="52" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A52" s="68" t="s">
-        <v>281</v>
+      <c r="A52" s="69" t="s">
+        <v>282</v>
       </c>
     </row>
     <row r="53" customFormat="false" ht="15" hidden="false" customHeight="true" outlineLevel="0" collapsed="false">
-      <c r="A53" s="68" t="s">
-        <v>282</v>
+      <c r="A53" s="69" t="s">
+        <v>283</v>
       </c>
     </row>
   </sheetData>
